--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DCB66C-274A-498A-BC70-D06BED4FCFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92B5EE3-9B92-47E1-915E-CED585977209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1266"/>
+  <dimension ref="A1:W1268"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -53499,7 +53499,7 @@
         <v>4150.9922145963383</v>
       </c>
       <c r="E1158" s="14">
-        <v>3840.8705315087991</v>
+        <v>3840.8705315088</v>
       </c>
       <c r="F1158" s="13">
         <v>882.2903</v>
@@ -53537,7 +53537,7 @@
         <v>3757.2628855111907</v>
       </c>
       <c r="E1159" s="14">
-        <v>3780.289792080996</v>
+        <v>3780.2897920809955</v>
       </c>
       <c r="F1159" s="13">
         <v>1494.2402999999999</v>
@@ -53575,7 +53575,7 @@
         <v>3966.9774403598576</v>
       </c>
       <c r="E1160" s="14">
-        <v>3927.1454924749778</v>
+        <v>3927.1454924749787</v>
       </c>
       <c r="F1160" s="13">
         <v>1675.7801999999999</v>
@@ -53613,7 +53613,7 @@
         <v>3836.9166844383958</v>
       </c>
       <c r="E1161" s="14">
-        <v>3873.8651916427129</v>
+        <v>3873.8651916427139</v>
       </c>
       <c r="F1161" s="13">
         <v>1355.5396000000001</v>
@@ -53748,7 +53748,7 @@
       <c r="L1164" s="13"/>
       <c r="M1164" s="13"/>
       <c r="N1164" s="15">
-        <v>57458.467500000006</v>
+        <v>57458.467499999999</v>
       </c>
     </row>
     <row r="1165" spans="1:14" ht="15.75" customHeight="1">
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309879</v>
+        <v>4180.3219217309888</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53777,7 +53777,7 @@
         <v>3930.3634262421583</v>
       </c>
       <c r="I1165" s="14">
-        <v>3575.1060841405915</v>
+        <v>3575.1060841405906</v>
       </c>
       <c r="J1165" s="13">
         <v>4062.5365999999999</v>
@@ -53803,7 +53803,7 @@
         <v>4144.4221019502211</v>
       </c>
       <c r="E1166" s="14">
-        <v>4237.0040886928518</v>
+        <v>4237.0040886928527</v>
       </c>
       <c r="F1166" s="13">
         <v>1411.7936999999999</v>
@@ -53815,7 +53815,7 @@
         <v>3909.3141944625277</v>
       </c>
       <c r="I1166" s="14">
-        <v>3720.2808034203026</v>
+        <v>3720.2808034203017</v>
       </c>
       <c r="J1166" s="13">
         <v>3419.8951999999999</v>
@@ -53824,7 +53824,7 @@
       <c r="L1166" s="13"/>
       <c r="M1166" s="13"/>
       <c r="N1166" s="15">
-        <v>31626.655099999996</v>
+        <v>31626.6551</v>
       </c>
     </row>
     <row r="1167" spans="1:14" ht="15.75" customHeight="1">
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.8558460563499</v>
+        <v>4171.855846056349</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -53853,7 +53853,7 @@
         <v>3239.1375010965894</v>
       </c>
       <c r="I1167" s="14">
-        <v>3596.986903872149</v>
+        <v>3596.9869038721486</v>
       </c>
       <c r="J1167" s="13">
         <v>7280.7353999999996</v>
@@ -53976,7 +53976,7 @@
       <c r="L1170" s="13"/>
       <c r="M1170" s="13"/>
       <c r="N1170" s="15">
-        <v>37348.153800000007</v>
+        <v>37348.1538</v>
       </c>
     </row>
     <row r="1171" spans="1:14" ht="15.75" customHeight="1">
@@ -54242,7 +54242,7 @@
       <c r="L1177" s="13"/>
       <c r="M1177" s="13"/>
       <c r="N1177" s="15">
-        <v>62161.926700000004</v>
+        <v>62161.926699999996</v>
       </c>
     </row>
     <row r="1178" spans="1:14" ht="15.75" customHeight="1">
@@ -54297,7 +54297,7 @@
         <v>4256.7265580616331</v>
       </c>
       <c r="E1179" s="14">
-        <v>4295.1344714147781</v>
+        <v>4295.134471414779</v>
       </c>
       <c r="F1179" s="13">
         <v>1120.1349</v>
@@ -54335,7 +54335,7 @@
         <v>4008.5523747206912</v>
       </c>
       <c r="E1180" s="14">
-        <v>4173.750113280711</v>
+        <v>4173.750113280712</v>
       </c>
       <c r="F1180" s="13">
         <v>909.47910000000002</v>
@@ -54356,7 +54356,7 @@
       <c r="L1180" s="13"/>
       <c r="M1180" s="13"/>
       <c r="N1180" s="15">
-        <v>56623.827599999997</v>
+        <v>56623.827600000004</v>
       </c>
     </row>
     <row r="1181" spans="1:14" ht="15.75" customHeight="1">
@@ -54385,7 +54385,7 @@
         <v>3932.1869092178767</v>
       </c>
       <c r="I1181" s="14">
-        <v>3763.2741964818451</v>
+        <v>3763.2741964818456</v>
       </c>
       <c r="J1181" s="13">
         <v>7024.5267000000003</v>
@@ -54394,7 +54394,7 @@
       <c r="L1181" s="13"/>
       <c r="M1181" s="13"/>
       <c r="N1181" s="15">
-        <v>52642.395300000004</v>
+        <v>52642.395299999996</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15.75" customHeight="1">
@@ -54411,7 +54411,7 @@
         <v>4033.0100843855616</v>
       </c>
       <c r="E1182" s="14">
-        <v>4020.0169955492406</v>
+        <v>4020.0169955492411</v>
       </c>
       <c r="F1182" s="13">
         <v>427.52350000000001</v>
@@ -54423,7 +54423,7 @@
         <v>4435.1671265846417</v>
       </c>
       <c r="I1182" s="14">
-        <v>3815.6421043550649</v>
+        <v>3815.6421043550654</v>
       </c>
       <c r="J1182" s="13">
         <v>6999.7999</v>
@@ -54461,7 +54461,7 @@
         <v>5020.0771469761667</v>
       </c>
       <c r="I1183" s="14">
-        <v>3892.3953212090469</v>
+        <v>3892.3953212090473</v>
       </c>
       <c r="J1183" s="13">
         <v>5037.4709000000003</v>
@@ -54525,7 +54525,7 @@
         <v>4059.2289950562249</v>
       </c>
       <c r="E1185" s="14">
-        <v>4136.2469995879528</v>
+        <v>4136.2469995879537</v>
       </c>
       <c r="F1185" s="13">
         <v>566.73659999999995</v>
@@ -54546,7 +54546,7 @@
       <c r="L1185" s="13"/>
       <c r="M1185" s="13"/>
       <c r="N1185" s="15">
-        <v>37483.069499999991</v>
+        <v>37483.069499999998</v>
       </c>
     </row>
     <row r="1186" spans="1:14" ht="15.75" customHeight="1">
@@ -54584,7 +54584,7 @@
       <c r="L1186" s="13"/>
       <c r="M1186" s="13"/>
       <c r="N1186" s="15">
-        <v>44453.567299999995</v>
+        <v>44453.567300000002</v>
       </c>
     </row>
     <row r="1187" spans="1:14" ht="15.75" customHeight="1">
@@ -54736,7 +54736,7 @@
       <c r="L1190" s="13"/>
       <c r="M1190" s="13"/>
       <c r="N1190" s="15">
-        <v>59168.145500000006</v>
+        <v>59168.145499999999</v>
       </c>
     </row>
     <row r="1191" spans="1:14" ht="15.75" customHeight="1">
@@ -54774,7 +54774,7 @@
       <c r="L1191" s="13"/>
       <c r="M1191" s="13"/>
       <c r="N1191" s="15">
-        <v>59039.229299999999</v>
+        <v>59039.229300000006</v>
       </c>
     </row>
     <row r="1192" spans="1:14" ht="15.75" customHeight="1">
@@ -54964,7 +54964,7 @@
       <c r="L1196" s="13"/>
       <c r="M1196" s="13"/>
       <c r="N1196" s="15">
-        <v>59285.673100000007</v>
+        <v>59285.6731</v>
       </c>
     </row>
     <row r="1197" spans="1:14" ht="15.75" customHeight="1">
@@ -55002,7 +55002,7 @@
       <c r="L1197" s="13"/>
       <c r="M1197" s="13"/>
       <c r="N1197" s="15">
-        <v>46861.756299999994</v>
+        <v>46861.756300000001</v>
       </c>
     </row>
     <row r="1198" spans="1:14" ht="15.75" customHeight="1">
@@ -55057,7 +55057,7 @@
         <v>4811.1216968574927</v>
       </c>
       <c r="E1199" s="14">
-        <v>4410.8853143259794</v>
+        <v>4410.8853143259776</v>
       </c>
       <c r="F1199" s="13">
         <v>923.27440000000001</v>
@@ -55078,7 +55078,7 @@
       <c r="L1199" s="13"/>
       <c r="M1199" s="13"/>
       <c r="N1199" s="15">
-        <v>45059.347400000006</v>
+        <v>45059.347399999999</v>
       </c>
     </row>
     <row r="1200" spans="1:14" ht="15.75" customHeight="1">
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551803</v>
+        <v>4487.7143253551785</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55154,7 +55154,7 @@
       <c r="L1201" s="13"/>
       <c r="M1201" s="13"/>
       <c r="N1201" s="15">
-        <v>64229.893499999998</v>
+        <v>64229.893500000006</v>
       </c>
     </row>
     <row r="1202" spans="1:14" ht="15.75" customHeight="1">
@@ -55230,7 +55230,7 @@
       <c r="L1203" s="13"/>
       <c r="M1203" s="13"/>
       <c r="N1203" s="15">
-        <v>79222.162899999981</v>
+        <v>79222.162899999996</v>
       </c>
     </row>
     <row r="1204" spans="1:14" ht="15.75" customHeight="1">
@@ -55268,7 +55268,7 @@
       <c r="L1204" s="13"/>
       <c r="M1204" s="13"/>
       <c r="N1204" s="15">
-        <v>86729.972700000013</v>
+        <v>86729.972699999998</v>
       </c>
     </row>
     <row r="1205" spans="1:14" ht="15.75" customHeight="1">
@@ -55335,7 +55335,7 @@
         <v>3932.5340059065734</v>
       </c>
       <c r="I1206" s="14">
-        <v>4333.5986404219693</v>
+        <v>4333.5986404219702</v>
       </c>
       <c r="J1206" s="13">
         <v>6089.9108999999999</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629657</v>
+        <v>4315.8033455629638</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55420,7 +55420,7 @@
       <c r="L1208" s="13"/>
       <c r="M1208" s="13"/>
       <c r="N1208" s="15">
-        <v>49051.207199999997</v>
+        <v>49051.207200000004</v>
       </c>
     </row>
     <row r="1209" spans="1:14" ht="15.75" customHeight="1">
@@ -55475,7 +55475,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="14">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="13">
         <v>1813.4111</v>
@@ -55572,7 +55572,7 @@
       <c r="L1212" s="13"/>
       <c r="M1212" s="13"/>
       <c r="N1212" s="15">
-        <v>45765.935099999995</v>
+        <v>45765.935100000002</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55648,7 +55648,7 @@
       <c r="L1214" s="13"/>
       <c r="M1214" s="13"/>
       <c r="N1214" s="15">
-        <v>76706.900300000008</v>
+        <v>76706.900299999994</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55656,16 +55656,16 @@
         <v>45703</v>
       </c>
       <c r="B1215" s="13">
-        <v>60861.612200000003</v>
+        <v>60861.251300000004</v>
       </c>
       <c r="C1215" s="13">
         <v>13448.997499999999</v>
       </c>
       <c r="D1215" s="13">
-        <v>4525.364228820773</v>
+        <v>4525.3373941068849</v>
       </c>
       <c r="E1215" s="14">
-        <v>4600.8673459638812</v>
+        <v>4600.8598600172372</v>
       </c>
       <c r="F1215" s="13">
         <v>1717.5505000000001</v>
@@ -55686,7 +55686,7 @@
       <c r="L1215" s="13"/>
       <c r="M1215" s="13"/>
       <c r="N1215" s="15">
-        <v>72272.347099999999</v>
+        <v>72271.986199999999</v>
       </c>
     </row>
     <row r="1216" spans="1:14" ht="15.75" customHeight="1">
@@ -55703,7 +55703,7 @@
         <v>5219.1591733611331</v>
       </c>
       <c r="E1216" s="14">
-        <v>4696.5728107936138</v>
+        <v>4696.5654401797765</v>
       </c>
       <c r="F1216" s="13">
         <v>989.77200000000005</v>
@@ -55741,7 +55741,7 @@
         <v>4774.7301007401384</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.368255219415</v>
+        <v>4706.3617422026982</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.5451527004752</v>
+        <v>4736.5378826348679</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55838,7 +55838,7 @@
       <c r="L1219" s="13"/>
       <c r="M1219" s="13"/>
       <c r="N1219" s="15">
-        <v>62677.385600000001</v>
+        <v>62677.385599999994</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55846,16 +55846,16 @@
         <v>45738</v>
       </c>
       <c r="B1220" s="13">
-        <v>42688.618199999997</v>
+        <v>42688.3678</v>
       </c>
       <c r="C1220" s="13">
         <v>9344.2111999999997</v>
       </c>
       <c r="D1220" s="13">
-        <v>4568.4560511645968</v>
+        <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.3201283037752</v>
+        <v>4663.3142855974838</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55876,7 +55876,7 @@
       <c r="L1220" s="13"/>
       <c r="M1220" s="13"/>
       <c r="N1220" s="15">
-        <v>50442.839099999997</v>
+        <v>50442.5887</v>
       </c>
     </row>
     <row r="1221" spans="1:14" ht="15.75" customHeight="1">
@@ -55893,7 +55893,7 @@
         <v>4701.8076037281035</v>
       </c>
       <c r="E1221" s="14">
-        <v>4670.5473471968171</v>
+        <v>4670.5416759697973</v>
       </c>
       <c r="F1221" s="13">
         <v>673.16070000000002</v>
@@ -55922,16 +55922,16 @@
         <v>45752</v>
       </c>
       <c r="B1222" s="13">
-        <v>48559.015899999999</v>
+        <v>48558.061399999999</v>
       </c>
       <c r="C1222" s="13">
         <v>10009.820100000001</v>
       </c>
       <c r="D1222" s="13">
-        <v>4851.1377242434155</v>
+        <v>4851.0423678843135</v>
       </c>
       <c r="E1222" s="14">
-        <v>4695.9889906735052</v>
+        <v>4695.9613964996215</v>
       </c>
       <c r="F1222" s="13">
         <v>1081.6878999999999</v>
@@ -55952,7 +55952,7 @@
       <c r="L1222" s="13"/>
       <c r="M1222" s="13"/>
       <c r="N1222" s="15">
-        <v>52980.643399999994</v>
+        <v>52979.688900000001</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -55969,7 +55969,7 @@
         <v>4613.3343787360272</v>
       </c>
       <c r="E1223" s="14">
-        <v>4695.6528467809931</v>
+        <v>4695.626162482773</v>
       </c>
       <c r="F1223" s="13">
         <v>1661.2738999999999</v>
@@ -56007,7 +56007,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="14">
-        <v>4673.3313732946226</v>
+        <v>4673.3021398798928</v>
       </c>
       <c r="F1224" s="13">
         <v>678.69989999999996</v>
@@ -56045,7 +56045,7 @@
         <v>5250.790273907136</v>
       </c>
       <c r="E1225" s="14">
-        <v>4738.7543938000908</v>
+        <v>4738.7314957118124</v>
       </c>
       <c r="F1225" s="13">
         <v>723.6875</v>
@@ -56112,16 +56112,16 @@
         <v>45787</v>
       </c>
       <c r="B1227" s="13">
-        <v>70762.153900000005</v>
+        <v>70761.334400000007</v>
       </c>
       <c r="C1227" s="13">
         <v>14282.969499999999</v>
       </c>
       <c r="D1227" s="13">
-        <v>4954.3026679431059</v>
+        <v>4954.2452919191637</v>
       </c>
       <c r="E1227" s="14">
-        <v>4890.6111910146301</v>
+        <v>4890.5928220892229</v>
       </c>
       <c r="F1227" s="13">
         <v>699.97680000000003</v>
@@ -56142,7 +56142,7 @@
       <c r="L1227" s="13"/>
       <c r="M1227" s="13"/>
       <c r="N1227" s="15">
-        <v>81065.336500000005</v>
+        <v>81064.517000000007</v>
       </c>
     </row>
     <row r="1228" spans="1:14" ht="15.75" customHeight="1">
@@ -56150,16 +56150,16 @@
         <v>45794</v>
       </c>
       <c r="B1228" s="13">
-        <v>74701.234899999996</v>
+        <v>74694.599300000002</v>
       </c>
       <c r="C1228" s="13">
         <v>14436.996499999999</v>
       </c>
       <c r="D1228" s="13">
-        <v>5174.2919588572313</v>
+        <v>5173.8323341700607</v>
       </c>
       <c r="E1228" s="14">
-        <v>5048.41606731724</v>
+        <v>5048.2712446182913</v>
       </c>
       <c r="F1228" s="13">
         <v>677.62339999999995</v>
@@ -56180,7 +56180,7 @@
       <c r="L1228" s="13"/>
       <c r="M1228" s="13"/>
       <c r="N1228" s="15">
-        <v>80241.846799999999</v>
+        <v>80235.211200000005</v>
       </c>
     </row>
     <row r="1229" spans="1:14" ht="15.75" customHeight="1">
@@ -56188,16 +56188,16 @@
         <v>45801</v>
       </c>
       <c r="B1229" s="13">
-        <v>54515.910300000003</v>
+        <v>54514.881399999998</v>
       </c>
       <c r="C1229" s="13">
         <v>10629.917100000001</v>
       </c>
       <c r="D1229" s="13">
-        <v>5128.5357907447842</v>
+        <v>5128.4389978920908</v>
       </c>
       <c r="E1229" s="14">
-        <v>4984.0678413823998</v>
+        <v>4983.9080207429033</v>
       </c>
       <c r="F1229" s="13">
         <v>465.10070000000002</v>
@@ -56218,7 +56218,7 @@
       <c r="L1229" s="13"/>
       <c r="M1229" s="13"/>
       <c r="N1229" s="15">
-        <v>66470.683999999994</v>
+        <v>66469.655100000004</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56235,7 +56235,7 @@
         <v>5223.8522965946941</v>
       </c>
       <c r="E1230" s="14">
-        <v>5028.8357218982637</v>
+        <v>5028.670746011142</v>
       </c>
       <c r="F1230" s="13">
         <v>186.41309999999999</v>
@@ -56273,7 +56273,7 @@
         <v>4742.3293933814848</v>
       </c>
       <c r="E1231" s="14">
-        <v>4961.7135906734002</v>
+        <v>4961.567844872673</v>
       </c>
       <c r="F1231" s="13">
         <v>1023.9116</v>
@@ -56311,7 +56311,7 @@
         <v>4822.1163386837061</v>
       </c>
       <c r="E1232" s="14">
-        <v>4910.0949138408505</v>
+        <v>4909.9829364434308</v>
       </c>
       <c r="F1232" s="13">
         <v>1933.1436000000001</v>
@@ -56332,7 +56332,7 @@
       <c r="L1232" s="13"/>
       <c r="M1232" s="13"/>
       <c r="N1232" s="15">
-        <v>68154.728999999992</v>
+        <v>68154.729000000007</v>
       </c>
     </row>
     <row r="1233" spans="1:15" ht="15.75" customHeight="1">
@@ -56349,7 +56349,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="14">
-        <v>4836.4394194233882</v>
+        <v>4836.4178813501176</v>
       </c>
       <c r="F1233" s="13">
         <v>910.61059999999998</v>
@@ -56408,7 +56408,7 @@
       <c r="L1234" s="13"/>
       <c r="M1234" s="13"/>
       <c r="N1234" s="15">
-        <v>43653.307299999993</v>
+        <v>43653.3073</v>
       </c>
     </row>
     <row r="1235" spans="1:15" ht="15.75" customHeight="1">
@@ -56425,7 +56425,7 @@
         <v>5125.621659266998</v>
       </c>
       <c r="E1235" s="14">
-        <v>4955.3969607385388</v>
+        <v>4955.3969607385379</v>
       </c>
       <c r="F1235" s="13">
         <v>1182.9712999999999</v>
@@ -56501,7 +56501,7 @@
         <v>5279.8066063917322</v>
       </c>
       <c r="E1237" s="14">
-        <v>4927.2749374102932</v>
+        <v>4927.2749374102941</v>
       </c>
       <c r="F1237" s="13">
         <v>770.73030000000006</v>
@@ -56530,16 +56530,16 @@
         <v>45864</v>
       </c>
       <c r="B1238" s="13">
-        <v>47774.681900000003</v>
+        <v>47774.333599999998</v>
       </c>
       <c r="C1238" s="13">
         <v>8648.6777000000002</v>
       </c>
       <c r="D1238" s="13">
-        <v>5523.9290394646114</v>
+        <v>5523.8887674123871</v>
       </c>
       <c r="E1238" s="14">
-        <v>5021.9091692425382</v>
+        <v>5021.9014563829769</v>
       </c>
       <c r="F1238" s="13">
         <v>937.15679999999998</v>
@@ -56560,7 +56560,7 @@
       <c r="L1238" s="13"/>
       <c r="M1238" s="13"/>
       <c r="N1238" s="15">
-        <v>53730.705999999998</v>
+        <v>53730.3577</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56577,7 +56577,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="14">
-        <v>4983.8947731923981</v>
+        <v>4983.8869191962531</v>
       </c>
       <c r="F1239" s="13">
         <v>1951.8497</v>
@@ -56615,7 +56615,7 @@
         <v>5736.0102439994189</v>
       </c>
       <c r="E1240" s="14">
-        <v>5190.3317916635515</v>
+        <v>5190.3220901089398</v>
       </c>
       <c r="F1240" s="13">
         <v>690.66629999999998</v>
@@ -56653,7 +56653,7 @@
         <v>5875.0162561948327</v>
       </c>
       <c r="E1241" s="14">
-        <v>5328.3062561328534</v>
+        <v>5328.2971232518175</v>
       </c>
       <c r="F1241" s="13">
         <v>356.61349999999999</v>
@@ -56668,13 +56668,13 @@
         <v>6187.5045092790242</v>
       </c>
       <c r="J1241" s="13">
-        <v>12824.4524</v>
+        <v>12876.365</v>
       </c>
       <c r="K1241" s="13"/>
       <c r="L1241" s="13"/>
       <c r="M1241" s="13"/>
       <c r="N1241" s="15">
-        <v>77424.733500000002</v>
+        <v>77476.646099999998</v>
       </c>
       <c r="O1241" s="16"/>
     </row>
@@ -56692,7 +56692,7 @@
         <v>5270.2482473396421</v>
       </c>
       <c r="E1242" s="14">
-        <v>5374.9209094320613</v>
+        <v>5374.9129597194378</v>
       </c>
       <c r="F1242" s="13">
         <v>1157.8651</v>
@@ -56745,13 +56745,13 @@
         <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="13">
-        <v>15514.602699999999</v>
+        <v>15514.227699999999</v>
       </c>
       <c r="K1243" s="13"/>
       <c r="L1243" s="13"/>
       <c r="M1243" s="13"/>
       <c r="N1243" s="15">
-        <v>89511.293000000005</v>
+        <v>89510.918000000005</v>
       </c>
     </row>
     <row r="1244" spans="1:15" ht="15.75" customHeight="1">
@@ -56821,13 +56821,13 @@
         <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="13">
-        <v>4208.6903000000002</v>
+        <v>4208.4350999999997</v>
       </c>
       <c r="K1245" s="13"/>
       <c r="L1245" s="13"/>
       <c r="M1245" s="13"/>
       <c r="N1245" s="15">
-        <v>48638.156400000007</v>
+        <v>48637.9012</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56835,16 +56835,16 @@
         <v>45920</v>
       </c>
       <c r="B1246" s="13">
-        <v>62650.865599999997</v>
+        <v>62649.8508</v>
       </c>
       <c r="C1246" s="13">
         <v>11947.379300000001</v>
       </c>
       <c r="D1246" s="13">
-        <v>5243.900275267898</v>
+        <v>5243.8153361381937</v>
       </c>
       <c r="E1246" s="14">
-        <v>5102.1744621158523</v>
+        <v>5102.1530919713095</v>
       </c>
       <c r="F1246" s="13">
         <v>977.74770000000001</v>
@@ -56865,7 +56865,7 @@
       <c r="L1246" s="13"/>
       <c r="M1246" s="13"/>
       <c r="N1246" s="15">
-        <v>70108.133200000011</v>
+        <v>70107.118400000007</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56882,7 +56882,7 @@
         <v>5283.5168258315707</v>
       </c>
       <c r="E1247" s="14">
-        <v>5104.5708504587583</v>
+        <v>5104.5479531329574</v>
       </c>
       <c r="F1247" s="13">
         <v>1625.8276000000001</v>
@@ -56894,7 +56894,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="14">
-        <v>5394.2932473875317</v>
+        <v>5394.2932473875308</v>
       </c>
       <c r="J1247" s="13">
         <v>13767.5789</v>
@@ -56903,7 +56903,7 @@
       <c r="L1247" s="13"/>
       <c r="M1247" s="13"/>
       <c r="N1247" s="15">
-        <v>60445.6512</v>
+        <v>60445.651200000008</v>
       </c>
     </row>
     <row r="1248" spans="1:15" ht="15.75" customHeight="1">
@@ -56911,16 +56911,16 @@
         <v>45934</v>
       </c>
       <c r="B1248" s="13">
-        <v>34875.249100000001</v>
+        <v>34873.983800000002</v>
       </c>
       <c r="C1248" s="13">
-        <v>7467.2049999999999</v>
+        <v>7466.8144000000002</v>
       </c>
       <c r="D1248" s="13">
-        <v>4670.4555586728902</v>
+        <v>4670.5304205766788</v>
       </c>
       <c r="E1248" s="14">
-        <v>5065.8588115488492</v>
+        <v>5065.8510751738395</v>
       </c>
       <c r="F1248" s="13">
         <v>1018.4743</v>
@@ -56941,7 +56941,7 @@
       <c r="L1248" s="13"/>
       <c r="M1248" s="13"/>
       <c r="N1248" s="15">
-        <v>40653.995800000004</v>
+        <v>40652.730500000005</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15.75" customHeight="1">
@@ -56949,16 +56949,16 @@
         <v>45941</v>
       </c>
       <c r="B1249" s="13">
-        <v>24110.178199999998</v>
+        <v>24109.855299999999</v>
       </c>
       <c r="C1249" s="13">
         <v>5500.9261999999999</v>
       </c>
       <c r="D1249" s="13">
-        <v>4382.9306781101695</v>
+        <v>4382.871978904207</v>
       </c>
       <c r="E1249" s="14">
-        <v>4973.8861475109807</v>
+        <v>4973.8684677050696</v>
       </c>
       <c r="F1249" s="13">
         <v>1116.6591000000001</v>
@@ -56970,16 +56970,16 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="14">
-        <v>5046.6456948691875</v>
+        <v>5046.6456948691884</v>
       </c>
       <c r="J1249" s="13">
-        <v>6200.7741999999998</v>
+        <v>6200.3991999999998</v>
       </c>
       <c r="K1249" s="13"/>
       <c r="L1249" s="13"/>
       <c r="M1249" s="13"/>
       <c r="N1249" s="15">
-        <v>31427.611499999999</v>
+        <v>31426.9136</v>
       </c>
     </row>
     <row r="1250" spans="1:14" ht="15.75" customHeight="1">
@@ -56987,16 +56987,16 @@
         <v>45948</v>
       </c>
       <c r="B1250" s="13">
-        <v>48243.912199999999</v>
+        <v>48243.658600000002</v>
       </c>
       <c r="C1250" s="13">
         <v>9782.5046999999995</v>
       </c>
       <c r="D1250" s="13">
-        <v>4931.6523405299258</v>
+        <v>4931.626416698783</v>
       </c>
       <c r="E1250" s="14">
-        <v>4941.3597020882944</v>
+        <v>4941.3621017537826</v>
       </c>
       <c r="F1250" s="13">
         <v>1339.0517</v>
@@ -57008,7 +57008,7 @@
         <v>6096.8579855739072</v>
       </c>
       <c r="I1250" s="14">
-        <v>5726.2108069747683</v>
+        <v>5726.2108069747692</v>
       </c>
       <c r="J1250" s="13">
         <v>12238.814899999999</v>
@@ -57017,7 +57017,7 @@
       <c r="L1250" s="13"/>
       <c r="M1250" s="13"/>
       <c r="N1250" s="15">
-        <v>61821.7788</v>
+        <v>61821.525200000004</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1">
@@ -57034,7 +57034,7 @@
         <v>5741.1686828543779</v>
       </c>
       <c r="E1251" s="14">
-        <v>5019.6772277930168</v>
+        <v>5019.6805229710126</v>
       </c>
       <c r="F1251" s="13">
         <v>1154.2166999999999</v>
@@ -57046,7 +57046,7 @@
         <v>4751.1729571527949</v>
       </c>
       <c r="I1251" s="14">
-        <v>5618.20286780065</v>
+        <v>5618.2028678006491</v>
       </c>
       <c r="J1251" s="13">
         <v>5375.8909000000003</v>
@@ -57055,7 +57055,7 @@
       <c r="L1251" s="13"/>
       <c r="M1251" s="13"/>
       <c r="N1251" s="15">
-        <v>61040.029799999997</v>
+        <v>61040.029800000004</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57063,16 +57063,16 @@
         <v>45962</v>
       </c>
       <c r="B1252" s="13">
-        <v>49051.051599999999</v>
+        <v>49050.922200000001</v>
       </c>
       <c r="C1252" s="13">
         <v>10403.208199999999</v>
       </c>
       <c r="D1252" s="13">
-        <v>4714.9927846296496</v>
+        <v>4714.9803461589863</v>
       </c>
       <c r="E1252" s="14">
-        <v>4992.9674924973551</v>
+        <v>4992.948178307438</v>
       </c>
       <c r="F1252" s="13">
         <v>979.83450000000005</v>
@@ -57084,7 +57084,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="14">
-        <v>5768.2127381128485</v>
+        <v>5768.2127381128494</v>
       </c>
       <c r="J1252" s="13">
         <v>10675.3544</v>
@@ -57093,7 +57093,7 @@
       <c r="L1252" s="13"/>
       <c r="M1252" s="13"/>
       <c r="N1252" s="15">
-        <v>60706.2405</v>
+        <v>60706.111100000002</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1">
@@ -57110,7 +57110,7 @@
         <v>5681.0885198146652</v>
       </c>
       <c r="E1253" s="14">
-        <v>5202.4701264931327</v>
+        <v>5202.4560270572392</v>
       </c>
       <c r="F1253" s="13">
         <v>3024.5275999999999</v>
@@ -57131,7 +57131,7 @@
       <c r="L1253" s="13"/>
       <c r="M1253" s="13"/>
       <c r="N1253" s="15">
-        <v>103367.6793</v>
+        <v>103367.67929999999</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1">
@@ -57148,7 +57148,7 @@
         <v>5052.8167796411517</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.5292769043917</v>
+        <v>5308.5264524312042</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57177,16 +57177,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="13">
-        <v>84503.003200000006</v>
+        <v>84502.6299</v>
       </c>
       <c r="C1255" s="13">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="13">
-        <v>6217.1818095610106</v>
+        <v>6217.1543445730031</v>
       </c>
       <c r="E1255" s="14">
-        <v>5580.876229429512</v>
+        <v>5580.8670927672501</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57207,7 +57207,7 @@
       <c r="L1255" s="13"/>
       <c r="M1255" s="13"/>
       <c r="N1255" s="15">
-        <v>99699.280900000012</v>
+        <v>99698.907600000006</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1">
@@ -57224,7 +57224,7 @@
         <v>5187.2554103923076</v>
       </c>
       <c r="E1256" s="14">
-        <v>5470.8196209791013</v>
+        <v>5470.8110381571441</v>
       </c>
       <c r="F1256" s="13">
         <v>3141.94</v>
@@ -57245,7 +57245,7 @@
       <c r="L1256" s="13"/>
       <c r="M1256" s="13"/>
       <c r="N1256" s="15">
-        <v>77294.448100000009</v>
+        <v>77294.448099999994</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57262,7 +57262,7 @@
         <v>5246.4612349567415</v>
       </c>
       <c r="E1257" s="14">
-        <v>5422.8728491686034</v>
+        <v>5422.8659324429282</v>
       </c>
       <c r="F1257" s="13">
         <v>2948.9110000000001</v>
@@ -57274,7 +57274,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="14">
-        <v>6858.778759653972</v>
+        <v>6858.7787596539711</v>
       </c>
       <c r="J1257" s="13">
         <v>6940.3462</v>
@@ -57291,16 +57291,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="13">
-        <v>60368.599000000002</v>
+        <v>60365.7281</v>
       </c>
       <c r="C1258" s="13">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="13">
-        <v>4975.272642532218</v>
+        <v>4975.0360375676173</v>
       </c>
       <c r="E1258" s="14">
-        <v>5453.542739051486</v>
+        <v>5453.4819508858691</v>
       </c>
       <c r="F1258" s="13">
         <v>4360.9017999999996</v>
@@ -57315,13 +57315,13 @@
         <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="13">
-        <v>10585.696599999999</v>
+        <v>10585.6872</v>
       </c>
       <c r="K1258" s="13"/>
       <c r="L1258" s="13"/>
       <c r="M1258" s="13"/>
       <c r="N1258" s="15">
-        <v>75315.197400000005</v>
+        <v>75312.3171</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57329,16 +57329,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="13">
-        <v>64423.140599999999</v>
+        <v>64226.661999999997</v>
       </c>
       <c r="C1259" s="13">
-        <v>11809.409900000001</v>
+        <v>11775.5465</v>
       </c>
       <c r="D1259" s="13">
-        <v>5455.2379115911626</v>
+        <v>5454.2404465049667</v>
       </c>
       <c r="E1259" s="14">
-        <v>5182.6739864638521</v>
+        <v>5182.2195612264441</v>
       </c>
       <c r="F1259" s="13">
         <v>3014.4270000000001</v>
@@ -57353,13 +57353,13 @@
         <v>7266.6202217096234</v>
       </c>
       <c r="J1259" s="13">
-        <v>14233.7824</v>
+        <v>14233.1824</v>
       </c>
       <c r="K1259" s="13"/>
       <c r="L1259" s="13"/>
       <c r="M1259" s="13"/>
       <c r="N1259" s="15">
-        <v>81671.349999999991</v>
+        <v>81474.271399999998</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57367,16 +57367,16 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="13">
-        <v>60699.285100000001</v>
+        <v>60697.9205</v>
       </c>
       <c r="C1260" s="13">
         <v>11702.9162</v>
       </c>
       <c r="D1260" s="13">
-        <v>5186.680316483852</v>
+        <v>5186.5637130683717</v>
       </c>
       <c r="E1260" s="14">
-        <v>5209.6862472592102</v>
+        <v>5209.2128561195932</v>
       </c>
       <c r="F1260" s="13">
         <v>2192.3276999999998</v>
@@ -57391,13 +57391,13 @@
         <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="13">
-        <v>7543.9557999999997</v>
+        <v>7543.7636000000002</v>
       </c>
       <c r="K1260" s="13"/>
       <c r="L1260" s="13"/>
       <c r="M1260" s="13"/>
       <c r="N1260" s="15">
-        <v>70435.568599999999</v>
+        <v>70434.011800000007</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57405,16 +57405,16 @@
         <v>46025</v>
       </c>
       <c r="B1261" s="13">
-        <v>36129.719400000002</v>
+        <v>36129.798799999997</v>
       </c>
       <c r="C1261" s="13">
         <v>6783.5308000000005</v>
       </c>
       <c r="D1261" s="13">
-        <v>5326.0935146045176</v>
+        <v>5326.105219423489</v>
       </c>
       <c r="E1261" s="14">
-        <v>5255.3639159833792</v>
+        <v>5254.8717235194954</v>
       </c>
       <c r="F1261" s="13">
         <v>1259.8376000000001</v>
@@ -57429,13 +57429,13 @@
         <v>6388.7537797193982</v>
       </c>
       <c r="J1261" s="13">
-        <v>15412.5653</v>
+        <v>15412.583500000001</v>
       </c>
       <c r="K1261" s="13"/>
       <c r="L1261" s="13"/>
       <c r="M1261" s="13"/>
       <c r="N1261" s="15">
-        <v>52802.122300000003</v>
+        <v>52802.219899999996</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15.75" customHeight="1">
@@ -57443,16 +57443,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="13">
-        <v>31640.644499999999</v>
+        <v>31640.719499999999</v>
       </c>
       <c r="C1262" s="13">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="13">
-        <v>5567.2218402801864</v>
+        <v>5567.2350366497494</v>
       </c>
       <c r="E1262" s="14">
-        <v>5255.9253788488613</v>
+        <v>5255.3845423297171</v>
       </c>
       <c r="F1262" s="13">
         <v>1210.1021000000001</v>
@@ -57467,13 +57467,13 @@
         <v>6331.7504578958606</v>
       </c>
       <c r="J1262" s="13">
-        <v>7770.5465000000004</v>
+        <v>7771.0213999999996</v>
       </c>
       <c r="K1262" s="13"/>
       <c r="L1262" s="13"/>
       <c r="M1262" s="13"/>
       <c r="N1262" s="15">
-        <v>40621.293099999995</v>
+        <v>40621.843000000001</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57490,7 +57490,7 @@
         <v>5220.845437147972</v>
       </c>
       <c r="E1263" s="14">
-        <v>5335.3901554128042</v>
+        <v>5334.9774264974976</v>
       </c>
       <c r="F1263" s="13">
         <v>3212.6219999999998</v>
@@ -57519,37 +57519,37 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="13">
-        <v>40276.888800000001</v>
+        <v>41416.982499999998</v>
       </c>
       <c r="C1264" s="13">
-        <v>7173.5888000000004</v>
+        <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="13">
-        <v>5614.6079630323939</v>
+        <v>5650.6592147478159</v>
       </c>
       <c r="E1264" s="14">
-        <v>5393.7805058135591</v>
+        <v>5402.3307505606708</v>
       </c>
       <c r="F1264" s="13">
-        <v>2043.3688</v>
+        <v>1803.3380999999999</v>
       </c>
       <c r="G1264" s="13">
-        <v>305.68990000000002</v>
+        <v>282.65449999999998</v>
       </c>
       <c r="H1264" s="13">
-        <v>6684.4498297130522</v>
+        <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="14">
-        <v>6593.7417610129596</v>
+        <v>6519.8821211785771</v>
       </c>
       <c r="J1264" s="13">
-        <v>6203.9503999999997</v>
+        <v>6221.1000999999997</v>
       </c>
       <c r="K1264" s="13"/>
       <c r="L1264" s="13"/>
       <c r="M1264" s="13"/>
       <c r="N1264" s="15">
-        <v>48524.207999999999</v>
+        <v>49441.420699999995</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57557,34 +57557,34 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="22">
-        <v>63544.9035</v>
+        <v>67196.251199999999</v>
       </c>
       <c r="C1265" s="22">
-        <v>11986.8099</v>
+        <v>12820.026599999999</v>
       </c>
       <c r="D1265" s="22">
-        <v>5301.2356106523384</v>
+        <v>5241.5063787777171</v>
       </c>
       <c r="E1265" s="23">
-        <v>5338.0279686621116</v>
+        <v>5325.8660648398436</v>
       </c>
       <c r="F1265" s="22">
-        <v>2355.1970000000001</v>
+        <v>2790.8292999999999</v>
       </c>
       <c r="G1265" s="22">
-        <v>357.86860000000001</v>
+        <v>456.13139999999999</v>
       </c>
       <c r="H1265" s="22">
-        <v>6581.1781195667909</v>
+        <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="23">
-        <v>7018.0263396397113</v>
+        <v>6770.0527178355378</v>
       </c>
       <c r="J1265" s="22">
-        <v>7905.6634999999997</v>
+        <v>8304.0838000000003</v>
       </c>
       <c r="N1265" s="21">
-        <v>73805.763999999996</v>
+        <v>78291.164300000004</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57592,34 +57592,104 @@
         <v>46060</v>
       </c>
       <c r="B1266" s="22">
-        <v>27609.502400000001</v>
+        <v>42300.282200000001</v>
       </c>
       <c r="C1266" s="22">
-        <v>4529.1652000000004</v>
+        <v>7887.6062000000002</v>
       </c>
       <c r="D1266" s="22">
-        <v>6095.9362665773378</v>
+        <v>5362.8795768226873</v>
       </c>
       <c r="E1266" s="23">
-        <v>5425.9088811518031</v>
+        <v>5326.7263249586904</v>
       </c>
       <c r="F1266" s="22">
-        <v>1325.7043000000001</v>
+        <v>1798.21</v>
       </c>
       <c r="G1266" s="22">
-        <v>187.72649999999999</v>
+        <v>260.18180000000001</v>
       </c>
       <c r="H1266" s="22">
-        <v>7061.8921675948795</v>
+        <v>6911.3596723521778</v>
       </c>
       <c r="I1266" s="23">
-        <v>7010.4934567378878</v>
+        <v>6762.5654950612061</v>
       </c>
       <c r="J1266" s="22">
-        <v>4703.2345999999998</v>
+        <v>7855.6562000000004</v>
       </c>
       <c r="N1266" s="21">
-        <v>33638.441299999999</v>
+        <v>51954.148400000005</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1267" s="20">
+        <v>46067</v>
+      </c>
+      <c r="B1267" s="22">
+        <v>66210.158100000001</v>
+      </c>
+      <c r="C1267" s="22">
+        <v>11283.4485</v>
+      </c>
+      <c r="D1267" s="22">
+        <v>5867.9009435812113</v>
+      </c>
+      <c r="E1267" s="23">
+        <v>5415.016226342168</v>
+      </c>
+      <c r="F1267" s="22">
+        <v>1401.6822999999999</v>
+      </c>
+      <c r="G1267" s="22">
+        <v>192.12569999999999</v>
+      </c>
+      <c r="H1267" s="22">
+        <v>7295.6522734855362</v>
+      </c>
+      <c r="I1267" s="23">
+        <v>6630.5931971154205</v>
+      </c>
+      <c r="J1267" s="22">
+        <v>12290.3796</v>
+      </c>
+      <c r="N1267" s="21">
+        <v>79902.22</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1268" s="20">
+        <v>46074</v>
+      </c>
+      <c r="B1268" s="22">
+        <v>34940.860699999997</v>
+      </c>
+      <c r="C1268" s="22">
+        <v>6777.3383999999996</v>
+      </c>
+      <c r="D1268" s="22">
+        <v>5155.543170162493</v>
+      </c>
+      <c r="E1268" s="23">
+        <v>5389.5771053997405</v>
+      </c>
+      <c r="F1268" s="22">
+        <v>1106.5137</v>
+      </c>
+      <c r="G1268" s="22">
+        <v>143.48220000000001</v>
+      </c>
+      <c r="H1268" s="22">
+        <v>7711.8534563869243</v>
+      </c>
+      <c r="I1268" s="23">
+        <v>6675.1849347609186</v>
+      </c>
+      <c r="J1268" s="22">
+        <v>4969.8365000000003</v>
+      </c>
+      <c r="N1268" s="21">
+        <v>41017.210899999998</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6BC464-22BF-4080-B5E3-053406500F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B88F8BD-F07B-4ED2-BAC5-28303EC6F3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1269"/>
+  <dimension ref="A1:W1270"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -915,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="35">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
@@ -53748,7 +53748,7 @@
       <c r="L1164" s="13"/>
       <c r="M1164" s="13"/>
       <c r="N1164" s="15">
-        <v>57458.467499999999</v>
+        <v>57458.467500000006</v>
       </c>
     </row>
     <row r="1165" spans="1:14" ht="15.75" customHeight="1">
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309888</v>
+        <v>4180.3219217309879</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53777,7 +53777,7 @@
         <v>3930.3634262421583</v>
       </c>
       <c r="I1165" s="14">
-        <v>3575.1060841405906</v>
+        <v>3575.1060841405915</v>
       </c>
       <c r="J1165" s="13">
         <v>4062.5365999999999</v>
@@ -53824,7 +53824,7 @@
       <c r="L1166" s="13"/>
       <c r="M1166" s="13"/>
       <c r="N1166" s="15">
-        <v>31626.6551</v>
+        <v>31626.655099999996</v>
       </c>
     </row>
     <row r="1167" spans="1:14" ht="15.75" customHeight="1">
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.855846056349</v>
+        <v>4171.8558460563499</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -53853,7 +53853,7 @@
         <v>3239.1375010965894</v>
       </c>
       <c r="I1167" s="14">
-        <v>3596.9869038721486</v>
+        <v>3596.986903872149</v>
       </c>
       <c r="J1167" s="13">
         <v>7280.7353999999996</v>
@@ -53879,7 +53879,7 @@
         <v>3877.0306064631195</v>
       </c>
       <c r="E1168" s="14">
-        <v>4055.3634375452443</v>
+        <v>4055.3634375452452</v>
       </c>
       <c r="F1168" s="13">
         <v>2016.7924</v>
@@ -53976,7 +53976,7 @@
       <c r="L1170" s="13"/>
       <c r="M1170" s="13"/>
       <c r="N1170" s="15">
-        <v>37348.1538</v>
+        <v>37348.153800000007</v>
       </c>
     </row>
     <row r="1171" spans="1:14" ht="15.75" customHeight="1">
@@ -54157,7 +54157,7 @@
         <v>3165.986834005897</v>
       </c>
       <c r="I1175" s="14">
-        <v>3345.9193035632734</v>
+        <v>3345.9193035632725</v>
       </c>
       <c r="J1175" s="13">
         <v>18463.542600000001</v>
@@ -54242,7 +54242,7 @@
       <c r="L1177" s="13"/>
       <c r="M1177" s="13"/>
       <c r="N1177" s="15">
-        <v>62161.926699999996</v>
+        <v>62161.926700000004</v>
       </c>
     </row>
     <row r="1178" spans="1:14" ht="15.75" customHeight="1">
@@ -54335,7 +54335,7 @@
         <v>4008.5523747206912</v>
       </c>
       <c r="E1180" s="14">
-        <v>4173.750113280712</v>
+        <v>4173.750113280711</v>
       </c>
       <c r="F1180" s="13">
         <v>909.47910000000002</v>
@@ -54356,7 +54356,7 @@
       <c r="L1180" s="13"/>
       <c r="M1180" s="13"/>
       <c r="N1180" s="15">
-        <v>56623.827600000004</v>
+        <v>56623.827599999997</v>
       </c>
     </row>
     <row r="1181" spans="1:14" ht="15.75" customHeight="1">
@@ -54385,7 +54385,7 @@
         <v>3932.1869092178767</v>
       </c>
       <c r="I1181" s="14">
-        <v>3763.2741964818451</v>
+        <v>3763.2741964818456</v>
       </c>
       <c r="J1181" s="13">
         <v>7024.5267000000003</v>
@@ -54394,7 +54394,7 @@
       <c r="L1181" s="13"/>
       <c r="M1181" s="13"/>
       <c r="N1181" s="15">
-        <v>52642.395299999996</v>
+        <v>52642.395300000004</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15.75" customHeight="1">
@@ -54411,7 +54411,7 @@
         <v>4033.0100843855616</v>
       </c>
       <c r="E1182" s="14">
-        <v>4020.0169955492411</v>
+        <v>4020.0169955492406</v>
       </c>
       <c r="F1182" s="13">
         <v>427.52350000000001</v>
@@ -54423,7 +54423,7 @@
         <v>4435.1671265846417</v>
       </c>
       <c r="I1182" s="14">
-        <v>3815.6421043550649</v>
+        <v>3815.6421043550654</v>
       </c>
       <c r="J1182" s="13">
         <v>6999.7999</v>
@@ -54546,7 +54546,7 @@
       <c r="L1185" s="13"/>
       <c r="M1185" s="13"/>
       <c r="N1185" s="15">
-        <v>37483.069499999998</v>
+        <v>37483.069499999991</v>
       </c>
     </row>
     <row r="1186" spans="1:14" ht="15.75" customHeight="1">
@@ -54584,7 +54584,7 @@
       <c r="L1186" s="13"/>
       <c r="M1186" s="13"/>
       <c r="N1186" s="15">
-        <v>44453.567300000002</v>
+        <v>44453.567299999995</v>
       </c>
     </row>
     <row r="1187" spans="1:14" ht="15.75" customHeight="1">
@@ -54736,7 +54736,7 @@
       <c r="L1190" s="13"/>
       <c r="M1190" s="13"/>
       <c r="N1190" s="15">
-        <v>59168.145499999999</v>
+        <v>59168.145500000006</v>
       </c>
     </row>
     <row r="1191" spans="1:14" ht="15.75" customHeight="1">
@@ -54774,7 +54774,7 @@
       <c r="L1191" s="13"/>
       <c r="M1191" s="13"/>
       <c r="N1191" s="15">
-        <v>59039.229300000006</v>
+        <v>59039.229299999999</v>
       </c>
     </row>
     <row r="1192" spans="1:14" ht="15.75" customHeight="1">
@@ -54964,7 +54964,7 @@
       <c r="L1196" s="13"/>
       <c r="M1196" s="13"/>
       <c r="N1196" s="15">
-        <v>59285.6731</v>
+        <v>59285.673100000007</v>
       </c>
     </row>
     <row r="1197" spans="1:14" ht="15.75" customHeight="1">
@@ -55002,7 +55002,7 @@
       <c r="L1197" s="13"/>
       <c r="M1197" s="13"/>
       <c r="N1197" s="15">
-        <v>46861.756300000001</v>
+        <v>46861.756299999994</v>
       </c>
     </row>
     <row r="1198" spans="1:14" ht="15.75" customHeight="1">
@@ -55078,7 +55078,7 @@
       <c r="L1199" s="13"/>
       <c r="M1199" s="13"/>
       <c r="N1199" s="15">
-        <v>45059.347399999999</v>
+        <v>45059.347400000006</v>
       </c>
     </row>
     <row r="1200" spans="1:14" ht="15.75" customHeight="1">
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551794</v>
+        <v>4487.7143253551803</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55154,7 +55154,7 @@
       <c r="L1201" s="13"/>
       <c r="M1201" s="13"/>
       <c r="N1201" s="15">
-        <v>64229.893500000006</v>
+        <v>64229.893499999998</v>
       </c>
     </row>
     <row r="1202" spans="1:14" ht="15.75" customHeight="1">
@@ -55230,7 +55230,7 @@
       <c r="L1203" s="13"/>
       <c r="M1203" s="13"/>
       <c r="N1203" s="15">
-        <v>79222.162899999996</v>
+        <v>79222.162899999981</v>
       </c>
     </row>
     <row r="1204" spans="1:14" ht="15.75" customHeight="1">
@@ -55268,7 +55268,7 @@
       <c r="L1204" s="13"/>
       <c r="M1204" s="13"/>
       <c r="N1204" s="15">
-        <v>86729.972699999998</v>
+        <v>86729.972700000013</v>
       </c>
     </row>
     <row r="1205" spans="1:14" ht="15.75" customHeight="1">
@@ -55335,7 +55335,7 @@
         <v>3932.5340059065734</v>
       </c>
       <c r="I1206" s="14">
-        <v>4333.5986404219702</v>
+        <v>4333.5986404219693</v>
       </c>
       <c r="J1206" s="13">
         <v>6089.9108999999999</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629657</v>
+        <v>4315.8033455629638</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55411,7 +55411,7 @@
         <v>4947.3851972485918</v>
       </c>
       <c r="I1208" s="14">
-        <v>4350.8974691132007</v>
+        <v>4350.8974691131998</v>
       </c>
       <c r="J1208" s="13">
         <v>9287.4572000000007</v>
@@ -55420,7 +55420,7 @@
       <c r="L1208" s="13"/>
       <c r="M1208" s="13"/>
       <c r="N1208" s="15">
-        <v>49051.207200000004</v>
+        <v>49051.207199999997</v>
       </c>
     </row>
     <row r="1209" spans="1:14" ht="15.75" customHeight="1">
@@ -55572,7 +55572,7 @@
       <c r="L1212" s="13"/>
       <c r="M1212" s="13"/>
       <c r="N1212" s="15">
-        <v>45765.935100000002</v>
+        <v>45765.935099999995</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55648,7 +55648,7 @@
       <c r="L1214" s="13"/>
       <c r="M1214" s="13"/>
       <c r="N1214" s="15">
-        <v>76702.561399999991</v>
+        <v>76702.561400000006</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55741,7 +55741,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.1866360758077</v>
+        <v>4706.1866360758067</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.4088847985458</v>
+        <v>4736.4088847985449</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55794,13 +55794,13 @@
         <v>4467.261635435777</v>
       </c>
       <c r="J1218" s="13">
-        <v>12199.373299999999</v>
+        <v>12197.8395</v>
       </c>
       <c r="K1218" s="13"/>
       <c r="L1218" s="13"/>
       <c r="M1218" s="13"/>
       <c r="N1218" s="15">
-        <v>49272.0501</v>
+        <v>49270.516300000003</v>
       </c>
     </row>
     <row r="1219" spans="1:14" ht="15.75" customHeight="1">
@@ -55817,7 +55817,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="14">
-        <v>4756.2469293655349</v>
+        <v>4756.246929365534</v>
       </c>
       <c r="F1219" s="13">
         <v>1866.9058</v>
@@ -55838,7 +55838,7 @@
       <c r="L1219" s="13"/>
       <c r="M1219" s="13"/>
       <c r="N1219" s="15">
-        <v>62677.385599999994</v>
+        <v>62677.385600000001</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55855,7 +55855,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.2967738120533</v>
+        <v>4663.2967738120524</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55952,7 +55952,7 @@
       <c r="L1222" s="13"/>
       <c r="M1222" s="13"/>
       <c r="N1222" s="15">
-        <v>52979.688900000001</v>
+        <v>52979.688899999994</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56218,7 +56218,7 @@
       <c r="L1229" s="13"/>
       <c r="M1229" s="13"/>
       <c r="N1229" s="15">
-        <v>66469.655100000004</v>
+        <v>66469.655099999989</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56387,7 +56387,7 @@
         <v>4897.4427637682502</v>
       </c>
       <c r="E1234" s="14">
-        <v>4765.8359934631844</v>
+        <v>4765.8359934631853</v>
       </c>
       <c r="F1234" s="13">
         <v>556.48080000000004</v>
@@ -56560,7 +56560,7 @@
       <c r="L1238" s="13"/>
       <c r="M1238" s="13"/>
       <c r="N1238" s="15">
-        <v>53730.3577</v>
+        <v>53730.357699999993</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56674,7 +56674,7 @@
       <c r="L1241" s="13"/>
       <c r="M1241" s="13"/>
       <c r="N1241" s="15">
-        <v>77476.646099999998</v>
+        <v>77476.646100000013</v>
       </c>
       <c r="O1241" s="16"/>
     </row>
@@ -56704,7 +56704,7 @@
         <v>6080.2534679336923</v>
       </c>
       <c r="I1242" s="14">
-        <v>6193.667101883063</v>
+        <v>6193.6671018830639</v>
       </c>
       <c r="J1242" s="13">
         <v>8322.0208999999995</v>
@@ -56745,13 +56745,13 @@
         <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="13">
-        <v>15514.227699999999</v>
+        <v>15660.4136</v>
       </c>
       <c r="K1243" s="13"/>
       <c r="L1243" s="13"/>
       <c r="M1243" s="13"/>
       <c r="N1243" s="15">
-        <v>89510.918000000005</v>
+        <v>89657.103900000002</v>
       </c>
     </row>
     <row r="1244" spans="1:15" ht="15.75" customHeight="1">
@@ -56783,13 +56783,13 @@
         <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="13">
-        <v>8181.2407000000003</v>
+        <v>8281.8516999999993</v>
       </c>
       <c r="K1244" s="13"/>
       <c r="L1244" s="13"/>
       <c r="M1244" s="13"/>
       <c r="N1244" s="15">
-        <v>57558.685400000002</v>
+        <v>57659.296399999999</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1">
@@ -56827,7 +56827,7 @@
       <c r="L1245" s="13"/>
       <c r="M1245" s="13"/>
       <c r="N1245" s="15">
-        <v>48637.9012</v>
+        <v>48637.901200000008</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56859,13 +56859,13 @@
         <v>5567.868517566978</v>
       </c>
       <c r="J1246" s="13">
-        <v>6479.5199000000002</v>
+        <v>6522.4556000000002</v>
       </c>
       <c r="K1246" s="13"/>
       <c r="L1246" s="13"/>
       <c r="M1246" s="13"/>
       <c r="N1246" s="15">
-        <v>70106.074099999998</v>
+        <v>70149.0098</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56903,7 +56903,7 @@
       <c r="L1247" s="13"/>
       <c r="M1247" s="13"/>
       <c r="N1247" s="15">
-        <v>60445.305200000003</v>
+        <v>60445.305199999995</v>
       </c>
     </row>
     <row r="1248" spans="1:15" ht="15.75" customHeight="1">
@@ -57055,7 +57055,7 @@
       <c r="L1251" s="13"/>
       <c r="M1251" s="13"/>
       <c r="N1251" s="15">
-        <v>61040.029800000004</v>
+        <v>61040.029799999997</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57084,7 +57084,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="14">
-        <v>5768.2127381128485</v>
+        <v>5768.2127381128494</v>
       </c>
       <c r="J1252" s="13">
         <v>10675.3544</v>
@@ -57093,7 +57093,7 @@
       <c r="L1252" s="13"/>
       <c r="M1252" s="13"/>
       <c r="N1252" s="15">
-        <v>60705.863900000004</v>
+        <v>60705.863899999997</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1">
@@ -57101,16 +57101,16 @@
         <v>45969</v>
       </c>
       <c r="B1253" s="13">
-        <v>88077.973499999993</v>
+        <v>88076.765400000004</v>
       </c>
       <c r="C1253" s="13">
         <v>15503.728800000001</v>
       </c>
       <c r="D1253" s="13">
-        <v>5681.0832178643368</v>
+        <v>5681.0052946746591</v>
       </c>
       <c r="E1253" s="14">
-        <v>5202.4494477199632</v>
+        <v>5202.4253174911737</v>
       </c>
       <c r="F1253" s="13">
         <v>3024.5275999999999</v>
@@ -57131,7 +57131,7 @@
       <c r="L1253" s="13"/>
       <c r="M1253" s="13"/>
       <c r="N1253" s="15">
-        <v>103367.59709999998</v>
+        <v>103366.38900000001</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1">
@@ -57148,7 +57148,7 @@
         <v>5052.6004887524759</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.4770918155373</v>
+        <v>5308.4507220623818</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57160,7 +57160,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="14">
-        <v>5620.2491328335427</v>
+        <v>5620.2491328335436</v>
       </c>
       <c r="J1254" s="13">
         <v>10574.364</v>
@@ -57177,16 +57177,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="13">
-        <v>84435.960300000006</v>
+        <v>84435.654299999995</v>
       </c>
       <c r="C1255" s="13">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="13">
-        <v>6212.2492286756469</v>
+        <v>6212.2267151842707</v>
       </c>
       <c r="E1255" s="14">
-        <v>5579.6142595340852</v>
+        <v>5579.586740496231</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57207,7 +57207,7 @@
       <c r="L1255" s="13"/>
       <c r="M1255" s="13"/>
       <c r="N1255" s="15">
-        <v>99632.238000000012</v>
+        <v>99631.932000000001</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1">
@@ -57224,7 +57224,7 @@
         <v>5187.2276632970024</v>
       </c>
       <c r="E1256" s="14">
-        <v>5469.6282119239213</v>
+        <v>5469.6023610173679</v>
       </c>
       <c r="F1256" s="13">
         <v>3141.94</v>
@@ -57262,7 +57262,7 @@
         <v>5246.4612349567415</v>
       </c>
       <c r="E1257" s="14">
-        <v>5421.5868755224838</v>
+        <v>5421.5588213720839</v>
       </c>
       <c r="F1257" s="13">
         <v>2948.9110000000001</v>
@@ -57300,7 +57300,7 @@
         <v>4975.0068379650684</v>
       </c>
       <c r="E1258" s="14">
-        <v>5452.1833753619612</v>
+        <v>5452.1776416899693</v>
       </c>
       <c r="F1258" s="13">
         <v>4360.9017999999996</v>
@@ -57312,7 +57312,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="14">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="13">
         <v>10585.9912</v>
@@ -57321,7 +57321,7 @@
       <c r="L1258" s="13"/>
       <c r="M1258" s="13"/>
       <c r="N1258" s="15">
-        <v>75312.266799999998</v>
+        <v>75312.266800000012</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57397,7 +57397,7 @@
       <c r="L1260" s="13"/>
       <c r="M1260" s="13"/>
       <c r="N1260" s="15">
-        <v>70434.128400000001</v>
+        <v>70434.128399999987</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57414,7 +57414,7 @@
         <v>5326.105219423489</v>
       </c>
       <c r="E1261" s="14">
-        <v>5254.9295941363753</v>
+        <v>5254.9295941363744</v>
       </c>
       <c r="F1261" s="13">
         <v>1259.8376000000001</v>
@@ -57452,7 +57452,7 @@
         <v>5567.2482330193116</v>
       </c>
       <c r="E1262" s="14">
-        <v>5255.4478965026346</v>
+        <v>5255.4478965026337</v>
       </c>
       <c r="F1262" s="13">
         <v>1210.1021000000001</v>
@@ -57473,7 +57473,7 @@
       <c r="L1262" s="13"/>
       <c r="M1262" s="13"/>
       <c r="N1262" s="15">
-        <v>40621.917999999998</v>
+        <v>40621.918000000005</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57584,7 +57584,7 @@
         <v>8304.0838000000003</v>
       </c>
       <c r="N1265" s="21">
-        <v>77849.856</v>
+        <v>77849.855999999985</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57627,34 +57627,34 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="22">
-        <v>71413.559099999999</v>
+        <v>77181.978400000007</v>
       </c>
       <c r="C1267" s="22">
-        <v>12344.4872</v>
+        <v>13537.1278</v>
       </c>
       <c r="D1267" s="22">
-        <v>5785.0567579672324</v>
+        <v>5701.5032686623526</v>
       </c>
       <c r="E1267" s="23">
-        <v>5390.5713253106833</v>
+        <v>5376.8010968356893</v>
       </c>
       <c r="F1267" s="22">
-        <v>1791.5183999999999</v>
+        <v>1828.6121000000001</v>
       </c>
       <c r="G1267" s="22">
         <v>269.9348</v>
       </c>
       <c r="H1267" s="22">
-        <v>6636.8560111552861</v>
+        <v>6774.2732689523546</v>
       </c>
       <c r="I1267" s="23">
-        <v>6544.0179494685599</v>
+        <v>6569.7313381807944</v>
       </c>
       <c r="J1267" s="22">
-        <v>12733.9503</v>
+        <v>13051.025600000001</v>
       </c>
       <c r="N1267" s="21">
-        <v>85939.027799999996</v>
+        <v>92061.616100000014</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57662,16 +57662,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="22">
-        <v>54026.789499999999</v>
+        <v>60612.054700000001</v>
       </c>
       <c r="C1268" s="22">
-        <v>10557.3855</v>
+        <v>11838.8037</v>
       </c>
       <c r="D1268" s="22">
-        <v>5117.4402507135883</v>
+        <v>5119.778673245507</v>
       </c>
       <c r="E1268" s="23">
-        <v>5338.8320627776247</v>
+        <v>5321.6485791411851</v>
       </c>
       <c r="F1268" s="22">
         <v>1208.7674</v>
@@ -57683,13 +57683,13 @@
         <v>7470.6302618128502</v>
       </c>
       <c r="I1268" s="23">
-        <v>6555.5185249098076</v>
+        <v>6585.4300491728982</v>
       </c>
       <c r="J1268" s="22">
-        <v>12968.013499999999</v>
+        <v>14206.0404</v>
       </c>
       <c r="N1268" s="21">
-        <v>68203.570399999997</v>
+        <v>76026.862500000003</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57697,34 +57697,69 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="22">
-        <v>30217.6672</v>
+        <v>49556.427900000002</v>
       </c>
       <c r="C1269" s="22">
-        <v>5583.1171999999997</v>
+        <v>9334.2222000000002</v>
       </c>
       <c r="D1269" s="22">
-        <v>5412.3290121869559</v>
+        <v>5309.1116579590325</v>
       </c>
       <c r="E1269" s="23">
-        <v>5340.3313535032412</v>
+        <v>5308.0386383939795</v>
       </c>
       <c r="F1269" s="22">
-        <v>413.86489999999998</v>
+        <v>946.99189999999999</v>
       </c>
       <c r="G1269" s="22">
-        <v>55.173299999999998</v>
+        <v>114.73480000000001</v>
       </c>
       <c r="H1269" s="22">
-        <v>7501.1808247830013</v>
+        <v>8253.7460299752129</v>
       </c>
       <c r="I1269" s="23">
-        <v>6398.6026836194933</v>
+        <v>6564.4404635417095</v>
       </c>
       <c r="J1269" s="22">
-        <v>4035.1709999999998</v>
+        <v>6945.6157999999996</v>
       </c>
       <c r="N1269" s="21">
-        <v>34666.703099999999</v>
+        <v>57449.035600000003</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1270" s="20">
+        <v>46088</v>
+      </c>
+      <c r="B1270" s="22">
+        <v>38324.2111</v>
+      </c>
+      <c r="C1270" s="22">
+        <v>5648.9180999999999</v>
+      </c>
+      <c r="D1270" s="22">
+        <v>6784.3453244613338</v>
+      </c>
+      <c r="E1270" s="23">
+        <v>5487.1952519306305</v>
+      </c>
+      <c r="F1270" s="22">
+        <v>1107.3652</v>
+      </c>
+      <c r="G1270" s="22">
+        <v>131.98410000000001</v>
+      </c>
+      <c r="H1270" s="22">
+        <v>8390.1409336427641</v>
+      </c>
+      <c r="I1270" s="23">
+        <v>7447.7692675197495</v>
+      </c>
+      <c r="J1270" s="22">
+        <v>4901.7485999999999</v>
+      </c>
+      <c r="N1270" s="21">
+        <v>44333.3249</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B88F8BD-F07B-4ED2-BAC5-28303EC6F3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CC010A-E8FE-4D66-B7B4-ED8F496AC49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1270"/>
+  <dimension ref="A1:W1271"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -53499,7 +53499,7 @@
         <v>4150.9922145963383</v>
       </c>
       <c r="E1158" s="14">
-        <v>3840.8705315087991</v>
+        <v>3840.8705315088</v>
       </c>
       <c r="F1158" s="13">
         <v>882.2903</v>
@@ -53549,7 +53549,7 @@
         <v>3982.0975670205294</v>
       </c>
       <c r="I1159" s="14">
-        <v>3617.6613635639042</v>
+        <v>3617.6613635639046</v>
       </c>
       <c r="J1159" s="13">
         <v>6212.6449000000002</v>
@@ -53575,7 +53575,7 @@
         <v>3966.9774403598576</v>
       </c>
       <c r="E1160" s="14">
-        <v>3927.1454924749778</v>
+        <v>3927.1454924749787</v>
       </c>
       <c r="F1160" s="13">
         <v>1675.7801999999999</v>
@@ -53689,7 +53689,7 @@
         <v>4184.0244468128631</v>
       </c>
       <c r="E1163" s="14">
-        <v>3997.1899679243247</v>
+        <v>3997.1899679243252</v>
       </c>
       <c r="F1163" s="13">
         <v>1277.3494000000001</v>
@@ -53748,7 +53748,7 @@
       <c r="L1164" s="13"/>
       <c r="M1164" s="13"/>
       <c r="N1164" s="15">
-        <v>57458.467500000006</v>
+        <v>57458.467499999999</v>
       </c>
     </row>
     <row r="1165" spans="1:14" ht="15.75" customHeight="1">
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309879</v>
+        <v>4180.3219217309888</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53777,7 +53777,7 @@
         <v>3930.3634262421583</v>
       </c>
       <c r="I1165" s="14">
-        <v>3575.1060841405915</v>
+        <v>3575.1060841405906</v>
       </c>
       <c r="J1165" s="13">
         <v>4062.5365999999999</v>
@@ -53803,7 +53803,7 @@
         <v>4144.4221019502211</v>
       </c>
       <c r="E1166" s="14">
-        <v>4237.0040886928518</v>
+        <v>4237.0040886928527</v>
       </c>
       <c r="F1166" s="13">
         <v>1411.7936999999999</v>
@@ -53824,7 +53824,7 @@
       <c r="L1166" s="13"/>
       <c r="M1166" s="13"/>
       <c r="N1166" s="15">
-        <v>31626.655099999996</v>
+        <v>31626.6551</v>
       </c>
     </row>
     <row r="1167" spans="1:14" ht="15.75" customHeight="1">
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.8558460563499</v>
+        <v>4171.855846056349</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -53853,7 +53853,7 @@
         <v>3239.1375010965894</v>
       </c>
       <c r="I1167" s="14">
-        <v>3596.986903872149</v>
+        <v>3596.9869038721486</v>
       </c>
       <c r="J1167" s="13">
         <v>7280.7353999999996</v>
@@ -53976,7 +53976,7 @@
       <c r="L1170" s="13"/>
       <c r="M1170" s="13"/>
       <c r="N1170" s="15">
-        <v>37348.153800000007</v>
+        <v>37348.1538</v>
       </c>
     </row>
     <row r="1171" spans="1:14" ht="15.75" customHeight="1">
@@ -54157,7 +54157,7 @@
         <v>3165.986834005897</v>
       </c>
       <c r="I1175" s="14">
-        <v>3345.9193035632725</v>
+        <v>3345.9193035632734</v>
       </c>
       <c r="J1175" s="13">
         <v>18463.542600000001</v>
@@ -54242,7 +54242,7 @@
       <c r="L1177" s="13"/>
       <c r="M1177" s="13"/>
       <c r="N1177" s="15">
-        <v>62161.926700000004</v>
+        <v>62161.926699999996</v>
       </c>
     </row>
     <row r="1178" spans="1:14" ht="15.75" customHeight="1">
@@ -54335,7 +54335,7 @@
         <v>4008.5523747206912</v>
       </c>
       <c r="E1180" s="14">
-        <v>4173.750113280711</v>
+        <v>4173.750113280712</v>
       </c>
       <c r="F1180" s="13">
         <v>909.47910000000002</v>
@@ -54347,7 +54347,7 @@
         <v>3932.0511251890948</v>
       </c>
       <c r="I1180" s="14">
-        <v>3820.0779903432685</v>
+        <v>3820.0779903432676</v>
       </c>
       <c r="J1180" s="13">
         <v>7100.3598000000002</v>
@@ -54356,7 +54356,7 @@
       <c r="L1180" s="13"/>
       <c r="M1180" s="13"/>
       <c r="N1180" s="15">
-        <v>56623.827599999997</v>
+        <v>56623.827600000004</v>
       </c>
     </row>
     <row r="1181" spans="1:14" ht="15.75" customHeight="1">
@@ -54385,7 +54385,7 @@
         <v>3932.1869092178767</v>
       </c>
       <c r="I1181" s="14">
-        <v>3763.2741964818456</v>
+        <v>3763.2741964818451</v>
       </c>
       <c r="J1181" s="13">
         <v>7024.5267000000003</v>
@@ -54394,7 +54394,7 @@
       <c r="L1181" s="13"/>
       <c r="M1181" s="13"/>
       <c r="N1181" s="15">
-        <v>52642.395300000004</v>
+        <v>52642.395299999996</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15.75" customHeight="1">
@@ -54411,7 +54411,7 @@
         <v>4033.0100843855616</v>
       </c>
       <c r="E1182" s="14">
-        <v>4020.0169955492406</v>
+        <v>4020.0169955492411</v>
       </c>
       <c r="F1182" s="13">
         <v>427.52350000000001</v>
@@ -54423,7 +54423,7 @@
         <v>4435.1671265846417</v>
       </c>
       <c r="I1182" s="14">
-        <v>3815.6421043550654</v>
+        <v>3815.6421043550649</v>
       </c>
       <c r="J1182" s="13">
         <v>6999.7999</v>
@@ -54487,7 +54487,7 @@
         <v>4658.79795304041</v>
       </c>
       <c r="E1184" s="14">
-        <v>4190.0226995693956</v>
+        <v>4190.0226995693947</v>
       </c>
       <c r="F1184" s="13">
         <v>936.56650000000002</v>
@@ -54525,7 +54525,7 @@
         <v>4059.2289950562249</v>
       </c>
       <c r="E1185" s="14">
-        <v>4136.2469995879528</v>
+        <v>4136.2469995879537</v>
       </c>
       <c r="F1185" s="13">
         <v>566.73659999999995</v>
@@ -54546,7 +54546,7 @@
       <c r="L1185" s="13"/>
       <c r="M1185" s="13"/>
       <c r="N1185" s="15">
-        <v>37483.069499999991</v>
+        <v>37483.069499999998</v>
       </c>
     </row>
     <row r="1186" spans="1:14" ht="15.75" customHeight="1">
@@ -54575,7 +54575,7 @@
         <v>4393.5575388702919</v>
       </c>
       <c r="I1186" s="14">
-        <v>4445.0065612912513</v>
+        <v>4445.0065612912522</v>
       </c>
       <c r="J1186" s="13">
         <v>7294.8577999999998</v>
@@ -54584,7 +54584,7 @@
       <c r="L1186" s="13"/>
       <c r="M1186" s="13"/>
       <c r="N1186" s="15">
-        <v>44453.567299999995</v>
+        <v>44453.567300000002</v>
       </c>
     </row>
     <row r="1187" spans="1:14" ht="15.75" customHeight="1">
@@ -54613,7 +54613,7 @@
         <v>4806.1907118779418</v>
       </c>
       <c r="I1187" s="14">
-        <v>4604.0956192242547</v>
+        <v>4604.0956192242566</v>
       </c>
       <c r="J1187" s="13">
         <v>21194.6531</v>
@@ -54639,7 +54639,7 @@
         <v>3791.6346654211702</v>
       </c>
       <c r="E1188" s="14">
-        <v>4022.1931810252645</v>
+        <v>4022.1931810252636</v>
       </c>
       <c r="F1188" s="13">
         <v>1017.2264</v>
@@ -54677,7 +54677,7 @@
         <v>4499.5444292922639</v>
       </c>
       <c r="E1189" s="14">
-        <v>4039.2368541021851</v>
+        <v>4039.2368541021842</v>
       </c>
       <c r="F1189" s="13">
         <v>520.32439999999997</v>
@@ -54727,7 +54727,7 @@
         <v>4531.757943331254</v>
       </c>
       <c r="I1190" s="14">
-        <v>4095.695696255355</v>
+        <v>4095.6956962553541</v>
       </c>
       <c r="J1190" s="13">
         <v>5596.1341000000002</v>
@@ -54736,7 +54736,7 @@
       <c r="L1190" s="13"/>
       <c r="M1190" s="13"/>
       <c r="N1190" s="15">
-        <v>59168.145500000006</v>
+        <v>59168.145499999999</v>
       </c>
     </row>
     <row r="1191" spans="1:14" ht="15.75" customHeight="1">
@@ -54765,7 +54765,7 @@
         <v>3350.0403096116738</v>
       </c>
       <c r="I1191" s="14">
-        <v>3875.9174025958691</v>
+        <v>3875.9174025958678</v>
       </c>
       <c r="J1191" s="13">
         <v>17500.0933</v>
@@ -54774,7 +54774,7 @@
       <c r="L1191" s="13"/>
       <c r="M1191" s="13"/>
       <c r="N1191" s="15">
-        <v>59039.229299999999</v>
+        <v>59039.229300000006</v>
       </c>
     </row>
     <row r="1192" spans="1:14" ht="15.75" customHeight="1">
@@ -54964,7 +54964,7 @@
       <c r="L1196" s="13"/>
       <c r="M1196" s="13"/>
       <c r="N1196" s="15">
-        <v>59285.673100000007</v>
+        <v>59285.6731</v>
       </c>
     </row>
     <row r="1197" spans="1:14" ht="15.75" customHeight="1">
@@ -55002,7 +55002,7 @@
       <c r="L1197" s="13"/>
       <c r="M1197" s="13"/>
       <c r="N1197" s="15">
-        <v>46861.756299999994</v>
+        <v>46861.756300000001</v>
       </c>
     </row>
     <row r="1198" spans="1:14" ht="15.75" customHeight="1">
@@ -55057,7 +55057,7 @@
         <v>4811.1216968574927</v>
       </c>
       <c r="E1199" s="14">
-        <v>4410.8853143259794</v>
+        <v>4410.8853143259776</v>
       </c>
       <c r="F1199" s="13">
         <v>923.27440000000001</v>
@@ -55078,7 +55078,7 @@
       <c r="L1199" s="13"/>
       <c r="M1199" s="13"/>
       <c r="N1199" s="15">
-        <v>45059.347400000006</v>
+        <v>45059.347399999999</v>
       </c>
     </row>
     <row r="1200" spans="1:14" ht="15.75" customHeight="1">
@@ -55095,7 +55095,7 @@
         <v>4513.7009686452229</v>
       </c>
       <c r="E1200" s="14">
-        <v>4435.3725877679126</v>
+        <v>4435.3725877679108</v>
       </c>
       <c r="F1200" s="13">
         <v>1429.8607</v>
@@ -55107,7 +55107,7 @@
         <v>5125.1875535419204</v>
       </c>
       <c r="I1200" s="14">
-        <v>4119.7835060629886</v>
+        <v>4119.7835060629877</v>
       </c>
       <c r="J1200" s="13">
         <v>5175.8775999999998</v>
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551803</v>
+        <v>4487.7143253551776</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55154,7 +55154,7 @@
       <c r="L1201" s="13"/>
       <c r="M1201" s="13"/>
       <c r="N1201" s="15">
-        <v>64229.893499999998</v>
+        <v>64229.893500000006</v>
       </c>
     </row>
     <row r="1202" spans="1:14" ht="15.75" customHeight="1">
@@ -55183,7 +55183,7 @@
         <v>5782.081258662286</v>
       </c>
       <c r="I1202" s="14">
-        <v>5126.6494289859602</v>
+        <v>5126.6494289859611</v>
       </c>
       <c r="J1202" s="13">
         <v>5202.1442999999999</v>
@@ -55230,7 +55230,7 @@
       <c r="L1203" s="13"/>
       <c r="M1203" s="13"/>
       <c r="N1203" s="15">
-        <v>79222.162899999981</v>
+        <v>79222.162899999996</v>
       </c>
     </row>
     <row r="1204" spans="1:14" ht="15.75" customHeight="1">
@@ -55268,7 +55268,7 @@
       <c r="L1204" s="13"/>
       <c r="M1204" s="13"/>
       <c r="N1204" s="15">
-        <v>86729.972700000013</v>
+        <v>86729.972699999998</v>
       </c>
     </row>
     <row r="1205" spans="1:14" ht="15.75" customHeight="1">
@@ -55323,7 +55323,7 @@
         <v>4670.2295803614725</v>
       </c>
       <c r="E1206" s="14">
-        <v>4619.2706025443222</v>
+        <v>4619.2706025443231</v>
       </c>
       <c r="F1206" s="13">
         <v>912.13160000000005</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629638</v>
+        <v>4315.8033455629657</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55399,7 +55399,7 @@
         <v>4713.6567672624096</v>
       </c>
       <c r="E1208" s="14">
-        <v>4405.2333301780845</v>
+        <v>4405.2333301780855</v>
       </c>
       <c r="F1208" s="13">
         <v>738.81479999999999</v>
@@ -55420,7 +55420,7 @@
       <c r="L1208" s="13"/>
       <c r="M1208" s="13"/>
       <c r="N1208" s="15">
-        <v>49051.207199999997</v>
+        <v>49051.207200000004</v>
       </c>
     </row>
     <row r="1209" spans="1:14" ht="15.75" customHeight="1">
@@ -55437,7 +55437,7 @@
         <v>4861.8722945889349</v>
       </c>
       <c r="E1209" s="14">
-        <v>4603.9520191017509</v>
+        <v>4603.9520191017518</v>
       </c>
       <c r="F1209" s="13">
         <v>2751.9634000000001</v>
@@ -55449,7 +55449,7 @@
         <v>5232.7977567123598</v>
       </c>
       <c r="I1209" s="14">
-        <v>4726.9079889175364</v>
+        <v>4726.9079889175373</v>
       </c>
       <c r="J1209" s="13">
         <v>6374.9992000000002</v>
@@ -55475,7 +55475,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="14">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="13">
         <v>1813.4111</v>
@@ -55572,7 +55572,7 @@
       <c r="L1212" s="13"/>
       <c r="M1212" s="13"/>
       <c r="N1212" s="15">
-        <v>45765.935099999995</v>
+        <v>45765.935100000002</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55648,7 +55648,7 @@
       <c r="L1214" s="13"/>
       <c r="M1214" s="13"/>
       <c r="N1214" s="15">
-        <v>76702.561400000006</v>
+        <v>76702.561399999991</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55715,7 +55715,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="14">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="13">
         <v>3920.1588999999999</v>
@@ -55741,7 +55741,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.1866360758067</v>
+        <v>4706.1866360758077</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.4088847985449</v>
+        <v>4736.4088847985458</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55817,7 +55817,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="14">
-        <v>4756.246929365534</v>
+        <v>4756.2469293655349</v>
       </c>
       <c r="F1219" s="13">
         <v>1866.9058</v>
@@ -55838,7 +55838,7 @@
       <c r="L1219" s="13"/>
       <c r="M1219" s="13"/>
       <c r="N1219" s="15">
-        <v>62677.385600000001</v>
+        <v>62677.385599999994</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55855,7 +55855,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.2967738120524</v>
+        <v>4663.2967738120533</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55893,7 +55893,7 @@
         <v>4701.8076037281035</v>
       </c>
       <c r="E1221" s="14">
-        <v>4670.5246781428059</v>
+        <v>4670.5246781428068</v>
       </c>
       <c r="F1221" s="13">
         <v>673.16070000000002</v>
@@ -55922,16 +55922,16 @@
         <v>45752</v>
       </c>
       <c r="B1222" s="13">
-        <v>48558.061399999999</v>
+        <v>48545.9398</v>
       </c>
       <c r="C1222" s="13">
         <v>10009.820100000001</v>
       </c>
       <c r="D1222" s="13">
-        <v>4851.0423678843135</v>
+        <v>4849.8313970697627</v>
       </c>
       <c r="E1222" s="14">
-        <v>4695.9613964996215</v>
+        <v>4695.6837921024498</v>
       </c>
       <c r="F1222" s="13">
         <v>1081.6878999999999</v>
@@ -55952,7 +55952,7 @@
       <c r="L1222" s="13"/>
       <c r="M1222" s="13"/>
       <c r="N1222" s="15">
-        <v>52979.688899999994</v>
+        <v>52967.567300000002</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -55969,7 +55969,7 @@
         <v>4613.3343787360272</v>
       </c>
       <c r="E1223" s="14">
-        <v>4695.626162482773</v>
+        <v>4695.3577116658489</v>
       </c>
       <c r="F1223" s="13">
         <v>1661.2738999999999</v>
@@ -56007,7 +56007,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="14">
-        <v>4673.3021398798928</v>
+        <v>4673.0080443035031</v>
       </c>
       <c r="F1224" s="13">
         <v>678.69989999999996</v>
@@ -56045,7 +56045,7 @@
         <v>5250.790273907136</v>
       </c>
       <c r="E1225" s="14">
-        <v>4738.7314957118124</v>
+        <v>4738.4407031849632</v>
       </c>
       <c r="F1225" s="13">
         <v>723.6875</v>
@@ -56218,7 +56218,7 @@
       <c r="L1229" s="13"/>
       <c r="M1229" s="13"/>
       <c r="N1229" s="15">
-        <v>66469.655099999989</v>
+        <v>66469.655100000004</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56349,7 +56349,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="14">
-        <v>4836.3955854983906</v>
+        <v>4836.3955854983897</v>
       </c>
       <c r="F1233" s="13">
         <v>910.61059999999998</v>
@@ -56387,7 +56387,7 @@
         <v>4897.4427637682502</v>
       </c>
       <c r="E1234" s="14">
-        <v>4765.8359934631853</v>
+        <v>4765.8359934631844</v>
       </c>
       <c r="F1234" s="13">
         <v>556.48080000000004</v>
@@ -56425,7 +56425,7 @@
         <v>5125.621659266998</v>
       </c>
       <c r="E1235" s="14">
-        <v>4954.9135213242962</v>
+        <v>4954.9135213242953</v>
       </c>
       <c r="F1235" s="13">
         <v>1182.9712999999999</v>
@@ -56463,7 +56463,7 @@
         <v>4468.4654995475621</v>
       </c>
       <c r="E1236" s="14">
-        <v>4833.0211489485218</v>
+        <v>4833.0211489485209</v>
       </c>
       <c r="F1236" s="13">
         <v>509.77510000000001</v>
@@ -56501,7 +56501,7 @@
         <v>5279.8066063917322</v>
       </c>
       <c r="E1237" s="14">
-        <v>4926.7513336432476</v>
+        <v>4926.7513336432485</v>
       </c>
       <c r="F1237" s="13">
         <v>770.73030000000006</v>
@@ -56560,7 +56560,7 @@
       <c r="L1238" s="13"/>
       <c r="M1238" s="13"/>
       <c r="N1238" s="15">
-        <v>53730.357699999993</v>
+        <v>53730.3577</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56577,7 +56577,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="14">
-        <v>4983.8869191962513</v>
+        <v>4983.8869191962531</v>
       </c>
       <c r="F1239" s="13">
         <v>1951.8497</v>
@@ -56674,7 +56674,7 @@
       <c r="L1241" s="13"/>
       <c r="M1241" s="13"/>
       <c r="N1241" s="15">
-        <v>77476.646100000013</v>
+        <v>77476.646099999998</v>
       </c>
       <c r="O1241" s="16"/>
     </row>
@@ -56704,7 +56704,7 @@
         <v>6080.2534679336923</v>
       </c>
       <c r="I1242" s="14">
-        <v>6193.6671018830639</v>
+        <v>6193.667101883063</v>
       </c>
       <c r="J1242" s="13">
         <v>8322.0208999999995</v>
@@ -56742,7 +56742,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="14">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="13">
         <v>15660.4136</v>
@@ -56768,7 +56768,7 @@
         <v>4780.8999076950913</v>
       </c>
       <c r="E1244" s="14">
-        <v>5246.8473557608249</v>
+        <v>5246.8473557608258</v>
       </c>
       <c r="F1244" s="13">
         <v>1388.6704</v>
@@ -56780,7 +56780,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="14">
-        <v>6056.5070840084427</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="13">
         <v>8281.8516999999993</v>
@@ -56789,7 +56789,7 @@
       <c r="L1244" s="13"/>
       <c r="M1244" s="13"/>
       <c r="N1244" s="15">
-        <v>57659.296399999999</v>
+        <v>57659.296399999992</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1">
@@ -56806,7 +56806,7 @@
         <v>5199.4152501760509</v>
       </c>
       <c r="E1245" s="14">
-        <v>5064.6354378721499</v>
+        <v>5064.6354378721508</v>
       </c>
       <c r="F1245" s="13">
         <v>1184.0114000000001</v>
@@ -56818,7 +56818,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="14">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="13">
         <v>4208.4350999999997</v>
@@ -56827,7 +56827,7 @@
       <c r="L1245" s="13"/>
       <c r="M1245" s="13"/>
       <c r="N1245" s="15">
-        <v>48637.901200000008</v>
+        <v>48637.9012</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56859,13 +56859,13 @@
         <v>5567.868517566978</v>
       </c>
       <c r="J1246" s="13">
-        <v>6522.4556000000002</v>
+        <v>6522.3077000000003</v>
       </c>
       <c r="K1246" s="13"/>
       <c r="L1246" s="13"/>
       <c r="M1246" s="13"/>
       <c r="N1246" s="15">
-        <v>70149.0098</v>
+        <v>70148.861900000004</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56873,16 +56873,16 @@
         <v>45927</v>
       </c>
       <c r="B1247" s="13">
-        <v>45051.898699999998</v>
+        <v>45051.898200000003</v>
       </c>
       <c r="C1247" s="13">
         <v>8526.9426000000003</v>
       </c>
       <c r="D1247" s="13">
-        <v>5283.4762485676865</v>
+        <v>5283.4761899300229</v>
       </c>
       <c r="E1247" s="14">
-        <v>5104.5165832550883</v>
+        <v>5104.516571973395</v>
       </c>
       <c r="F1247" s="13">
         <v>1625.8276000000001</v>
@@ -56894,7 +56894,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="14">
-        <v>5394.2932473875308</v>
+        <v>5394.2932473875317</v>
       </c>
       <c r="J1247" s="13">
         <v>13767.5789</v>
@@ -56903,7 +56903,7 @@
       <c r="L1247" s="13"/>
       <c r="M1247" s="13"/>
       <c r="N1247" s="15">
-        <v>60445.305199999995</v>
+        <v>60445.304700000008</v>
       </c>
     </row>
     <row r="1248" spans="1:15" ht="15.75" customHeight="1">
@@ -56920,7 +56920,7 @@
         <v>4670.5304205766788</v>
       </c>
       <c r="E1248" s="14">
-        <v>5065.815385874409</v>
+        <v>5065.8153730393024</v>
       </c>
       <c r="F1248" s="13">
         <v>1018.4743</v>
@@ -56958,7 +56958,7 @@
         <v>4382.871978904207</v>
       </c>
       <c r="E1249" s="14">
-        <v>4973.8312362123061</v>
+        <v>4973.8312228225723</v>
       </c>
       <c r="F1249" s="13">
         <v>1116.6591000000001</v>
@@ -56996,7 +56996,7 @@
         <v>4931.626416698783</v>
       </c>
       <c r="E1250" s="14">
-        <v>4941.3526982391786</v>
+        <v>4941.3526846502846</v>
       </c>
       <c r="F1250" s="13">
         <v>1339.0517</v>
@@ -57011,13 +57011,13 @@
         <v>5726.2108069747692</v>
       </c>
       <c r="J1250" s="13">
-        <v>12238.814899999999</v>
+        <v>12437.3822</v>
       </c>
       <c r="K1250" s="13"/>
       <c r="L1250" s="13"/>
       <c r="M1250" s="13"/>
       <c r="N1250" s="15">
-        <v>61821.525200000004</v>
+        <v>62020.092499999999</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1">
@@ -57034,7 +57034,7 @@
         <v>5741.1686828543779</v>
       </c>
       <c r="E1251" s="14">
-        <v>5019.6709328400975</v>
+        <v>5019.6709189815274</v>
       </c>
       <c r="F1251" s="13">
         <v>1154.2166999999999</v>
@@ -57049,13 +57049,13 @@
         <v>5618.2028678006491</v>
       </c>
       <c r="J1251" s="13">
-        <v>5375.8909000000003</v>
+        <v>5419.7007999999996</v>
       </c>
       <c r="K1251" s="13"/>
       <c r="L1251" s="13"/>
       <c r="M1251" s="13"/>
       <c r="N1251" s="15">
-        <v>61040.029799999997</v>
+        <v>61083.839699999997</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57084,16 +57084,16 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="14">
-        <v>5768.2127381128494</v>
+        <v>5768.2127381128485</v>
       </c>
       <c r="J1252" s="13">
-        <v>10675.3544</v>
+        <v>10772.394200000001</v>
       </c>
       <c r="K1252" s="13"/>
       <c r="L1252" s="13"/>
       <c r="M1252" s="13"/>
       <c r="N1252" s="15">
-        <v>60705.863899999997</v>
+        <v>60802.903700000003</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1">
@@ -57125,13 +57125,13 @@
         <v>5539.4813027075452</v>
       </c>
       <c r="J1253" s="13">
-        <v>12265.096</v>
+        <v>12356.630499999999</v>
       </c>
       <c r="K1253" s="13"/>
       <c r="L1253" s="13"/>
       <c r="M1253" s="13"/>
       <c r="N1253" s="15">
-        <v>103366.38900000001</v>
+        <v>103457.9235</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1">
@@ -57148,7 +57148,7 @@
         <v>5052.6004887524759</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.4507220623818</v>
+        <v>5308.4507220623827</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57160,16 +57160,16 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="14">
-        <v>5620.2491328335436</v>
+        <v>5620.2491328335427</v>
       </c>
       <c r="J1254" s="13">
-        <v>10574.364</v>
+        <v>10669.626700000001</v>
       </c>
       <c r="K1254" s="13"/>
       <c r="L1254" s="13"/>
       <c r="M1254" s="13"/>
       <c r="N1254" s="15">
-        <v>57830.456200000001</v>
+        <v>57925.7189</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1">
@@ -57177,16 +57177,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="13">
-        <v>84435.654299999995</v>
+        <v>84435.340800000005</v>
       </c>
       <c r="C1255" s="13">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="13">
-        <v>6212.2267151842707</v>
+        <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="14">
-        <v>5579.586740496231</v>
+        <v>5579.5810425777527</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57198,7 +57198,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="14">
-        <v>5979.7288428128713</v>
+        <v>5979.7288428128722</v>
       </c>
       <c r="J1255" s="13">
         <v>12450.415499999999</v>
@@ -57207,7 +57207,7 @@
       <c r="L1255" s="13"/>
       <c r="M1255" s="13"/>
       <c r="N1255" s="15">
-        <v>99631.932000000001</v>
+        <v>99631.618500000011</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1">
@@ -57224,7 +57224,7 @@
         <v>5187.2276632970024</v>
       </c>
       <c r="E1256" s="14">
-        <v>5469.6023610173679</v>
+        <v>5469.5970084916407</v>
       </c>
       <c r="F1256" s="13">
         <v>3141.94</v>
@@ -57262,7 +57262,7 @@
         <v>5246.4612349567415</v>
       </c>
       <c r="E1257" s="14">
-        <v>5421.5588213720839</v>
+        <v>5421.5530126565773</v>
       </c>
       <c r="F1257" s="13">
         <v>2948.9110000000001</v>
@@ -57274,7 +57274,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="14">
-        <v>6858.778759653972</v>
+        <v>6858.7787596539711</v>
       </c>
       <c r="J1257" s="13">
         <v>6940.3462</v>
@@ -57291,16 +57291,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="13">
-        <v>60365.373800000001</v>
+        <v>60364.837500000001</v>
       </c>
       <c r="C1258" s="13">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="13">
-        <v>4975.0068379650684</v>
+        <v>4974.9626388489314</v>
       </c>
       <c r="E1258" s="14">
-        <v>5452.1776416899693</v>
+        <v>5452.1617185708183</v>
       </c>
       <c r="F1258" s="13">
         <v>4360.9017999999996</v>
@@ -57312,7 +57312,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="14">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="13">
         <v>10585.9912</v>
@@ -57321,7 +57321,7 @@
       <c r="L1258" s="13"/>
       <c r="M1258" s="13"/>
       <c r="N1258" s="15">
-        <v>75312.266800000012</v>
+        <v>75311.730500000005</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57329,16 +57329,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="13">
-        <v>64229.681799999998</v>
+        <v>64229.735000000001</v>
       </c>
       <c r="C1259" s="13">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="13">
-        <v>5454.4968932015172</v>
+        <v>5454.5014110385446</v>
       </c>
       <c r="E1259" s="14">
-        <v>5182.2577556391407</v>
+        <v>5182.2485495717983</v>
       </c>
       <c r="F1259" s="13">
         <v>3014.4270000000001</v>
@@ -57353,13 +57353,13 @@
         <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="13">
-        <v>14233.113499999999</v>
+        <v>14233.2034</v>
       </c>
       <c r="K1259" s="13"/>
       <c r="L1259" s="13"/>
       <c r="M1259" s="13"/>
       <c r="N1259" s="15">
-        <v>81477.222299999994</v>
+        <v>81477.36540000001</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57376,7 +57376,7 @@
         <v>5186.5637130683717</v>
       </c>
       <c r="E1260" s="14">
-        <v>5209.2647907076453</v>
+        <v>5209.2553779897735</v>
       </c>
       <c r="F1260" s="13">
         <v>2192.3276999999998</v>
@@ -57391,13 +57391,13 @@
         <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="13">
-        <v>7543.8801999999996</v>
+        <v>7543.9057000000003</v>
       </c>
       <c r="K1260" s="13"/>
       <c r="L1260" s="13"/>
       <c r="M1260" s="13"/>
       <c r="N1260" s="15">
-        <v>70434.128399999987</v>
+        <v>70434.153900000005</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57414,7 +57414,7 @@
         <v>5326.105219423489</v>
       </c>
       <c r="E1261" s="14">
-        <v>5254.9295941363744</v>
+        <v>5254.919105561994</v>
       </c>
       <c r="F1261" s="13">
         <v>1259.8376000000001</v>
@@ -57443,16 +57443,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="13">
-        <v>31640.7945</v>
+        <v>31640.869600000002</v>
       </c>
       <c r="C1262" s="13">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="13">
-        <v>5567.2482330193116</v>
+        <v>5567.2614469840346</v>
       </c>
       <c r="E1262" s="14">
-        <v>5255.4478965026337</v>
+        <v>5255.4509676683947</v>
       </c>
       <c r="F1262" s="13">
         <v>1210.1021000000001</v>
@@ -57467,13 +57467,13 @@
         <v>6331.7504578958606</v>
       </c>
       <c r="J1262" s="13">
-        <v>7771.0213999999996</v>
+        <v>7777.6869999999999</v>
       </c>
       <c r="K1262" s="13"/>
       <c r="L1262" s="13"/>
       <c r="M1262" s="13"/>
       <c r="N1262" s="15">
-        <v>40621.918000000005</v>
+        <v>40628.6587</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57490,7 +57490,7 @@
         <v>5220.845437147972</v>
       </c>
       <c r="E1263" s="14">
-        <v>5334.9792420899066</v>
+        <v>5334.981060103104</v>
       </c>
       <c r="F1263" s="13">
         <v>3212.6219999999998</v>
@@ -57528,7 +57528,7 @@
         <v>5650.6592147478159</v>
       </c>
       <c r="E1264" s="14">
-        <v>5402.3329055322138</v>
+        <v>5402.3350633770524</v>
       </c>
       <c r="F1264" s="13">
         <v>1803.3380999999999</v>
@@ -57566,7 +57566,7 @@
         <v>5217.4413755030191</v>
       </c>
       <c r="E1265" s="23">
-        <v>5318.2563103010307</v>
+        <v>5318.2581798828433</v>
       </c>
       <c r="F1265" s="22">
         <v>2790.8292999999999</v>
@@ -57584,7 +57584,7 @@
         <v>8304.0838000000003</v>
       </c>
       <c r="N1265" s="21">
-        <v>77849.855999999985</v>
+        <v>77849.856</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57592,16 +57592,16 @@
         <v>46060</v>
       </c>
       <c r="B1266" s="22">
-        <v>43073.549800000001</v>
+        <v>43291.907800000001</v>
       </c>
       <c r="C1266" s="22">
-        <v>8085.4219000000003</v>
+        <v>8158.2079000000003</v>
       </c>
       <c r="D1266" s="22">
-        <v>5327.3101061059033</v>
+        <v>5306.5462820578532</v>
       </c>
       <c r="E1266" s="23">
-        <v>5312.6316505918403</v>
+        <v>5308.5912661795492</v>
       </c>
       <c r="F1266" s="22">
         <v>1799.4023999999999</v>
@@ -57619,7 +57619,7 @@
         <v>10003.6175</v>
       </c>
       <c r="N1266" s="21">
-        <v>54876.5697</v>
+        <v>55094.9277</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15.75" customHeight="1">
@@ -57636,7 +57636,7 @@
         <v>5701.5032686623526</v>
       </c>
       <c r="E1267" s="23">
-        <v>5376.8010968356893</v>
+        <v>5373.2003865429378</v>
       </c>
       <c r="F1267" s="22">
         <v>1828.6121000000001</v>
@@ -57662,34 +57662,34 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="22">
-        <v>60612.054700000001</v>
+        <v>65268.852099999996</v>
       </c>
       <c r="C1268" s="22">
-        <v>11838.8037</v>
+        <v>12718.373299999999</v>
       </c>
       <c r="D1268" s="22">
-        <v>5119.778673245507</v>
+        <v>5131.8553529168703</v>
       </c>
       <c r="E1268" s="23">
-        <v>5321.6485791411851</v>
+        <v>5317.8432010292154</v>
       </c>
       <c r="F1268" s="22">
-        <v>1208.7674</v>
+        <v>1326.8929000000001</v>
       </c>
       <c r="G1268" s="22">
-        <v>161.80260000000001</v>
+        <v>186.91679999999999</v>
       </c>
       <c r="H1268" s="22">
-        <v>7470.6302618128502</v>
+        <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="23">
-        <v>6585.4300491728982</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="22">
-        <v>14206.0404</v>
+        <v>14843.3467</v>
       </c>
       <c r="N1268" s="21">
-        <v>76026.862500000003</v>
+        <v>81439.09169999999</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57697,34 +57697,34 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="22">
-        <v>49556.427900000002</v>
+        <v>53112.1636</v>
       </c>
       <c r="C1269" s="22">
-        <v>9334.2222000000002</v>
+        <v>10128.4987</v>
       </c>
       <c r="D1269" s="22">
-        <v>5309.1116579590325</v>
+        <v>5243.8337776555181</v>
       </c>
       <c r="E1269" s="23">
-        <v>5308.0386383939795</v>
+        <v>5291.1674452553234</v>
       </c>
       <c r="F1269" s="22">
-        <v>946.99189999999999</v>
+        <v>1217.7628999999999</v>
       </c>
       <c r="G1269" s="22">
-        <v>114.73480000000001</v>
+        <v>157.60050000000001</v>
       </c>
       <c r="H1269" s="22">
-        <v>8253.7460299752129</v>
+        <v>7726.8974400461921</v>
       </c>
       <c r="I1269" s="23">
-        <v>6564.4404635417095</v>
+        <v>6516.9746980314958</v>
       </c>
       <c r="J1269" s="22">
-        <v>6945.6157999999996</v>
+        <v>7866.1765999999998</v>
       </c>
       <c r="N1269" s="21">
-        <v>57449.035600000003</v>
+        <v>62196.1031</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57732,34 +57732,69 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="22">
-        <v>38324.2111</v>
+        <v>49790.911999999997</v>
       </c>
       <c r="C1270" s="22">
-        <v>5648.9180999999999</v>
+        <v>8058.9301999999998</v>
       </c>
       <c r="D1270" s="22">
-        <v>6784.3453244613338</v>
+        <v>6178.3525560253647</v>
       </c>
       <c r="E1270" s="23">
-        <v>5487.1952519306305</v>
+        <v>5431.3331732455999</v>
       </c>
       <c r="F1270" s="22">
-        <v>1107.3652</v>
+        <v>1105.9253000000001</v>
       </c>
       <c r="G1270" s="22">
         <v>131.98410000000001</v>
       </c>
       <c r="H1270" s="22">
-        <v>8390.1409336427641</v>
+        <v>8379.2312861928058</v>
       </c>
       <c r="I1270" s="23">
-        <v>7447.7692675197495</v>
+        <v>7308.7373154792704</v>
       </c>
       <c r="J1270" s="22">
-        <v>4901.7485999999999</v>
+        <v>5360.7565000000004</v>
       </c>
       <c r="N1270" s="21">
-        <v>44333.3249</v>
+        <v>56257.593799999995</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1271" s="20">
+        <v>46095</v>
+      </c>
+      <c r="B1271" s="22">
+        <v>32986.155100000004</v>
+      </c>
+      <c r="C1271" s="22">
+        <v>5532.4879000000001</v>
+      </c>
+      <c r="D1271" s="22">
+        <v>5962.2643006593844</v>
+      </c>
+      <c r="E1271" s="23">
+        <v>5488.7231627661113</v>
+      </c>
+      <c r="F1271" s="22">
+        <v>909.49450000000002</v>
+      </c>
+      <c r="G1271" s="22">
+        <v>143.4068</v>
+      </c>
+      <c r="H1271" s="22">
+        <v>6342.0597907491137</v>
+      </c>
+      <c r="I1271" s="23">
+        <v>7516.9287926091783</v>
+      </c>
+      <c r="J1271" s="22">
+        <v>4850.7052999999996</v>
+      </c>
+      <c r="N1271" s="21">
+        <v>38746.354900000006</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CC010A-E8FE-4D66-B7B4-ED8F496AC49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248D3FC3-B891-4FEB-8E0F-966B9261E34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1271"/>
+  <dimension ref="A1:W1272"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -915,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="35">
-        <v>46092</v>
+        <v>46106</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
@@ -53499,7 +53499,7 @@
         <v>4150.9922145963383</v>
       </c>
       <c r="E1158" s="14">
-        <v>3840.8705315088</v>
+        <v>3840.8705315087991</v>
       </c>
       <c r="F1158" s="13">
         <v>882.2903</v>
@@ -53549,7 +53549,7 @@
         <v>3982.0975670205294</v>
       </c>
       <c r="I1159" s="14">
-        <v>3617.6613635639046</v>
+        <v>3617.6613635639042</v>
       </c>
       <c r="J1159" s="13">
         <v>6212.6449000000002</v>
@@ -53727,7 +53727,7 @@
         <v>4274.3049517318423</v>
       </c>
       <c r="E1164" s="14">
-        <v>4101.720044836743</v>
+        <v>4101.7200448367421</v>
       </c>
       <c r="F1164" s="13">
         <v>902.06470000000002</v>
@@ -53739,7 +53739,7 @@
         <v>3294.3855571640811</v>
       </c>
       <c r="I1164" s="14">
-        <v>3579.4806019611101</v>
+        <v>3579.4806019611092</v>
       </c>
       <c r="J1164" s="13">
         <v>14285.5708</v>
@@ -53748,7 +53748,7 @@
       <c r="L1164" s="13"/>
       <c r="M1164" s="13"/>
       <c r="N1164" s="15">
-        <v>57458.467499999999</v>
+        <v>57458.467500000006</v>
       </c>
     </row>
     <row r="1165" spans="1:14" ht="15.75" customHeight="1">
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309888</v>
+        <v>4180.3219217309879</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53777,7 +53777,7 @@
         <v>3930.3634262421583</v>
       </c>
       <c r="I1165" s="14">
-        <v>3575.1060841405906</v>
+        <v>3575.1060841405902</v>
       </c>
       <c r="J1165" s="13">
         <v>4062.5365999999999</v>
@@ -53803,7 +53803,7 @@
         <v>4144.4221019502211</v>
       </c>
       <c r="E1166" s="14">
-        <v>4237.0040886928527</v>
+        <v>4237.0040886928537</v>
       </c>
       <c r="F1166" s="13">
         <v>1411.7936999999999</v>
@@ -53815,7 +53815,7 @@
         <v>3909.3141944625277</v>
       </c>
       <c r="I1166" s="14">
-        <v>3720.2808034203017</v>
+        <v>3720.2808034203026</v>
       </c>
       <c r="J1166" s="13">
         <v>3419.8951999999999</v>
@@ -53824,7 +53824,7 @@
       <c r="L1166" s="13"/>
       <c r="M1166" s="13"/>
       <c r="N1166" s="15">
-        <v>31626.6551</v>
+        <v>31626.655099999996</v>
       </c>
     </row>
     <row r="1167" spans="1:14" ht="15.75" customHeight="1">
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.855846056349</v>
+        <v>4171.8558460563499</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -53879,7 +53879,7 @@
         <v>3877.0306064631195</v>
       </c>
       <c r="E1168" s="14">
-        <v>4055.3634375452452</v>
+        <v>4055.3634375452461</v>
       </c>
       <c r="F1168" s="13">
         <v>2016.7924</v>
@@ -53917,7 +53917,7 @@
         <v>3932.8336637875082</v>
       </c>
       <c r="E1169" s="14">
-        <v>4049.5261191257582</v>
+        <v>4049.5261191257591</v>
       </c>
       <c r="F1169" s="13">
         <v>972.27260000000001</v>
@@ -53955,7 +53955,7 @@
         <v>4162.4812039586277</v>
       </c>
       <c r="E1170" s="14">
-        <v>3979.2022758044022</v>
+        <v>3979.2022758044027</v>
       </c>
       <c r="F1170" s="13">
         <v>1026.8530000000001</v>
@@ -53976,7 +53976,7 @@
       <c r="L1170" s="13"/>
       <c r="M1170" s="13"/>
       <c r="N1170" s="15">
-        <v>37348.1538</v>
+        <v>37348.153800000007</v>
       </c>
     </row>
     <row r="1171" spans="1:14" ht="15.75" customHeight="1">
@@ -54145,7 +54145,7 @@
         <v>4151.5723390857438</v>
       </c>
       <c r="E1175" s="14">
-        <v>3955.4372729635274</v>
+        <v>3955.4372729635284</v>
       </c>
       <c r="F1175" s="13">
         <v>1393.8427999999999</v>
@@ -54157,7 +54157,7 @@
         <v>3165.986834005897</v>
       </c>
       <c r="I1175" s="14">
-        <v>3345.9193035632734</v>
+        <v>3345.9193035632725</v>
       </c>
       <c r="J1175" s="13">
         <v>18463.542600000001</v>
@@ -54221,7 +54221,7 @@
         <v>4611.2745069454377</v>
       </c>
       <c r="E1177" s="14">
-        <v>4199.3537107264319</v>
+        <v>4199.3537107264328</v>
       </c>
       <c r="F1177" s="13">
         <v>850.38009999999997</v>
@@ -54242,7 +54242,7 @@
       <c r="L1177" s="13"/>
       <c r="M1177" s="13"/>
       <c r="N1177" s="15">
-        <v>62161.926699999996</v>
+        <v>62161.926700000004</v>
       </c>
     </row>
     <row r="1178" spans="1:14" ht="15.75" customHeight="1">
@@ -54335,7 +54335,7 @@
         <v>4008.5523747206912</v>
       </c>
       <c r="E1180" s="14">
-        <v>4173.750113280712</v>
+        <v>4173.750113280711</v>
       </c>
       <c r="F1180" s="13">
         <v>909.47910000000002</v>
@@ -54347,7 +54347,7 @@
         <v>3932.0511251890948</v>
       </c>
       <c r="I1180" s="14">
-        <v>3820.0779903432676</v>
+        <v>3820.0779903432685</v>
       </c>
       <c r="J1180" s="13">
         <v>7100.3598000000002</v>
@@ -54356,7 +54356,7 @@
       <c r="L1180" s="13"/>
       <c r="M1180" s="13"/>
       <c r="N1180" s="15">
-        <v>56623.827600000004</v>
+        <v>56623.827599999997</v>
       </c>
     </row>
     <row r="1181" spans="1:14" ht="15.75" customHeight="1">
@@ -54394,7 +54394,7 @@
       <c r="L1181" s="13"/>
       <c r="M1181" s="13"/>
       <c r="N1181" s="15">
-        <v>52642.395299999996</v>
+        <v>52642.395300000004</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15.75" customHeight="1">
@@ -54411,7 +54411,7 @@
         <v>4033.0100843855616</v>
       </c>
       <c r="E1182" s="14">
-        <v>4020.0169955492411</v>
+        <v>4020.0169955492406</v>
       </c>
       <c r="F1182" s="13">
         <v>427.52350000000001</v>
@@ -54449,7 +54449,7 @@
         <v>3939.2689570133098</v>
       </c>
       <c r="E1183" s="14">
-        <v>4029.5735323808312</v>
+        <v>4029.5735323808303</v>
       </c>
       <c r="F1183" s="13">
         <v>440.14429999999999</v>
@@ -54461,7 +54461,7 @@
         <v>5020.0771469761667</v>
       </c>
       <c r="I1183" s="14">
-        <v>3892.3953212090473</v>
+        <v>3892.3953212090469</v>
       </c>
       <c r="J1183" s="13">
         <v>5037.4709000000003</v>
@@ -54546,7 +54546,7 @@
       <c r="L1185" s="13"/>
       <c r="M1185" s="13"/>
       <c r="N1185" s="15">
-        <v>37483.069499999998</v>
+        <v>37483.069499999991</v>
       </c>
     </row>
     <row r="1186" spans="1:14" ht="15.75" customHeight="1">
@@ -54563,7 +54563,7 @@
         <v>3921.1801257461875</v>
       </c>
       <c r="E1186" s="14">
-        <v>4103.7917850861213</v>
+        <v>4103.7917850861204</v>
       </c>
       <c r="F1186" s="13">
         <v>1199.8832</v>
@@ -54575,7 +54575,7 @@
         <v>4393.5575388702919</v>
       </c>
       <c r="I1186" s="14">
-        <v>4445.0065612912522</v>
+        <v>4445.0065612912513</v>
       </c>
       <c r="J1186" s="13">
         <v>7294.8577999999998</v>
@@ -54584,7 +54584,7 @@
       <c r="L1186" s="13"/>
       <c r="M1186" s="13"/>
       <c r="N1186" s="15">
-        <v>44453.567300000002</v>
+        <v>44453.567299999995</v>
       </c>
     </row>
     <row r="1187" spans="1:14" ht="15.75" customHeight="1">
@@ -54601,7 +54601,7 @@
         <v>4366.3367641502828</v>
       </c>
       <c r="E1187" s="14">
-        <v>4240.9406009288687</v>
+        <v>4240.9406009288678</v>
       </c>
       <c r="F1187" s="13">
         <v>748.68579999999997</v>
@@ -54613,7 +54613,7 @@
         <v>4806.1907118779418</v>
       </c>
       <c r="I1187" s="14">
-        <v>4604.0956192242566</v>
+        <v>4604.0956192242547</v>
       </c>
       <c r="J1187" s="13">
         <v>21194.6531</v>
@@ -54654,13 +54654,13 @@
         <v>4117.0960126626724</v>
       </c>
       <c r="J1188" s="13">
-        <v>12451.4519</v>
+        <v>12450.511399999999</v>
       </c>
       <c r="K1188" s="13"/>
       <c r="L1188" s="13"/>
       <c r="M1188" s="13"/>
       <c r="N1188" s="15">
-        <v>49252.318800000001</v>
+        <v>49251.378299999997</v>
       </c>
     </row>
     <row r="1189" spans="1:14" ht="15.75" customHeight="1">
@@ -54727,7 +54727,7 @@
         <v>4531.757943331254</v>
       </c>
       <c r="I1190" s="14">
-        <v>4095.6956962553541</v>
+        <v>4095.695696255355</v>
       </c>
       <c r="J1190" s="13">
         <v>5596.1341000000002</v>
@@ -54736,7 +54736,7 @@
       <c r="L1190" s="13"/>
       <c r="M1190" s="13"/>
       <c r="N1190" s="15">
-        <v>59168.145499999999</v>
+        <v>59168.145500000006</v>
       </c>
     </row>
     <row r="1191" spans="1:14" ht="15.75" customHeight="1">
@@ -54765,7 +54765,7 @@
         <v>3350.0403096116738</v>
       </c>
       <c r="I1191" s="14">
-        <v>3875.9174025958678</v>
+        <v>3875.9174025958691</v>
       </c>
       <c r="J1191" s="13">
         <v>17500.0933</v>
@@ -54774,7 +54774,7 @@
       <c r="L1191" s="13"/>
       <c r="M1191" s="13"/>
       <c r="N1191" s="15">
-        <v>59039.229300000006</v>
+        <v>59039.229299999999</v>
       </c>
     </row>
     <row r="1192" spans="1:14" ht="15.75" customHeight="1">
@@ -54964,7 +54964,7 @@
       <c r="L1196" s="13"/>
       <c r="M1196" s="13"/>
       <c r="N1196" s="15">
-        <v>59285.6731</v>
+        <v>59285.673100000007</v>
       </c>
     </row>
     <row r="1197" spans="1:14" ht="15.75" customHeight="1">
@@ -55002,7 +55002,7 @@
       <c r="L1197" s="13"/>
       <c r="M1197" s="13"/>
       <c r="N1197" s="15">
-        <v>46861.756300000001</v>
+        <v>46861.756299999994</v>
       </c>
     </row>
     <row r="1198" spans="1:14" ht="15.75" customHeight="1">
@@ -55078,7 +55078,7 @@
       <c r="L1199" s="13"/>
       <c r="M1199" s="13"/>
       <c r="N1199" s="15">
-        <v>45059.347399999999</v>
+        <v>45059.347400000006</v>
       </c>
     </row>
     <row r="1200" spans="1:14" ht="15.75" customHeight="1">
@@ -55095,7 +55095,7 @@
         <v>4513.7009686452229</v>
       </c>
       <c r="E1200" s="14">
-        <v>4435.3725877679108</v>
+        <v>4435.3725877679126</v>
       </c>
       <c r="F1200" s="13">
         <v>1429.8607</v>
@@ -55107,7 +55107,7 @@
         <v>5125.1875535419204</v>
       </c>
       <c r="I1200" s="14">
-        <v>4119.7835060629877</v>
+        <v>4119.7835060629886</v>
       </c>
       <c r="J1200" s="13">
         <v>5175.8775999999998</v>
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551776</v>
+        <v>4487.7143253551785</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55154,7 +55154,7 @@
       <c r="L1201" s="13"/>
       <c r="M1201" s="13"/>
       <c r="N1201" s="15">
-        <v>64229.893500000006</v>
+        <v>64229.893499999998</v>
       </c>
     </row>
     <row r="1202" spans="1:14" ht="15.75" customHeight="1">
@@ -55183,7 +55183,7 @@
         <v>5782.081258662286</v>
       </c>
       <c r="I1202" s="14">
-        <v>5126.6494289859611</v>
+        <v>5126.6494289859602</v>
       </c>
       <c r="J1202" s="13">
         <v>5202.1442999999999</v>
@@ -55209,7 +55209,7 @@
         <v>4938.8935854309739</v>
       </c>
       <c r="E1203" s="14">
-        <v>4717.3485788226399</v>
+        <v>4717.3485788226408</v>
       </c>
       <c r="F1203" s="13">
         <v>1626.8607999999999</v>
@@ -55230,7 +55230,7 @@
       <c r="L1203" s="13"/>
       <c r="M1203" s="13"/>
       <c r="N1203" s="15">
-        <v>79222.162899999996</v>
+        <v>79222.162899999981</v>
       </c>
     </row>
     <row r="1204" spans="1:14" ht="15.75" customHeight="1">
@@ -55247,7 +55247,7 @@
         <v>4266.1272976812243</v>
       </c>
       <c r="E1204" s="14">
-        <v>4525.0475976807111</v>
+        <v>4525.047597680712</v>
       </c>
       <c r="F1204" s="13">
         <v>1885.9646</v>
@@ -55268,7 +55268,7 @@
       <c r="L1204" s="13"/>
       <c r="M1204" s="13"/>
       <c r="N1204" s="15">
-        <v>86729.972699999998</v>
+        <v>86729.972700000013</v>
       </c>
     </row>
     <row r="1205" spans="1:14" ht="15.75" customHeight="1">
@@ -55285,7 +55285,7 @@
         <v>4424.3978008967133</v>
       </c>
       <c r="E1205" s="14">
-        <v>4552.8231579350831</v>
+        <v>4552.8231579350822</v>
       </c>
       <c r="F1205" s="13">
         <v>1070.8937000000001</v>
@@ -55361,7 +55361,7 @@
         <v>4252.7279635792374</v>
       </c>
       <c r="E1207" s="14">
-        <v>4389.4044684956052</v>
+        <v>4389.4044684956043</v>
       </c>
       <c r="F1207" s="13">
         <v>1109.1464000000001</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629657</v>
+        <v>4315.8033455629666</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55411,7 +55411,7 @@
         <v>4947.3851972485918</v>
       </c>
       <c r="I1208" s="14">
-        <v>4350.8974691131998</v>
+        <v>4350.8974691132007</v>
       </c>
       <c r="J1208" s="13">
         <v>9287.4572000000007</v>
@@ -55420,7 +55420,7 @@
       <c r="L1208" s="13"/>
       <c r="M1208" s="13"/>
       <c r="N1208" s="15">
-        <v>49051.207200000004</v>
+        <v>49051.207199999997</v>
       </c>
     </row>
     <row r="1209" spans="1:14" ht="15.75" customHeight="1">
@@ -55449,7 +55449,7 @@
         <v>5232.7977567123598</v>
       </c>
       <c r="I1209" s="14">
-        <v>4726.9079889175373</v>
+        <v>4726.9079889175364</v>
       </c>
       <c r="J1209" s="13">
         <v>6374.9992000000002</v>
@@ -55475,7 +55475,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="14">
-        <v>4508.5895396139713</v>
+        <v>4508.5895396139722</v>
       </c>
       <c r="F1210" s="13">
         <v>1813.4111</v>
@@ -55487,7 +55487,7 @@
         <v>6882.5719118850975</v>
       </c>
       <c r="I1210" s="14">
-        <v>5131.0721532756534</v>
+        <v>5131.0721532756543</v>
       </c>
       <c r="J1210" s="13">
         <v>5833.4898999999996</v>
@@ -55525,7 +55525,7 @@
         <v>6099.4532507976128</v>
       </c>
       <c r="I1211" s="14">
-        <v>5615.5313175907377</v>
+        <v>5615.5313175907386</v>
       </c>
       <c r="J1211" s="13">
         <v>4923.6122999999998</v>
@@ -55572,7 +55572,7 @@
       <c r="L1212" s="13"/>
       <c r="M1212" s="13"/>
       <c r="N1212" s="15">
-        <v>45765.935100000002</v>
+        <v>45765.935099999995</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55639,7 +55639,7 @@
         <v>5483.9420094229508</v>
       </c>
       <c r="I1214" s="14">
-        <v>5618.8491234155317</v>
+        <v>5618.8491234155326</v>
       </c>
       <c r="J1214" s="13">
         <v>8807.2849999999999</v>
@@ -55648,7 +55648,7 @@
       <c r="L1214" s="13"/>
       <c r="M1214" s="13"/>
       <c r="N1214" s="15">
-        <v>76702.561399999991</v>
+        <v>76702.561400000006</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55715,7 +55715,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="14">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="13">
         <v>3920.1588999999999</v>
@@ -55741,7 +55741,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.1866360758077</v>
+        <v>4706.1866360758067</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.4088847985458</v>
+        <v>4736.4088847985449</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55817,7 +55817,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="14">
-        <v>4756.2469293655349</v>
+        <v>4756.246929365534</v>
       </c>
       <c r="F1219" s="13">
         <v>1866.9058</v>
@@ -55838,7 +55838,7 @@
       <c r="L1219" s="13"/>
       <c r="M1219" s="13"/>
       <c r="N1219" s="15">
-        <v>62677.385599999994</v>
+        <v>62677.385600000001</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55855,7 +55855,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.2967738120533</v>
+        <v>4663.2967738120524</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55952,7 +55952,7 @@
       <c r="L1222" s="13"/>
       <c r="M1222" s="13"/>
       <c r="N1222" s="15">
-        <v>52967.567300000002</v>
+        <v>52967.567299999995</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56007,7 +56007,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="14">
-        <v>4673.0080443035031</v>
+        <v>4673.008044303504</v>
       </c>
       <c r="F1224" s="13">
         <v>678.69989999999996</v>
@@ -56218,7 +56218,7 @@
       <c r="L1229" s="13"/>
       <c r="M1229" s="13"/>
       <c r="N1229" s="15">
-        <v>66469.655100000004</v>
+        <v>66469.655099999989</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56437,7 +56437,7 @@
         <v>5270.8131997196551</v>
       </c>
       <c r="I1235" s="14">
-        <v>6279.4686229430436</v>
+        <v>6279.4686229430445</v>
       </c>
       <c r="J1235" s="13">
         <v>12601.2554</v>
@@ -56501,7 +56501,7 @@
         <v>5279.8066063917322</v>
       </c>
       <c r="E1237" s="14">
-        <v>4926.7513336432485</v>
+        <v>4926.7513336432476</v>
       </c>
       <c r="F1237" s="13">
         <v>770.73030000000006</v>
@@ -56539,7 +56539,7 @@
         <v>5523.8887674123871</v>
       </c>
       <c r="E1238" s="14">
-        <v>5021.4125766800344</v>
+        <v>5021.4125766800362</v>
       </c>
       <c r="F1238" s="13">
         <v>937.15679999999998</v>
@@ -56551,7 +56551,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="14">
-        <v>5662.7424793253522</v>
+        <v>5662.7424793253513</v>
       </c>
       <c r="J1238" s="13">
         <v>5018.8672999999999</v>
@@ -56560,7 +56560,7 @@
       <c r="L1238" s="13"/>
       <c r="M1238" s="13"/>
       <c r="N1238" s="15">
-        <v>53730.3577</v>
+        <v>53730.357699999993</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56589,7 +56589,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="14">
-        <v>6067.7529720316097</v>
+        <v>6067.7529720316088</v>
       </c>
       <c r="J1239" s="13">
         <v>8211.3163000000004</v>
@@ -56627,7 +56627,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="14">
-        <v>6497.7712544712294</v>
+        <v>6497.7712544712276</v>
       </c>
       <c r="J1240" s="13">
         <v>2117.8483999999999</v>
@@ -56674,7 +56674,7 @@
       <c r="L1241" s="13"/>
       <c r="M1241" s="13"/>
       <c r="N1241" s="15">
-        <v>77476.646099999998</v>
+        <v>77476.646100000013</v>
       </c>
       <c r="O1241" s="16"/>
     </row>
@@ -56742,7 +56742,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="14">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="13">
         <v>15660.4136</v>
@@ -56780,7 +56780,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="14">
-        <v>6056.5070840084409</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="13">
         <v>8281.8516999999993</v>
@@ -56789,7 +56789,7 @@
       <c r="L1244" s="13"/>
       <c r="M1244" s="13"/>
       <c r="N1244" s="15">
-        <v>57659.296399999992</v>
+        <v>57659.296399999999</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1">
@@ -56818,7 +56818,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="14">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="13">
         <v>4208.4350999999997</v>
@@ -56827,7 +56827,7 @@
       <c r="L1245" s="13"/>
       <c r="M1245" s="13"/>
       <c r="N1245" s="15">
-        <v>48637.9012</v>
+        <v>48637.901200000008</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56903,7 +56903,7 @@
       <c r="L1247" s="13"/>
       <c r="M1247" s="13"/>
       <c r="N1247" s="15">
-        <v>60445.304700000008</v>
+        <v>60445.304700000001</v>
       </c>
     </row>
     <row r="1248" spans="1:15" ht="15.75" customHeight="1">
@@ -56949,16 +56949,16 @@
         <v>45941</v>
       </c>
       <c r="B1249" s="13">
-        <v>24109.855299999999</v>
+        <v>24109.8053</v>
       </c>
       <c r="C1249" s="13">
         <v>5500.9261999999999</v>
       </c>
       <c r="D1249" s="13">
-        <v>4382.871978904207</v>
+        <v>4382.862889525768</v>
       </c>
       <c r="E1249" s="14">
-        <v>4973.8312228225723</v>
+        <v>4973.8298838492292</v>
       </c>
       <c r="F1249" s="13">
         <v>1116.6591000000001</v>
@@ -56970,7 +56970,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="14">
-        <v>5046.6456948691884</v>
+        <v>5046.6456948691875</v>
       </c>
       <c r="J1249" s="13">
         <v>6200.3991999999998</v>
@@ -56979,7 +56979,7 @@
       <c r="L1249" s="13"/>
       <c r="M1249" s="13"/>
       <c r="N1249" s="15">
-        <v>31426.9136</v>
+        <v>31426.863600000001</v>
       </c>
     </row>
     <row r="1250" spans="1:14" ht="15.75" customHeight="1">
@@ -56987,16 +56987,16 @@
         <v>45948</v>
       </c>
       <c r="B1250" s="13">
-        <v>48243.658600000002</v>
+        <v>48135.016499999998</v>
       </c>
       <c r="C1250" s="13">
-        <v>9782.5046999999995</v>
+        <v>9753.8886999999995</v>
       </c>
       <c r="D1250" s="13">
-        <v>4931.626416698783</v>
+        <v>4934.9565061163757</v>
       </c>
       <c r="E1250" s="14">
-        <v>4941.3526846502846</v>
+        <v>4942.2423524485912</v>
       </c>
       <c r="F1250" s="13">
         <v>1339.0517</v>
@@ -57017,7 +57017,7 @@
       <c r="L1250" s="13"/>
       <c r="M1250" s="13"/>
       <c r="N1250" s="15">
-        <v>62020.092499999999</v>
+        <v>61911.450400000002</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1">
@@ -57034,7 +57034,7 @@
         <v>5741.1686828543779</v>
       </c>
       <c r="E1251" s="14">
-        <v>5019.6709189815274</v>
+        <v>5020.6404242965937</v>
       </c>
       <c r="F1251" s="13">
         <v>1154.2166999999999</v>
@@ -57072,7 +57072,7 @@
         <v>4714.9565842583061</v>
       </c>
       <c r="E1252" s="14">
-        <v>4992.9414146472209</v>
+        <v>4993.8775112095673</v>
       </c>
       <c r="F1252" s="13">
         <v>979.83450000000005</v>
@@ -57101,16 +57101,16 @@
         <v>45969</v>
       </c>
       <c r="B1253" s="13">
-        <v>88076.765400000004</v>
+        <v>88068.536600000007</v>
       </c>
       <c r="C1253" s="13">
         <v>15503.728800000001</v>
       </c>
       <c r="D1253" s="13">
-        <v>5681.0052946746591</v>
+        <v>5680.4745320364482</v>
       </c>
       <c r="E1253" s="14">
-        <v>5202.4253174911737</v>
+        <v>5203.0638762466097</v>
       </c>
       <c r="F1253" s="13">
         <v>3024.5275999999999</v>
@@ -57131,7 +57131,7 @@
       <c r="L1253" s="13"/>
       <c r="M1253" s="13"/>
       <c r="N1253" s="15">
-        <v>103457.9235</v>
+        <v>103449.69470000001</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1">
@@ -57139,16 +57139,16 @@
         <v>45976</v>
       </c>
       <c r="B1254" s="13">
-        <v>45131.924899999998</v>
+        <v>45131.583299999998</v>
       </c>
       <c r="C1254" s="13">
         <v>8932.4151000000002</v>
       </c>
       <c r="D1254" s="13">
-        <v>5052.6004887524759</v>
+        <v>5052.5622460156374</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.4507220623827</v>
+        <v>5308.2636520082096</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57160,7 +57160,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="14">
-        <v>5620.2491328335427</v>
+        <v>5620.2491328335436</v>
       </c>
       <c r="J1254" s="13">
         <v>10669.626700000001</v>
@@ -57169,7 +57169,7 @@
       <c r="L1254" s="13"/>
       <c r="M1254" s="13"/>
       <c r="N1254" s="15">
-        <v>57925.7189</v>
+        <v>57925.3773</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1">
@@ -57186,7 +57186,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="14">
-        <v>5579.5810425777527</v>
+        <v>5579.4252740274405</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57198,7 +57198,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="14">
-        <v>5979.7288428128722</v>
+        <v>5979.7288428128713</v>
       </c>
       <c r="J1255" s="13">
         <v>12450.415499999999</v>
@@ -57215,16 +57215,16 @@
         <v>45990</v>
       </c>
       <c r="B1256" s="13">
-        <v>65001.364600000001</v>
+        <v>64999.004300000001</v>
       </c>
       <c r="C1256" s="13">
         <v>12531.0414</v>
       </c>
       <c r="D1256" s="13">
-        <v>5187.2276632970024</v>
+        <v>5187.0393070443452</v>
       </c>
       <c r="E1256" s="14">
-        <v>5469.5970084916407</v>
+        <v>5469.4103837612756</v>
       </c>
       <c r="F1256" s="13">
         <v>3141.94</v>
@@ -57245,7 +57245,7 @@
       <c r="L1256" s="13"/>
       <c r="M1256" s="13"/>
       <c r="N1256" s="15">
-        <v>77294.100399999996</v>
+        <v>77291.740099999995</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57253,16 +57253,16 @@
         <v>45997</v>
       </c>
       <c r="B1257" s="13">
-        <v>68682.279200000004</v>
+        <v>68681.739700000006</v>
       </c>
       <c r="C1257" s="13">
         <v>13091.163</v>
       </c>
       <c r="D1257" s="13">
-        <v>5246.4612349567415</v>
+        <v>5246.420023950508</v>
       </c>
       <c r="E1257" s="14">
-        <v>5421.5530126565773</v>
+        <v>5421.4802990261533</v>
       </c>
       <c r="F1257" s="13">
         <v>2948.9110000000001</v>
@@ -57274,7 +57274,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="14">
-        <v>6858.7787596539711</v>
+        <v>6858.778759653972</v>
       </c>
       <c r="J1257" s="13">
         <v>6940.3462</v>
@@ -57283,7 +57283,7 @@
       <c r="L1257" s="13"/>
       <c r="M1257" s="13"/>
       <c r="N1257" s="15">
-        <v>78571.536400000012</v>
+        <v>78570.996899999998</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1">
@@ -57291,16 +57291,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="13">
-        <v>60364.837500000001</v>
+        <v>60363.892500000002</v>
       </c>
       <c r="C1258" s="13">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="13">
-        <v>4974.9626388489314</v>
+        <v>4974.884756759152</v>
       </c>
       <c r="E1258" s="14">
-        <v>5452.1617185708183</v>
+        <v>5452.0896766686064</v>
       </c>
       <c r="F1258" s="13">
         <v>4360.9017999999996</v>
@@ -57312,7 +57312,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="14">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="13">
         <v>10585.9912</v>
@@ -57321,7 +57321,7 @@
       <c r="L1258" s="13"/>
       <c r="M1258" s="13"/>
       <c r="N1258" s="15">
-        <v>75311.730500000005</v>
+        <v>75310.785499999998</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57338,7 +57338,7 @@
         <v>5454.5014110385446</v>
       </c>
       <c r="E1259" s="14">
-        <v>5182.2485495717983</v>
+        <v>5182.1752821577702</v>
       </c>
       <c r="F1259" s="13">
         <v>3014.4270000000001</v>
@@ -57350,7 +57350,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="14">
-        <v>7266.6202217096225</v>
+        <v>7266.6202217096234</v>
       </c>
       <c r="J1259" s="13">
         <v>14233.2034</v>
@@ -57359,7 +57359,7 @@
       <c r="L1259" s="13"/>
       <c r="M1259" s="13"/>
       <c r="N1259" s="15">
-        <v>81477.36540000001</v>
+        <v>81477.365399999995</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57367,16 +57367,16 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="13">
-        <v>60697.9205</v>
+        <v>60697.535499999998</v>
       </c>
       <c r="C1260" s="13">
         <v>11702.9162</v>
       </c>
       <c r="D1260" s="13">
-        <v>5186.5637130683717</v>
+        <v>5186.5308152851685</v>
       </c>
       <c r="E1260" s="14">
-        <v>5209.2553779897735</v>
+        <v>5209.2189526615548</v>
       </c>
       <c r="F1260" s="13">
         <v>2192.3276999999998</v>
@@ -57388,7 +57388,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="14">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="13">
         <v>7543.9057000000003</v>
@@ -57397,7 +57397,7 @@
       <c r="L1260" s="13"/>
       <c r="M1260" s="13"/>
       <c r="N1260" s="15">
-        <v>70434.153900000005</v>
+        <v>70433.768899999995</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57414,7 +57414,7 @@
         <v>5326.105219423489</v>
       </c>
       <c r="E1261" s="14">
-        <v>5254.919105561994</v>
+        <v>5254.8902299587489</v>
       </c>
       <c r="F1261" s="13">
         <v>1259.8376000000001</v>
@@ -57443,16 +57443,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="13">
-        <v>31640.869600000002</v>
+        <v>31640.768100000001</v>
       </c>
       <c r="C1262" s="13">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="13">
-        <v>5567.2614469840346</v>
+        <v>5567.2435878972265</v>
       </c>
       <c r="E1262" s="14">
-        <v>5255.4509676683947</v>
+        <v>5255.4393130495009</v>
       </c>
       <c r="F1262" s="13">
         <v>1210.1021000000001</v>
@@ -57467,13 +57467,13 @@
         <v>6331.7504578958606</v>
       </c>
       <c r="J1262" s="13">
-        <v>7777.6869999999999</v>
+        <v>7785.9323000000004</v>
       </c>
       <c r="K1262" s="13"/>
       <c r="L1262" s="13"/>
       <c r="M1262" s="13"/>
       <c r="N1262" s="15">
-        <v>40628.6587</v>
+        <v>40636.802500000005</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57481,16 +57481,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="13">
-        <v>58966.716099999998</v>
+        <v>58966.4162</v>
       </c>
       <c r="C1263" s="13">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="13">
-        <v>5220.845437147972</v>
+        <v>5220.8188843458129</v>
       </c>
       <c r="E1263" s="14">
-        <v>5334.981060103104</v>
+        <v>5334.9620230114951</v>
       </c>
       <c r="F1263" s="13">
         <v>3212.6219999999998</v>
@@ -57511,7 +57511,7 @@
       <c r="L1263" s="13"/>
       <c r="M1263" s="13"/>
       <c r="N1263" s="15">
-        <v>70003.601899999994</v>
+        <v>70003.301999999996</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1">
@@ -57519,16 +57519,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="13">
-        <v>41416.982499999998</v>
+        <v>41413.846899999997</v>
       </c>
       <c r="C1264" s="13">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="13">
-        <v>5650.6592147478159</v>
+        <v>5650.2314142185578</v>
       </c>
       <c r="E1264" s="14">
-        <v>5402.3350633770524</v>
+        <v>5402.2334349190742</v>
       </c>
       <c r="F1264" s="13">
         <v>1803.3380999999999</v>
@@ -57543,13 +57543,13 @@
         <v>6519.8821211785771</v>
       </c>
       <c r="J1264" s="13">
-        <v>6221.1000999999997</v>
+        <v>6272.0586999999996</v>
       </c>
       <c r="K1264" s="13"/>
       <c r="L1264" s="13"/>
       <c r="M1264" s="13"/>
       <c r="N1264" s="15">
-        <v>49441.420699999995</v>
+        <v>49489.243699999999</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57557,16 +57557,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="22">
-        <v>66754.942899999995</v>
+        <v>66743.979900000006</v>
       </c>
       <c r="C1265" s="22">
         <v>12794.5746</v>
       </c>
       <c r="D1265" s="22">
-        <v>5217.4413755030191</v>
+        <v>5216.5845279451496</v>
       </c>
       <c r="E1265" s="23">
-        <v>5318.2581798828433</v>
+        <v>5317.8972086941922</v>
       </c>
       <c r="F1265" s="22">
         <v>2790.8292999999999</v>
@@ -57581,10 +57581,10 @@
         <v>6770.0527178355378</v>
       </c>
       <c r="J1265" s="22">
-        <v>8304.0838000000003</v>
+        <v>8313.8631000000005</v>
       </c>
       <c r="N1265" s="21">
-        <v>77849.856</v>
+        <v>77848.672300000006</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57592,16 +57592,16 @@
         <v>46060</v>
       </c>
       <c r="B1266" s="22">
-        <v>43291.907800000001</v>
+        <v>45427.528200000001</v>
       </c>
       <c r="C1266" s="22">
-        <v>8158.2079000000003</v>
+        <v>8456.2919000000002</v>
       </c>
       <c r="D1266" s="22">
-        <v>5306.5462820578532</v>
+        <v>5372.0388010730803</v>
       </c>
       <c r="E1266" s="23">
-        <v>5308.5912661795492</v>
+        <v>5321.4326663860802</v>
       </c>
       <c r="F1266" s="22">
         <v>1799.4023999999999</v>
@@ -57616,10 +57616,10 @@
         <v>6763.3705390493242</v>
       </c>
       <c r="J1266" s="22">
-        <v>10003.6175</v>
+        <v>10047.7572</v>
       </c>
       <c r="N1266" s="21">
-        <v>55094.9277</v>
+        <v>57274.6878</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15.75" customHeight="1">
@@ -57627,16 +57627,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="22">
-        <v>77181.978400000007</v>
+        <v>77854.597699999998</v>
       </c>
       <c r="C1267" s="22">
-        <v>13537.1278</v>
+        <v>13633.935799999999</v>
       </c>
       <c r="D1267" s="22">
-        <v>5701.5032686623526</v>
+        <v>5710.3538436788012</v>
       </c>
       <c r="E1267" s="23">
-        <v>5373.2003865429378</v>
+        <v>5387.0794560602153</v>
       </c>
       <c r="F1267" s="22">
         <v>1828.6121000000001</v>
@@ -57651,10 +57651,10 @@
         <v>6569.7313381807944</v>
       </c>
       <c r="J1267" s="22">
-        <v>13051.025600000001</v>
+        <v>13111.058999999999</v>
       </c>
       <c r="N1267" s="21">
-        <v>92061.616100000014</v>
+        <v>92794.268799999991</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57662,16 +57662,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="22">
-        <v>65268.852099999996</v>
+        <v>65267.608200000002</v>
       </c>
       <c r="C1268" s="22">
         <v>12718.373299999999</v>
       </c>
       <c r="D1268" s="22">
-        <v>5131.8553529168703</v>
+        <v>5131.7575495287601</v>
       </c>
       <c r="E1268" s="23">
-        <v>5317.8432010292154</v>
+        <v>5331.4154834195961</v>
       </c>
       <c r="F1268" s="22">
         <v>1326.8929000000001</v>
@@ -57683,13 +57683,13 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="23">
-        <v>6548.0752800166811</v>
+        <v>6548.0752800166792</v>
       </c>
       <c r="J1268" s="22">
         <v>14843.3467</v>
       </c>
       <c r="N1268" s="21">
-        <v>81439.09169999999</v>
+        <v>81437.847800000003</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57697,16 +57697,16 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="22">
-        <v>53112.1636</v>
+        <v>55640.316299999999</v>
       </c>
       <c r="C1269" s="22">
-        <v>10128.4987</v>
+        <v>10493.8631</v>
       </c>
       <c r="D1269" s="22">
-        <v>5243.8337776555181</v>
+        <v>5302.1766883922846</v>
       </c>
       <c r="E1269" s="23">
-        <v>5291.1674452553234</v>
+        <v>5316.9712402308378</v>
       </c>
       <c r="F1269" s="22">
         <v>1217.7628999999999</v>
@@ -57718,13 +57718,13 @@
         <v>7726.8974400461921</v>
       </c>
       <c r="I1269" s="23">
-        <v>6516.9746980314958</v>
+        <v>6516.974698031494</v>
       </c>
       <c r="J1269" s="22">
-        <v>7866.1765999999998</v>
+        <v>8066.3113999999996</v>
       </c>
       <c r="N1269" s="21">
-        <v>62196.1031</v>
+        <v>64924.390599999999</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57732,34 +57732,34 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="22">
-        <v>49790.911999999997</v>
+        <v>57609.357100000001</v>
       </c>
       <c r="C1270" s="22">
-        <v>8058.9301999999998</v>
+        <v>9733.1779999999999</v>
       </c>
       <c r="D1270" s="22">
-        <v>6178.3525560253647</v>
+        <v>5918.864023651885</v>
       </c>
       <c r="E1270" s="23">
-        <v>5431.3331732455999</v>
+        <v>5429.9623822716185</v>
       </c>
       <c r="F1270" s="22">
-        <v>1105.9253000000001</v>
+        <v>1172.5832</v>
       </c>
       <c r="G1270" s="22">
-        <v>131.98410000000001</v>
+        <v>150.60980000000001</v>
       </c>
       <c r="H1270" s="22">
-        <v>8379.2312861928058</v>
+        <v>7785.5703944896013</v>
       </c>
       <c r="I1270" s="23">
-        <v>7308.7373154792704</v>
+        <v>7229.1954833922346</v>
       </c>
       <c r="J1270" s="22">
-        <v>5360.7565000000004</v>
+        <v>6221.6495999999997</v>
       </c>
       <c r="N1270" s="21">
-        <v>56257.593799999995</v>
+        <v>65003.589899999999</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1">
@@ -57767,34 +57767,69 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="22">
-        <v>32986.155100000004</v>
+        <v>53314.267200000002</v>
       </c>
       <c r="C1271" s="22">
-        <v>5532.4879000000001</v>
+        <v>9442.4534000000003</v>
       </c>
       <c r="D1271" s="22">
-        <v>5962.2643006593844</v>
+        <v>5646.2303748303384</v>
       </c>
       <c r="E1271" s="23">
-        <v>5488.7231627661113</v>
+        <v>5446.2201638433908</v>
       </c>
       <c r="F1271" s="22">
-        <v>909.49450000000002</v>
+        <v>1390.9612</v>
       </c>
       <c r="G1271" s="22">
-        <v>143.4068</v>
+        <v>215.2818</v>
       </c>
       <c r="H1271" s="22">
-        <v>6342.0597907491137</v>
+        <v>6461.1184038780793</v>
       </c>
       <c r="I1271" s="23">
-        <v>7516.9287926091783</v>
+        <v>7360.0779016402776</v>
       </c>
       <c r="J1271" s="22">
-        <v>4850.7052999999996</v>
+        <v>8173.8128999999999</v>
       </c>
       <c r="N1271" s="21">
-        <v>38746.354900000006</v>
+        <v>62879.041299999997</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1272" s="20">
+        <v>46102</v>
+      </c>
+      <c r="B1272" s="22">
+        <v>24492.0762</v>
+      </c>
+      <c r="C1272" s="22">
+        <v>3918.3249999999998</v>
+      </c>
+      <c r="D1272" s="22">
+        <v>6250.6494994672466</v>
+      </c>
+      <c r="E1272" s="23">
+        <v>5647.5906744285521</v>
+      </c>
+      <c r="F1272" s="22">
+        <v>498.24779999999998</v>
+      </c>
+      <c r="G1272" s="22">
+        <v>94.123800000000003</v>
+      </c>
+      <c r="H1272" s="22">
+        <v>5293.5368100310443</v>
+      </c>
+      <c r="I1272" s="23">
+        <v>6986.851642997698</v>
+      </c>
+      <c r="J1272" s="22">
+        <v>5699.4417999999996</v>
+      </c>
+      <c r="N1272" s="21">
+        <v>30689.765800000001</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248D3FC3-B891-4FEB-8E0F-966B9261E34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B2AD0F-1797-415A-A09C-DD30B42EC67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1272"/>
+  <dimension ref="A1:W1274"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -53499,7 +53499,7 @@
         <v>4150.9922145963383</v>
       </c>
       <c r="E1158" s="14">
-        <v>3840.8705315087991</v>
+        <v>3840.8705315088</v>
       </c>
       <c r="F1158" s="13">
         <v>882.2903</v>
@@ -53549,7 +53549,7 @@
         <v>3982.0975670205294</v>
       </c>
       <c r="I1159" s="14">
-        <v>3617.6613635639042</v>
+        <v>3617.6613635639046</v>
       </c>
       <c r="J1159" s="13">
         <v>6212.6449000000002</v>
@@ -53651,7 +53651,7 @@
         <v>4066.2996598472291</v>
       </c>
       <c r="E1162" s="14">
-        <v>3926.2226648625219</v>
+        <v>3926.2226648625228</v>
       </c>
       <c r="F1162" s="13">
         <v>1349.8824999999999</v>
@@ -53727,7 +53727,7 @@
         <v>4274.3049517318423</v>
       </c>
       <c r="E1164" s="14">
-        <v>4101.7200448367421</v>
+        <v>4101.720044836743</v>
       </c>
       <c r="F1164" s="13">
         <v>902.06470000000002</v>
@@ -53739,7 +53739,7 @@
         <v>3294.3855571640811</v>
       </c>
       <c r="I1164" s="14">
-        <v>3579.4806019611092</v>
+        <v>3579.4806019611101</v>
       </c>
       <c r="J1164" s="13">
         <v>14285.5708</v>
@@ -53748,7 +53748,7 @@
       <c r="L1164" s="13"/>
       <c r="M1164" s="13"/>
       <c r="N1164" s="15">
-        <v>57458.467500000006</v>
+        <v>57458.467499999999</v>
       </c>
     </row>
     <row r="1165" spans="1:14" ht="15.75" customHeight="1">
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309879</v>
+        <v>4180.3219217309888</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53777,7 +53777,7 @@
         <v>3930.3634262421583</v>
       </c>
       <c r="I1165" s="14">
-        <v>3575.1060841405902</v>
+        <v>3575.1060841405906</v>
       </c>
       <c r="J1165" s="13">
         <v>4062.5365999999999</v>
@@ -53803,7 +53803,7 @@
         <v>4144.4221019502211</v>
       </c>
       <c r="E1166" s="14">
-        <v>4237.0040886928537</v>
+        <v>4237.0040886928527</v>
       </c>
       <c r="F1166" s="13">
         <v>1411.7936999999999</v>
@@ -53815,7 +53815,7 @@
         <v>3909.3141944625277</v>
       </c>
       <c r="I1166" s="14">
-        <v>3720.2808034203026</v>
+        <v>3720.2808034203017</v>
       </c>
       <c r="J1166" s="13">
         <v>3419.8951999999999</v>
@@ -53824,7 +53824,7 @@
       <c r="L1166" s="13"/>
       <c r="M1166" s="13"/>
       <c r="N1166" s="15">
-        <v>31626.655099999996</v>
+        <v>31626.6551</v>
       </c>
     </row>
     <row r="1167" spans="1:14" ht="15.75" customHeight="1">
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.8558460563499</v>
+        <v>4171.855846056349</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -53879,7 +53879,7 @@
         <v>3877.0306064631195</v>
       </c>
       <c r="E1168" s="14">
-        <v>4055.3634375452461</v>
+        <v>4055.3634375452452</v>
       </c>
       <c r="F1168" s="13">
         <v>2016.7924</v>
@@ -53917,7 +53917,7 @@
         <v>3932.8336637875082</v>
       </c>
       <c r="E1169" s="14">
-        <v>4049.5261191257591</v>
+        <v>4049.5261191257582</v>
       </c>
       <c r="F1169" s="13">
         <v>972.27260000000001</v>
@@ -53955,7 +53955,7 @@
         <v>4162.4812039586277</v>
       </c>
       <c r="E1170" s="14">
-        <v>3979.2022758044027</v>
+        <v>3979.2022758044022</v>
       </c>
       <c r="F1170" s="13">
         <v>1026.8530000000001</v>
@@ -53967,7 +53967,7 @@
         <v>3858.4943555335612</v>
       </c>
       <c r="I1170" s="14">
-        <v>3611.9989982892371</v>
+        <v>3611.9989982892366</v>
       </c>
       <c r="J1170" s="13">
         <v>3777.6279</v>
@@ -53976,7 +53976,7 @@
       <c r="L1170" s="13"/>
       <c r="M1170" s="13"/>
       <c r="N1170" s="15">
-        <v>37348.153800000007</v>
+        <v>37348.1538</v>
       </c>
     </row>
     <row r="1171" spans="1:14" ht="15.75" customHeight="1">
@@ -54031,7 +54031,7 @@
         <v>3938.8172877014799</v>
       </c>
       <c r="E1172" s="14">
-        <v>4014.1752681459825</v>
+        <v>4014.1752681459816</v>
       </c>
       <c r="F1172" s="13">
         <v>2680.7141999999999</v>
@@ -54107,7 +54107,7 @@
         <v>4351.7719768865618</v>
       </c>
       <c r="E1174" s="14">
-        <v>3939.3430114280172</v>
+        <v>3939.3430114280163</v>
       </c>
       <c r="F1174" s="13">
         <v>625.44079999999997</v>
@@ -54145,7 +54145,7 @@
         <v>4151.5723390857438</v>
       </c>
       <c r="E1175" s="14">
-        <v>3955.4372729635284</v>
+        <v>3955.4372729635274</v>
       </c>
       <c r="F1175" s="13">
         <v>1393.8427999999999</v>
@@ -54157,7 +54157,7 @@
         <v>3165.986834005897</v>
       </c>
       <c r="I1175" s="14">
-        <v>3345.9193035632725</v>
+        <v>3345.9193035632734</v>
       </c>
       <c r="J1175" s="13">
         <v>18463.542600000001</v>
@@ -54221,7 +54221,7 @@
         <v>4611.2745069454377</v>
       </c>
       <c r="E1177" s="14">
-        <v>4199.3537107264328</v>
+        <v>4199.3537107264319</v>
       </c>
       <c r="F1177" s="13">
         <v>850.38009999999997</v>
@@ -54242,7 +54242,7 @@
       <c r="L1177" s="13"/>
       <c r="M1177" s="13"/>
       <c r="N1177" s="15">
-        <v>62161.926700000004</v>
+        <v>62161.926699999996</v>
       </c>
     </row>
     <row r="1178" spans="1:14" ht="15.75" customHeight="1">
@@ -54335,7 +54335,7 @@
         <v>4008.5523747206912</v>
       </c>
       <c r="E1180" s="14">
-        <v>4173.750113280711</v>
+        <v>4173.750113280712</v>
       </c>
       <c r="F1180" s="13">
         <v>909.47910000000002</v>
@@ -54347,7 +54347,7 @@
         <v>3932.0511251890948</v>
       </c>
       <c r="I1180" s="14">
-        <v>3820.0779903432685</v>
+        <v>3820.0779903432676</v>
       </c>
       <c r="J1180" s="13">
         <v>7100.3598000000002</v>
@@ -54356,7 +54356,7 @@
       <c r="L1180" s="13"/>
       <c r="M1180" s="13"/>
       <c r="N1180" s="15">
-        <v>56623.827599999997</v>
+        <v>56623.827600000004</v>
       </c>
     </row>
     <row r="1181" spans="1:14" ht="15.75" customHeight="1">
@@ -54394,7 +54394,7 @@
       <c r="L1181" s="13"/>
       <c r="M1181" s="13"/>
       <c r="N1181" s="15">
-        <v>52642.395300000004</v>
+        <v>52642.395299999996</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15.75" customHeight="1">
@@ -54411,7 +54411,7 @@
         <v>4033.0100843855616</v>
       </c>
       <c r="E1182" s="14">
-        <v>4020.0169955492406</v>
+        <v>4020.0169955492411</v>
       </c>
       <c r="F1182" s="13">
         <v>427.52350000000001</v>
@@ -54449,7 +54449,7 @@
         <v>3939.2689570133098</v>
       </c>
       <c r="E1183" s="14">
-        <v>4029.5735323808303</v>
+        <v>4029.5735323808312</v>
       </c>
       <c r="F1183" s="13">
         <v>440.14429999999999</v>
@@ -54461,7 +54461,7 @@
         <v>5020.0771469761667</v>
       </c>
       <c r="I1183" s="14">
-        <v>3892.3953212090469</v>
+        <v>3892.3953212090473</v>
       </c>
       <c r="J1183" s="13">
         <v>5037.4709000000003</v>
@@ -54546,7 +54546,7 @@
       <c r="L1185" s="13"/>
       <c r="M1185" s="13"/>
       <c r="N1185" s="15">
-        <v>37483.069499999991</v>
+        <v>37483.069499999998</v>
       </c>
     </row>
     <row r="1186" spans="1:14" ht="15.75" customHeight="1">
@@ -54563,7 +54563,7 @@
         <v>3921.1801257461875</v>
       </c>
       <c r="E1186" s="14">
-        <v>4103.7917850861204</v>
+        <v>4103.7917850861213</v>
       </c>
       <c r="F1186" s="13">
         <v>1199.8832</v>
@@ -54575,7 +54575,7 @@
         <v>4393.5575388702919</v>
       </c>
       <c r="I1186" s="14">
-        <v>4445.0065612912513</v>
+        <v>4445.0065612912522</v>
       </c>
       <c r="J1186" s="13">
         <v>7294.8577999999998</v>
@@ -54584,7 +54584,7 @@
       <c r="L1186" s="13"/>
       <c r="M1186" s="13"/>
       <c r="N1186" s="15">
-        <v>44453.567299999995</v>
+        <v>44453.567300000002</v>
       </c>
     </row>
     <row r="1187" spans="1:14" ht="15.75" customHeight="1">
@@ -54601,7 +54601,7 @@
         <v>4366.3367641502828</v>
       </c>
       <c r="E1187" s="14">
-        <v>4240.9406009288678</v>
+        <v>4240.9406009288687</v>
       </c>
       <c r="F1187" s="13">
         <v>748.68579999999997</v>
@@ -54613,7 +54613,7 @@
         <v>4806.1907118779418</v>
       </c>
       <c r="I1187" s="14">
-        <v>4604.0956192242547</v>
+        <v>4604.0956192242566</v>
       </c>
       <c r="J1187" s="13">
         <v>21194.6531</v>
@@ -54727,7 +54727,7 @@
         <v>4531.757943331254</v>
       </c>
       <c r="I1190" s="14">
-        <v>4095.695696255355</v>
+        <v>4095.6956962553541</v>
       </c>
       <c r="J1190" s="13">
         <v>5596.1341000000002</v>
@@ -54736,7 +54736,7 @@
       <c r="L1190" s="13"/>
       <c r="M1190" s="13"/>
       <c r="N1190" s="15">
-        <v>59168.145500000006</v>
+        <v>59168.145499999999</v>
       </c>
     </row>
     <row r="1191" spans="1:14" ht="15.75" customHeight="1">
@@ -54765,7 +54765,7 @@
         <v>3350.0403096116738</v>
       </c>
       <c r="I1191" s="14">
-        <v>3875.9174025958691</v>
+        <v>3875.9174025958678</v>
       </c>
       <c r="J1191" s="13">
         <v>17500.0933</v>
@@ -54774,7 +54774,7 @@
       <c r="L1191" s="13"/>
       <c r="M1191" s="13"/>
       <c r="N1191" s="15">
-        <v>59039.229299999999</v>
+        <v>59039.229300000006</v>
       </c>
     </row>
     <row r="1192" spans="1:14" ht="15.75" customHeight="1">
@@ -54917,7 +54917,7 @@
         <v>4494.0008399611515</v>
       </c>
       <c r="I1195" s="14">
-        <v>4403.0055020784703</v>
+        <v>4403.0055020784712</v>
       </c>
       <c r="J1195" s="13">
         <v>3683.5691000000002</v>
@@ -54964,7 +54964,7 @@
       <c r="L1196" s="13"/>
       <c r="M1196" s="13"/>
       <c r="N1196" s="15">
-        <v>59285.673100000007</v>
+        <v>59285.6731</v>
       </c>
     </row>
     <row r="1197" spans="1:14" ht="15.75" customHeight="1">
@@ -55002,7 +55002,7 @@
       <c r="L1197" s="13"/>
       <c r="M1197" s="13"/>
       <c r="N1197" s="15">
-        <v>46861.756299999994</v>
+        <v>46861.756300000001</v>
       </c>
     </row>
     <row r="1198" spans="1:14" ht="15.75" customHeight="1">
@@ -55078,7 +55078,7 @@
       <c r="L1199" s="13"/>
       <c r="M1199" s="13"/>
       <c r="N1199" s="15">
-        <v>45059.347400000006</v>
+        <v>45059.347399999999</v>
       </c>
     </row>
     <row r="1200" spans="1:14" ht="15.75" customHeight="1">
@@ -55095,7 +55095,7 @@
         <v>4513.7009686452229</v>
       </c>
       <c r="E1200" s="14">
-        <v>4435.3725877679126</v>
+        <v>4435.3725877679108</v>
       </c>
       <c r="F1200" s="13">
         <v>1429.8607</v>
@@ -55107,7 +55107,7 @@
         <v>5125.1875535419204</v>
       </c>
       <c r="I1200" s="14">
-        <v>4119.7835060629886</v>
+        <v>4119.7835060629877</v>
       </c>
       <c r="J1200" s="13">
         <v>5175.8775999999998</v>
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551785</v>
+        <v>4487.7143253551776</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55154,7 +55154,7 @@
       <c r="L1201" s="13"/>
       <c r="M1201" s="13"/>
       <c r="N1201" s="15">
-        <v>64229.893499999998</v>
+        <v>64229.893500000006</v>
       </c>
     </row>
     <row r="1202" spans="1:14" ht="15.75" customHeight="1">
@@ -55183,7 +55183,7 @@
         <v>5782.081258662286</v>
       </c>
       <c r="I1202" s="14">
-        <v>5126.6494289859602</v>
+        <v>5126.6494289859611</v>
       </c>
       <c r="J1202" s="13">
         <v>5202.1442999999999</v>
@@ -55209,7 +55209,7 @@
         <v>4938.8935854309739</v>
       </c>
       <c r="E1203" s="14">
-        <v>4717.3485788226408</v>
+        <v>4717.3485788226399</v>
       </c>
       <c r="F1203" s="13">
         <v>1626.8607999999999</v>
@@ -55221,7 +55221,7 @@
         <v>4417.2715705925184</v>
       </c>
       <c r="I1203" s="14">
-        <v>5085.9482018840408</v>
+        <v>5085.9482018840399</v>
       </c>
       <c r="J1203" s="13">
         <v>8027.7326999999996</v>
@@ -55230,7 +55230,7 @@
       <c r="L1203" s="13"/>
       <c r="M1203" s="13"/>
       <c r="N1203" s="15">
-        <v>79222.162899999981</v>
+        <v>79222.162899999996</v>
       </c>
     </row>
     <row r="1204" spans="1:14" ht="15.75" customHeight="1">
@@ -55247,7 +55247,7 @@
         <v>4266.1272976812243</v>
       </c>
       <c r="E1204" s="14">
-        <v>4525.047597680712</v>
+        <v>4525.0475976807111</v>
       </c>
       <c r="F1204" s="13">
         <v>1885.9646</v>
@@ -55268,7 +55268,7 @@
       <c r="L1204" s="13"/>
       <c r="M1204" s="13"/>
       <c r="N1204" s="15">
-        <v>86729.972700000013</v>
+        <v>86729.972699999998</v>
       </c>
     </row>
     <row r="1205" spans="1:14" ht="15.75" customHeight="1">
@@ -55285,7 +55285,7 @@
         <v>4424.3978008967133</v>
       </c>
       <c r="E1205" s="14">
-        <v>4552.8231579350822</v>
+        <v>4552.8231579350831</v>
       </c>
       <c r="F1205" s="13">
         <v>1070.8937000000001</v>
@@ -55335,7 +55335,7 @@
         <v>3932.5340059065734</v>
       </c>
       <c r="I1206" s="14">
-        <v>4333.5986404219693</v>
+        <v>4333.5986404219711</v>
       </c>
       <c r="J1206" s="13">
         <v>6089.9108999999999</v>
@@ -55361,7 +55361,7 @@
         <v>4252.7279635792374</v>
       </c>
       <c r="E1207" s="14">
-        <v>4389.4044684956043</v>
+        <v>4389.4044684956052</v>
       </c>
       <c r="F1207" s="13">
         <v>1109.1464000000001</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629666</v>
+        <v>4315.8033455629657</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55411,7 +55411,7 @@
         <v>4947.3851972485918</v>
       </c>
       <c r="I1208" s="14">
-        <v>4350.8974691132007</v>
+        <v>4350.8974691131998</v>
       </c>
       <c r="J1208" s="13">
         <v>9287.4572000000007</v>
@@ -55420,7 +55420,7 @@
       <c r="L1208" s="13"/>
       <c r="M1208" s="13"/>
       <c r="N1208" s="15">
-        <v>49051.207199999997</v>
+        <v>49051.207200000004</v>
       </c>
     </row>
     <row r="1209" spans="1:14" ht="15.75" customHeight="1">
@@ -55449,7 +55449,7 @@
         <v>5232.7977567123598</v>
       </c>
       <c r="I1209" s="14">
-        <v>4726.9079889175364</v>
+        <v>4726.9079889175373</v>
       </c>
       <c r="J1209" s="13">
         <v>6374.9992000000002</v>
@@ -55475,7 +55475,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="14">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="13">
         <v>1813.4111</v>
@@ -55487,7 +55487,7 @@
         <v>6882.5719118850975</v>
       </c>
       <c r="I1210" s="14">
-        <v>5131.0721532756543</v>
+        <v>5131.0721532756534</v>
       </c>
       <c r="J1210" s="13">
         <v>5833.4898999999996</v>
@@ -55525,7 +55525,7 @@
         <v>6099.4532507976128</v>
       </c>
       <c r="I1211" s="14">
-        <v>5615.5313175907386</v>
+        <v>5615.5313175907377</v>
       </c>
       <c r="J1211" s="13">
         <v>4923.6122999999998</v>
@@ -55572,7 +55572,7 @@
       <c r="L1212" s="13"/>
       <c r="M1212" s="13"/>
       <c r="N1212" s="15">
-        <v>45765.935099999995</v>
+        <v>45765.935100000002</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55601,7 +55601,7 @@
         <v>5196.6505136827682</v>
       </c>
       <c r="I1213" s="14">
-        <v>5637.214495755039</v>
+        <v>5637.2144957550399</v>
       </c>
       <c r="J1213" s="13">
         <v>10879.186799999999</v>
@@ -55648,7 +55648,7 @@
       <c r="L1214" s="13"/>
       <c r="M1214" s="13"/>
       <c r="N1214" s="15">
-        <v>76702.561400000006</v>
+        <v>76702.561399999991</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55715,7 +55715,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="14">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="13">
         <v>3920.1588999999999</v>
@@ -55741,7 +55741,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.1866360758067</v>
+        <v>4706.1866360758077</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.4088847985449</v>
+        <v>4736.4088847985458</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55817,7 +55817,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="14">
-        <v>4756.246929365534</v>
+        <v>4756.2469293655349</v>
       </c>
       <c r="F1219" s="13">
         <v>1866.9058</v>
@@ -55838,7 +55838,7 @@
       <c r="L1219" s="13"/>
       <c r="M1219" s="13"/>
       <c r="N1219" s="15">
-        <v>62677.385600000001</v>
+        <v>62677.385599999994</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55855,7 +55855,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.2967738120524</v>
+        <v>4663.2967738120533</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55931,7 +55931,7 @@
         <v>4849.8313970697627</v>
       </c>
       <c r="E1222" s="14">
-        <v>4695.6837921024498</v>
+        <v>4695.6837921024489</v>
       </c>
       <c r="F1222" s="13">
         <v>1081.6878999999999</v>
@@ -55952,7 +55952,7 @@
       <c r="L1222" s="13"/>
       <c r="M1222" s="13"/>
       <c r="N1222" s="15">
-        <v>52967.567299999995</v>
+        <v>52967.567300000002</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56007,7 +56007,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="14">
-        <v>4673.008044303504</v>
+        <v>4673.0080443035031</v>
       </c>
       <c r="F1224" s="13">
         <v>678.69989999999996</v>
@@ -56218,7 +56218,7 @@
       <c r="L1229" s="13"/>
       <c r="M1229" s="13"/>
       <c r="N1229" s="15">
-        <v>66469.655099999989</v>
+        <v>66469.655100000004</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56235,7 +56235,7 @@
         <v>5223.7943789585233</v>
       </c>
       <c r="E1230" s="14">
-        <v>5028.6483389254818</v>
+        <v>5028.6483389254827</v>
       </c>
       <c r="F1230" s="13">
         <v>186.41309999999999</v>
@@ -56273,7 +56273,7 @@
         <v>4742.3293933814848</v>
       </c>
       <c r="E1231" s="14">
-        <v>4961.5475609355053</v>
+        <v>4961.5475609355035</v>
       </c>
       <c r="F1231" s="13">
         <v>1023.9116</v>
@@ -56437,7 +56437,7 @@
         <v>5270.8131997196551</v>
       </c>
       <c r="I1235" s="14">
-        <v>6279.4686229430445</v>
+        <v>6279.4686229430436</v>
       </c>
       <c r="J1235" s="13">
         <v>12601.2554</v>
@@ -56501,7 +56501,7 @@
         <v>5279.8066063917322</v>
       </c>
       <c r="E1237" s="14">
-        <v>4926.7513336432476</v>
+        <v>4926.7513336432485</v>
       </c>
       <c r="F1237" s="13">
         <v>770.73030000000006</v>
@@ -56539,7 +56539,7 @@
         <v>5523.8887674123871</v>
       </c>
       <c r="E1238" s="14">
-        <v>5021.4125766800362</v>
+        <v>5021.4125766800344</v>
       </c>
       <c r="F1238" s="13">
         <v>937.15679999999998</v>
@@ -56551,7 +56551,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="14">
-        <v>5662.7424793253513</v>
+        <v>5662.7424793253522</v>
       </c>
       <c r="J1238" s="13">
         <v>5018.8672999999999</v>
@@ -56560,7 +56560,7 @@
       <c r="L1238" s="13"/>
       <c r="M1238" s="13"/>
       <c r="N1238" s="15">
-        <v>53730.357699999993</v>
+        <v>53730.3577</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56589,7 +56589,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="14">
-        <v>6067.7529720316088</v>
+        <v>6067.7529720316097</v>
       </c>
       <c r="J1239" s="13">
         <v>8211.3163000000004</v>
@@ -56627,7 +56627,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="14">
-        <v>6497.7712544712276</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="13">
         <v>2117.8483999999999</v>
@@ -56644,16 +56644,16 @@
         <v>45885</v>
       </c>
       <c r="B1241" s="13">
-        <v>64243.667600000001</v>
+        <v>64240.383500000004</v>
       </c>
       <c r="C1241" s="13">
         <v>10935.062099999999</v>
       </c>
       <c r="D1241" s="13">
-        <v>5875.0162561948327</v>
+        <v>5874.7159286822889</v>
       </c>
       <c r="E1241" s="14">
-        <v>5328.2971232518175</v>
+        <v>5328.2110098593139</v>
       </c>
       <c r="F1241" s="13">
         <v>356.61349999999999</v>
@@ -56674,7 +56674,7 @@
       <c r="L1241" s="13"/>
       <c r="M1241" s="13"/>
       <c r="N1241" s="15">
-        <v>77476.646100000013</v>
+        <v>77473.362000000008</v>
       </c>
       <c r="O1241" s="16"/>
     </row>
@@ -56692,7 +56692,7 @@
         <v>5270.233180814248</v>
       </c>
       <c r="E1242" s="14">
-        <v>5374.9074293853319</v>
+        <v>5374.8324720174633</v>
       </c>
       <c r="F1242" s="13">
         <v>1157.8651</v>
@@ -56730,7 +56730,7 @@
         <v>5140.7635630848727</v>
       </c>
       <c r="E1243" s="14">
-        <v>5338.9287177228089</v>
+        <v>5338.8626499419361</v>
       </c>
       <c r="F1243" s="13">
         <v>913.81010000000003</v>
@@ -56742,7 +56742,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="14">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="13">
         <v>15660.4136</v>
@@ -56768,7 +56768,7 @@
         <v>4780.8999076950913</v>
       </c>
       <c r="E1244" s="14">
-        <v>5246.8473557608258</v>
+        <v>5246.7848462393104</v>
       </c>
       <c r="F1244" s="13">
         <v>1388.6704</v>
@@ -56780,7 +56780,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="14">
-        <v>6056.5070840084427</v>
+        <v>6056.50708400844</v>
       </c>
       <c r="J1244" s="13">
         <v>8281.8516999999993</v>
@@ -56789,7 +56789,7 @@
       <c r="L1244" s="13"/>
       <c r="M1244" s="13"/>
       <c r="N1244" s="15">
-        <v>57659.296399999999</v>
+        <v>57659.296399999992</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1">
@@ -56818,7 +56818,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="14">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="13">
         <v>4208.4350999999997</v>
@@ -56827,7 +56827,7 @@
       <c r="L1245" s="13"/>
       <c r="M1245" s="13"/>
       <c r="N1245" s="15">
-        <v>48637.901200000008</v>
+        <v>48637.9012</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56903,7 +56903,7 @@
       <c r="L1247" s="13"/>
       <c r="M1247" s="13"/>
       <c r="N1247" s="15">
-        <v>60445.304700000001</v>
+        <v>60445.304700000008</v>
       </c>
     </row>
     <row r="1248" spans="1:15" ht="15.75" customHeight="1">
@@ -56970,7 +56970,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="14">
-        <v>5046.6456948691875</v>
+        <v>5046.6456948691884</v>
       </c>
       <c r="J1249" s="13">
         <v>6200.3991999999998</v>
@@ -57025,16 +57025,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="13">
-        <v>54509.922200000001</v>
+        <v>54500.556900000003</v>
       </c>
       <c r="C1251" s="13">
         <v>9494.5689999999995</v>
       </c>
       <c r="D1251" s="13">
-        <v>5741.1686828543779</v>
+        <v>5740.1822979010431</v>
       </c>
       <c r="E1251" s="14">
-        <v>5020.6404242965937</v>
+        <v>5020.3806389027459</v>
       </c>
       <c r="F1251" s="13">
         <v>1154.2166999999999</v>
@@ -57055,7 +57055,7 @@
       <c r="L1251" s="13"/>
       <c r="M1251" s="13"/>
       <c r="N1251" s="15">
-        <v>61083.839699999997</v>
+        <v>61074.474400000006</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57072,7 +57072,7 @@
         <v>4714.9565842583061</v>
       </c>
       <c r="E1252" s="14">
-        <v>4993.8775112095673</v>
+        <v>4993.621065652168</v>
       </c>
       <c r="F1252" s="13">
         <v>979.83450000000005</v>
@@ -57084,7 +57084,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="14">
-        <v>5768.2127381128485</v>
+        <v>5768.2127381128475</v>
       </c>
       <c r="J1252" s="13">
         <v>10772.394200000001</v>
@@ -57101,16 +57101,16 @@
         <v>45969</v>
       </c>
       <c r="B1253" s="13">
-        <v>88068.536600000007</v>
+        <v>88069.229600000006</v>
       </c>
       <c r="C1253" s="13">
         <v>15503.728800000001</v>
       </c>
       <c r="D1253" s="13">
-        <v>5680.4745320364482</v>
+        <v>5680.5192309607482</v>
       </c>
       <c r="E1253" s="14">
-        <v>5203.0638762466097</v>
+        <v>5202.890559252688</v>
       </c>
       <c r="F1253" s="13">
         <v>3024.5275999999999</v>
@@ -57131,7 +57131,7 @@
       <c r="L1253" s="13"/>
       <c r="M1253" s="13"/>
       <c r="N1253" s="15">
-        <v>103449.69470000001</v>
+        <v>103450.38770000001</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1">
@@ -57148,7 +57148,7 @@
         <v>5052.5622460156374</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.2636520082096</v>
+        <v>5308.0743577359699</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57160,7 +57160,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="14">
-        <v>5620.2491328335436</v>
+        <v>5620.2491328335427</v>
       </c>
       <c r="J1254" s="13">
         <v>10669.626700000001</v>
@@ -57186,7 +57186,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="14">
-        <v>5579.4252740274405</v>
+        <v>5579.2676534264356</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57215,16 +57215,16 @@
         <v>45990</v>
       </c>
       <c r="B1256" s="13">
-        <v>64999.004300000001</v>
+        <v>64998.440499999997</v>
       </c>
       <c r="C1256" s="13">
         <v>12531.0414</v>
       </c>
       <c r="D1256" s="13">
-        <v>5187.0393070443452</v>
+        <v>5186.9943147741897</v>
       </c>
       <c r="E1256" s="14">
-        <v>5469.4103837612756</v>
+        <v>5469.4125896506666</v>
       </c>
       <c r="F1256" s="13">
         <v>3141.94</v>
@@ -57245,7 +57245,7 @@
       <c r="L1256" s="13"/>
       <c r="M1256" s="13"/>
       <c r="N1256" s="15">
-        <v>77291.740099999995</v>
+        <v>77291.176299999992</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57262,7 +57262,7 @@
         <v>5246.420023950508</v>
       </c>
       <c r="E1257" s="14">
-        <v>5421.4802990261533</v>
+        <v>5421.4698526025386</v>
       </c>
       <c r="F1257" s="13">
         <v>2948.9110000000001</v>
@@ -57291,16 +57291,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="13">
-        <v>60363.892500000002</v>
+        <v>60363.868199999997</v>
       </c>
       <c r="C1258" s="13">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="13">
-        <v>4974.884756759152</v>
+        <v>4974.8827540768425</v>
       </c>
       <c r="E1258" s="14">
-        <v>5452.0896766686064</v>
+        <v>5452.078657150636</v>
       </c>
       <c r="F1258" s="13">
         <v>4360.9017999999996</v>
@@ -57312,16 +57312,16 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="14">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="13">
-        <v>10585.9912</v>
+        <v>10585.9136</v>
       </c>
       <c r="K1258" s="13"/>
       <c r="L1258" s="13"/>
       <c r="M1258" s="13"/>
       <c r="N1258" s="15">
-        <v>75310.785499999998</v>
+        <v>75310.683599999989</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57338,7 +57338,7 @@
         <v>5454.5014110385446</v>
       </c>
       <c r="E1259" s="14">
-        <v>5182.1752821577702</v>
+        <v>5182.1640751857058</v>
       </c>
       <c r="F1259" s="13">
         <v>3014.4270000000001</v>
@@ -57350,7 +57350,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="14">
-        <v>7266.6202217096234</v>
+        <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="13">
         <v>14233.2034</v>
@@ -57359,7 +57359,7 @@
       <c r="L1259" s="13"/>
       <c r="M1259" s="13"/>
       <c r="N1259" s="15">
-        <v>81477.365399999995</v>
+        <v>81477.36540000001</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57376,7 +57376,7 @@
         <v>5186.5308152851685</v>
       </c>
       <c r="E1260" s="14">
-        <v>5209.2189526615548</v>
+        <v>5209.2184792004828</v>
       </c>
       <c r="F1260" s="13">
         <v>2192.3276999999998</v>
@@ -57388,7 +57388,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="14">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="13">
         <v>7543.9057000000003</v>
@@ -57414,7 +57414,7 @@
         <v>5326.105219423489</v>
       </c>
       <c r="E1261" s="14">
-        <v>5254.8902299587489</v>
+        <v>5254.8897023819372</v>
       </c>
       <c r="F1261" s="13">
         <v>1259.8376000000001</v>
@@ -57452,7 +57452,7 @@
         <v>5567.2435878972265</v>
       </c>
       <c r="E1262" s="14">
-        <v>5255.4393130495009</v>
+        <v>5255.4393130495018</v>
       </c>
       <c r="F1262" s="13">
         <v>1210.1021000000001</v>
@@ -57528,7 +57528,7 @@
         <v>5650.2314142185578</v>
       </c>
       <c r="E1264" s="14">
-        <v>5402.2334349190742</v>
+        <v>5402.2334349190778</v>
       </c>
       <c r="F1264" s="13">
         <v>1803.3380999999999</v>
@@ -57566,7 +57566,7 @@
         <v>5216.5845279451496</v>
       </c>
       <c r="E1265" s="23">
-        <v>5317.8972086941922</v>
+        <v>5317.8972086941903</v>
       </c>
       <c r="F1265" s="22">
         <v>2790.8292999999999</v>
@@ -57592,16 +57592,16 @@
         <v>46060</v>
       </c>
       <c r="B1266" s="22">
-        <v>45427.528200000001</v>
+        <v>45422.882799999999</v>
       </c>
       <c r="C1266" s="22">
         <v>8456.2919000000002</v>
       </c>
       <c r="D1266" s="22">
-        <v>5372.0388010730803</v>
+        <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="23">
-        <v>5321.4326663860802</v>
+        <v>5321.321954260301</v>
       </c>
       <c r="F1266" s="22">
         <v>1799.4023999999999</v>
@@ -57619,7 +57619,7 @@
         <v>10047.7572</v>
       </c>
       <c r="N1266" s="21">
-        <v>57274.6878</v>
+        <v>57270.042399999998</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15.75" customHeight="1">
@@ -57636,7 +57636,7 @@
         <v>5710.3538436788012</v>
       </c>
       <c r="E1267" s="23">
-        <v>5387.0794560602153</v>
+        <v>5386.9835567087621</v>
       </c>
       <c r="F1267" s="22">
         <v>1828.6121000000001</v>
@@ -57651,10 +57651,10 @@
         <v>6569.7313381807944</v>
       </c>
       <c r="J1267" s="22">
-        <v>13111.058999999999</v>
+        <v>13246.216200000001</v>
       </c>
       <c r="N1267" s="21">
-        <v>92794.268799999991</v>
+        <v>92929.426000000007</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57671,7 +57671,7 @@
         <v>5131.7575495287601</v>
       </c>
       <c r="E1268" s="23">
-        <v>5331.4154834195961</v>
+        <v>5331.3245727394215</v>
       </c>
       <c r="F1268" s="22">
         <v>1326.8929000000001</v>
@@ -57683,7 +57683,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="23">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="22">
         <v>14843.3467</v>
@@ -57697,34 +57697,34 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="22">
-        <v>55640.316299999999</v>
+        <v>55628.328699999998</v>
       </c>
       <c r="C1269" s="22">
         <v>10493.8631</v>
       </c>
       <c r="D1269" s="22">
-        <v>5302.1766883922846</v>
+        <v>5301.0343445399049</v>
       </c>
       <c r="E1269" s="23">
-        <v>5316.9712402308378</v>
+        <v>5316.6423104439555</v>
       </c>
       <c r="F1269" s="22">
-        <v>1217.7628999999999</v>
+        <v>1050.4068</v>
       </c>
       <c r="G1269" s="22">
-        <v>157.60050000000001</v>
+        <v>135.29339999999999</v>
       </c>
       <c r="H1269" s="22">
-        <v>7726.8974400461921</v>
+        <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="23">
-        <v>6516.974698031494</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="22">
-        <v>8066.3113999999996</v>
+        <v>8128.4333999999999</v>
       </c>
       <c r="N1269" s="21">
-        <v>64924.390599999999</v>
+        <v>64807.168899999997</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57732,16 +57732,16 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="22">
-        <v>57609.357100000001</v>
+        <v>57506.729399999997</v>
       </c>
       <c r="C1270" s="22">
-        <v>9733.1779999999999</v>
+        <v>9697.8808000000008</v>
       </c>
       <c r="D1270" s="22">
-        <v>5918.864023651885</v>
+        <v>5929.8243179066494</v>
       </c>
       <c r="E1270" s="23">
-        <v>5429.9623822716185</v>
+        <v>5431.3747097650958</v>
       </c>
       <c r="F1270" s="22">
         <v>1172.5832</v>
@@ -57753,13 +57753,13 @@
         <v>7785.5703944896013</v>
       </c>
       <c r="I1270" s="23">
-        <v>7229.1954833922346</v>
+        <v>7222.0356794484687</v>
       </c>
       <c r="J1270" s="22">
-        <v>6221.6495999999997</v>
+        <v>6080.7852999999996</v>
       </c>
       <c r="N1270" s="21">
-        <v>65003.589899999999</v>
+        <v>64760.097899999993</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1">
@@ -57767,34 +57767,34 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="22">
-        <v>53314.267200000002</v>
+        <v>65320.845699999998</v>
       </c>
       <c r="C1271" s="22">
-        <v>9442.4534000000003</v>
+        <v>11979.2505</v>
       </c>
       <c r="D1271" s="22">
-        <v>5646.2303748303384</v>
+        <v>5452.8324372213428</v>
       </c>
       <c r="E1271" s="23">
-        <v>5446.2201638433908</v>
+        <v>5410.9762416246313</v>
       </c>
       <c r="F1271" s="22">
-        <v>1390.9612</v>
+        <v>1808.0657000000001</v>
       </c>
       <c r="G1271" s="22">
-        <v>215.2818</v>
+        <v>256.40100000000001</v>
       </c>
       <c r="H1271" s="22">
-        <v>6461.1184038780793</v>
+        <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="23">
-        <v>7360.0779016402776</v>
+        <v>7489.2724524389059</v>
       </c>
       <c r="J1271" s="22">
-        <v>8173.8128999999999</v>
+        <v>9586.0277000000006</v>
       </c>
       <c r="N1271" s="21">
-        <v>62879.041299999997</v>
+        <v>76714.939100000003</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1">
@@ -57802,34 +57802,104 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="22">
-        <v>24492.0762</v>
+        <v>36047.857900000003</v>
       </c>
       <c r="C1272" s="22">
-        <v>3918.3249999999998</v>
+        <v>5910.6274999999996</v>
       </c>
       <c r="D1272" s="22">
-        <v>6250.6494994672466</v>
+        <v>6098.8207935621067</v>
       </c>
       <c r="E1272" s="23">
-        <v>5647.5906744285521</v>
+        <v>5603.2909134213978</v>
       </c>
       <c r="F1272" s="22">
-        <v>498.24779999999998</v>
+        <v>677.63319999999999</v>
       </c>
       <c r="G1272" s="22">
-        <v>94.123800000000003</v>
+        <v>100.11669999999999</v>
       </c>
       <c r="H1272" s="22">
-        <v>5293.5368100310443</v>
+        <v>6768.4332384107747</v>
       </c>
       <c r="I1272" s="23">
-        <v>6986.851642997698</v>
+        <v>7302.288742792538</v>
       </c>
       <c r="J1272" s="22">
-        <v>5699.4417999999996</v>
+        <v>7886.5470999999998</v>
       </c>
       <c r="N1272" s="21">
-        <v>30689.765800000001</v>
+        <v>44612.038200000003</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1273" s="20">
+        <v>46109</v>
+      </c>
+      <c r="B1273" s="22">
+        <v>48711.053200000002</v>
+      </c>
+      <c r="C1273" s="22">
+        <v>8233.5599000000002</v>
+      </c>
+      <c r="D1273" s="22">
+        <v>5916.159448843021</v>
+      </c>
+      <c r="E1273" s="23">
+        <v>5703.3050193110284</v>
+      </c>
+      <c r="F1273" s="22">
+        <v>720.25890000000004</v>
+      </c>
+      <c r="G1273" s="22">
+        <v>114.3421</v>
+      </c>
+      <c r="H1273" s="22">
+        <v>6299.1575281545465</v>
+      </c>
+      <c r="I1273" s="23">
+        <v>7159.4977018096261</v>
+      </c>
+      <c r="J1273" s="22">
+        <v>9724.2219999999998</v>
+      </c>
+      <c r="N1273" s="21">
+        <v>59155.534100000004</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1274" s="20">
+        <v>46116</v>
+      </c>
+      <c r="B1274" s="22">
+        <v>23041.115399999999</v>
+      </c>
+      <c r="C1274" s="22">
+        <v>3747.3872999999999</v>
+      </c>
+      <c r="D1274" s="22">
+        <v>6148.5812795490874</v>
+      </c>
+      <c r="E1274" s="23">
+        <v>5729.6463487492692</v>
+      </c>
+      <c r="F1274" s="22">
+        <v>90.856499999999997</v>
+      </c>
+      <c r="G1274" s="22">
+        <v>18.032800000000002</v>
+      </c>
+      <c r="H1274" s="22">
+        <v>5038.4022447983671</v>
+      </c>
+      <c r="I1274" s="23">
+        <v>7230.4853929932488</v>
+      </c>
+      <c r="J1274" s="22">
+        <v>3315.7556</v>
+      </c>
+      <c r="N1274" s="21">
+        <v>26447.727499999997</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B2AD0F-1797-415A-A09C-DD30B42EC67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49109C22-53D2-476E-801E-4C0CD9650A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1274"/>
+  <dimension ref="A1:W1275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -915,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="35">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
@@ -53499,7 +53499,7 @@
         <v>4150.9922145963383</v>
       </c>
       <c r="E1158" s="14">
-        <v>3840.8705315088</v>
+        <v>3840.8705315087991</v>
       </c>
       <c r="F1158" s="13">
         <v>882.2903</v>
@@ -53549,7 +53549,7 @@
         <v>3982.0975670205294</v>
       </c>
       <c r="I1159" s="14">
-        <v>3617.6613635639046</v>
+        <v>3617.6613635639042</v>
       </c>
       <c r="J1159" s="13">
         <v>6212.6449000000002</v>
@@ -53651,7 +53651,7 @@
         <v>4066.2996598472291</v>
       </c>
       <c r="E1162" s="14">
-        <v>3926.2226648625228</v>
+        <v>3926.2226648625219</v>
       </c>
       <c r="F1162" s="13">
         <v>1349.8824999999999</v>
@@ -53727,7 +53727,7 @@
         <v>4274.3049517318423</v>
       </c>
       <c r="E1164" s="14">
-        <v>4101.720044836743</v>
+        <v>4101.7200448367421</v>
       </c>
       <c r="F1164" s="13">
         <v>902.06470000000002</v>
@@ -53739,7 +53739,7 @@
         <v>3294.3855571640811</v>
       </c>
       <c r="I1164" s="14">
-        <v>3579.4806019611101</v>
+        <v>3579.4806019611092</v>
       </c>
       <c r="J1164" s="13">
         <v>14285.5708</v>
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309888</v>
+        <v>4180.3219217309879</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.855846056349</v>
+        <v>4171.8558460563499</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -53967,7 +53967,7 @@
         <v>3858.4943555335612</v>
       </c>
       <c r="I1170" s="14">
-        <v>3611.9989982892366</v>
+        <v>3611.9989982892371</v>
       </c>
       <c r="J1170" s="13">
         <v>3777.6279</v>
@@ -54031,7 +54031,7 @@
         <v>3938.8172877014799</v>
       </c>
       <c r="E1172" s="14">
-        <v>4014.1752681459816</v>
+        <v>4014.1752681459825</v>
       </c>
       <c r="F1172" s="13">
         <v>2680.7141999999999</v>
@@ -54107,7 +54107,7 @@
         <v>4351.7719768865618</v>
       </c>
       <c r="E1174" s="14">
-        <v>3939.3430114280163</v>
+        <v>3939.3430114280172</v>
       </c>
       <c r="F1174" s="13">
         <v>625.44079999999997</v>
@@ -54157,7 +54157,7 @@
         <v>3165.986834005897</v>
       </c>
       <c r="I1175" s="14">
-        <v>3345.9193035632734</v>
+        <v>3345.9193035632725</v>
       </c>
       <c r="J1175" s="13">
         <v>18463.542600000001</v>
@@ -54347,7 +54347,7 @@
         <v>3932.0511251890948</v>
       </c>
       <c r="I1180" s="14">
-        <v>3820.0779903432676</v>
+        <v>3820.0779903432685</v>
       </c>
       <c r="J1180" s="13">
         <v>7100.3598000000002</v>
@@ -54385,7 +54385,7 @@
         <v>3932.1869092178767</v>
       </c>
       <c r="I1181" s="14">
-        <v>3763.2741964818451</v>
+        <v>3763.2741964818456</v>
       </c>
       <c r="J1181" s="13">
         <v>7024.5267000000003</v>
@@ -54423,7 +54423,7 @@
         <v>4435.1671265846417</v>
       </c>
       <c r="I1182" s="14">
-        <v>3815.6421043550649</v>
+        <v>3815.6421043550654</v>
       </c>
       <c r="J1182" s="13">
         <v>6999.7999</v>
@@ -54461,7 +54461,7 @@
         <v>5020.0771469761667</v>
       </c>
       <c r="I1183" s="14">
-        <v>3892.3953212090473</v>
+        <v>3892.3953212090469</v>
       </c>
       <c r="J1183" s="13">
         <v>5037.4709000000003</v>
@@ -54563,7 +54563,7 @@
         <v>3921.1801257461875</v>
       </c>
       <c r="E1186" s="14">
-        <v>4103.7917850861213</v>
+        <v>4103.7917850861204</v>
       </c>
       <c r="F1186" s="13">
         <v>1199.8832</v>
@@ -54575,7 +54575,7 @@
         <v>4393.5575388702919</v>
       </c>
       <c r="I1186" s="14">
-        <v>4445.0065612912522</v>
+        <v>4445.0065612912513</v>
       </c>
       <c r="J1186" s="13">
         <v>7294.8577999999998</v>
@@ -54601,7 +54601,7 @@
         <v>4366.3367641502828</v>
       </c>
       <c r="E1187" s="14">
-        <v>4240.9406009288687</v>
+        <v>4240.9406009288678</v>
       </c>
       <c r="F1187" s="13">
         <v>748.68579999999997</v>
@@ -54613,7 +54613,7 @@
         <v>4806.1907118779418</v>
       </c>
       <c r="I1187" s="14">
-        <v>4604.0956192242566</v>
+        <v>4604.0956192242547</v>
       </c>
       <c r="J1187" s="13">
         <v>21194.6531</v>
@@ -54727,7 +54727,7 @@
         <v>4531.757943331254</v>
       </c>
       <c r="I1190" s="14">
-        <v>4095.6956962553541</v>
+        <v>4095.695696255355</v>
       </c>
       <c r="J1190" s="13">
         <v>5596.1341000000002</v>
@@ -54765,7 +54765,7 @@
         <v>3350.0403096116738</v>
       </c>
       <c r="I1191" s="14">
-        <v>3875.9174025958678</v>
+        <v>3875.9174025958691</v>
       </c>
       <c r="J1191" s="13">
         <v>17500.0933</v>
@@ -54917,7 +54917,7 @@
         <v>4494.0008399611515</v>
       </c>
       <c r="I1195" s="14">
-        <v>4403.0055020784712</v>
+        <v>4403.0055020784703</v>
       </c>
       <c r="J1195" s="13">
         <v>3683.5691000000002</v>
@@ -55095,7 +55095,7 @@
         <v>4513.7009686452229</v>
       </c>
       <c r="E1200" s="14">
-        <v>4435.3725877679108</v>
+        <v>4435.3725877679126</v>
       </c>
       <c r="F1200" s="13">
         <v>1429.8607</v>
@@ -55107,7 +55107,7 @@
         <v>5125.1875535419204</v>
       </c>
       <c r="I1200" s="14">
-        <v>4119.7835060629877</v>
+        <v>4119.7835060629886</v>
       </c>
       <c r="J1200" s="13">
         <v>5175.8775999999998</v>
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551776</v>
+        <v>4487.7143253551785</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55183,7 +55183,7 @@
         <v>5782.081258662286</v>
       </c>
       <c r="I1202" s="14">
-        <v>5126.6494289859611</v>
+        <v>5126.6494289859602</v>
       </c>
       <c r="J1202" s="13">
         <v>5202.1442999999999</v>
@@ -55209,7 +55209,7 @@
         <v>4938.8935854309739</v>
       </c>
       <c r="E1203" s="14">
-        <v>4717.3485788226399</v>
+        <v>4717.3485788226408</v>
       </c>
       <c r="F1203" s="13">
         <v>1626.8607999999999</v>
@@ -55221,7 +55221,7 @@
         <v>4417.2715705925184</v>
       </c>
       <c r="I1203" s="14">
-        <v>5085.9482018840399</v>
+        <v>5085.9482018840408</v>
       </c>
       <c r="J1203" s="13">
         <v>8027.7326999999996</v>
@@ -55285,7 +55285,7 @@
         <v>4424.3978008967133</v>
       </c>
       <c r="E1205" s="14">
-        <v>4552.8231579350831</v>
+        <v>4552.8231579350822</v>
       </c>
       <c r="F1205" s="13">
         <v>1070.8937000000001</v>
@@ -55335,7 +55335,7 @@
         <v>3932.5340059065734</v>
       </c>
       <c r="I1206" s="14">
-        <v>4333.5986404219711</v>
+        <v>4333.5986404219702</v>
       </c>
       <c r="J1206" s="13">
         <v>6089.9108999999999</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629657</v>
+        <v>4315.8033455629638</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55449,7 +55449,7 @@
         <v>5232.7977567123598</v>
       </c>
       <c r="I1209" s="14">
-        <v>4726.9079889175373</v>
+        <v>4726.9079889175364</v>
       </c>
       <c r="J1209" s="13">
         <v>6374.9992000000002</v>
@@ -55601,7 +55601,7 @@
         <v>5196.6505136827682</v>
       </c>
       <c r="I1213" s="14">
-        <v>5637.2144957550399</v>
+        <v>5637.214495755039</v>
       </c>
       <c r="J1213" s="13">
         <v>10879.186799999999</v>
@@ -55639,7 +55639,7 @@
         <v>5483.9420094229508</v>
       </c>
       <c r="I1214" s="14">
-        <v>5618.8491234155326</v>
+        <v>5618.8491234155317</v>
       </c>
       <c r="J1214" s="13">
         <v>8807.2849999999999</v>
@@ -55715,7 +55715,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="14">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="13">
         <v>3920.1588999999999</v>
@@ -55741,7 +55741,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.1866360758077</v>
+        <v>4706.1866360758067</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.4088847985458</v>
+        <v>4736.4088847985449</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55817,7 +55817,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="14">
-        <v>4756.2469293655349</v>
+        <v>4756.246929365534</v>
       </c>
       <c r="F1219" s="13">
         <v>1866.9058</v>
@@ -55855,7 +55855,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.2967738120533</v>
+        <v>4663.2967738120524</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55931,7 +55931,7 @@
         <v>4849.8313970697627</v>
       </c>
       <c r="E1222" s="14">
-        <v>4695.6837921024489</v>
+        <v>4695.6837921024498</v>
       </c>
       <c r="F1222" s="13">
         <v>1081.6878999999999</v>
@@ -56007,7 +56007,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="14">
-        <v>4673.0080443035031</v>
+        <v>4673.008044303504</v>
       </c>
       <c r="F1224" s="13">
         <v>678.69989999999996</v>
@@ -56235,7 +56235,7 @@
         <v>5223.7943789585233</v>
       </c>
       <c r="E1230" s="14">
-        <v>5028.6483389254827</v>
+        <v>5028.6483389254818</v>
       </c>
       <c r="F1230" s="13">
         <v>186.41309999999999</v>
@@ -56273,7 +56273,7 @@
         <v>4742.3293933814848</v>
       </c>
       <c r="E1231" s="14">
-        <v>4961.5475609355035</v>
+        <v>4961.5475609355053</v>
       </c>
       <c r="F1231" s="13">
         <v>1023.9116</v>
@@ -56627,7 +56627,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="14">
-        <v>6497.7712544712294</v>
+        <v>6497.7712544712285</v>
       </c>
       <c r="J1240" s="13">
         <v>2117.8483999999999</v>
@@ -56704,7 +56704,7 @@
         <v>6080.2534679336923</v>
       </c>
       <c r="I1242" s="14">
-        <v>6193.667101883063</v>
+        <v>6193.6671018830639</v>
       </c>
       <c r="J1242" s="13">
         <v>8322.0208999999995</v>
@@ -56742,7 +56742,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="14">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="13">
         <v>15660.4136</v>
@@ -56780,7 +56780,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="14">
-        <v>6056.50708400844</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="13">
         <v>8281.8516999999993</v>
@@ -56818,7 +56818,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="14">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="13">
         <v>4208.4350999999997</v>
@@ -56894,7 +56894,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="14">
-        <v>5394.2932473875317</v>
+        <v>5394.2932473875308</v>
       </c>
       <c r="J1247" s="13">
         <v>13767.5789</v>
@@ -56911,16 +56911,16 @@
         <v>45934</v>
       </c>
       <c r="B1248" s="13">
-        <v>34873.983800000002</v>
+        <v>34853.894699999997</v>
       </c>
       <c r="C1248" s="13">
         <v>7466.8144000000002</v>
       </c>
       <c r="D1248" s="13">
-        <v>4670.5304205766788</v>
+        <v>4667.8399693448919</v>
       </c>
       <c r="E1248" s="14">
-        <v>5065.8153730393024</v>
+        <v>5065.2996815301831</v>
       </c>
       <c r="F1248" s="13">
         <v>1018.4743</v>
@@ -56941,7 +56941,7 @@
       <c r="L1248" s="13"/>
       <c r="M1248" s="13"/>
       <c r="N1248" s="15">
-        <v>40652.730500000005</v>
+        <v>40632.641399999993</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15.75" customHeight="1">
@@ -56958,7 +56958,7 @@
         <v>4382.862889525768</v>
       </c>
       <c r="E1249" s="14">
-        <v>4973.8298838492292</v>
+        <v>4973.291908461707</v>
       </c>
       <c r="F1249" s="13">
         <v>1116.6591000000001</v>
@@ -56996,7 +56996,7 @@
         <v>4934.9565061163757</v>
       </c>
       <c r="E1250" s="14">
-        <v>4942.2423524485912</v>
+        <v>4941.6959502025229</v>
       </c>
       <c r="F1250" s="13">
         <v>1339.0517</v>
@@ -57034,7 +57034,7 @@
         <v>5740.1822979010431</v>
       </c>
       <c r="E1251" s="14">
-        <v>5020.3806389027459</v>
+        <v>5019.8233844895904</v>
       </c>
       <c r="F1251" s="13">
         <v>1154.2166999999999</v>
@@ -57072,7 +57072,7 @@
         <v>4714.9565842583061</v>
       </c>
       <c r="E1252" s="14">
-        <v>4993.621065652168</v>
+        <v>4993.0709753777355</v>
       </c>
       <c r="F1252" s="13">
         <v>979.83450000000005</v>
@@ -57084,7 +57084,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="14">
-        <v>5768.2127381128475</v>
+        <v>5768.2127381128485</v>
       </c>
       <c r="J1252" s="13">
         <v>10772.394200000001</v>
@@ -57148,7 +57148,7 @@
         <v>5052.5622460156374</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.0743577359699</v>
+        <v>5308.074357735969</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57160,7 +57160,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="14">
-        <v>5620.2491328335427</v>
+        <v>5620.2491328335436</v>
       </c>
       <c r="J1254" s="13">
         <v>10669.626700000001</v>
@@ -57186,7 +57186,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="14">
-        <v>5579.2676534264356</v>
+        <v>5579.2676534264347</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57312,7 +57312,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="14">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="13">
         <v>10585.9136</v>
@@ -57353,13 +57353,13 @@
         <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="13">
-        <v>14233.2034</v>
+        <v>14233.6034</v>
       </c>
       <c r="K1259" s="13"/>
       <c r="L1259" s="13"/>
       <c r="M1259" s="13"/>
       <c r="N1259" s="15">
-        <v>81477.36540000001</v>
+        <v>81477.765400000004</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57388,7 +57388,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="14">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="13">
         <v>7543.9057000000003</v>
@@ -57467,13 +57467,13 @@
         <v>6331.7504578958606</v>
       </c>
       <c r="J1262" s="13">
-        <v>7785.9323000000004</v>
+        <v>7785.9663</v>
       </c>
       <c r="K1262" s="13"/>
       <c r="L1262" s="13"/>
       <c r="M1262" s="13"/>
       <c r="N1262" s="15">
-        <v>40636.802500000005</v>
+        <v>40636.836500000005</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57519,16 +57519,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="13">
-        <v>41413.846899999997</v>
+        <v>41413.847800000003</v>
       </c>
       <c r="C1264" s="13">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="13">
-        <v>5650.2314142185578</v>
+        <v>5650.2315370086071</v>
       </c>
       <c r="E1264" s="14">
-        <v>5402.2334349190778</v>
+        <v>5402.2334607787343</v>
       </c>
       <c r="F1264" s="13">
         <v>1803.3380999999999</v>
@@ -57549,7 +57549,7 @@
       <c r="L1264" s="13"/>
       <c r="M1264" s="13"/>
       <c r="N1264" s="15">
-        <v>49489.243699999999</v>
+        <v>49489.244600000005</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57566,7 +57566,7 @@
         <v>5216.5845279451496</v>
       </c>
       <c r="E1265" s="23">
-        <v>5317.8972086941903</v>
+        <v>5317.8972310993004</v>
       </c>
       <c r="F1265" s="22">
         <v>2790.8292999999999</v>
@@ -57601,7 +57601,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="23">
-        <v>5321.321954260301</v>
+        <v>5321.3219757096722</v>
       </c>
       <c r="F1266" s="22">
         <v>1799.4023999999999</v>
@@ -57627,16 +57627,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="22">
-        <v>77854.597699999998</v>
+        <v>77877.121700000003</v>
       </c>
       <c r="C1267" s="22">
         <v>13633.935799999999</v>
       </c>
       <c r="D1267" s="22">
-        <v>5710.3538436788012</v>
+        <v>5712.0058978127217</v>
       </c>
       <c r="E1267" s="23">
-        <v>5386.9835567087621</v>
+        <v>5387.4485593568743</v>
       </c>
       <c r="F1267" s="22">
         <v>1828.6121000000001</v>
@@ -57651,10 +57651,10 @@
         <v>6569.7313381807944</v>
       </c>
       <c r="J1267" s="22">
-        <v>13246.216200000001</v>
+        <v>13246.2163</v>
       </c>
       <c r="N1267" s="21">
-        <v>92929.426000000007</v>
+        <v>92951.950100000002</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57662,16 +57662,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="22">
-        <v>65267.608200000002</v>
+        <v>65265.4516</v>
       </c>
       <c r="C1268" s="22">
         <v>12718.373299999999</v>
       </c>
       <c r="D1268" s="22">
-        <v>5131.7575495287601</v>
+        <v>5131.5879838186547</v>
       </c>
       <c r="E1268" s="23">
-        <v>5331.3245727394215</v>
+        <v>5331.7231812568798</v>
       </c>
       <c r="F1268" s="22">
         <v>1326.8929000000001</v>
@@ -57683,13 +57683,13 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="23">
-        <v>6548.0752800166811</v>
+        <v>6548.0752800166792</v>
       </c>
       <c r="J1268" s="22">
         <v>14843.3467</v>
       </c>
       <c r="N1268" s="21">
-        <v>81437.847800000003</v>
+        <v>81435.691200000001</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57706,7 +57706,7 @@
         <v>5301.0343445399049</v>
       </c>
       <c r="E1269" s="23">
-        <v>5316.6423104439555</v>
+        <v>5317.0450907326212</v>
       </c>
       <c r="F1269" s="22">
         <v>1050.4068</v>
@@ -57718,7 +57718,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="23">
-        <v>6498.4408173314478</v>
+        <v>6498.4408173314459</v>
       </c>
       <c r="J1269" s="22">
         <v>8128.4333999999999</v>
@@ -57741,7 +57741,7 @@
         <v>5929.8243179066494</v>
       </c>
       <c r="E1270" s="23">
-        <v>5431.3747097650958</v>
+        <v>5431.7720133038956</v>
       </c>
       <c r="F1270" s="22">
         <v>1172.5832</v>
@@ -57756,10 +57756,10 @@
         <v>7222.0356794484687</v>
       </c>
       <c r="J1270" s="22">
-        <v>6080.7852999999996</v>
+        <v>6117.0985000000001</v>
       </c>
       <c r="N1270" s="21">
-        <v>64760.097899999993</v>
+        <v>64796.411099999998</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1">
@@ -57767,16 +57767,16 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="22">
-        <v>65320.845699999998</v>
+        <v>65146.041700000002</v>
       </c>
       <c r="C1271" s="22">
-        <v>11979.2505</v>
+        <v>11941.232099999999</v>
       </c>
       <c r="D1271" s="22">
-        <v>5452.8324372213428</v>
+        <v>5455.5544314392819</v>
       </c>
       <c r="E1271" s="23">
-        <v>5410.9762416246313</v>
+        <v>5411.5619252211218</v>
       </c>
       <c r="F1271" s="22">
         <v>1808.0657000000001</v>
@@ -57788,13 +57788,13 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="23">
-        <v>7489.2724524389059</v>
+        <v>7489.2724524389041</v>
       </c>
       <c r="J1271" s="22">
-        <v>9586.0277000000006</v>
+        <v>9610.9421999999995</v>
       </c>
       <c r="N1271" s="21">
-        <v>76714.939100000003</v>
+        <v>76565.049599999998</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1">
@@ -57802,34 +57802,34 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="22">
-        <v>36047.857900000003</v>
+        <v>37610.071199999998</v>
       </c>
       <c r="C1272" s="22">
-        <v>5910.6274999999996</v>
+        <v>6205.7831999999999</v>
       </c>
       <c r="D1272" s="22">
-        <v>6098.8207935621067</v>
+        <v>6060.4874498355011</v>
       </c>
       <c r="E1272" s="23">
-        <v>5603.2909134213978</v>
+        <v>5602.0731551966028</v>
       </c>
       <c r="F1272" s="22">
-        <v>677.63319999999999</v>
+        <v>697.31119999999999</v>
       </c>
       <c r="G1272" s="22">
-        <v>100.11669999999999</v>
+        <v>102.6143</v>
       </c>
       <c r="H1272" s="22">
-        <v>6768.4332384107747</v>
+        <v>6795.4583328054659</v>
       </c>
       <c r="I1272" s="23">
-        <v>7302.288742792538</v>
+        <v>7304.0585980662427</v>
       </c>
       <c r="J1272" s="22">
-        <v>7886.5470999999998</v>
+        <v>8073.0517</v>
       </c>
       <c r="N1272" s="21">
-        <v>44612.038200000003</v>
+        <v>46380.434099999999</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1">
@@ -57837,34 +57837,34 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="22">
-        <v>48711.053200000002</v>
+        <v>61776.260399999999</v>
       </c>
       <c r="C1273" s="22">
-        <v>8233.5599000000002</v>
+        <v>10757.154200000001</v>
       </c>
       <c r="D1273" s="22">
-        <v>5916.159448843021</v>
+        <v>5742.8069962964737</v>
       </c>
       <c r="E1273" s="23">
-        <v>5703.3050193110284</v>
+        <v>5671.0788489388178</v>
       </c>
       <c r="F1273" s="22">
-        <v>720.25890000000004</v>
+        <v>700.99080000000004</v>
       </c>
       <c r="G1273" s="22">
-        <v>114.3421</v>
+        <v>111.7256</v>
       </c>
       <c r="H1273" s="22">
-        <v>6299.1575281545465</v>
+        <v>6274.2182633165548</v>
       </c>
       <c r="I1273" s="23">
-        <v>7159.4977018096261</v>
+        <v>7161.2268208604146</v>
       </c>
       <c r="J1273" s="22">
-        <v>9724.2219999999998</v>
+        <v>10894.0506</v>
       </c>
       <c r="N1273" s="21">
-        <v>59155.534100000004</v>
+        <v>73371.301800000001</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1">
@@ -57872,34 +57872,69 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="22">
-        <v>23041.115399999999</v>
+        <v>43282.447999999997</v>
       </c>
       <c r="C1274" s="22">
-        <v>3747.3872999999999</v>
+        <v>7938.0126</v>
       </c>
       <c r="D1274" s="22">
-        <v>6148.5812795490874</v>
+        <v>5452.5547112384274</v>
       </c>
       <c r="E1274" s="23">
-        <v>5729.6463487492692</v>
+        <v>5598.9494007571411</v>
       </c>
       <c r="F1274" s="22">
-        <v>90.856499999999997</v>
+        <v>609.18629999999996</v>
       </c>
       <c r="G1274" s="22">
-        <v>18.032800000000002</v>
+        <v>142.2978</v>
       </c>
       <c r="H1274" s="22">
-        <v>5038.4022447983671</v>
+        <v>4281.0661865468046</v>
       </c>
       <c r="I1274" s="23">
-        <v>7230.4853929932488</v>
+        <v>6671.9395073139312</v>
       </c>
       <c r="J1274" s="22">
-        <v>3315.7556</v>
+        <v>6379.0343000000003</v>
       </c>
       <c r="N1274" s="21">
-        <v>26447.727499999997</v>
+        <v>50270.668599999997</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1275" s="20">
+        <v>46123</v>
+      </c>
+      <c r="B1275" s="22">
+        <v>22836.638299999999</v>
+      </c>
+      <c r="C1275" s="22">
+        <v>3469.7655</v>
+      </c>
+      <c r="D1275" s="22">
+        <v>6581.608555390846</v>
+      </c>
+      <c r="E1275" s="23">
+        <v>5734.8751099279998</v>
+      </c>
+      <c r="F1275" s="22">
+        <v>1151.3224</v>
+      </c>
+      <c r="G1275" s="22">
+        <v>173.50749999999999</v>
+      </c>
+      <c r="H1275" s="22">
+        <v>6635.5771364350239</v>
+      </c>
+      <c r="I1275" s="23">
+        <v>6005.0652965169047</v>
+      </c>
+      <c r="J1275" s="22">
+        <v>2187.5484999999999</v>
+      </c>
+      <c r="N1275" s="21">
+        <v>26175.5092</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49109C22-53D2-476E-801E-4C0CD9650A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFB8E1A-B247-4BCD-936F-DEC9D6223A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1275"/>
+  <dimension ref="A1:W1276"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="20" customWidth="1"/>
@@ -53499,7 +53499,7 @@
         <v>4150.9922145963383</v>
       </c>
       <c r="E1158" s="14">
-        <v>3840.8705315087991</v>
+        <v>3840.8705315088</v>
       </c>
       <c r="F1158" s="13">
         <v>882.2903</v>
@@ -53549,7 +53549,7 @@
         <v>3982.0975670205294</v>
       </c>
       <c r="I1159" s="14">
-        <v>3617.6613635639042</v>
+        <v>3617.6613635639046</v>
       </c>
       <c r="J1159" s="13">
         <v>6212.6449000000002</v>
@@ -53651,7 +53651,7 @@
         <v>4066.2996598472291</v>
       </c>
       <c r="E1162" s="14">
-        <v>3926.2226648625219</v>
+        <v>3926.2226648625228</v>
       </c>
       <c r="F1162" s="13">
         <v>1349.8824999999999</v>
@@ -53727,7 +53727,7 @@
         <v>4274.3049517318423</v>
       </c>
       <c r="E1164" s="14">
-        <v>4101.7200448367421</v>
+        <v>4101.720044836743</v>
       </c>
       <c r="F1164" s="13">
         <v>902.06470000000002</v>
@@ -53739,7 +53739,7 @@
         <v>3294.3855571640811</v>
       </c>
       <c r="I1164" s="14">
-        <v>3579.4806019611092</v>
+        <v>3579.4806019611101</v>
       </c>
       <c r="J1164" s="13">
         <v>14285.5708</v>
@@ -53765,7 +53765,7 @@
         <v>4422.3044460821966</v>
       </c>
       <c r="E1165" s="14">
-        <v>4180.3219217309879</v>
+        <v>4180.3219217309888</v>
       </c>
       <c r="F1165" s="13">
         <v>1064.4956999999999</v>
@@ -53841,7 +53841,7 @@
         <v>3950.294345928874</v>
       </c>
       <c r="E1167" s="14">
-        <v>4171.8558460563499</v>
+        <v>4171.855846056349</v>
       </c>
       <c r="F1167" s="13">
         <v>2041.8347000000001</v>
@@ -54107,7 +54107,7 @@
         <v>4351.7719768865618</v>
       </c>
       <c r="E1174" s="14">
-        <v>3939.3430114280172</v>
+        <v>3939.3430114280163</v>
       </c>
       <c r="F1174" s="13">
         <v>625.44079999999997</v>
@@ -54157,7 +54157,7 @@
         <v>3165.986834005897</v>
       </c>
       <c r="I1175" s="14">
-        <v>3345.9193035632725</v>
+        <v>3345.9193035632734</v>
       </c>
       <c r="J1175" s="13">
         <v>18463.542600000001</v>
@@ -54385,7 +54385,7 @@
         <v>3932.1869092178767</v>
       </c>
       <c r="I1181" s="14">
-        <v>3763.2741964818456</v>
+        <v>3763.2741964818451</v>
       </c>
       <c r="J1181" s="13">
         <v>7024.5267000000003</v>
@@ -54423,7 +54423,7 @@
         <v>4435.1671265846417</v>
       </c>
       <c r="I1182" s="14">
-        <v>3815.6421043550654</v>
+        <v>3815.6421043550649</v>
       </c>
       <c r="J1182" s="13">
         <v>6999.7999</v>
@@ -54461,7 +54461,7 @@
         <v>5020.0771469761667</v>
       </c>
       <c r="I1183" s="14">
-        <v>3892.3953212090469</v>
+        <v>3892.3953212090473</v>
       </c>
       <c r="J1183" s="13">
         <v>5037.4709000000003</v>
@@ -54563,7 +54563,7 @@
         <v>3921.1801257461875</v>
       </c>
       <c r="E1186" s="14">
-        <v>4103.7917850861204</v>
+        <v>4103.7917850861213</v>
       </c>
       <c r="F1186" s="13">
         <v>1199.8832</v>
@@ -54575,7 +54575,7 @@
         <v>4393.5575388702919</v>
       </c>
       <c r="I1186" s="14">
-        <v>4445.0065612912513</v>
+        <v>4445.0065612912522</v>
       </c>
       <c r="J1186" s="13">
         <v>7294.8577999999998</v>
@@ -54601,7 +54601,7 @@
         <v>4366.3367641502828</v>
       </c>
       <c r="E1187" s="14">
-        <v>4240.9406009288678</v>
+        <v>4240.9406009288687</v>
       </c>
       <c r="F1187" s="13">
         <v>748.68579999999997</v>
@@ -54613,7 +54613,7 @@
         <v>4806.1907118779418</v>
       </c>
       <c r="I1187" s="14">
-        <v>4604.0956192242547</v>
+        <v>4604.0956192242566</v>
       </c>
       <c r="J1187" s="13">
         <v>21194.6531</v>
@@ -54727,7 +54727,7 @@
         <v>4531.757943331254</v>
       </c>
       <c r="I1190" s="14">
-        <v>4095.695696255355</v>
+        <v>4095.6956962553541</v>
       </c>
       <c r="J1190" s="13">
         <v>5596.1341000000002</v>
@@ -54765,7 +54765,7 @@
         <v>3350.0403096116738</v>
       </c>
       <c r="I1191" s="14">
-        <v>3875.9174025958691</v>
+        <v>3875.9174025958678</v>
       </c>
       <c r="J1191" s="13">
         <v>17500.0933</v>
@@ -55095,7 +55095,7 @@
         <v>4513.7009686452229</v>
       </c>
       <c r="E1200" s="14">
-        <v>4435.3725877679126</v>
+        <v>4435.3725877679108</v>
       </c>
       <c r="F1200" s="13">
         <v>1429.8607</v>
@@ -55133,7 +55133,7 @@
         <v>4458.3467251750426</v>
       </c>
       <c r="E1201" s="14">
-        <v>4487.7143253551785</v>
+        <v>4487.7143253551776</v>
       </c>
       <c r="F1201" s="13">
         <v>1677.1370999999999</v>
@@ -55221,7 +55221,7 @@
         <v>4417.2715705925184</v>
       </c>
       <c r="I1203" s="14">
-        <v>5085.9482018840408</v>
+        <v>5085.9482018840399</v>
       </c>
       <c r="J1203" s="13">
         <v>8027.7326999999996</v>
@@ -55373,7 +55373,7 @@
         <v>4145.9867547787508</v>
       </c>
       <c r="I1207" s="14">
-        <v>4315.8033455629638</v>
+        <v>4315.8033455629666</v>
       </c>
       <c r="J1207" s="13">
         <v>8213.6905999999999</v>
@@ -55411,7 +55411,7 @@
         <v>4947.3851972485918</v>
       </c>
       <c r="I1208" s="14">
-        <v>4350.8974691131998</v>
+        <v>4350.8974691132007</v>
       </c>
       <c r="J1208" s="13">
         <v>9287.4572000000007</v>
@@ -55601,7 +55601,7 @@
         <v>5196.6505136827682</v>
       </c>
       <c r="I1213" s="14">
-        <v>5637.214495755039</v>
+        <v>5637.2144957550399</v>
       </c>
       <c r="J1213" s="13">
         <v>10879.186799999999</v>
@@ -55639,7 +55639,7 @@
         <v>5483.9420094229508</v>
       </c>
       <c r="I1214" s="14">
-        <v>5618.8491234155317</v>
+        <v>5618.8491234155326</v>
       </c>
       <c r="J1214" s="13">
         <v>8807.2849999999999</v>
@@ -55715,7 +55715,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="14">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="13">
         <v>3920.1588999999999</v>
@@ -55741,7 +55741,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="14">
-        <v>4706.1866360758067</v>
+        <v>4706.1866360758077</v>
       </c>
       <c r="F1217" s="13">
         <v>1668.2316000000001</v>
@@ -55779,7 +55779,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="14">
-        <v>4736.4088847985449</v>
+        <v>4736.4088847985458</v>
       </c>
       <c r="F1218" s="13">
         <v>1098.2744</v>
@@ -55817,7 +55817,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="14">
-        <v>4756.246929365534</v>
+        <v>4756.2469293655349</v>
       </c>
       <c r="F1219" s="13">
         <v>1866.9058</v>
@@ -55855,7 +55855,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="14">
-        <v>4663.2967738120524</v>
+        <v>4663.2967738120533</v>
       </c>
       <c r="F1220" s="13">
         <v>779.47170000000006</v>
@@ -55931,7 +55931,7 @@
         <v>4849.8313970697627</v>
       </c>
       <c r="E1222" s="14">
-        <v>4695.6837921024498</v>
+        <v>4695.6837921024489</v>
       </c>
       <c r="F1222" s="13">
         <v>1081.6878999999999</v>
@@ -56007,7 +56007,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="14">
-        <v>4673.008044303504</v>
+        <v>4673.0080443035031</v>
       </c>
       <c r="F1224" s="13">
         <v>678.69989999999996</v>
@@ -56112,16 +56112,16 @@
         <v>45787</v>
       </c>
       <c r="B1227" s="13">
-        <v>70760.703800000003</v>
+        <v>70760.958700000003</v>
       </c>
       <c r="C1227" s="13">
         <v>14282.969499999999</v>
       </c>
       <c r="D1227" s="13">
-        <v>4954.2011414363096</v>
+        <v>4954.2189878652343</v>
       </c>
       <c r="E1227" s="14">
-        <v>4890.5786873188008</v>
+        <v>4890.5844008503273</v>
       </c>
       <c r="F1227" s="13">
         <v>699.97680000000003</v>
@@ -56142,7 +56142,7 @@
       <c r="L1227" s="13"/>
       <c r="M1227" s="13"/>
       <c r="N1227" s="15">
-        <v>81063.886400000003</v>
+        <v>81064.141300000003</v>
       </c>
     </row>
     <row r="1228" spans="1:14" ht="15.75" customHeight="1">
@@ -56159,7 +56159,7 @@
         <v>5173.8323341700607</v>
       </c>
       <c r="E1228" s="14">
-        <v>5048.2589945889222</v>
+        <v>5048.2639462738034</v>
       </c>
       <c r="F1228" s="13">
         <v>677.62339999999995</v>
@@ -56188,16 +56188,16 @@
         <v>45801</v>
       </c>
       <c r="B1229" s="13">
-        <v>54514.881399999998</v>
+        <v>54495.981399999997</v>
       </c>
       <c r="C1229" s="13">
         <v>10629.917100000001</v>
       </c>
       <c r="D1229" s="13">
-        <v>5128.4389978920908</v>
+        <v>5126.6609971962998</v>
       </c>
       <c r="E1229" s="14">
-        <v>4983.8961415709</v>
+        <v>4983.5449072703941</v>
       </c>
       <c r="F1229" s="13">
         <v>465.10070000000002</v>
@@ -56218,7 +56218,7 @@
       <c r="L1229" s="13"/>
       <c r="M1229" s="13"/>
       <c r="N1229" s="15">
-        <v>66469.655100000004</v>
+        <v>66450.755099999995</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56235,7 +56235,7 @@
         <v>5223.7943789585233</v>
       </c>
       <c r="E1230" s="14">
-        <v>5028.6483389254818</v>
+        <v>5028.2857750507765</v>
       </c>
       <c r="F1230" s="13">
         <v>186.41309999999999</v>
@@ -56273,7 +56273,7 @@
         <v>4742.3293933814848</v>
       </c>
       <c r="E1231" s="14">
-        <v>4961.5475609355053</v>
+        <v>4961.2148642311049</v>
       </c>
       <c r="F1231" s="13">
         <v>1023.9116</v>
@@ -56311,7 +56311,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="14">
-        <v>4909.9621204831556</v>
+        <v>4909.5927451670368</v>
       </c>
       <c r="F1232" s="13">
         <v>1933.1436000000001</v>
@@ -56349,7 +56349,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="14">
-        <v>4836.3955854983897</v>
+        <v>4835.9999497856616</v>
       </c>
       <c r="F1233" s="13">
         <v>910.61059999999998</v>
@@ -56416,16 +56416,16 @@
         <v>45843</v>
       </c>
       <c r="B1235" s="13">
-        <v>72125.569600000003</v>
+        <v>72103.003299999997</v>
       </c>
       <c r="C1235" s="13">
         <v>14071.575000000001</v>
       </c>
       <c r="D1235" s="13">
-        <v>5125.621659266998</v>
+        <v>5124.017979508335</v>
       </c>
       <c r="E1235" s="14">
-        <v>4954.9135213242953</v>
+        <v>4954.4312381262243</v>
       </c>
       <c r="F1235" s="13">
         <v>1182.9712999999999</v>
@@ -56446,7 +56446,7 @@
       <c r="L1235" s="13"/>
       <c r="M1235" s="13"/>
       <c r="N1235" s="15">
-        <v>85909.796300000002</v>
+        <v>85887.23</v>
       </c>
     </row>
     <row r="1236" spans="1:15" ht="15.75" customHeight="1">
@@ -56463,7 +56463,7 @@
         <v>4468.4654995475621</v>
       </c>
       <c r="E1236" s="14">
-        <v>4833.0211489485209</v>
+        <v>4832.5311005118747</v>
       </c>
       <c r="F1236" s="13">
         <v>509.77510000000001</v>
@@ -56501,7 +56501,7 @@
         <v>5279.8066063917322</v>
       </c>
       <c r="E1237" s="14">
-        <v>4926.7513336432485</v>
+        <v>4926.2161250692443</v>
       </c>
       <c r="F1237" s="13">
         <v>770.73030000000006</v>
@@ -56530,16 +56530,16 @@
         <v>45864</v>
       </c>
       <c r="B1238" s="13">
-        <v>47774.333599999998</v>
+        <v>47769.335400000004</v>
       </c>
       <c r="C1238" s="13">
         <v>8648.6777000000002</v>
       </c>
       <c r="D1238" s="13">
-        <v>5523.8887674123871</v>
+        <v>5523.3108524786403</v>
       </c>
       <c r="E1238" s="14">
-        <v>5021.4125766800344</v>
+        <v>5020.8021801328723</v>
       </c>
       <c r="F1238" s="13">
         <v>937.15679999999998</v>
@@ -56560,7 +56560,7 @@
       <c r="L1238" s="13"/>
       <c r="M1238" s="13"/>
       <c r="N1238" s="15">
-        <v>53730.3577</v>
+        <v>53725.359500000006</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56577,7 +56577,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="14">
-        <v>4983.8869191962531</v>
+        <v>4983.7742122093496</v>
       </c>
       <c r="F1239" s="13">
         <v>1951.8497</v>
@@ -56615,7 +56615,7 @@
         <v>5736.0102439994189</v>
       </c>
       <c r="E1240" s="14">
-        <v>5190.3220901089398</v>
+        <v>5190.1828701541526</v>
       </c>
       <c r="F1240" s="13">
         <v>690.66629999999998</v>
@@ -56627,7 +56627,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="14">
-        <v>6497.7712544712285</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="13">
         <v>2117.8483999999999</v>
@@ -56653,7 +56653,7 @@
         <v>5874.7159286822889</v>
       </c>
       <c r="E1241" s="14">
-        <v>5328.2110098593139</v>
+        <v>5328.0799505254308</v>
       </c>
       <c r="F1241" s="13">
         <v>356.61349999999999</v>
@@ -56692,7 +56692,7 @@
         <v>5270.233180814248</v>
       </c>
       <c r="E1242" s="14">
-        <v>5374.8324720174633</v>
+        <v>5374.7183914729967</v>
       </c>
       <c r="F1242" s="13">
         <v>1157.8651</v>
@@ -56704,7 +56704,7 @@
         <v>6080.2534679336923</v>
       </c>
       <c r="I1242" s="14">
-        <v>6193.6671018830639</v>
+        <v>6193.667101883063</v>
       </c>
       <c r="J1242" s="13">
         <v>8322.0208999999995</v>
@@ -56742,7 +56742,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="14">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="13">
         <v>15660.4136</v>
@@ -56780,7 +56780,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="14">
-        <v>6056.5070840084427</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="13">
         <v>8281.8516999999993</v>
@@ -56818,7 +56818,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="14">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072237</v>
       </c>
       <c r="J1245" s="13">
         <v>4208.4350999999997</v>
@@ -56894,7 +56894,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="14">
-        <v>5394.2932473875308</v>
+        <v>5394.2932473875317</v>
       </c>
       <c r="J1247" s="13">
         <v>13767.5789</v>
@@ -56949,16 +56949,16 @@
         <v>45941</v>
       </c>
       <c r="B1249" s="13">
-        <v>24109.8053</v>
+        <v>24109.5556</v>
       </c>
       <c r="C1249" s="13">
         <v>5500.9261999999999</v>
       </c>
       <c r="D1249" s="13">
-        <v>4382.862889525768</v>
+        <v>4382.8174971698409</v>
       </c>
       <c r="E1249" s="14">
-        <v>4973.291908461707</v>
+        <v>4973.2852216288347</v>
       </c>
       <c r="F1249" s="13">
         <v>1116.6591000000001</v>
@@ -56979,7 +56979,7 @@
       <c r="L1249" s="13"/>
       <c r="M1249" s="13"/>
       <c r="N1249" s="15">
-        <v>31426.863600000001</v>
+        <v>31426.6139</v>
       </c>
     </row>
     <row r="1250" spans="1:14" ht="15.75" customHeight="1">
@@ -56987,16 +56987,16 @@
         <v>45948</v>
       </c>
       <c r="B1250" s="13">
-        <v>48135.016499999998</v>
+        <v>48133.927000000003</v>
       </c>
       <c r="C1250" s="13">
         <v>9753.8886999999995</v>
       </c>
       <c r="D1250" s="13">
-        <v>4934.9565061163757</v>
+        <v>4934.8448070767918</v>
       </c>
       <c r="E1250" s="14">
-        <v>4941.6959502025229</v>
+        <v>4941.6595253807081</v>
       </c>
       <c r="F1250" s="13">
         <v>1339.0517</v>
@@ -57017,7 +57017,7 @@
       <c r="L1250" s="13"/>
       <c r="M1250" s="13"/>
       <c r="N1250" s="15">
-        <v>61911.450400000002</v>
+        <v>61910.3609</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1">
@@ -57025,16 +57025,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="13">
-        <v>54500.556900000003</v>
+        <v>54501.171399999999</v>
       </c>
       <c r="C1251" s="13">
         <v>9494.5689999999995</v>
       </c>
       <c r="D1251" s="13">
-        <v>5740.1822979010431</v>
+        <v>5740.2470191116627</v>
       </c>
       <c r="E1251" s="14">
-        <v>5019.8233844895904</v>
+        <v>5019.80328193282</v>
       </c>
       <c r="F1251" s="13">
         <v>1154.2166999999999</v>
@@ -57055,7 +57055,7 @@
       <c r="L1251" s="13"/>
       <c r="M1251" s="13"/>
       <c r="N1251" s="15">
-        <v>61074.474400000006</v>
+        <v>61075.088900000002</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57072,7 +57072,7 @@
         <v>4714.9565842583061</v>
       </c>
       <c r="E1252" s="14">
-        <v>4993.0709753777355</v>
+        <v>4993.0511312621757</v>
       </c>
       <c r="F1252" s="13">
         <v>979.83450000000005</v>
@@ -57101,16 +57101,16 @@
         <v>45969</v>
       </c>
       <c r="B1253" s="13">
-        <v>88069.229600000006</v>
+        <v>88062.250899999999</v>
       </c>
       <c r="C1253" s="13">
         <v>15503.728800000001</v>
       </c>
       <c r="D1253" s="13">
-        <v>5680.5192309607482</v>
+        <v>5680.0691005379304</v>
       </c>
       <c r="E1253" s="14">
-        <v>5202.890559252688</v>
+        <v>5202.7366058457519</v>
       </c>
       <c r="F1253" s="13">
         <v>3024.5275999999999</v>
@@ -57131,7 +57131,7 @@
       <c r="L1253" s="13"/>
       <c r="M1253" s="13"/>
       <c r="N1253" s="15">
-        <v>103450.38770000001</v>
+        <v>103443.409</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1">
@@ -57139,16 +57139,16 @@
         <v>45976</v>
       </c>
       <c r="B1254" s="13">
-        <v>45131.583299999998</v>
+        <v>45129.964399999997</v>
       </c>
       <c r="C1254" s="13">
         <v>8932.4151000000002</v>
       </c>
       <c r="D1254" s="13">
-        <v>5052.5622460156374</v>
+        <v>5052.3810072373371</v>
       </c>
       <c r="E1254" s="14">
-        <v>5308.074357735969</v>
+        <v>5307.9001069484375</v>
       </c>
       <c r="F1254" s="13">
         <v>2124.1673000000001</v>
@@ -57160,7 +57160,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="14">
-        <v>5620.2491328335436</v>
+        <v>5620.2491328335427</v>
       </c>
       <c r="J1254" s="13">
         <v>10669.626700000001</v>
@@ -57169,7 +57169,7 @@
       <c r="L1254" s="13"/>
       <c r="M1254" s="13"/>
       <c r="N1254" s="15">
-        <v>57925.3773</v>
+        <v>57923.758399999999</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1">
@@ -57186,7 +57186,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="14">
-        <v>5579.2676534264347</v>
+        <v>5579.111390511267</v>
       </c>
       <c r="F1255" s="13">
         <v>2745.8622</v>
@@ -57198,7 +57198,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="14">
-        <v>5979.7288428128713</v>
+        <v>5979.7288428128722</v>
       </c>
       <c r="J1255" s="13">
         <v>12450.415499999999</v>
@@ -57215,16 +57215,16 @@
         <v>45990</v>
       </c>
       <c r="B1256" s="13">
-        <v>64998.440499999997</v>
+        <v>64995.902499999997</v>
       </c>
       <c r="C1256" s="13">
         <v>12531.0414</v>
       </c>
       <c r="D1256" s="13">
-        <v>5186.9943147741897</v>
+        <v>5186.7917777368448</v>
       </c>
       <c r="E1256" s="14">
-        <v>5469.4125896506666</v>
+        <v>5469.2224665709509</v>
       </c>
       <c r="F1256" s="13">
         <v>3141.94</v>
@@ -57245,7 +57245,7 @@
       <c r="L1256" s="13"/>
       <c r="M1256" s="13"/>
       <c r="N1256" s="15">
-        <v>77291.176299999992</v>
+        <v>77288.638299999991</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57253,16 +57253,16 @@
         <v>45997</v>
       </c>
       <c r="B1257" s="13">
-        <v>68681.739700000006</v>
+        <v>68680.454599999997</v>
       </c>
       <c r="C1257" s="13">
         <v>13091.163</v>
       </c>
       <c r="D1257" s="13">
-        <v>5246.420023950508</v>
+        <v>5246.3218584933966</v>
       </c>
       <c r="E1257" s="14">
-        <v>5421.4698526025386</v>
+        <v>5421.2423751506794</v>
       </c>
       <c r="F1257" s="13">
         <v>2948.9110000000001</v>
@@ -57274,7 +57274,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="14">
-        <v>6858.778759653972</v>
+        <v>6858.7787596539711</v>
       </c>
       <c r="J1257" s="13">
         <v>6940.3462</v>
@@ -57283,7 +57283,7 @@
       <c r="L1257" s="13"/>
       <c r="M1257" s="13"/>
       <c r="N1257" s="15">
-        <v>78570.996899999998</v>
+        <v>78569.71179999999</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1">
@@ -57291,16 +57291,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="13">
-        <v>60363.868199999997</v>
+        <v>60363.653299999998</v>
       </c>
       <c r="C1258" s="13">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="13">
-        <v>4974.8827540768425</v>
+        <v>4974.8650431127226</v>
       </c>
       <c r="E1258" s="14">
-        <v>5452.078657150636</v>
+        <v>5452.0029951653187</v>
       </c>
       <c r="F1258" s="13">
         <v>4360.9017999999996</v>
@@ -57312,16 +57312,16 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="14">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="13">
-        <v>10585.9136</v>
+        <v>10586.2176</v>
       </c>
       <c r="K1258" s="13"/>
       <c r="L1258" s="13"/>
       <c r="M1258" s="13"/>
       <c r="N1258" s="15">
-        <v>75310.683599999989</v>
+        <v>75310.772700000001</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57329,16 +57329,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="13">
-        <v>64229.735000000001</v>
+        <v>64210.6005</v>
       </c>
       <c r="C1259" s="13">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="13">
-        <v>5454.5014110385446</v>
+        <v>5452.8764758391462</v>
       </c>
       <c r="E1259" s="14">
-        <v>5182.1640751857058</v>
+        <v>5181.7224945699163</v>
       </c>
       <c r="F1259" s="13">
         <v>3014.4270000000001</v>
@@ -57359,7 +57359,7 @@
       <c r="L1259" s="13"/>
       <c r="M1259" s="13"/>
       <c r="N1259" s="15">
-        <v>81477.765400000004</v>
+        <v>81458.630900000004</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57367,16 +57367,16 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="13">
-        <v>60697.535499999998</v>
+        <v>60694.124900000003</v>
       </c>
       <c r="C1260" s="13">
         <v>11702.9162</v>
       </c>
       <c r="D1260" s="13">
-        <v>5186.5308152851685</v>
+        <v>5186.239383650377</v>
       </c>
       <c r="E1260" s="14">
-        <v>5209.2184792004828</v>
+        <v>5208.7499845979037</v>
       </c>
       <c r="F1260" s="13">
         <v>2192.3276999999998</v>
@@ -57388,7 +57388,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="14">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="13">
         <v>7543.9057000000003</v>
@@ -57397,7 +57397,7 @@
       <c r="L1260" s="13"/>
       <c r="M1260" s="13"/>
       <c r="N1260" s="15">
-        <v>70433.768899999995</v>
+        <v>70430.358300000007</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57405,16 +57405,16 @@
         <v>46025</v>
       </c>
       <c r="B1261" s="13">
-        <v>36129.798799999997</v>
+        <v>36110.9035</v>
       </c>
       <c r="C1261" s="13">
         <v>6783.5308000000005</v>
       </c>
       <c r="D1261" s="13">
-        <v>5326.105219423489</v>
+        <v>5323.3197525984551</v>
       </c>
       <c r="E1261" s="14">
-        <v>5254.8897023819372</v>
+        <v>5253.9853250015803</v>
       </c>
       <c r="F1261" s="13">
         <v>1259.8376000000001</v>
@@ -57435,7 +57435,7 @@
       <c r="L1261" s="13"/>
       <c r="M1261" s="13"/>
       <c r="N1261" s="15">
-        <v>52802.219899999996</v>
+        <v>52783.3246</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15.75" customHeight="1">
@@ -57443,16 +57443,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="13">
-        <v>31640.768100000001</v>
+        <v>31634.073</v>
       </c>
       <c r="C1262" s="13">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="13">
-        <v>5567.2435878972265</v>
+        <v>5566.0655743791112</v>
       </c>
       <c r="E1262" s="14">
-        <v>5255.4393130495018</v>
+        <v>5254.2861765485241</v>
       </c>
       <c r="F1262" s="13">
         <v>1210.1021000000001</v>
@@ -57473,7 +57473,7 @@
       <c r="L1262" s="13"/>
       <c r="M1262" s="13"/>
       <c r="N1262" s="15">
-        <v>40636.836500000005</v>
+        <v>40630.1414</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57490,7 +57490,7 @@
         <v>5220.8188843458129</v>
       </c>
       <c r="E1263" s="14">
-        <v>5334.9620230114951</v>
+        <v>5334.2599697386731</v>
       </c>
       <c r="F1263" s="13">
         <v>3212.6219999999998</v>
@@ -57519,16 +57519,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="13">
-        <v>41413.847800000003</v>
+        <v>41413.079299999998</v>
       </c>
       <c r="C1264" s="13">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="13">
-        <v>5650.2315370086071</v>
+        <v>5650.1266879504565</v>
       </c>
       <c r="E1264" s="14">
-        <v>5402.2334607787343</v>
+        <v>5401.4577715885225</v>
       </c>
       <c r="F1264" s="13">
         <v>1803.3380999999999</v>
@@ -57549,7 +57549,7 @@
       <c r="L1264" s="13"/>
       <c r="M1264" s="13"/>
       <c r="N1264" s="15">
-        <v>49489.244600000005</v>
+        <v>49488.4761</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57557,16 +57557,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="22">
-        <v>66743.979900000006</v>
+        <v>66743.524999999994</v>
       </c>
       <c r="C1265" s="22">
         <v>12794.5746</v>
       </c>
       <c r="D1265" s="22">
-        <v>5216.5845279451496</v>
+        <v>5216.5489738126962</v>
       </c>
       <c r="E1265" s="23">
-        <v>5317.8972310993004</v>
+        <v>5317.544425327882</v>
       </c>
       <c r="F1265" s="22">
         <v>2790.8292999999999</v>
@@ -57584,7 +57584,7 @@
         <v>8313.8631000000005</v>
       </c>
       <c r="N1265" s="21">
-        <v>77848.672300000006</v>
+        <v>77848.217399999994</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57601,7 +57601,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="23">
-        <v>5321.3219757096722</v>
+        <v>5321.2351415015792</v>
       </c>
       <c r="F1266" s="22">
         <v>1799.4023999999999</v>
@@ -57627,16 +57627,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="22">
-        <v>77877.121700000003</v>
+        <v>77876.820699999997</v>
       </c>
       <c r="C1267" s="22">
         <v>13633.935799999999</v>
       </c>
       <c r="D1267" s="22">
-        <v>5712.0058978127217</v>
+        <v>5711.9838205487231</v>
       </c>
       <c r="E1267" s="23">
-        <v>5387.4485593568743</v>
+        <v>5387.4170897371732</v>
       </c>
       <c r="F1267" s="22">
         <v>1828.6121000000001</v>
@@ -57651,10 +57651,10 @@
         <v>6569.7313381807944</v>
       </c>
       <c r="J1267" s="22">
-        <v>13246.2163</v>
+        <v>13246.460300000001</v>
       </c>
       <c r="N1267" s="21">
-        <v>92951.950100000002</v>
+        <v>92951.893100000001</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57662,16 +57662,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="22">
-        <v>65265.4516</v>
+        <v>65262.584900000002</v>
       </c>
       <c r="C1268" s="22">
         <v>12718.373299999999</v>
       </c>
       <c r="D1268" s="22">
-        <v>5131.5879838186547</v>
+        <v>5131.3625854966849</v>
       </c>
       <c r="E1268" s="23">
-        <v>5331.7231812568798</v>
+        <v>5331.6522868172178</v>
       </c>
       <c r="F1268" s="22">
         <v>1326.8929000000001</v>
@@ -57683,13 +57683,13 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="23">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="22">
-        <v>14843.3467</v>
+        <v>14837.3172</v>
       </c>
       <c r="N1268" s="21">
-        <v>81435.691200000001</v>
+        <v>81426.794999999998</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57706,7 +57706,7 @@
         <v>5301.0343445399049</v>
       </c>
       <c r="E1269" s="23">
-        <v>5317.0450907326212</v>
+        <v>5316.9824471394086</v>
       </c>
       <c r="F1269" s="22">
         <v>1050.4068</v>
@@ -57718,13 +57718,13 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="23">
-        <v>6498.4408173314459</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="22">
-        <v>8128.4333999999999</v>
+        <v>8128.2731999999996</v>
       </c>
       <c r="N1269" s="21">
-        <v>64807.168899999997</v>
+        <v>64807.008699999998</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57732,16 +57732,16 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="22">
-        <v>57506.729399999997</v>
+        <v>57506.741399999999</v>
       </c>
       <c r="C1270" s="22">
         <v>9697.8808000000008</v>
       </c>
       <c r="D1270" s="22">
-        <v>5929.8243179066494</v>
+        <v>5929.8255552903884</v>
       </c>
       <c r="E1270" s="23">
-        <v>5431.7720133038956</v>
+        <v>5431.7104555804062</v>
       </c>
       <c r="F1270" s="22">
         <v>1172.5832</v>
@@ -57759,7 +57759,7 @@
         <v>6117.0985000000001</v>
       </c>
       <c r="N1270" s="21">
-        <v>64796.411099999998</v>
+        <v>64796.4231</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1">
@@ -57767,16 +57767,16 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="22">
-        <v>65146.041700000002</v>
+        <v>65145.661899999999</v>
       </c>
       <c r="C1271" s="22">
         <v>11941.232099999999</v>
       </c>
       <c r="D1271" s="22">
-        <v>5455.5544314392819</v>
+        <v>5455.5226256761225</v>
       </c>
       <c r="E1271" s="23">
-        <v>5411.5619252211218</v>
+        <v>5411.4960471540562</v>
       </c>
       <c r="F1271" s="22">
         <v>1808.0657000000001</v>
@@ -57788,13 +57788,13 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="23">
-        <v>7489.2724524389041</v>
+        <v>7489.2724524389059</v>
       </c>
       <c r="J1271" s="22">
-        <v>9610.9421999999995</v>
+        <v>9735.2654000000002</v>
       </c>
       <c r="N1271" s="21">
-        <v>76565.049599999998</v>
+        <v>76688.993000000002</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1">
@@ -57802,16 +57802,16 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="22">
-        <v>37610.071199999998</v>
+        <v>37488.710899999998</v>
       </c>
       <c r="C1272" s="22">
-        <v>6205.7831999999999</v>
+        <v>6179.0317999999997</v>
       </c>
       <c r="D1272" s="22">
-        <v>6060.4874498355011</v>
+        <v>6067.0849598152254</v>
       </c>
       <c r="E1272" s="23">
-        <v>5602.0731551966028</v>
+        <v>5602.6496788455115</v>
       </c>
       <c r="F1272" s="22">
         <v>697.31119999999999</v>
@@ -57826,10 +57826,10 @@
         <v>7304.0585980662427</v>
       </c>
       <c r="J1272" s="22">
-        <v>8073.0517</v>
+        <v>7915.2548999999999</v>
       </c>
       <c r="N1272" s="21">
-        <v>46380.434099999999</v>
+        <v>46101.277000000002</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1">
@@ -57837,16 +57837,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="22">
-        <v>61776.260399999999</v>
+        <v>62623.837299999999</v>
       </c>
       <c r="C1273" s="22">
-        <v>10757.154200000001</v>
+        <v>10905.8454</v>
       </c>
       <c r="D1273" s="22">
-        <v>5742.8069962964737</v>
+        <v>5742.226760339001</v>
       </c>
       <c r="E1273" s="23">
-        <v>5671.0788489388178</v>
+        <v>5671.8628406085381</v>
       </c>
       <c r="F1273" s="22">
         <v>700.99080000000004</v>
@@ -57858,13 +57858,13 @@
         <v>6274.2182633165548</v>
       </c>
       <c r="I1273" s="23">
-        <v>7161.2268208604146</v>
+        <v>7161.2268208604155</v>
       </c>
       <c r="J1273" s="22">
-        <v>10894.0506</v>
+        <v>11036.475</v>
       </c>
       <c r="N1273" s="21">
-        <v>73371.301800000001</v>
+        <v>74361.303100000005</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1">
@@ -57872,34 +57872,34 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="22">
-        <v>43282.447999999997</v>
+        <v>49413.447200000002</v>
       </c>
       <c r="C1274" s="22">
-        <v>7938.0126</v>
+        <v>9218.1185000000005</v>
       </c>
       <c r="D1274" s="22">
-        <v>5452.5547112384274</v>
+        <v>5360.469948395651</v>
       </c>
       <c r="E1274" s="23">
-        <v>5598.9494007571411</v>
+        <v>5575.0571154329664</v>
       </c>
       <c r="F1274" s="22">
-        <v>609.18629999999996</v>
+        <v>1047.6364000000001</v>
       </c>
       <c r="G1274" s="22">
-        <v>142.2978</v>
+        <v>231.1103</v>
       </c>
       <c r="H1274" s="22">
-        <v>4281.0661865468046</v>
+        <v>4533.0580246747986</v>
       </c>
       <c r="I1274" s="23">
-        <v>6671.9395073139312</v>
+        <v>6471.0708305987373</v>
       </c>
       <c r="J1274" s="22">
-        <v>6379.0343000000003</v>
+        <v>8434.2473000000009</v>
       </c>
       <c r="N1274" s="21">
-        <v>50270.668599999997</v>
+        <v>58895.330900000001</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57907,34 +57907,69 @@
         <v>46123</v>
       </c>
       <c r="B1275" s="22">
-        <v>22836.638299999999</v>
+        <v>28515.918300000001</v>
       </c>
       <c r="C1275" s="22">
-        <v>3469.7655</v>
+        <v>4595.0243</v>
       </c>
       <c r="D1275" s="22">
-        <v>6581.608555390846</v>
+        <v>6205.825353306619</v>
       </c>
       <c r="E1275" s="23">
-        <v>5734.8751099279998</v>
+        <v>5681.7788494081324</v>
       </c>
       <c r="F1275" s="22">
-        <v>1151.3224</v>
+        <v>1342.8128999999999</v>
       </c>
       <c r="G1275" s="22">
-        <v>173.50749999999999</v>
+        <v>209.40639999999999</v>
       </c>
       <c r="H1275" s="22">
-        <v>6635.5771364350239</v>
+        <v>6412.4730667257545</v>
       </c>
       <c r="I1275" s="23">
-        <v>6005.0652965169047</v>
+        <v>5838.8404398158273</v>
       </c>
       <c r="J1275" s="22">
-        <v>2187.5484999999999</v>
+        <v>3518.9982</v>
       </c>
       <c r="N1275" s="21">
-        <v>26175.5092</v>
+        <v>33377.729400000004</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1276" s="20">
+        <v>46130</v>
+      </c>
+      <c r="B1276" s="22">
+        <v>32105.1397</v>
+      </c>
+      <c r="C1276" s="22">
+        <v>5322.4408000000003</v>
+      </c>
+      <c r="D1276" s="22">
+        <v>6032.0332167903116</v>
+      </c>
+      <c r="E1276" s="23">
+        <v>5742.1337864799561</v>
+      </c>
+      <c r="F1276" s="22">
+        <v>283.16950000000003</v>
+      </c>
+      <c r="G1276" s="22">
+        <v>63.649099999999997</v>
+      </c>
+      <c r="H1276" s="22">
+        <v>4448.9160098100365</v>
+      </c>
+      <c r="I1276" s="23">
+        <v>5593.6833092115658</v>
+      </c>
+      <c r="J1276" s="22">
+        <v>5444.4718000000003</v>
+      </c>
+      <c r="N1276" s="21">
+        <v>37832.781000000003</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BAF1C9-8D30-4298-9E32-16F1D862ADFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7B9097-76CA-4DB7-8BBB-492FAFAB3DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -827,7 +827,7 @@
     <col min="2" max="4" width="17.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="16.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="12" customWidth="1"/>
     <col min="10" max="10" width="23.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="1.42578125" style="11" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="0.5703125" style="11" hidden="1" customWidth="1"/>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55725,7 +55725,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55751,7 +55751,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4706.1866360758077</v>
+        <v>4706.1866360758067</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55789,7 +55789,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.4088847985458</v>
+        <v>4736.4088847985449</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55865,7 +55865,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4663.2967738120533</v>
+        <v>4663.2967738120524</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -56017,7 +56017,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803249</v>
+        <v>4673.0018865803258</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56752,7 +56752,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084409</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56904,7 +56904,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5394.2932473875317</v>
+        <v>5394.2932473875308</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -57035,16 +57035,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="35">
-        <v>54501.171399999999</v>
+        <v>54377.964800000002</v>
       </c>
       <c r="C1251" s="35">
         <v>9494.5689999999995</v>
       </c>
       <c r="D1251" s="35">
-        <v>5740.2470191116627</v>
+        <v>5727.270484842441</v>
       </c>
       <c r="E1251" s="36">
-        <v>5020.1251515254262</v>
+        <v>5016.7040376494278</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57065,7 +57065,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>61075.088900000002</v>
+        <v>60951.882299999997</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57082,7 +57082,7 @@
         <v>4714.9413389611873</v>
       </c>
       <c r="E1252" s="36">
-        <v>4993.0467883937781</v>
+        <v>4989.6730806415162</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57120,7 +57120,7 @@
         <v>5680.0691005379304</v>
       </c>
       <c r="E1253" s="36">
-        <v>5202.7334362050296</v>
+        <v>5200.271136982984</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57158,7 +57158,7 @@
         <v>5052.3810072373371</v>
       </c>
       <c r="E1254" s="36">
-        <v>5307.8966451134484</v>
+        <v>5305.2073581097511</v>
       </c>
       <c r="F1254" s="35">
         <v>2124.1673000000001</v>
@@ -57196,7 +57196,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="36">
-        <v>5579.1085079279474</v>
+        <v>5576.8692059734512</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57263,16 +57263,16 @@
         <v>45997</v>
       </c>
       <c r="B1257" s="35">
-        <v>68679.607099999994</v>
+        <v>68679.238400000002</v>
       </c>
       <c r="C1257" s="35">
         <v>13091.163</v>
       </c>
       <c r="D1257" s="35">
-        <v>5246.2571201657174</v>
+        <v>5246.2289561286498</v>
       </c>
       <c r="E1257" s="36">
-        <v>5421.2266721637816</v>
+        <v>5421.219840669658</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57284,7 +57284,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6858.7787596539711</v>
+        <v>6858.778759653972</v>
       </c>
       <c r="J1257" s="35">
         <v>6940.3462</v>
@@ -57293,7 +57293,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78568.864299999987</v>
+        <v>78568.495599999995</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1">
@@ -57310,7 +57310,7 @@
         <v>4974.8650431127226</v>
       </c>
       <c r="E1258" s="36">
-        <v>5451.9871151423977</v>
+        <v>5451.9802066297707</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57322,7 +57322,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="35">
         <v>10586.2176</v>
@@ -57348,7 +57348,7 @@
         <v>5452.8764758391462</v>
       </c>
       <c r="E1259" s="36">
-        <v>5181.7063444103787</v>
+        <v>5181.6993183763707</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57386,7 +57386,7 @@
         <v>5186.239383650377</v>
       </c>
       <c r="E1260" s="36">
-        <v>5208.7334719123392</v>
+        <v>5208.7262881634688</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57398,7 +57398,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="35">
         <v>7543.9057000000003</v>
@@ -57424,7 +57424,7 @@
         <v>5322.9469673816475</v>
       </c>
       <c r="E1261" s="36">
-        <v>5253.9304222756491</v>
+        <v>5253.9224174373667</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57538,7 +57538,7 @@
         <v>5650.0987873227514</v>
       </c>
       <c r="E1264" s="36">
-        <v>5401.4570676311514</v>
+        <v>5401.4570676311505</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57550,7 +57550,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763587</v>
+        <v>6539.4433219763569</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57588,7 +57588,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796991011</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57681,16 +57681,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="40">
-        <v>65262.584900000002</v>
+        <v>65282.188399999999</v>
       </c>
       <c r="C1268" s="40">
-        <v>12718.373299999999</v>
+        <v>12725.730299999999</v>
       </c>
       <c r="D1268" s="40">
-        <v>5131.3625854966849</v>
+        <v>5129.9365035262454</v>
       </c>
       <c r="E1268" s="41">
-        <v>5331.599471183762</v>
+        <v>5331.2155411239046</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57705,13 +57705,13 @@
         <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
-        <v>14837.3172</v>
+        <v>14839.3699</v>
       </c>
       <c r="K1268" s="40"/>
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81426.794999999998</v>
+        <v>81448.451199999996</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57728,7 +57728,7 @@
         <v>5300.4005264753259</v>
       </c>
       <c r="E1269" s="41">
-        <v>5316.7975440246755</v>
+        <v>5316.4117324804283</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57740,7 +57740,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314478</v>
+        <v>6498.4408173314469</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57757,16 +57757,16 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="40">
-        <v>57489.909899999999</v>
+        <v>57490.242899999997</v>
       </c>
       <c r="C1270" s="40">
         <v>9697.8808000000008</v>
       </c>
       <c r="D1270" s="40">
-        <v>5928.08996992415</v>
+        <v>5928.1243073228943</v>
       </c>
       <c r="E1270" s="41">
-        <v>5431.1997373443492</v>
+        <v>5430.8092502031732</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57787,7 +57787,7 @@
       <c r="L1270" s="40"/>
       <c r="M1270" s="40"/>
       <c r="N1270" s="40">
-        <v>64779.5916</v>
+        <v>64779.924599999998</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1">
@@ -57804,7 +57804,7 @@
         <v>5455.5226256761225</v>
       </c>
       <c r="E1271" s="41">
-        <v>5411.017767702685</v>
+        <v>5410.6130818540623</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -57842,7 +57842,7 @@
         <v>6067.0849598152254</v>
       </c>
       <c r="E1272" s="41">
-        <v>5602.1138998323031</v>
+        <v>5601.6284987702275</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57871,16 +57871,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="40">
-        <v>62478.667300000001</v>
+        <v>62478.582300000002</v>
       </c>
       <c r="C1273" s="40">
         <v>10894.957700000001</v>
       </c>
       <c r="D1273" s="40">
-        <v>5734.6406494079365</v>
+        <v>5734.6328476337267</v>
       </c>
       <c r="E1273" s="41">
-        <v>5669.420172469906</v>
+        <v>5669.4258393217715</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57901,7 +57901,7 @@
       <c r="L1273" s="40"/>
       <c r="M1273" s="40"/>
       <c r="N1273" s="40">
-        <v>74216.133100000006</v>
+        <v>74216.0481</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1">
@@ -57909,16 +57909,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52043.3024</v>
+        <v>52043.902399999999</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5400.9668590865595</v>
+        <v>5401.0291260828108</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.8045105789461</v>
+        <v>5579.8167800506408</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57939,7 +57939,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61492.689599999998</v>
+        <v>61493.289599999996</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57947,16 +57947,16 @@
         <v>46123</v>
       </c>
       <c r="B1275" s="40">
-        <v>24828.836599999999</v>
+        <v>25434.4172</v>
       </c>
       <c r="C1275" s="40">
-        <v>4091.7673</v>
+        <v>4164.0848999999998</v>
       </c>
       <c r="D1275" s="40">
-        <v>6067.9981972581863</v>
+        <v>6108.0448191630294</v>
       </c>
       <c r="E1275" s="41">
-        <v>5663.9667983753925</v>
+        <v>5669.2995666176721</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57977,7 +57977,7 @@
       <c r="L1275" s="40"/>
       <c r="M1275" s="40"/>
       <c r="N1275" s="40">
-        <v>30004.416799999999</v>
+        <v>30609.9974</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15.75" customHeight="1">
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>42640.720500000003</v>
+        <v>45015.169099999999</v>
       </c>
       <c r="C1276" s="40">
-        <v>7306.1909999999998</v>
+        <v>7786.9242000000004</v>
       </c>
       <c r="D1276" s="40">
-        <v>5836.2449736121052</v>
+        <v>5780.8664812738252</v>
       </c>
       <c r="E1276" s="41">
-        <v>5697.9928650266193</v>
+        <v>5693.0638514854209</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58006,16 +58006,16 @@
         <v>4448.9160098100365</v>
       </c>
       <c r="I1276" s="41">
-        <v>5606.9800390513046</v>
+        <v>5606.9800390513055</v>
       </c>
       <c r="J1276" s="40">
-        <v>6013.5465999999997</v>
+        <v>6570.7921999999999</v>
       </c>
       <c r="K1276" s="40"/>
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>48937.436600000001</v>
+        <v>51869.130799999999</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58023,54 +58023,76 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>24307.820400000001</v>
+        <v>28988.227699999999</v>
       </c>
       <c r="C1277" s="40">
-        <v>3830.2993999999999</v>
+        <v>4967.0739000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>6346.1933028002986</v>
+        <v>5836.0773935737088</v>
       </c>
       <c r="E1277" s="41">
-        <v>5696.8025895262845</v>
+        <v>5634.9767572383653</v>
       </c>
       <c r="F1277" s="40">
-        <v>828.12189999999998</v>
+        <v>808.10479999999995</v>
       </c>
       <c r="G1277" s="40">
         <v>137.62110000000001</v>
       </c>
       <c r="H1277" s="40">
-        <v>6017.4050345477544</v>
+        <v>5871.9542279490561</v>
       </c>
       <c r="I1277" s="41">
-        <v>5590.7769974939465</v>
+        <v>5563.2808752561132</v>
       </c>
       <c r="J1277" s="40">
-        <v>3939.8847999999998</v>
+        <v>4951.3876</v>
       </c>
       <c r="K1277" s="40"/>
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>29075.827100000002</v>
+        <v>34747.720099999999</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1278" s="39"/>
-      <c r="B1278" s="40"/>
-      <c r="C1278" s="40"/>
-      <c r="D1278" s="40"/>
-      <c r="E1278" s="41"/>
-      <c r="F1278" s="40"/>
-      <c r="G1278" s="40"/>
-      <c r="H1278" s="40"/>
-      <c r="I1278" s="41"/>
-      <c r="J1278" s="40"/>
+      <c r="A1278" s="39">
+        <v>46144</v>
+      </c>
+      <c r="B1278" s="40">
+        <v>21174.276399999999</v>
+      </c>
+      <c r="C1278" s="40">
+        <v>4174.9956000000002</v>
+      </c>
+      <c r="D1278" s="40">
+        <v>5071.6883150727144</v>
+      </c>
+      <c r="E1278" s="41">
+        <v>5537.6848826517835</v>
+      </c>
+      <c r="F1278" s="40">
+        <v>230.48830000000001</v>
+      </c>
+      <c r="G1278" s="40">
+        <v>32.171399999999998</v>
+      </c>
+      <c r="H1278" s="40">
+        <v>7164.3851371093588</v>
+      </c>
+      <c r="I1278" s="41">
+        <v>5674.1832325331761</v>
+      </c>
+      <c r="J1278" s="40">
+        <v>9358.4413999999997</v>
+      </c>
       <c r="K1278" s="40"/>
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
-      <c r="N1278" s="40"/>
+      <c r="N1278" s="40">
+        <v>30763.206099999999</v>
+      </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1279" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7B9097-76CA-4DB7-8BBB-492FAFAB3DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561FE948-9CC6-4ADB-B176-841B45A25B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55704,16 +55704,16 @@
         <v>45710</v>
       </c>
       <c r="B1216" s="35">
-        <v>51142.551700000004</v>
+        <v>51142.244500000001</v>
       </c>
       <c r="C1216" s="35">
         <v>9799.0020999999997</v>
       </c>
       <c r="D1216" s="35">
-        <v>5219.1591733611331</v>
+        <v>5219.127823230082</v>
       </c>
       <c r="E1216" s="36">
-        <v>4696.3826044347661</v>
+        <v>4696.3763305290568</v>
       </c>
       <c r="F1216" s="35">
         <v>989.77200000000005</v>
@@ -55725,7 +55725,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55734,7 +55734,7 @@
       <c r="L1216" s="35"/>
       <c r="M1216" s="35"/>
       <c r="N1216" s="37">
-        <v>56052.482600000003</v>
+        <v>56052.1754</v>
       </c>
     </row>
     <row r="1217" spans="1:14" ht="15.75" customHeight="1">
@@ -55751,7 +55751,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4706.1866360758067</v>
+        <v>4706.1810921613305</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55789,7 +55789,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.4088847985449</v>
+        <v>4736.4026964800241</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55827,7 +55827,7 @@
         <v>4760.4158560393298</v>
       </c>
       <c r="E1219" s="36">
-        <v>4756.2469293655349</v>
+        <v>4756.2400878861072</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55865,7 +55865,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4663.2967738120524</v>
+        <v>4663.2967738120533</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -56017,7 +56017,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803258</v>
+        <v>4673.0018865803249</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56752,7 +56752,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084427</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56904,7 +56904,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5394.2932473875308</v>
+        <v>5394.2932473875317</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -57120,7 +57120,7 @@
         <v>5680.0691005379304</v>
       </c>
       <c r="E1253" s="36">
-        <v>5200.271136982984</v>
+        <v>5200.2711369829831</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57149,16 +57149,16 @@
         <v>45976</v>
       </c>
       <c r="B1254" s="35">
-        <v>45129.964399999997</v>
+        <v>45106.893900000003</v>
       </c>
       <c r="C1254" s="35">
         <v>8932.4151000000002</v>
       </c>
       <c r="D1254" s="35">
-        <v>5052.3810072373371</v>
+        <v>5049.7982231031792</v>
       </c>
       <c r="E1254" s="36">
-        <v>5305.2073581097511</v>
+        <v>5304.7037877180792</v>
       </c>
       <c r="F1254" s="35">
         <v>2124.1673000000001</v>
@@ -57179,7 +57179,7 @@
       <c r="L1254" s="35"/>
       <c r="M1254" s="35"/>
       <c r="N1254" s="37">
-        <v>57923.758399999999</v>
+        <v>57900.687900000004</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1">
@@ -57196,7 +57196,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="36">
-        <v>5576.8692059734512</v>
+        <v>5576.4498955165354</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57208,7 +57208,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5979.7288428128713</v>
+        <v>5979.7288428128722</v>
       </c>
       <c r="J1255" s="35">
         <v>12450.415499999999</v>
@@ -57234,7 +57234,7 @@
         <v>5186.7917777368448</v>
       </c>
       <c r="E1256" s="36">
-        <v>5469.219758722209</v>
+        <v>5468.8258657563547</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57272,7 +57272,7 @@
         <v>5246.2289561286498</v>
       </c>
       <c r="E1257" s="36">
-        <v>5421.219840669658</v>
+        <v>5420.7923766469567</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57284,7 +57284,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6858.778759653972</v>
+        <v>6858.7787596539711</v>
       </c>
       <c r="J1257" s="35">
         <v>6940.3462</v>
@@ -57322,7 +57322,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="35">
         <v>10586.2176</v>
@@ -57339,16 +57339,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="35">
-        <v>64210.6005</v>
+        <v>64206.770499999999</v>
       </c>
       <c r="C1259" s="35">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="35">
-        <v>5452.8764758391462</v>
+        <v>5452.5512255418462</v>
       </c>
       <c r="E1259" s="36">
-        <v>5181.6993183763707</v>
+        <v>5181.626332994626</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57369,7 +57369,7 @@
       <c r="L1259" s="35"/>
       <c r="M1259" s="35"/>
       <c r="N1259" s="37">
-        <v>81458.630900000004</v>
+        <v>81454.800900000002</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57386,7 +57386,7 @@
         <v>5186.239383650377</v>
       </c>
       <c r="E1260" s="36">
-        <v>5208.7262881634688</v>
+        <v>5208.6516644635094</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57398,7 +57398,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="35">
         <v>7543.9057000000003</v>
@@ -57415,16 +57415,16 @@
         <v>46025</v>
       </c>
       <c r="B1261" s="35">
-        <v>36108.3747</v>
+        <v>35892.316800000001</v>
       </c>
       <c r="C1261" s="35">
-        <v>6783.5308000000005</v>
+        <v>6748.5475999999999</v>
       </c>
       <c r="D1261" s="35">
-        <v>5322.9469673816475</v>
+        <v>5318.5246555866324</v>
       </c>
       <c r="E1261" s="36">
-        <v>5253.9224174373667</v>
+        <v>5253.1382969068554</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57445,7 +57445,7 @@
       <c r="L1261" s="35"/>
       <c r="M1261" s="35"/>
       <c r="N1261" s="37">
-        <v>52780.7958</v>
+        <v>52564.7379</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15.75" customHeight="1">
@@ -57453,16 +57453,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="35">
-        <v>31637.522799999999</v>
+        <v>31637.811799999999</v>
       </c>
       <c r="C1262" s="35">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="35">
-        <v>5566.6725721886714</v>
+        <v>5566.7234221993867</v>
       </c>
       <c r="E1262" s="36">
-        <v>5254.3082400716485</v>
+        <v>5253.450220554756</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57477,13 +57477,13 @@
         <v>6331.7504578958606</v>
       </c>
       <c r="J1262" s="35">
-        <v>7785.9663</v>
+        <v>7740.6167999999998</v>
       </c>
       <c r="K1262" s="35"/>
       <c r="L1262" s="35"/>
       <c r="M1262" s="35"/>
       <c r="N1262" s="37">
-        <v>40633.591199999995</v>
+        <v>40588.530700000003</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57500,7 +57500,7 @@
         <v>5220.7532770553807</v>
       </c>
       <c r="E1263" s="36">
-        <v>5334.2643271604557</v>
+        <v>5333.465049507693</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57529,16 +57529,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41412.874799999998</v>
+        <v>41409.7065</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5650.0987873227514</v>
+        <v>5649.6665254217287</v>
       </c>
       <c r="E1264" s="36">
-        <v>5401.4570676311505</v>
+        <v>5400.5948747404409</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57550,7 +57550,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763569</v>
+        <v>6539.4433219763587</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57559,7 +57559,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49488.2716</v>
+        <v>49485.103300000002</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57576,7 +57576,7 @@
         <v>5216.5489738126962</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.6067687863479</v>
+        <v>5317.5350898661063</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57588,7 +57588,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796991011</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57614,7 +57614,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="41">
-        <v>5321.294825571108</v>
+        <v>5321.2193166314892</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57652,7 +57652,7 @@
         <v>5711.7858733059311</v>
       </c>
       <c r="E1267" s="41">
-        <v>5387.3571541908113</v>
+        <v>5387.2917480007718</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57690,7 +57690,7 @@
         <v>5129.9365035262454</v>
       </c>
       <c r="E1268" s="41">
-        <v>5331.2155411239046</v>
+        <v>5331.2085047493283</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57740,7 +57740,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314469</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57795,16 +57795,16 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="40">
-        <v>65145.661899999999</v>
+        <v>65144.978900000002</v>
       </c>
       <c r="C1271" s="40">
         <v>11941.232099999999</v>
       </c>
       <c r="D1271" s="40">
-        <v>5455.5226256761225</v>
+        <v>5455.4654288982456</v>
       </c>
       <c r="E1271" s="41">
-        <v>5410.6130818540623</v>
+        <v>5410.5991730648511</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -57825,7 +57825,7 @@
       <c r="L1271" s="40"/>
       <c r="M1271" s="40"/>
       <c r="N1271" s="40">
-        <v>76688.993000000002</v>
+        <v>76688.31</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1">
@@ -57842,7 +57842,7 @@
         <v>6067.0849598152254</v>
       </c>
       <c r="E1272" s="41">
-        <v>5601.6284987702275</v>
+        <v>5601.6129181235647</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57871,16 +57871,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="40">
-        <v>62478.582300000002</v>
+        <v>62476.6757</v>
       </c>
       <c r="C1273" s="40">
         <v>10894.957700000001</v>
       </c>
       <c r="D1273" s="40">
-        <v>5734.6328476337267</v>
+        <v>5734.4578492489236</v>
       </c>
       <c r="E1273" s="41">
-        <v>5669.4258393217715</v>
+        <v>5669.3666664201901</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57901,7 +57901,7 @@
       <c r="L1273" s="40"/>
       <c r="M1273" s="40"/>
       <c r="N1273" s="40">
-        <v>74216.0481</v>
+        <v>74214.141499999998</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1">
@@ -57918,7 +57918,7 @@
         <v>5401.0291260828108</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.8167800506408</v>
+        <v>5579.755084858597</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57933,13 +57933,13 @@
         <v>6471.0708305987373</v>
       </c>
       <c r="J1274" s="40">
-        <v>8401.7507999999998</v>
+        <v>8401.7510000000002</v>
       </c>
       <c r="K1274" s="40"/>
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61493.289599999996</v>
+        <v>61493.289799999999</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57947,16 +57947,16 @@
         <v>46123</v>
       </c>
       <c r="B1275" s="40">
-        <v>25434.4172</v>
+        <v>25434.627400000001</v>
       </c>
       <c r="C1275" s="40">
         <v>4164.0848999999998</v>
       </c>
       <c r="D1275" s="40">
-        <v>6108.0448191630294</v>
+        <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5669.2995666176721</v>
+        <v>5669.2535263269374</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57971,13 +57971,13 @@
         <v>5845.0234884410311</v>
       </c>
       <c r="J1275" s="40">
-        <v>3726.5886999999998</v>
+        <v>3726.7337000000002</v>
       </c>
       <c r="K1275" s="40"/>
       <c r="L1275" s="40"/>
       <c r="M1275" s="40"/>
       <c r="N1275" s="40">
-        <v>30609.9974</v>
+        <v>30610.352600000002</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15.75" customHeight="1">
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45015.169099999999</v>
+        <v>45240.427000000003</v>
       </c>
       <c r="C1276" s="40">
-        <v>7786.9242000000004</v>
+        <v>7820.8504000000003</v>
       </c>
       <c r="D1276" s="40">
-        <v>5780.8664812738252</v>
+        <v>5784.591788125751</v>
       </c>
       <c r="E1276" s="41">
-        <v>5693.0638514854209</v>
+        <v>5693.9411243517052</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58009,13 +58009,13 @@
         <v>5606.9800390513055</v>
       </c>
       <c r="J1276" s="40">
-        <v>6570.7921999999999</v>
+        <v>6631.9080999999996</v>
       </c>
       <c r="K1276" s="40"/>
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>51869.130799999999</v>
+        <v>52155.5046</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58023,37 +58023,37 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>28988.227699999999</v>
+        <v>32391.687600000001</v>
       </c>
       <c r="C1277" s="40">
-        <v>4967.0739000000003</v>
+        <v>5512.1736000000001</v>
       </c>
       <c r="D1277" s="40">
-        <v>5836.0773935737088</v>
+        <v>5876.3910483515974</v>
       </c>
       <c r="E1277" s="41">
-        <v>5634.9767572383653</v>
+        <v>5646.2278324312365</v>
       </c>
       <c r="F1277" s="40">
-        <v>808.10479999999995</v>
+        <v>577.98320000000001</v>
       </c>
       <c r="G1277" s="40">
-        <v>137.62110000000001</v>
+        <v>110.4393</v>
       </c>
       <c r="H1277" s="40">
-        <v>5871.9542279490561</v>
+        <v>5233.4920630608849</v>
       </c>
       <c r="I1277" s="41">
-        <v>5563.2808752561132</v>
+        <v>5450.6954327773046</v>
       </c>
       <c r="J1277" s="40">
-        <v>4951.3876</v>
+        <v>5158.3368</v>
       </c>
       <c r="K1277" s="40"/>
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>34747.720099999999</v>
+        <v>38128.007599999997</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1">
@@ -58061,54 +58061,76 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>21174.276399999999</v>
+        <v>27013.474600000001</v>
       </c>
       <c r="C1278" s="40">
-        <v>4174.9956000000002</v>
+        <v>5293.1484</v>
       </c>
       <c r="D1278" s="40">
-        <v>5071.6883150727144</v>
+        <v>5103.4795472577343</v>
       </c>
       <c r="E1278" s="41">
-        <v>5537.6848826517835</v>
+        <v>5540.1585503039132</v>
       </c>
       <c r="F1278" s="40">
-        <v>230.48830000000001</v>
+        <v>412.21159999999998</v>
       </c>
       <c r="G1278" s="40">
-        <v>32.171399999999998</v>
+        <v>54.4024</v>
       </c>
       <c r="H1278" s="40">
-        <v>7164.3851371093588</v>
+        <v>7577.0848344925953</v>
       </c>
       <c r="I1278" s="41">
-        <v>5674.1832325331761</v>
+        <v>5643.202064907332</v>
       </c>
       <c r="J1278" s="40">
-        <v>9358.4413999999997</v>
+        <v>10302.5502</v>
       </c>
       <c r="K1278" s="40"/>
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>30763.206099999999</v>
+        <v>37728.236400000002</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1279" s="39"/>
-      <c r="B1279" s="40"/>
-      <c r="C1279" s="40"/>
-      <c r="D1279" s="40"/>
-      <c r="E1279" s="41"/>
-      <c r="F1279" s="40"/>
-      <c r="G1279" s="40"/>
-      <c r="H1279" s="40"/>
-      <c r="I1279" s="41"/>
-      <c r="J1279" s="40"/>
+      <c r="A1279" s="39">
+        <v>46151</v>
+      </c>
+      <c r="B1279" s="40">
+        <v>24912.0141</v>
+      </c>
+      <c r="C1279" s="40">
+        <v>3457.6192999999998</v>
+      </c>
+      <c r="D1279" s="40">
+        <v>7204.9615468076554</v>
+      </c>
+      <c r="E1279" s="41">
+        <v>5810.8235559359337</v>
+      </c>
+      <c r="F1279" s="40">
+        <v>967.56820000000005</v>
+      </c>
+      <c r="G1279" s="40">
+        <v>136.0829</v>
+      </c>
+      <c r="H1279" s="40">
+        <v>7110.1380114621315</v>
+      </c>
+      <c r="I1279" s="41">
+        <v>6124.4418631648059</v>
+      </c>
+      <c r="J1279" s="40">
+        <v>3100.2694999999999</v>
+      </c>
       <c r="K1279" s="40"/>
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
-      <c r="N1279" s="40"/>
+      <c r="N1279" s="40">
+        <v>28979.8518</v>
+      </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1280" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561FE948-9CC6-4ADB-B176-841B45A25B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C0C2F0-FA2F-4A6E-9522-B27BA70BD80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55485,7 +55485,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139713</v>
+        <v>4508.5895396139722</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55582,7 +55582,7 @@
       <c r="L1212" s="35"/>
       <c r="M1212" s="35"/>
       <c r="N1212" s="37">
-        <v>45765.935100000002</v>
+        <v>45765.935099999995</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55658,7 +55658,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76702.561399999991</v>
+        <v>76702.561400000006</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55725,7 +55725,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55751,7 +55751,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4706.1810921613305</v>
+        <v>4706.1810921613296</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55789,7 +55789,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.4026964800241</v>
+        <v>4736.4026964800232</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55818,16 +55818,16 @@
         <v>45731</v>
       </c>
       <c r="B1219" s="35">
-        <v>42483.928099999997</v>
+        <v>42447.218500000003</v>
       </c>
       <c r="C1219" s="35">
         <v>8924.4153000000006</v>
       </c>
       <c r="D1219" s="35">
-        <v>4760.4158560393298</v>
+        <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4756.2400878861072</v>
+        <v>4755.4225489108812</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55848,7 +55848,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62677.385599999994</v>
+        <v>62640.675999999999</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55865,7 +55865,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4663.2967738120533</v>
+        <v>4662.4402106695079</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -55903,7 +55903,7 @@
         <v>4701.8076037281035</v>
       </c>
       <c r="E1221" s="36">
-        <v>4670.5246781428068</v>
+        <v>4669.693254518922</v>
       </c>
       <c r="F1221" s="35">
         <v>673.16070000000002</v>
@@ -55941,7 +55941,7 @@
         <v>4849.8060419687263</v>
       </c>
       <c r="E1222" s="36">
-        <v>4695.6779796687779</v>
+        <v>4694.8372699952697</v>
       </c>
       <c r="F1222" s="35">
         <v>1081.6878999999999</v>
@@ -55962,7 +55962,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313500000004</v>
+        <v>52967.313499999997</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56017,7 +56017,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803249</v>
+        <v>4673.0018865803258</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56084,16 +56084,16 @@
         <v>45780</v>
       </c>
       <c r="B1226" s="35">
-        <v>51687.046799999996</v>
+        <v>51675.6158</v>
       </c>
       <c r="C1226" s="35">
         <v>10739.004300000001</v>
       </c>
       <c r="D1226" s="35">
-        <v>4813.0204026457086</v>
+        <v>4811.955965042308</v>
       </c>
       <c r="E1226" s="36">
-        <v>4821.9812675094718</v>
+        <v>4821.6953261187473</v>
       </c>
       <c r="F1226" s="35">
         <v>823.7826</v>
@@ -56114,7 +56114,7 @@
       <c r="L1226" s="35"/>
       <c r="M1226" s="35"/>
       <c r="N1226" s="37">
-        <v>67381.683499999999</v>
+        <v>67370.252500000002</v>
       </c>
     </row>
     <row r="1227" spans="1:14" ht="15.75" customHeight="1">
@@ -56122,16 +56122,16 @@
         <v>45787</v>
       </c>
       <c r="B1227" s="35">
-        <v>70760.958700000003</v>
+        <v>70759.626999999993</v>
       </c>
       <c r="C1227" s="35">
         <v>14282.969499999999</v>
       </c>
       <c r="D1227" s="35">
-        <v>4954.2189878652343</v>
+        <v>4954.1257509511597</v>
       </c>
       <c r="E1227" s="36">
-        <v>4890.5844008503273</v>
+        <v>4890.2983275320939</v>
       </c>
       <c r="F1227" s="35">
         <v>699.97680000000003</v>
@@ -56152,7 +56152,7 @@
       <c r="L1227" s="35"/>
       <c r="M1227" s="35"/>
       <c r="N1227" s="37">
-        <v>81064.141300000003</v>
+        <v>81062.809599999993</v>
       </c>
     </row>
     <row r="1228" spans="1:14" ht="15.75" customHeight="1">
@@ -56169,7 +56169,7 @@
         <v>5173.8323341700607</v>
       </c>
       <c r="E1228" s="36">
-        <v>5048.2639462738034</v>
+        <v>5048.0160181896881</v>
       </c>
       <c r="F1228" s="35">
         <v>677.62339999999995</v>
@@ -56207,7 +56207,7 @@
         <v>5126.6609971962998</v>
       </c>
       <c r="E1229" s="36">
-        <v>4983.5449072703941</v>
+        <v>4983.3044849606677</v>
       </c>
       <c r="F1229" s="35">
         <v>465.10070000000002</v>
@@ -56245,7 +56245,7 @@
         <v>5223.7943789585233</v>
       </c>
       <c r="E1230" s="36">
-        <v>5028.2857750507765</v>
+        <v>5028.2598794368114</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56274,16 +56274,16 @@
         <v>45815</v>
       </c>
       <c r="B1231" s="35">
-        <v>59293.162300000004</v>
+        <v>59291.998699999996</v>
       </c>
       <c r="C1231" s="35">
         <v>12502.961600000001</v>
       </c>
       <c r="D1231" s="35">
-        <v>4742.3293933814848</v>
+        <v>4742.2363274314139</v>
       </c>
       <c r="E1231" s="36">
-        <v>4961.2148642311049</v>
+        <v>4961.194416586035</v>
       </c>
       <c r="F1231" s="35">
         <v>1023.9116</v>
@@ -56304,7 +56304,7 @@
       <c r="L1231" s="35"/>
       <c r="M1231" s="35"/>
       <c r="N1231" s="37">
-        <v>75299.290300000008</v>
+        <v>75298.126700000008</v>
       </c>
     </row>
     <row r="1232" spans="1:14" ht="15.75" customHeight="1">
@@ -56321,7 +56321,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.5927451670368</v>
+        <v>4909.5700041555092</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56359,7 +56359,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="36">
-        <v>4835.9999497856616</v>
+        <v>4835.9755920229454</v>
       </c>
       <c r="F1233" s="35">
         <v>910.61059999999998</v>
@@ -56397,7 +56397,7 @@
         <v>4897.4427637682502</v>
       </c>
       <c r="E1234" s="36">
-        <v>4765.8359934631844</v>
+        <v>4765.8101461375481</v>
       </c>
       <c r="F1234" s="35">
         <v>556.48080000000004</v>
@@ -56409,7 +56409,7 @@
         <v>6232.9559455378785</v>
       </c>
       <c r="I1234" s="36">
-        <v>6273.3822151253544</v>
+        <v>6273.3822151253535</v>
       </c>
       <c r="J1234" s="35">
         <v>8405.0920000000006</v>
@@ -56435,7 +56435,7 @@
         <v>5123.1647487932232</v>
       </c>
       <c r="E1235" s="36">
-        <v>4954.1746414860563</v>
+        <v>4954.14977322102</v>
       </c>
       <c r="F1235" s="35">
         <v>1182.9712999999999</v>
@@ -56447,7 +56447,7 @@
         <v>5270.8131997196551</v>
       </c>
       <c r="I1235" s="36">
-        <v>6279.4686229430436</v>
+        <v>6279.4686229430445</v>
       </c>
       <c r="J1235" s="35">
         <v>12601.2554</v>
@@ -56540,16 +56540,16 @@
         <v>45864</v>
       </c>
       <c r="B1238" s="35">
-        <v>47769.335400000004</v>
+        <v>47769.335299999999</v>
       </c>
       <c r="C1238" s="35">
         <v>8648.6777000000002</v>
       </c>
       <c r="D1238" s="35">
-        <v>5523.3108524786403</v>
+        <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.5363090282181</v>
+        <v>5020.5363068137885</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56561,7 +56561,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253522</v>
+        <v>5662.7424793253513</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56570,7 +56570,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359500000006</v>
+        <v>53725.359399999994</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56587,7 +56587,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="36">
-        <v>4983.7742122093496</v>
+        <v>4983.7742099543975</v>
       </c>
       <c r="F1239" s="35">
         <v>1951.8497</v>
@@ -56599,7 +56599,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316097</v>
+        <v>6067.7529720316088</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56625,7 +56625,7 @@
         <v>5736.0102439994189</v>
       </c>
       <c r="E1240" s="36">
-        <v>5190.1828701541526</v>
+        <v>5190.1828673687514</v>
       </c>
       <c r="F1240" s="35">
         <v>690.66629999999998</v>
@@ -56637,7 +56637,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712294</v>
+        <v>6497.7712544712276</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56663,7 +56663,7 @@
         <v>5874.7159286822889</v>
       </c>
       <c r="E1241" s="36">
-        <v>5328.0799505254308</v>
+        <v>5328.0799479032994</v>
       </c>
       <c r="F1241" s="35">
         <v>356.61349999999999</v>
@@ -56702,7 +56702,7 @@
         <v>5269.8946658978402</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.594135844156</v>
+        <v>5374.5941335617226</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56740,7 +56740,7 @@
         <v>5139.5984958808658</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.4199247954284</v>
+        <v>5338.4199247954266</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56752,7 +56752,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56769,16 +56769,16 @@
         <v>45906</v>
       </c>
       <c r="B1244" s="35">
-        <v>47988.774299999997</v>
+        <v>47987.968800000002</v>
       </c>
       <c r="C1244" s="35">
         <v>10037.602800000001</v>
       </c>
       <c r="D1244" s="35">
-        <v>4780.8999076950913</v>
+        <v>4780.81965945096</v>
       </c>
       <c r="E1244" s="36">
-        <v>5246.3659652551814</v>
+        <v>5246.3506333774749</v>
       </c>
       <c r="F1244" s="35">
         <v>1388.6704</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084409</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56799,7 +56799,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57659.296399999992</v>
+        <v>57658.490900000004</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1">
@@ -56816,7 +56816,7 @@
         <v>5199.2635555698389</v>
       </c>
       <c r="E1245" s="36">
-        <v>5064.1889255424285</v>
+        <v>5064.173468482878</v>
       </c>
       <c r="F1245" s="35">
         <v>1184.0114000000001</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56837,7 +56837,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639499999997</v>
+        <v>48636.639500000005</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56845,16 +56845,16 @@
         <v>45920</v>
       </c>
       <c r="B1246" s="35">
-        <v>62648.806499999999</v>
+        <v>62615.676500000001</v>
       </c>
       <c r="C1246" s="35">
         <v>11947.379300000001</v>
       </c>
       <c r="D1246" s="35">
-        <v>5243.7279278477408</v>
+        <v>5240.9549347780394</v>
       </c>
       <c r="E1246" s="36">
-        <v>5101.7557395300573</v>
+        <v>5101.0411095141517</v>
       </c>
       <c r="F1246" s="35">
         <v>977.74770000000001</v>
@@ -56875,7 +56875,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70148.861900000004</v>
+        <v>70115.731900000013</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56892,7 +56892,7 @@
         <v>5285.9764895954595</v>
       </c>
       <c r="E1247" s="36">
-        <v>5104.8197608395776</v>
+        <v>5104.0534290358937</v>
       </c>
       <c r="F1247" s="35">
         <v>1625.8276000000001</v>
@@ -56921,16 +56921,16 @@
         <v>45934</v>
       </c>
       <c r="B1248" s="35">
-        <v>34853.894699999997</v>
+        <v>34613.0389</v>
       </c>
       <c r="C1248" s="35">
-        <v>7466.8144000000002</v>
+        <v>7429.8518000000004</v>
       </c>
       <c r="D1248" s="35">
-        <v>4667.8399693448919</v>
+        <v>4658.6445909997819</v>
       </c>
       <c r="E1248" s="36">
-        <v>5065.607828525247</v>
+        <v>5063.3560682685538</v>
       </c>
       <c r="F1248" s="35">
         <v>1018.4743</v>
@@ -56951,7 +56951,7 @@
       <c r="L1248" s="35"/>
       <c r="M1248" s="35"/>
       <c r="N1248" s="37">
-        <v>40632.641399999993</v>
+        <v>40391.785600000003</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15.75" customHeight="1">
@@ -56968,7 +56968,7 @@
         <v>4382.8174971698409</v>
       </c>
       <c r="E1249" s="36">
-        <v>4973.5165498838687</v>
+        <v>4971.0975735298489</v>
       </c>
       <c r="F1249" s="35">
         <v>1116.6591000000001</v>
@@ -56980,7 +56980,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691884</v>
+        <v>5046.6456948691875</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57006,7 +57006,7 @@
         <v>4934.8448070767918</v>
       </c>
       <c r="E1250" s="36">
-        <v>4941.8973620526885</v>
+        <v>4940.2794968107246</v>
       </c>
       <c r="F1250" s="35">
         <v>1339.0517</v>
@@ -57044,7 +57044,7 @@
         <v>5727.270484842441</v>
       </c>
       <c r="E1251" s="36">
-        <v>5016.7040376494278</v>
+        <v>5015.1634437707298</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57082,7 +57082,7 @@
         <v>4714.9413389611873</v>
       </c>
       <c r="E1252" s="36">
-        <v>4989.6730806415162</v>
+        <v>4988.1265519761864</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57158,7 +57158,7 @@
         <v>5049.7982231031792</v>
       </c>
       <c r="E1254" s="36">
-        <v>5304.7037877180792</v>
+        <v>5304.7037877180774</v>
       </c>
       <c r="F1254" s="35">
         <v>2124.1673000000001</v>
@@ -57170,7 +57170,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="36">
-        <v>5620.2491328335427</v>
+        <v>5620.2491328335436</v>
       </c>
       <c r="J1254" s="35">
         <v>10669.626700000001</v>
@@ -57196,7 +57196,7 @@
         <v>6212.2036498916368</v>
       </c>
       <c r="E1255" s="36">
-        <v>5576.4498955165354</v>
+        <v>5576.4498955165345</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57208,7 +57208,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5979.7288428128722</v>
+        <v>5979.7288428128713</v>
       </c>
       <c r="J1255" s="35">
         <v>12450.415499999999</v>
@@ -57263,16 +57263,16 @@
         <v>45997</v>
       </c>
       <c r="B1257" s="35">
-        <v>68679.238400000002</v>
+        <v>68665.6446</v>
       </c>
       <c r="C1257" s="35">
         <v>13091.163</v>
       </c>
       <c r="D1257" s="35">
-        <v>5246.2289561286498</v>
+        <v>5245.1905609914102</v>
       </c>
       <c r="E1257" s="36">
-        <v>5420.7923766469567</v>
+        <v>5420.5405025899672</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57284,7 +57284,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6858.7787596539711</v>
+        <v>6858.778759653972</v>
       </c>
       <c r="J1257" s="35">
         <v>6940.3462</v>
@@ -57293,7 +57293,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78568.495599999995</v>
+        <v>78554.901799999992</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1">
@@ -57310,7 +57310,7 @@
         <v>4974.8650431127226</v>
       </c>
       <c r="E1258" s="36">
-        <v>5451.9802066297707</v>
+        <v>5451.7254929358678</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57322,7 +57322,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="35">
         <v>10586.2176</v>
@@ -57339,16 +57339,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="35">
-        <v>64206.770499999999</v>
+        <v>64211.297400000003</v>
       </c>
       <c r="C1259" s="35">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="35">
-        <v>5452.5512255418462</v>
+        <v>5452.9356578057759</v>
       </c>
       <c r="E1259" s="36">
-        <v>5181.626332994626</v>
+        <v>5181.4535520134932</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57360,7 +57360,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096225</v>
+        <v>7266.6202217096234</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57369,7 +57369,7 @@
       <c r="L1259" s="35"/>
       <c r="M1259" s="35"/>
       <c r="N1259" s="37">
-        <v>81454.800900000002</v>
+        <v>81459.327799999999</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57377,16 +57377,16 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="35">
-        <v>60694.124900000003</v>
+        <v>60691.1515</v>
       </c>
       <c r="C1260" s="35">
         <v>11702.9162</v>
       </c>
       <c r="D1260" s="35">
-        <v>5186.239383650377</v>
+        <v>5185.9853102254974</v>
       </c>
       <c r="E1260" s="36">
-        <v>5208.6516644635094</v>
+        <v>5208.4170713213134</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57398,7 +57398,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="35">
         <v>7543.9057000000003</v>
@@ -57407,7 +57407,7 @@
       <c r="L1260" s="35"/>
       <c r="M1260" s="35"/>
       <c r="N1260" s="37">
-        <v>70430.358300000007</v>
+        <v>70427.38489999999</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57415,16 +57415,16 @@
         <v>46025</v>
       </c>
       <c r="B1261" s="35">
-        <v>35892.316800000001</v>
+        <v>35891.826500000003</v>
       </c>
       <c r="C1261" s="35">
         <v>6748.5475999999999</v>
       </c>
       <c r="D1261" s="35">
-        <v>5318.5246555866324</v>
+        <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5253.1382969068554</v>
+        <v>5253.0898424485085</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57445,7 +57445,7 @@
       <c r="L1261" s="35"/>
       <c r="M1261" s="35"/>
       <c r="N1261" s="37">
-        <v>52564.7379</v>
+        <v>52564.247600000002</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15.75" customHeight="1">
@@ -57453,16 +57453,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="35">
-        <v>31637.811799999999</v>
+        <v>31628.322899999999</v>
       </c>
       <c r="C1262" s="35">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="35">
-        <v>5566.7234221993867</v>
+        <v>5565.0538351174855</v>
       </c>
       <c r="E1262" s="36">
-        <v>5253.450220554756</v>
+        <v>5253.2482047532058</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57483,7 +57483,7 @@
       <c r="L1262" s="35"/>
       <c r="M1262" s="35"/>
       <c r="N1262" s="37">
-        <v>40588.530700000003</v>
+        <v>40579.041800000006</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57491,16 +57491,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58965.675199999998</v>
+        <v>58954.989800000003</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5220.7532770553807</v>
+        <v>5219.8072039903755</v>
       </c>
       <c r="E1263" s="36">
-        <v>5333.465049507693</v>
+        <v>5333.0020178055702</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57512,7 +57512,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.391308042289</v>
+        <v>6206.3913080422872</v>
       </c>
       <c r="J1263" s="35">
         <v>7830.9169000000002</v>
@@ -57521,7 +57521,7 @@
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69895.914699999994</v>
+        <v>69885.229300000006</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1">
@@ -57538,7 +57538,7 @@
         <v>5649.6665254217287</v>
       </c>
       <c r="E1264" s="36">
-        <v>5400.5948747404409</v>
+        <v>5400.0005223154585</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57550,7 +57550,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763587</v>
+        <v>6539.4433219763569</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57576,7 +57576,7 @@
         <v>5216.5489738126962</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.5350898661063</v>
+        <v>5317.0206561331479</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57588,7 +57588,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796991011</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57614,7 +57614,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="41">
-        <v>5321.2193166314892</v>
+        <v>5320.8385735936845</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57702,7 +57702,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166811</v>
+        <v>6548.0752800166792</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57711,7 +57711,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81448.451199999996</v>
+        <v>81448.45120000001</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57719,16 +57719,16 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="40">
-        <v>55621.677499999998</v>
+        <v>55620.511599999998</v>
       </c>
       <c r="C1269" s="40">
         <v>10493.8631</v>
       </c>
       <c r="D1269" s="40">
-        <v>5300.4005264753259</v>
+        <v>5300.2894234440701</v>
       </c>
       <c r="E1269" s="41">
-        <v>5316.4117324804283</v>
+        <v>5316.3886793059364</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57740,7 +57740,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314478</v>
+        <v>6498.4408173314459</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57749,7 +57749,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64800.357499999998</v>
+        <v>64799.191599999991</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57757,16 +57757,16 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="40">
-        <v>57490.242899999997</v>
+        <v>57409.225899999998</v>
       </c>
       <c r="C1270" s="40">
-        <v>9697.8808000000008</v>
+        <v>9688.8088000000007</v>
       </c>
       <c r="D1270" s="40">
-        <v>5928.1243073228943</v>
+        <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5430.8092502031732</v>
+        <v>5430.1671690365274</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57787,7 +57787,7 @@
       <c r="L1270" s="40"/>
       <c r="M1270" s="40"/>
       <c r="N1270" s="40">
-        <v>64779.924599999998</v>
+        <v>64698.907599999999</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1">
@@ -57795,16 +57795,16 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="40">
-        <v>65144.978900000002</v>
+        <v>65143.186999999998</v>
       </c>
       <c r="C1271" s="40">
         <v>11941.232099999999</v>
       </c>
       <c r="D1271" s="40">
-        <v>5455.4654288982456</v>
+        <v>5455.3153690061854</v>
       </c>
       <c r="E1271" s="41">
-        <v>5410.5991730648511</v>
+        <v>5409.888535936635</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -57816,7 +57816,7 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="41">
-        <v>7489.2724524389059</v>
+        <v>7489.2724524389041</v>
       </c>
       <c r="J1271" s="40">
         <v>9735.2654000000002</v>
@@ -57825,7 +57825,7 @@
       <c r="L1271" s="40"/>
       <c r="M1271" s="40"/>
       <c r="N1271" s="40">
-        <v>76688.31</v>
+        <v>76686.518100000001</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1">
@@ -57833,16 +57833,16 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="40">
-        <v>37488.710899999998</v>
+        <v>37487.454599999997</v>
       </c>
       <c r="C1272" s="40">
         <v>6179.0317999999997</v>
       </c>
       <c r="D1272" s="40">
-        <v>6067.0849598152254</v>
+        <v>6066.88164317264</v>
       </c>
       <c r="E1272" s="41">
-        <v>5601.6129181235647</v>
+        <v>5600.827717612131</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57863,7 +57863,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>46101.277000000002</v>
+        <v>46100.020699999994</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1">
@@ -57880,7 +57880,7 @@
         <v>5734.4578492489236</v>
       </c>
       <c r="E1273" s="41">
-        <v>5669.3666664201901</v>
+        <v>5668.6208476663942</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57918,7 +57918,7 @@
         <v>5401.0291260828108</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.755084858597</v>
+        <v>5578.958095900497</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57956,7 +57956,7 @@
         <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5669.2535263269374</v>
+        <v>5669.1707954743952</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45240.427000000003</v>
+        <v>45235.525000000001</v>
       </c>
       <c r="C1276" s="40">
         <v>7820.8504000000003</v>
       </c>
       <c r="D1276" s="40">
-        <v>5784.591788125751</v>
+        <v>5783.9650020667823</v>
       </c>
       <c r="E1276" s="41">
-        <v>5693.9411243517052</v>
+        <v>5693.7997453817243</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58015,7 +58015,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52155.5046</v>
+        <v>52150.602600000006</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58023,16 +58023,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32391.687600000001</v>
+        <v>32391.607599999999</v>
       </c>
       <c r="C1277" s="40">
-        <v>5512.1736000000001</v>
+        <v>5512.1714000000002</v>
       </c>
       <c r="D1277" s="40">
-        <v>5876.3910483515974</v>
+        <v>5876.3788803809684</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.2278324312365</v>
+        <v>5646.0743194379202</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58053,7 +58053,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>38128.007599999997</v>
+        <v>38127.927600000003</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1">
@@ -58061,16 +58061,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>27013.474600000001</v>
+        <v>28730.868999999999</v>
       </c>
       <c r="C1278" s="40">
-        <v>5293.1484</v>
+        <v>5668.1521000000002</v>
       </c>
       <c r="D1278" s="40">
-        <v>5103.4795472577343</v>
+        <v>5068.8246351046228</v>
       </c>
       <c r="E1278" s="41">
-        <v>5540.1585503039132</v>
+        <v>5527.3666701680477</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58085,13 +58085,13 @@
         <v>5643.202064907332</v>
       </c>
       <c r="J1278" s="40">
-        <v>10302.5502</v>
+        <v>11097.2752</v>
       </c>
       <c r="K1278" s="40"/>
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>37728.236400000002</v>
+        <v>40240.355799999998</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1">
@@ -58099,16 +58099,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>24912.0141</v>
+        <v>32140.0039</v>
       </c>
       <c r="C1279" s="40">
-        <v>3457.6192999999998</v>
+        <v>4837.1805000000004</v>
       </c>
       <c r="D1279" s="40">
-        <v>7204.9615468076554</v>
+        <v>6644.3672920619765</v>
       </c>
       <c r="E1279" s="41">
-        <v>5810.8235559359337</v>
+        <v>5762.4279395066451</v>
       </c>
       <c r="F1279" s="40">
         <v>967.56820000000005</v>
@@ -58123,30 +58123,46 @@
         <v>6124.4418631648059</v>
       </c>
       <c r="J1279" s="40">
-        <v>3100.2694999999999</v>
+        <v>3514.6612</v>
       </c>
       <c r="K1279" s="40"/>
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>28979.8518</v>
+        <v>36622.2333</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1280" s="39"/>
-      <c r="B1280" s="40"/>
-      <c r="C1280" s="40"/>
-      <c r="D1280" s="40"/>
-      <c r="E1280" s="41"/>
+      <c r="A1280" s="39">
+        <v>46158</v>
+      </c>
+      <c r="B1280" s="40">
+        <v>36741.566800000001</v>
+      </c>
+      <c r="C1280" s="40">
+        <v>5029.3342000000002</v>
+      </c>
+      <c r="D1280" s="40">
+        <v>7305.453433577748</v>
+      </c>
+      <c r="E1280" s="41">
+        <v>6078.1483242930153</v>
+      </c>
       <c r="F1280" s="40"/>
       <c r="G1280" s="40"/>
       <c r="H1280" s="40"/>
-      <c r="I1280" s="41"/>
-      <c r="J1280" s="40"/>
+      <c r="I1280" s="41">
+        <v>6089</v>
+      </c>
+      <c r="J1280" s="40">
+        <v>3419.1138999999998</v>
+      </c>
       <c r="K1280" s="40"/>
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
-      <c r="N1280" s="40"/>
+      <c r="N1280" s="40">
+        <v>40160.680699999997</v>
+      </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1281" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C0C2F0-FA2F-4A6E-9522-B27BA70BD80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590DEFE4-704F-4F04-B2D4-1E9E1EE67870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INAC" sheetId="1" r:id="rId1"/>
@@ -55485,7 +55485,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55582,7 +55582,7 @@
       <c r="L1212" s="35"/>
       <c r="M1212" s="35"/>
       <c r="N1212" s="37">
-        <v>45765.935099999995</v>
+        <v>45765.935100000002</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55658,7 +55658,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76702.561400000006</v>
+        <v>76702.561399999991</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55725,7 +55725,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55751,7 +55751,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4706.1810921613296</v>
+        <v>4706.1810921613305</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55789,7 +55789,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.4026964800232</v>
+        <v>4736.4026964800241</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55848,7 +55848,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.675999999999</v>
+        <v>62640.676000000007</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55962,7 +55962,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313499999997</v>
+        <v>52967.313500000004</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56017,7 +56017,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803258</v>
+        <v>4673.0018865803249</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56304,7 +56304,7 @@
       <c r="L1231" s="35"/>
       <c r="M1231" s="35"/>
       <c r="N1231" s="37">
-        <v>75298.126700000008</v>
+        <v>75298.126699999993</v>
       </c>
     </row>
     <row r="1232" spans="1:14" ht="15.75" customHeight="1">
@@ -56321,7 +56321,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.5700041555092</v>
+        <v>4909.570004155511</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56409,7 +56409,7 @@
         <v>6232.9559455378785</v>
       </c>
       <c r="I1234" s="36">
-        <v>6273.3822151253535</v>
+        <v>6273.3822151253544</v>
       </c>
       <c r="J1234" s="35">
         <v>8405.0920000000006</v>
@@ -56447,7 +56447,7 @@
         <v>5270.8131997196551</v>
       </c>
       <c r="I1235" s="36">
-        <v>6279.4686229430445</v>
+        <v>6279.4686229430436</v>
       </c>
       <c r="J1235" s="35">
         <v>12601.2554</v>
@@ -56561,7 +56561,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253513</v>
+        <v>5662.7424793253522</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56570,7 +56570,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359399999994</v>
+        <v>53725.359400000001</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56599,7 +56599,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316088</v>
+        <v>6067.7529720316097</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56637,7 +56637,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712276</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56740,7 +56740,7 @@
         <v>5139.5984958808658</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.4199247954266</v>
+        <v>5338.4199247954284</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56752,7 +56752,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084427</v>
+        <v>6056.50708400844</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56837,7 +56837,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639500000005</v>
+        <v>48636.639499999997</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56875,7 +56875,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70115.731900000013</v>
+        <v>70115.731899999999</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56980,7 +56980,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691875</v>
+        <v>5046.6456948691884</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57094,7 +57094,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="36">
-        <v>5768.2127381128485</v>
+        <v>5768.2127381128475</v>
       </c>
       <c r="J1252" s="35">
         <v>10772.394200000001</v>
@@ -57158,7 +57158,7 @@
         <v>5049.7982231031792</v>
       </c>
       <c r="E1254" s="36">
-        <v>5304.7037877180774</v>
+        <v>5304.7037877180792</v>
       </c>
       <c r="F1254" s="35">
         <v>2124.1673000000001</v>
@@ -57170,7 +57170,7 @@
         <v>6068.3177628297399</v>
       </c>
       <c r="I1254" s="36">
-        <v>5620.2491328335436</v>
+        <v>5620.2491328335427</v>
       </c>
       <c r="J1254" s="35">
         <v>10669.626700000001</v>
@@ -57187,16 +57187,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="35">
-        <v>84435.340800000005</v>
+        <v>84435.007599999997</v>
       </c>
       <c r="C1255" s="35">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="35">
-        <v>6212.2036498916368</v>
+        <v>6212.1791352010268</v>
       </c>
       <c r="E1255" s="36">
-        <v>5576.4498955165345</v>
+        <v>5576.4438395470397</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57217,7 +57217,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99631.618500000011</v>
+        <v>99631.285299999989</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1">
@@ -57234,7 +57234,7 @@
         <v>5186.7917777368448</v>
       </c>
       <c r="E1256" s="36">
-        <v>5468.8258657563547</v>
+        <v>5468.8201768837152</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57272,7 +57272,7 @@
         <v>5245.1905609914102</v>
       </c>
       <c r="E1257" s="36">
-        <v>5420.5405025899672</v>
+        <v>5420.5343288610766</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57310,7 +57310,7 @@
         <v>4974.8650431127226</v>
       </c>
       <c r="E1258" s="36">
-        <v>5451.7254929358678</v>
+        <v>5451.7192496041425</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57322,7 +57322,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="35">
         <v>10586.2176</v>
@@ -57360,7 +57360,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096234</v>
+        <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57398,7 +57398,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="35">
         <v>7543.9057000000003</v>
@@ -57407,7 +57407,7 @@
       <c r="L1260" s="35"/>
       <c r="M1260" s="35"/>
       <c r="N1260" s="37">
-        <v>70427.38489999999</v>
+        <v>70427.384900000005</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57424,7 +57424,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5253.0898424485085</v>
+        <v>5253.0898424485076</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57483,7 +57483,7 @@
       <c r="L1262" s="35"/>
       <c r="M1262" s="35"/>
       <c r="N1262" s="37">
-        <v>40579.041800000006</v>
+        <v>40579.041799999999</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57512,7 +57512,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.3913080422872</v>
+        <v>6206.391308042289</v>
       </c>
       <c r="J1263" s="35">
         <v>7830.9169000000002</v>
@@ -57550,7 +57550,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763569</v>
+        <v>6539.4433219763587</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57576,7 +57576,7 @@
         <v>5216.5489738126962</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.0206561331479</v>
+        <v>5317.0206561331461</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57588,7 +57588,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796991011</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57702,7 +57702,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57711,7 +57711,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81448.45120000001</v>
+        <v>81448.451199999996</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57740,7 +57740,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314459</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57749,7 +57749,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64799.191599999991</v>
+        <v>64799.191599999998</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57816,7 +57816,7 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="41">
-        <v>7489.2724524389041</v>
+        <v>7489.2724524389059</v>
       </c>
       <c r="J1271" s="40">
         <v>9735.2654000000002</v>
@@ -57842,7 +57842,7 @@
         <v>6066.88164317264</v>
       </c>
       <c r="E1272" s="41">
-        <v>5600.827717612131</v>
+        <v>5600.8277176121292</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57933,13 +57933,13 @@
         <v>6471.0708305987373</v>
       </c>
       <c r="J1274" s="40">
-        <v>8401.7510000000002</v>
+        <v>8467.8510000000006</v>
       </c>
       <c r="K1274" s="40"/>
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61493.289799999999</v>
+        <v>61559.389799999997</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57956,7 +57956,7 @@
         <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5669.1707954743952</v>
+        <v>5669.1707954743943</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57971,13 +57971,13 @@
         <v>5845.0234884410311</v>
       </c>
       <c r="J1275" s="40">
-        <v>3726.7337000000002</v>
+        <v>3741.9837000000002</v>
       </c>
       <c r="K1275" s="40"/>
       <c r="L1275" s="40"/>
       <c r="M1275" s="40"/>
       <c r="N1275" s="40">
-        <v>30610.352600000002</v>
+        <v>30625.602600000002</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15.75" customHeight="1">
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45235.525000000001</v>
+        <v>45552.054100000001</v>
       </c>
       <c r="C1276" s="40">
-        <v>7820.8504000000003</v>
+        <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5783.9650020667823</v>
+        <v>5803.4735490814192</v>
       </c>
       <c r="E1276" s="41">
-        <v>5693.7997453817243</v>
+        <v>5698.2858344238148</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58015,7 +58015,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52150.602600000006</v>
+        <v>52467.131699999998</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58023,16 +58023,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32391.607599999999</v>
+        <v>32076.707399999999</v>
       </c>
       <c r="C1277" s="40">
-        <v>5512.1714000000002</v>
+        <v>5483.9201000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>5876.3788803809684</v>
+        <v>5849.2295319911746</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.0743194379202</v>
+        <v>5646.1246370503568</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58047,13 +58047,13 @@
         <v>5450.6954327773046</v>
       </c>
       <c r="J1277" s="40">
-        <v>5158.3368</v>
+        <v>5191.1725999999999</v>
       </c>
       <c r="K1277" s="40"/>
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>38127.927600000003</v>
+        <v>37845.8632</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1">
@@ -58061,16 +58061,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>28730.868999999999</v>
+        <v>29337.1374</v>
       </c>
       <c r="C1278" s="40">
-        <v>5668.1521000000002</v>
+        <v>5721.3356999999996</v>
       </c>
       <c r="D1278" s="40">
-        <v>5068.8246351046228</v>
+        <v>5127.672791512653</v>
       </c>
       <c r="E1278" s="41">
-        <v>5527.3666701680477</v>
+        <v>5538.3436776552799</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58085,13 +58085,13 @@
         <v>5643.202064907332</v>
       </c>
       <c r="J1278" s="40">
-        <v>11097.2752</v>
+        <v>12627.7737</v>
       </c>
       <c r="K1278" s="40"/>
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>40240.355799999998</v>
+        <v>42377.1227</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1">
@@ -58099,37 +58099,37 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>32140.0039</v>
+        <v>34284.5602</v>
       </c>
       <c r="C1279" s="40">
-        <v>4837.1805000000004</v>
+        <v>5257.8001000000004</v>
       </c>
       <c r="D1279" s="40">
-        <v>6644.3672920619765</v>
+        <v>6520.7043911768351</v>
       </c>
       <c r="E1279" s="41">
-        <v>5762.4279395066451</v>
+        <v>5763.2685052457218</v>
       </c>
       <c r="F1279" s="40">
-        <v>967.56820000000005</v>
+        <v>968.41610000000003</v>
       </c>
       <c r="G1279" s="40">
         <v>136.0829</v>
       </c>
       <c r="H1279" s="40">
-        <v>7110.1380114621315</v>
+        <v>7116.3687722704326</v>
       </c>
       <c r="I1279" s="41">
-        <v>6124.4418631648059</v>
+        <v>6125.9423204335426</v>
       </c>
       <c r="J1279" s="40">
-        <v>3514.6612</v>
+        <v>4263.8330999999998</v>
       </c>
       <c r="K1279" s="40"/>
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>36622.2333</v>
+        <v>39516.809399999998</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1">
@@ -58137,48 +58137,76 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>36741.566800000001</v>
+        <v>59321.112200000003</v>
       </c>
       <c r="C1280" s="40">
-        <v>5029.3342000000002</v>
+        <v>8882.1231000000007</v>
       </c>
       <c r="D1280" s="40">
-        <v>7305.453433577748</v>
+        <v>6678.7086299220509</v>
       </c>
       <c r="E1280" s="41">
-        <v>6078.1483242930153</v>
-      </c>
-      <c r="F1280" s="40"/>
-      <c r="G1280" s="40"/>
-      <c r="H1280" s="40"/>
+        <v>6043.5025591101848</v>
+      </c>
+      <c r="F1280" s="40">
+        <v>362.1782</v>
+      </c>
+      <c r="G1280" s="40">
+        <v>41.4559</v>
+      </c>
+      <c r="H1280" s="40">
+        <v>8736.4693565933921</v>
+      </c>
       <c r="I1280" s="41">
-        <v>6089</v>
+        <v>6378.4960931619516</v>
       </c>
       <c r="J1280" s="40">
-        <v>3419.1138999999998</v>
+        <v>5752.4165000000003</v>
       </c>
       <c r="K1280" s="40"/>
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>40160.680699999997</v>
+        <v>65435.706900000005</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1281" s="39"/>
-      <c r="B1281" s="40"/>
-      <c r="C1281" s="40"/>
-      <c r="D1281" s="40"/>
-      <c r="E1281" s="41"/>
-      <c r="F1281" s="40"/>
-      <c r="G1281" s="40"/>
-      <c r="H1281" s="40"/>
-      <c r="I1281" s="41"/>
-      <c r="J1281" s="40"/>
+      <c r="A1281" s="39">
+        <v>46165</v>
+      </c>
+      <c r="B1281" s="40">
+        <v>41672.445899999999</v>
+      </c>
+      <c r="C1281" s="40">
+        <v>6015.1122999999998</v>
+      </c>
+      <c r="D1281" s="40">
+        <v>6927.9580865015605</v>
+      </c>
+      <c r="E1281" s="41">
+        <v>6343.9733408001248</v>
+      </c>
+      <c r="F1281" s="40">
+        <v>2144.5378999999998</v>
+      </c>
+      <c r="G1281" s="40">
+        <v>243.31120000000001</v>
+      </c>
+      <c r="H1281" s="40">
+        <v>8813.9711612124702</v>
+      </c>
+      <c r="I1281" s="41">
+        <v>7949.6286399529408</v>
+      </c>
+      <c r="J1281" s="40">
+        <v>3276.6959999999999</v>
+      </c>
       <c r="K1281" s="40"/>
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
-      <c r="N1281" s="40"/>
+      <c r="N1281" s="40">
+        <v>47093.679799999998</v>
+      </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1282" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590DEFE4-704F-4F04-B2D4-1E9E1EE67870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177882A8-369C-4D8C-A076-CB4F600D017B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INAC" sheetId="1" r:id="rId1"/>
@@ -55485,7 +55485,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139713</v>
+        <v>4508.5895396139722</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55497,7 +55497,7 @@
         <v>6882.5719118850975</v>
       </c>
       <c r="I1210" s="36">
-        <v>5131.0721532756534</v>
+        <v>5131.0721532756543</v>
       </c>
       <c r="J1210" s="35">
         <v>5833.4898999999996</v>
@@ -55582,7 +55582,7 @@
       <c r="L1212" s="35"/>
       <c r="M1212" s="35"/>
       <c r="N1212" s="37">
-        <v>45765.935100000002</v>
+        <v>45765.935099999995</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55649,7 +55649,7 @@
         <v>5483.9420094229508</v>
       </c>
       <c r="I1214" s="36">
-        <v>5618.8491234155317</v>
+        <v>5618.8491234155326</v>
       </c>
       <c r="J1214" s="35">
         <v>8807.2849999999999</v>
@@ -55658,7 +55658,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76702.561399999991</v>
+        <v>76702.561400000006</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55751,7 +55751,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4706.1810921613305</v>
+        <v>4706.1810921613296</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55789,7 +55789,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.4026964800241</v>
+        <v>4736.4026964800232</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55827,7 +55827,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4755.4225489108812</v>
+        <v>4755.4225489108821</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55848,7 +55848,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.676000000007</v>
+        <v>62640.675999999999</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55962,7 +55962,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313500000004</v>
+        <v>52967.313499999997</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56017,7 +56017,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803249</v>
+        <v>4673.0018865803258</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56304,7 +56304,7 @@
       <c r="L1231" s="35"/>
       <c r="M1231" s="35"/>
       <c r="N1231" s="37">
-        <v>75298.126699999993</v>
+        <v>75298.126700000008</v>
       </c>
     </row>
     <row r="1232" spans="1:14" ht="15.75" customHeight="1">
@@ -56321,7 +56321,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.570004155511</v>
+        <v>4909.5700041555092</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56409,7 +56409,7 @@
         <v>6232.9559455378785</v>
       </c>
       <c r="I1234" s="36">
-        <v>6273.3822151253544</v>
+        <v>6273.3822151253535</v>
       </c>
       <c r="J1234" s="35">
         <v>8405.0920000000006</v>
@@ -56447,7 +56447,7 @@
         <v>5270.8131997196551</v>
       </c>
       <c r="I1235" s="36">
-        <v>6279.4686229430436</v>
+        <v>6279.4686229430445</v>
       </c>
       <c r="J1235" s="35">
         <v>12601.2554</v>
@@ -56561,7 +56561,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253522</v>
+        <v>5662.7424793253513</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56570,7 +56570,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359400000001</v>
+        <v>53725.359399999994</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56599,7 +56599,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316097</v>
+        <v>6067.7529720316088</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56616,16 +56616,16 @@
         <v>45878</v>
       </c>
       <c r="B1240" s="35">
-        <v>18370.016199999998</v>
+        <v>18369.821199999998</v>
       </c>
       <c r="C1240" s="35">
         <v>3202.5772999999999</v>
       </c>
       <c r="D1240" s="35">
-        <v>5736.0102439994189</v>
+        <v>5735.9493555393647</v>
       </c>
       <c r="E1240" s="36">
-        <v>5190.1828673687514</v>
+        <v>5190.1774358351622</v>
       </c>
       <c r="F1240" s="35">
         <v>690.66629999999998</v>
@@ -56637,7 +56637,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712294</v>
+        <v>6497.7712544712276</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56646,7 +56646,7 @@
       <c r="L1240" s="35"/>
       <c r="M1240" s="35"/>
       <c r="N1240" s="37">
-        <v>21178.530899999998</v>
+        <v>21178.335899999998</v>
       </c>
     </row>
     <row r="1241" spans="1:15" ht="15.75" customHeight="1">
@@ -56663,7 +56663,7 @@
         <v>5874.7159286822889</v>
       </c>
       <c r="E1241" s="36">
-        <v>5328.0799479032994</v>
+        <v>5328.0748347485423</v>
       </c>
       <c r="F1241" s="35">
         <v>356.61349999999999</v>
@@ -56702,7 +56702,7 @@
         <v>5269.8946658978402</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.5941335617226</v>
+        <v>5374.5896828182213</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56740,7 +56740,7 @@
         <v>5139.5984958808658</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.4199247954284</v>
+        <v>5338.4160018889179</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56752,7 +56752,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56778,7 +56778,7 @@
         <v>4780.81965945096</v>
       </c>
       <c r="E1244" s="36">
-        <v>5246.3506333774749</v>
+        <v>5246.3469217497241</v>
       </c>
       <c r="F1244" s="35">
         <v>1388.6704</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.50708400844</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56837,7 +56837,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639499999997</v>
+        <v>48636.639500000005</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56875,7 +56875,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70115.731899999999</v>
+        <v>70115.731900000013</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56945,13 +56945,13 @@
         <v>4998.564138263052</v>
       </c>
       <c r="J1248" s="35">
-        <v>4760.2723999999998</v>
+        <v>4728.5609000000004</v>
       </c>
       <c r="K1248" s="35"/>
       <c r="L1248" s="35"/>
       <c r="M1248" s="35"/>
       <c r="N1248" s="37">
-        <v>40391.785600000003</v>
+        <v>40360.074099999998</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15.75" customHeight="1">
@@ -56980,7 +56980,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691884</v>
+        <v>5046.6456948691875</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57073,16 +57073,16 @@
         <v>45962</v>
       </c>
       <c r="B1252" s="35">
-        <v>49050.5164</v>
+        <v>49050.521399999998</v>
       </c>
       <c r="C1252" s="35">
         <v>10403.208199999999</v>
       </c>
       <c r="D1252" s="35">
-        <v>4714.9413389611873</v>
+        <v>4714.9418195821554</v>
       </c>
       <c r="E1252" s="36">
-        <v>4988.1265519761864</v>
+        <v>4988.1266890275238</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57094,7 +57094,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="36">
-        <v>5768.2127381128475</v>
+        <v>5768.2127381128485</v>
       </c>
       <c r="J1252" s="35">
         <v>10772.394200000001</v>
@@ -57103,7 +57103,7 @@
       <c r="L1252" s="35"/>
       <c r="M1252" s="35"/>
       <c r="N1252" s="37">
-        <v>60802.7451</v>
+        <v>60802.750099999997</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1">
@@ -57120,7 +57120,7 @@
         <v>5680.0691005379304</v>
       </c>
       <c r="E1253" s="36">
-        <v>5200.2711369829831</v>
+        <v>5200.2712369086048</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57149,28 +57149,28 @@
         <v>45976</v>
       </c>
       <c r="B1254" s="35">
-        <v>45106.893900000003</v>
+        <v>45094.776400000002</v>
       </c>
       <c r="C1254" s="35">
         <v>8932.4151000000002</v>
       </c>
       <c r="D1254" s="35">
-        <v>5049.7982231031792</v>
+        <v>5048.4416470972119</v>
       </c>
       <c r="E1254" s="36">
-        <v>5304.7037877180792</v>
+        <v>5304.4394026215632</v>
       </c>
       <c r="F1254" s="35">
-        <v>2124.1673000000001</v>
+        <v>2122.2244000000001</v>
       </c>
       <c r="G1254" s="35">
         <v>350.04219999999998</v>
       </c>
       <c r="H1254" s="35">
-        <v>6068.3177628297399</v>
+        <v>6062.7672892011306</v>
       </c>
       <c r="I1254" s="36">
-        <v>5620.2491328335427</v>
+        <v>5618.8509728722129</v>
       </c>
       <c r="J1254" s="35">
         <v>10669.626700000001</v>
@@ -57179,7 +57179,7 @@
       <c r="L1254" s="35"/>
       <c r="M1254" s="35"/>
       <c r="N1254" s="37">
-        <v>57900.687900000004</v>
+        <v>57886.627500000002</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1">
@@ -57196,7 +57196,7 @@
         <v>6212.1791352010268</v>
       </c>
       <c r="E1255" s="36">
-        <v>5576.4438395470397</v>
+        <v>5576.2236926967571</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57208,16 +57208,16 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5979.7288428128713</v>
+        <v>5978.5241558371008</v>
       </c>
       <c r="J1255" s="35">
-        <v>12450.415499999999</v>
+        <v>12541.2435</v>
       </c>
       <c r="K1255" s="35"/>
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99631.285299999989</v>
+        <v>99722.113299999997</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1">
@@ -57234,7 +57234,7 @@
         <v>5186.7917777368448</v>
       </c>
       <c r="E1256" s="36">
-        <v>5468.8201768837152</v>
+        <v>5468.6133747533368</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57246,7 +57246,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6259.7552690414777</v>
+        <v>6258.6852471244511</v>
       </c>
       <c r="J1256" s="35">
         <v>9150.7957999999999</v>
@@ -57263,16 +57263,16 @@
         <v>45997</v>
       </c>
       <c r="B1257" s="35">
-        <v>68665.6446</v>
+        <v>68664.174299999999</v>
       </c>
       <c r="C1257" s="35">
         <v>13091.163</v>
       </c>
       <c r="D1257" s="35">
-        <v>5245.1905609914102</v>
+        <v>5245.0782485864693</v>
       </c>
       <c r="E1257" s="36">
-        <v>5420.5343288610766</v>
+        <v>5420.2825659756754</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57284,7 +57284,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6858.778759653972</v>
+        <v>6857.6810418042405</v>
       </c>
       <c r="J1257" s="35">
         <v>6940.3462</v>
@@ -57293,7 +57293,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78554.901799999992</v>
+        <v>78553.431500000006</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1">
@@ -57310,7 +57310,7 @@
         <v>4974.8650431127226</v>
       </c>
       <c r="E1258" s="36">
-        <v>5451.7192496041425</v>
+        <v>5451.5043249706196</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57322,7 +57322,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="35">
         <v>10586.2176</v>
@@ -57339,16 +57339,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="35">
-        <v>64211.297400000003</v>
+        <v>64208.7857</v>
       </c>
       <c r="C1259" s="35">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="35">
-        <v>5452.9356578057759</v>
+        <v>5452.7223598497103</v>
       </c>
       <c r="E1259" s="36">
-        <v>5181.4535520134932</v>
+        <v>5181.3776700839608</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57360,7 +57360,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096225</v>
+        <v>7266.6202217096234</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57369,7 +57369,7 @@
       <c r="L1259" s="35"/>
       <c r="M1259" s="35"/>
       <c r="N1259" s="37">
-        <v>81459.327799999999</v>
+        <v>81456.816099999996</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57377,16 +57377,16 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="35">
-        <v>60691.1515</v>
+        <v>60663.281799999997</v>
       </c>
       <c r="C1260" s="35">
         <v>11702.9162</v>
       </c>
       <c r="D1260" s="35">
-        <v>5185.9853102254974</v>
+        <v>5183.603878151328</v>
       </c>
       <c r="E1260" s="36">
-        <v>5208.4170713213134</v>
+        <v>5207.796472965184</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57398,7 +57398,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="35">
         <v>7543.9057000000003</v>
@@ -57407,7 +57407,7 @@
       <c r="L1260" s="35"/>
       <c r="M1260" s="35"/>
       <c r="N1260" s="37">
-        <v>70427.384900000005</v>
+        <v>70399.515199999994</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57424,7 +57424,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5253.0898424485076</v>
+        <v>5252.4024891994541</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57453,16 +57453,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="35">
-        <v>31628.322899999999</v>
+        <v>31628.157599999999</v>
       </c>
       <c r="C1262" s="35">
         <v>5683.3813</v>
       </c>
       <c r="D1262" s="35">
-        <v>5565.0538351174855</v>
+        <v>5565.0247503189694</v>
       </c>
       <c r="E1262" s="36">
-        <v>5253.2482047532058</v>
+        <v>5252.515812656975</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57483,7 +57483,7 @@
       <c r="L1262" s="35"/>
       <c r="M1262" s="35"/>
       <c r="N1262" s="37">
-        <v>40579.041799999999</v>
+        <v>40578.876499999998</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1">
@@ -57500,7 +57500,7 @@
         <v>5219.8072039903755</v>
       </c>
       <c r="E1263" s="36">
-        <v>5333.0020178055702</v>
+        <v>5332.3227741320497</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57512,7 +57512,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.391308042289</v>
+        <v>6206.3913080422872</v>
       </c>
       <c r="J1263" s="35">
         <v>7830.9169000000002</v>
@@ -57529,16 +57529,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41409.7065</v>
+        <v>41409.502</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5649.6665254217287</v>
+        <v>5649.6386247940227</v>
       </c>
       <c r="E1264" s="36">
-        <v>5400.0005223154585</v>
+        <v>5399.9898861779702</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57550,7 +57550,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763587</v>
+        <v>6539.4433219763569</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57559,7 +57559,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49485.103300000002</v>
+        <v>49484.898800000003</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57576,7 +57576,7 @@
         <v>5216.5489738126962</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.0206561331461</v>
+        <v>5317.0114501231092</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57588,7 +57588,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796991011</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57614,7 +57614,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.8385735936845</v>
+        <v>5320.8336998196892</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57643,16 +57643,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77874.121899999998</v>
+        <v>77838.612500000003</v>
       </c>
       <c r="C1267" s="40">
         <v>13633.935799999999</v>
       </c>
       <c r="D1267" s="40">
-        <v>5711.7858733059311</v>
+        <v>5709.1813869330381</v>
       </c>
       <c r="E1267" s="41">
-        <v>5387.2917480007718</v>
+        <v>5386.5544724490755</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57673,7 +57673,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92949.194300000003</v>
+        <v>92913.684900000007</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57690,7 +57690,7 @@
         <v>5129.9365035262454</v>
       </c>
       <c r="E1268" s="41">
-        <v>5331.2085047493283</v>
+        <v>5330.513684283942</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57702,7 +57702,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166811</v>
+        <v>6548.0752800166792</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57711,7 +57711,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81448.451199999996</v>
+        <v>81448.45120000001</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57728,7 +57728,7 @@
         <v>5300.2894234440701</v>
       </c>
       <c r="E1269" s="41">
-        <v>5316.3886793059364</v>
+        <v>5315.6865570019045</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57740,7 +57740,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314478</v>
+        <v>6498.4408173314459</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57749,7 +57749,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64799.191599999998</v>
+        <v>64799.191599999991</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57766,7 +57766,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5430.1671690365274</v>
+        <v>5429.4744698079076</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57816,7 +57816,7 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="41">
-        <v>7489.2724524389059</v>
+        <v>7489.2724524389041</v>
       </c>
       <c r="J1271" s="40">
         <v>9735.2654000000002</v>
@@ -57833,16 +57833,16 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="40">
-        <v>37487.454599999997</v>
+        <v>37487.286899999999</v>
       </c>
       <c r="C1272" s="40">
         <v>6179.0317999999997</v>
       </c>
       <c r="D1272" s="40">
-        <v>6066.88164317264</v>
+        <v>6066.8545029983497</v>
       </c>
       <c r="E1272" s="41">
-        <v>5600.8277176121292</v>
+        <v>5600.8238912354163</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57863,7 +57863,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>46100.020699999994</v>
+        <v>46099.852999999996</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1">
@@ -57880,7 +57880,7 @@
         <v>5734.4578492489236</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.6208476663942</v>
+        <v>5668.6170148917981</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57909,16 +57909,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52043.902399999999</v>
+        <v>52043.895600000003</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5401.0291260828108</v>
+        <v>5401.0284203901874</v>
       </c>
       <c r="E1274" s="41">
-        <v>5578.958095900497</v>
+        <v>5578.9539376759185</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57939,7 +57939,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61559.389799999997</v>
+        <v>61559.383000000009</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57956,7 +57956,7 @@
         <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5669.1707954743943</v>
+        <v>5669.1660595449366</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45552.054100000001</v>
+        <v>45552.171999999999</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.4735490814192</v>
+        <v>5803.4885699085789</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.2858344238148</v>
+        <v>5698.2890360590227</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58009,13 +58009,13 @@
         <v>5606.9800390513055</v>
       </c>
       <c r="J1276" s="40">
-        <v>6631.9080999999996</v>
+        <v>6631.9624999999996</v>
       </c>
       <c r="K1276" s="40"/>
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52467.131699999998</v>
+        <v>52467.304000000004</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58023,16 +58023,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32076.707399999999</v>
+        <v>32077.028399999999</v>
       </c>
       <c r="C1277" s="40">
         <v>5483.9201000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>5849.2295319911746</v>
+        <v>5849.2880667608551</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.1246370503568</v>
+        <v>5646.1379848558299</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58047,13 +58047,13 @@
         <v>5450.6954327773046</v>
       </c>
       <c r="J1277" s="40">
-        <v>5191.1725999999999</v>
+        <v>5191.2498999999998</v>
       </c>
       <c r="K1277" s="40"/>
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37845.8632</v>
+        <v>37846.261500000001</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1">
@@ -58070,7 +58070,7 @@
         <v>5127.672791512653</v>
       </c>
       <c r="E1278" s="41">
-        <v>5538.3436776552799</v>
+        <v>5538.3590243161561</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58108,7 +58108,7 @@
         <v>6520.7043911768351</v>
       </c>
       <c r="E1279" s="41">
-        <v>5763.2685052457218</v>
+        <v>5763.2851258514602</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58123,13 +58123,13 @@
         <v>6125.9423204335426</v>
       </c>
       <c r="J1279" s="40">
-        <v>4263.8330999999998</v>
+        <v>4317.2205000000004</v>
       </c>
       <c r="K1279" s="40"/>
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>39516.809399999998</v>
+        <v>39570.196800000005</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1">
@@ -58137,37 +58137,37 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>59321.112200000003</v>
+        <v>61519.981500000002</v>
       </c>
       <c r="C1280" s="40">
-        <v>8882.1231000000007</v>
+        <v>9411.0357000000004</v>
       </c>
       <c r="D1280" s="40">
-        <v>6678.7086299220509</v>
+        <v>6537.0043703053852</v>
       </c>
       <c r="E1280" s="41">
-        <v>6043.5025591101848</v>
+        <v>6008.3885012354249</v>
       </c>
       <c r="F1280" s="40">
-        <v>362.1782</v>
+        <v>105.7779</v>
       </c>
       <c r="G1280" s="40">
-        <v>41.4559</v>
+        <v>20.419</v>
       </c>
       <c r="H1280" s="40">
-        <v>8736.4693565933921</v>
+        <v>5180.36632548117</v>
       </c>
       <c r="I1280" s="41">
-        <v>6378.4960931619516</v>
+        <v>6039.8726482427201</v>
       </c>
       <c r="J1280" s="40">
-        <v>5752.4165000000003</v>
+        <v>6284.5168000000003</v>
       </c>
       <c r="K1280" s="40"/>
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>65435.706900000005</v>
+        <v>67910.276200000008</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1">
@@ -58175,54 +58175,76 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>41672.445899999999</v>
+        <v>52399.4614</v>
       </c>
       <c r="C1281" s="40">
-        <v>6015.1122999999998</v>
+        <v>7859.3931000000002</v>
       </c>
       <c r="D1281" s="40">
-        <v>6927.9580865015605</v>
+        <v>6667.112935221423</v>
       </c>
       <c r="E1281" s="41">
-        <v>6343.9733408001248</v>
+        <v>6270.6904790005983</v>
       </c>
       <c r="F1281" s="40">
-        <v>2144.5378999999998</v>
+        <v>2628.1927000000001</v>
       </c>
       <c r="G1281" s="40">
-        <v>243.31120000000001</v>
+        <v>291.64049999999997</v>
       </c>
       <c r="H1281" s="40">
-        <v>8813.9711612124702</v>
+        <v>9011.7548831523764</v>
       </c>
       <c r="I1281" s="41">
-        <v>7949.6286399529408</v>
+        <v>7968.3881375710962</v>
       </c>
       <c r="J1281" s="40">
-        <v>3276.6959999999999</v>
+        <v>4667.2160999999996</v>
       </c>
       <c r="K1281" s="40"/>
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>47093.679799999998</v>
+        <v>59694.870199999998</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1282" s="39"/>
-      <c r="B1282" s="40"/>
-      <c r="C1282" s="40"/>
-      <c r="D1282" s="40"/>
-      <c r="E1282" s="41"/>
-      <c r="F1282" s="40"/>
-      <c r="G1282" s="40"/>
-      <c r="H1282" s="40"/>
-      <c r="I1282" s="41"/>
-      <c r="J1282" s="40"/>
+      <c r="A1282" s="39">
+        <v>46172</v>
+      </c>
+      <c r="B1282" s="40">
+        <v>34578.747900000002</v>
+      </c>
+      <c r="C1282" s="40">
+        <v>5780.4363000000003</v>
+      </c>
+      <c r="D1282" s="40">
+        <v>5982.030785461644</v>
+      </c>
+      <c r="E1282" s="41">
+        <v>6460.9162499408712</v>
+      </c>
+      <c r="F1282" s="40">
+        <v>1069.8532</v>
+      </c>
+      <c r="G1282" s="40">
+        <v>177.16669999999999</v>
+      </c>
+      <c r="H1282" s="40">
+        <v>6038.6810839734553</v>
+      </c>
+      <c r="I1282" s="41">
+        <v>7607.974533085011</v>
+      </c>
+      <c r="J1282" s="40">
+        <v>11542.048699999999</v>
+      </c>
       <c r="K1282" s="40"/>
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
-      <c r="N1282" s="40"/>
+      <c r="N1282" s="40">
+        <v>47190.649799999999</v>
+      </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1283" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177882A8-369C-4D8C-A076-CB4F600D017B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496AF834-5847-4254-AA7D-F1F0589E7FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55497,7 +55497,7 @@
         <v>6882.5719118850975</v>
       </c>
       <c r="I1210" s="36">
-        <v>5131.0721532756543</v>
+        <v>5131.0721532756534</v>
       </c>
       <c r="J1210" s="35">
         <v>5833.4898999999996</v>
@@ -55725,7 +55725,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -56198,16 +56198,16 @@
         <v>45801</v>
       </c>
       <c r="B1229" s="35">
-        <v>54495.981399999997</v>
+        <v>54494.046499999997</v>
       </c>
       <c r="C1229" s="35">
         <v>10629.917100000001</v>
       </c>
       <c r="D1229" s="35">
-        <v>5126.6609971962998</v>
+        <v>5126.4789731991414</v>
       </c>
       <c r="E1229" s="36">
-        <v>4983.3044849606677</v>
+        <v>4983.2680355316998</v>
       </c>
       <c r="F1229" s="35">
         <v>465.10070000000002</v>
@@ -56228,7 +56228,7 @@
       <c r="L1229" s="35"/>
       <c r="M1229" s="35"/>
       <c r="N1229" s="37">
-        <v>66450.755099999995</v>
+        <v>66448.820199999987</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56245,7 +56245,7 @@
         <v>5223.7943789585233</v>
       </c>
       <c r="E1230" s="36">
-        <v>5028.2598794368114</v>
+        <v>5028.2222542783966</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56283,7 +56283,7 @@
         <v>4742.2363274314139</v>
       </c>
       <c r="E1231" s="36">
-        <v>4961.194416586035</v>
+        <v>4961.1603565408841</v>
       </c>
       <c r="F1231" s="35">
         <v>1023.9116</v>
@@ -56321,7 +56321,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.5700041555092</v>
+        <v>4909.5321891132262</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56409,7 +56409,7 @@
         <v>6232.9559455378785</v>
       </c>
       <c r="I1234" s="36">
-        <v>6273.3822151253535</v>
+        <v>6273.3822151253544</v>
       </c>
       <c r="J1234" s="35">
         <v>8405.0920000000006</v>
@@ -56502,16 +56502,16 @@
         <v>45857</v>
       </c>
       <c r="B1237" s="35">
-        <v>45810.579400000002</v>
+        <v>45802.864500000003</v>
       </c>
       <c r="C1237" s="35">
         <v>8676.5638999999992</v>
       </c>
       <c r="D1237" s="35">
-        <v>5279.8066063917322</v>
+        <v>5278.9174410390733</v>
       </c>
       <c r="E1237" s="36">
-        <v>4925.9313697171456</v>
+        <v>4925.748394190472</v>
       </c>
       <c r="F1237" s="35">
         <v>770.73030000000006</v>
@@ -56532,7 +56532,7 @@
       <c r="L1237" s="35"/>
       <c r="M1237" s="35"/>
       <c r="N1237" s="37">
-        <v>54396.929900000003</v>
+        <v>54389.215000000004</v>
       </c>
     </row>
     <row r="1238" spans="1:15" ht="15.75" customHeight="1">
@@ -56549,7 +56549,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.5363068137885</v>
+        <v>5020.3654657565703</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56587,7 +56587,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="36">
-        <v>4983.7742099543975</v>
+        <v>4983.6002426995319</v>
       </c>
       <c r="F1239" s="35">
         <v>1951.8497</v>
@@ -56625,7 +56625,7 @@
         <v>5735.9493555393647</v>
       </c>
       <c r="E1240" s="36">
-        <v>5190.1774358351622</v>
+        <v>5189.9625448685747</v>
       </c>
       <c r="F1240" s="35">
         <v>690.66629999999998</v>
@@ -56663,7 +56663,7 @@
         <v>5874.7159286822889</v>
       </c>
       <c r="E1241" s="36">
-        <v>5328.0748347485423</v>
+        <v>5327.8725399914329</v>
       </c>
       <c r="F1241" s="35">
         <v>356.61349999999999</v>
@@ -56702,7 +56702,7 @@
         <v>5269.8946658978402</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.5896828182213</v>
+        <v>5374.5896828182204</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56945,13 +56945,13 @@
         <v>4998.564138263052</v>
       </c>
       <c r="J1248" s="35">
-        <v>4728.5609000000004</v>
+        <v>4728.5039999999999</v>
       </c>
       <c r="K1248" s="35"/>
       <c r="L1248" s="35"/>
       <c r="M1248" s="35"/>
       <c r="N1248" s="37">
-        <v>40360.074099999998</v>
+        <v>40360.017200000002</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15.75" customHeight="1">
@@ -57035,16 +57035,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="35">
-        <v>54377.964800000002</v>
+        <v>54430.097099999999</v>
       </c>
       <c r="C1251" s="35">
-        <v>9494.5689999999995</v>
+        <v>9527.3052000000007</v>
       </c>
       <c r="D1251" s="35">
-        <v>5727.270484842441</v>
+        <v>5713.0632384905648</v>
       </c>
       <c r="E1251" s="36">
-        <v>5015.1634437707298</v>
+        <v>5012.0518895670184</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57065,7 +57065,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>60951.882299999997</v>
+        <v>61004.014599999995</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1">
@@ -57082,7 +57082,7 @@
         <v>4714.9418195821554</v>
       </c>
       <c r="E1252" s="36">
-        <v>4988.1266890275238</v>
+        <v>4985.0824949390271</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57120,7 +57120,7 @@
         <v>5680.0691005379304</v>
       </c>
       <c r="E1253" s="36">
-        <v>5200.2712369086048</v>
+        <v>5197.9124406208248</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57149,16 +57149,16 @@
         <v>45976</v>
       </c>
       <c r="B1254" s="35">
-        <v>45094.776400000002</v>
+        <v>45068.991300000002</v>
       </c>
       <c r="C1254" s="35">
         <v>8932.4151000000002</v>
       </c>
       <c r="D1254" s="35">
-        <v>5048.4416470972119</v>
+        <v>5045.5549585912104</v>
       </c>
       <c r="E1254" s="36">
-        <v>5304.4394026215632</v>
+        <v>5301.2265139181754</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57179,7 +57179,7 @@
       <c r="L1254" s="35"/>
       <c r="M1254" s="35"/>
       <c r="N1254" s="37">
-        <v>57886.627500000002</v>
+        <v>57860.842400000001</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1">
@@ -57187,16 +57187,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="35">
-        <v>84435.007599999997</v>
+        <v>84407.725099999996</v>
       </c>
       <c r="C1255" s="35">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="35">
-        <v>6212.1791352010268</v>
+        <v>6210.1718661538207</v>
       </c>
       <c r="E1255" s="36">
-        <v>5576.2236926967571</v>
+        <v>5572.8908998252309</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57217,7 +57217,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99722.113299999997</v>
+        <v>99694.830799999996</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1">
@@ -57234,7 +57234,7 @@
         <v>5186.7917777368448</v>
       </c>
       <c r="E1256" s="36">
-        <v>5468.6133747533368</v>
+        <v>5467.7073278815797</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57249,13 +57249,13 @@
         <v>6258.6852471244511</v>
       </c>
       <c r="J1256" s="35">
-        <v>9150.7957999999999</v>
+        <v>9248.3009999999995</v>
       </c>
       <c r="K1256" s="35"/>
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77288.638299999991</v>
+        <v>77386.143500000006</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57272,7 +57272,7 @@
         <v>5245.0782485864693</v>
       </c>
       <c r="E1257" s="36">
-        <v>5420.2825659756754</v>
+        <v>5419.299297742602</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57301,16 +57301,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="35">
-        <v>60363.653299999998</v>
+        <v>60353.478300000002</v>
       </c>
       <c r="C1258" s="35">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="35">
-        <v>4974.8650431127226</v>
+        <v>4974.0264714053064</v>
       </c>
       <c r="E1258" s="36">
-        <v>5451.5043249706196</v>
+        <v>5450.802465432489</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57325,13 +57325,13 @@
         <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="35">
-        <v>10586.2176</v>
+        <v>10671.651599999999</v>
       </c>
       <c r="K1258" s="35"/>
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75310.772700000001</v>
+        <v>75386.031699999992</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57339,16 +57339,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="35">
-        <v>64208.7857</v>
+        <v>64199.741600000001</v>
       </c>
       <c r="C1259" s="35">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="35">
-        <v>5452.7223598497103</v>
+        <v>5451.9543190628137</v>
       </c>
       <c r="E1259" s="36">
-        <v>5181.3776700839608</v>
+        <v>5181.0114263893702</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57369,7 +57369,7 @@
       <c r="L1259" s="35"/>
       <c r="M1259" s="35"/>
       <c r="N1259" s="37">
-        <v>81456.816099999996</v>
+        <v>81447.771999999997</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1">
@@ -57377,16 +57377,16 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="35">
-        <v>60663.281799999997</v>
+        <v>60630.440399999999</v>
       </c>
       <c r="C1260" s="35">
         <v>11702.9162</v>
       </c>
       <c r="D1260" s="35">
-        <v>5183.603878151328</v>
+        <v>5180.797620340134</v>
       </c>
       <c r="E1260" s="36">
-        <v>5207.796472965184</v>
+        <v>5206.7821264556014</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57407,7 +57407,7 @@
       <c r="L1260" s="35"/>
       <c r="M1260" s="35"/>
       <c r="N1260" s="37">
-        <v>70399.515199999994</v>
+        <v>70366.67379999999</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57424,7 +57424,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5252.4024891994541</v>
+        <v>5251.2713456055353</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57462,7 +57462,7 @@
         <v>5565.0247503189694</v>
       </c>
       <c r="E1262" s="36">
-        <v>5252.515812656975</v>
+        <v>5251.2676025810651</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57500,7 +57500,7 @@
         <v>5219.8072039903755</v>
       </c>
       <c r="E1263" s="36">
-        <v>5332.3227741320497</v>
+        <v>5331.3079547674261</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57529,16 +57529,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41409.502</v>
+        <v>41408.165699999998</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5649.6386247940227</v>
+        <v>5649.4563088585564</v>
       </c>
       <c r="E1264" s="36">
-        <v>5399.9898861779702</v>
+        <v>5399.95145169845</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57559,7 +57559,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49484.898800000003</v>
+        <v>49483.5625</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57576,7 +57576,7 @@
         <v>5216.5489738126962</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.0114501231092</v>
+        <v>5316.9781835162548</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57614,7 +57614,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.8336998196892</v>
+        <v>5320.8018522686316</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57652,7 +57652,7 @@
         <v>5709.1813869330381</v>
       </c>
       <c r="E1267" s="41">
-        <v>5386.5544724490755</v>
+        <v>5386.5268859541893</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57690,7 +57690,7 @@
         <v>5129.9365035262454</v>
       </c>
       <c r="E1268" s="41">
-        <v>5330.513684283942</v>
+        <v>5330.487536599444</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57833,16 +57833,16 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="40">
-        <v>37487.286899999999</v>
+        <v>37374.408199999998</v>
       </c>
       <c r="C1272" s="40">
-        <v>6179.0317999999997</v>
+        <v>6156.4367000000002</v>
       </c>
       <c r="D1272" s="40">
-        <v>6066.8545029983497</v>
+        <v>6070.7857517644898</v>
       </c>
       <c r="E1272" s="41">
-        <v>5600.8238912354163</v>
+        <v>5601.1360142451704</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57863,7 +57863,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>46099.852999999996</v>
+        <v>45986.974299999994</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1">
@@ -57880,7 +57880,7 @@
         <v>5734.4578492489236</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.6170148917981</v>
+        <v>5668.9646871781533</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57909,16 +57909,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52043.895600000003</v>
+        <v>52121.303800000002</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5401.0284203901874</v>
+        <v>5409.061713888902</v>
       </c>
       <c r="E1274" s="41">
-        <v>5578.9539376759185</v>
+        <v>5581.1137200602316</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57939,7 +57939,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61559.383000000009</v>
+        <v>61636.791200000007</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57956,7 +57956,7 @@
         <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5669.1660595449366</v>
+        <v>5671.6814408484342</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45552.171999999999</v>
+        <v>45554.624799999998</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.4885699085789</v>
+        <v>5803.8010642670097</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.2890360590227</v>
+        <v>5700.5904383029092</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58009,13 +58009,13 @@
         <v>5606.9800390513055</v>
       </c>
       <c r="J1276" s="40">
-        <v>6631.9624999999996</v>
+        <v>6631.9660000000003</v>
       </c>
       <c r="K1276" s="40"/>
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52467.304000000004</v>
+        <v>52469.760300000002</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58023,16 +58023,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32077.028399999999</v>
+        <v>32077.017100000001</v>
       </c>
       <c r="C1277" s="40">
         <v>5483.9201000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>5849.2880667608551</v>
+        <v>5849.2860061910824</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.1379848558299</v>
+        <v>5648.6045857876179</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58047,13 +58047,13 @@
         <v>5450.6954327773046</v>
       </c>
       <c r="J1277" s="40">
-        <v>5191.2498999999998</v>
+        <v>5183.0592999999999</v>
       </c>
       <c r="K1277" s="40"/>
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37846.261500000001</v>
+        <v>37838.059600000001</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1">
@@ -58061,16 +58061,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>29337.1374</v>
+        <v>29337.917399999998</v>
       </c>
       <c r="C1278" s="40">
         <v>5721.3356999999996</v>
       </c>
       <c r="D1278" s="40">
-        <v>5127.672791512653</v>
+        <v>5127.8091233136347</v>
       </c>
       <c r="E1278" s="41">
-        <v>5538.3590243161561</v>
+        <v>5539.7385838806958</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58091,7 +58091,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42377.1227</v>
+        <v>42377.902699999999</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1">
@@ -58099,16 +58099,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>34284.5602</v>
+        <v>34280.161200000002</v>
       </c>
       <c r="C1279" s="40">
         <v>5257.8001000000004</v>
       </c>
       <c r="D1279" s="40">
-        <v>6520.7043911768351</v>
+        <v>6519.8677294711151</v>
       </c>
       <c r="E1279" s="41">
-        <v>5763.2851258514602</v>
+        <v>5763.2405353678496</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58129,7 +58129,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>39570.196800000005</v>
+        <v>39565.797800000008</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1">
@@ -58137,16 +58137,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61519.981500000002</v>
+        <v>61910.565600000002</v>
       </c>
       <c r="C1280" s="40">
-        <v>9411.0357000000004</v>
+        <v>9475.2666000000008</v>
       </c>
       <c r="D1280" s="40">
-        <v>6537.0043703053852</v>
+        <v>6533.9127872138179</v>
       </c>
       <c r="E1280" s="41">
-        <v>6008.3885012354249</v>
+        <v>6008.4246709199278</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58161,13 +58161,13 @@
         <v>6039.8726482427201</v>
       </c>
       <c r="J1280" s="40">
-        <v>6284.5168000000003</v>
+        <v>6167.6786000000002</v>
       </c>
       <c r="K1280" s="40"/>
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>67910.276200000008</v>
+        <v>68184.022100000002</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1">
@@ -58175,16 +58175,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>52399.4614</v>
+        <v>57692.023999999998</v>
       </c>
       <c r="C1281" s="40">
-        <v>7859.3931000000002</v>
+        <v>8631.2489999999998</v>
       </c>
       <c r="D1281" s="40">
-        <v>6667.112935221423</v>
+        <v>6684.0875521028302</v>
       </c>
       <c r="E1281" s="41">
-        <v>6270.6904790005983</v>
+        <v>6285.2973397819242</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58199,13 +58199,13 @@
         <v>7968.3881375710962</v>
       </c>
       <c r="J1281" s="40">
-        <v>4667.2160999999996</v>
+        <v>5104.8814000000002</v>
       </c>
       <c r="K1281" s="40"/>
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>59694.870199999998</v>
+        <v>65425.098099999996</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1">
@@ -58213,54 +58213,76 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>34578.747900000002</v>
+        <v>51580.081100000003</v>
       </c>
       <c r="C1282" s="40">
-        <v>5780.4363000000003</v>
+        <v>9002.8482000000004</v>
       </c>
       <c r="D1282" s="40">
-        <v>5982.030785461644</v>
+        <v>5729.3069875375659</v>
       </c>
       <c r="E1282" s="41">
-        <v>6460.9162499408712</v>
+        <v>6354.8186012473689</v>
       </c>
       <c r="F1282" s="40">
-        <v>1069.8532</v>
+        <v>2066.8542000000002</v>
       </c>
       <c r="G1282" s="40">
-        <v>177.16669999999999</v>
+        <v>307.53489999999999</v>
       </c>
       <c r="H1282" s="40">
-        <v>6038.6810839734553</v>
+        <v>6720.7142994177257</v>
       </c>
       <c r="I1282" s="41">
-        <v>7607.974533085011</v>
+        <v>7614.5278909516492</v>
       </c>
       <c r="J1282" s="40">
-        <v>11542.048699999999</v>
+        <v>15282.974099999999</v>
       </c>
       <c r="K1282" s="40"/>
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>47190.649799999999</v>
+        <v>68929.909400000004</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1283" s="39"/>
-      <c r="B1283" s="40"/>
-      <c r="C1283" s="40"/>
-      <c r="D1283" s="40"/>
-      <c r="E1283" s="41"/>
-      <c r="F1283" s="40"/>
-      <c r="G1283" s="40"/>
-      <c r="H1283" s="40"/>
-      <c r="I1283" s="41"/>
-      <c r="J1283" s="40"/>
+      <c r="A1283" s="39">
+        <v>46179</v>
+      </c>
+      <c r="B1283" s="40">
+        <v>37665.340600000003</v>
+      </c>
+      <c r="C1283" s="40">
+        <v>6493.8464000000004</v>
+      </c>
+      <c r="D1283" s="40">
+        <v>5800.1588396054458</v>
+      </c>
+      <c r="E1283" s="41">
+        <v>6156.3103501088408</v>
+      </c>
+      <c r="F1283" s="40">
+        <v>1201.9286</v>
+      </c>
+      <c r="G1283" s="40">
+        <v>168.2158</v>
+      </c>
+      <c r="H1283" s="40">
+        <v>7145.1587781884928</v>
+      </c>
+      <c r="I1283" s="41">
+        <v>7646.8025379423061</v>
+      </c>
+      <c r="J1283" s="40">
+        <v>5643.9061000000002</v>
+      </c>
       <c r="K1283" s="40"/>
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
-      <c r="N1283" s="40"/>
+      <c r="N1283" s="40">
+        <v>44511.175300000003</v>
+      </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1284" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496AF834-5847-4254-AA7D-F1F0589E7FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E046B533-FA1F-4014-9AAD-642C0B1777DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46183</v>
+        <v>46190</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55485,7 +55485,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55582,7 +55582,7 @@
       <c r="L1212" s="35"/>
       <c r="M1212" s="35"/>
       <c r="N1212" s="37">
-        <v>45765.935099999995</v>
+        <v>45765.935100000002</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1">
@@ -55649,7 +55649,7 @@
         <v>5483.9420094229508</v>
       </c>
       <c r="I1214" s="36">
-        <v>5618.8491234155326</v>
+        <v>5618.8491234155317</v>
       </c>
       <c r="J1214" s="35">
         <v>8807.2849999999999</v>
@@ -55658,7 +55658,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76702.561400000006</v>
+        <v>76702.561399999991</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1">
@@ -55725,7 +55725,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55751,7 +55751,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4706.1810921613296</v>
+        <v>4706.1810921613305</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55789,7 +55789,7 @@
         <v>4730.2049304767315</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.4026964800232</v>
+        <v>4736.4026964800241</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55827,7 +55827,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4755.4225489108821</v>
+        <v>4755.4225489108812</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55848,7 +55848,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.675999999999</v>
+        <v>62640.676000000007</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1">
@@ -55962,7 +55962,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313499999997</v>
+        <v>52967.313500000004</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1">
@@ -56228,7 +56228,7 @@
       <c r="L1229" s="35"/>
       <c r="M1229" s="35"/>
       <c r="N1229" s="37">
-        <v>66448.820199999987</v>
+        <v>66448.820200000002</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1">
@@ -56304,7 +56304,7 @@
       <c r="L1231" s="35"/>
       <c r="M1231" s="35"/>
       <c r="N1231" s="37">
-        <v>75298.126700000008</v>
+        <v>75298.126699999993</v>
       </c>
     </row>
     <row r="1232" spans="1:14" ht="15.75" customHeight="1">
@@ -56321,7 +56321,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.5321891132262</v>
+        <v>4909.532189113228</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56447,7 +56447,7 @@
         <v>5270.8131997196551</v>
       </c>
       <c r="I1235" s="36">
-        <v>6279.4686229430445</v>
+        <v>6279.4686229430436</v>
       </c>
       <c r="J1235" s="35">
         <v>12601.2554</v>
@@ -56561,7 +56561,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253513</v>
+        <v>5662.7424793253522</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56570,7 +56570,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359399999994</v>
+        <v>53725.359400000001</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1">
@@ -56599,7 +56599,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316088</v>
+        <v>6067.7529720316097</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56637,7 +56637,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712276</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56702,7 +56702,7 @@
         <v>5269.8946658978402</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.5896828182204</v>
+        <v>5374.5896828182213</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56752,7 +56752,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084427</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072237</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56837,7 +56837,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639500000005</v>
+        <v>48636.639499999997</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1">
@@ -56875,7 +56875,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70115.731900000013</v>
+        <v>70115.731899999999</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1">
@@ -56904,7 +56904,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5394.2932473875317</v>
+        <v>5394.2932473875308</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -56980,7 +56980,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691875</v>
+        <v>5046.6456948691884</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57073,16 +57073,16 @@
         <v>45962</v>
       </c>
       <c r="B1252" s="35">
-        <v>49050.521399999998</v>
+        <v>49049.664499999999</v>
       </c>
       <c r="C1252" s="35">
         <v>10403.208199999999</v>
       </c>
       <c r="D1252" s="35">
-        <v>4714.9418195821554</v>
+        <v>4714.859450760584</v>
       </c>
       <c r="E1252" s="36">
-        <v>4985.0824949390271</v>
+        <v>4985.0590281379182</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57103,7 +57103,7 @@
       <c r="L1252" s="35"/>
       <c r="M1252" s="35"/>
       <c r="N1252" s="37">
-        <v>60802.750099999997</v>
+        <v>60801.893199999999</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1">
@@ -57120,7 +57120,7 @@
         <v>5680.0691005379304</v>
       </c>
       <c r="E1253" s="36">
-        <v>5197.9124406208248</v>
+        <v>5197.8953265644177</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57158,7 +57158,7 @@
         <v>5045.5549585912104</v>
       </c>
       <c r="E1254" s="36">
-        <v>5301.2265139181754</v>
+        <v>5301.2078233239317</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57196,7 +57196,7 @@
         <v>6210.1718661538207</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.8908998252309</v>
+        <v>5572.8753347757183</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57234,7 +57234,7 @@
         <v>5186.7917777368448</v>
       </c>
       <c r="E1256" s="36">
-        <v>5467.7073278815797</v>
+        <v>5467.6926976445911</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57246,7 +57246,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244511</v>
+        <v>6258.6852471244501</v>
       </c>
       <c r="J1256" s="35">
         <v>9248.3009999999995</v>
@@ -57255,7 +57255,7 @@
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77386.143500000006</v>
+        <v>77386.143499999991</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57284,7 +57284,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6857.6810418042405</v>
+        <v>6857.6810418042396</v>
       </c>
       <c r="J1257" s="35">
         <v>6940.3462</v>
@@ -57310,7 +57310,7 @@
         <v>4974.0264714053064</v>
       </c>
       <c r="E1258" s="36">
-        <v>5450.802465432489</v>
+        <v>5450.8024654324872</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57322,7 +57322,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="35">
         <v>10671.651599999999</v>
@@ -57331,7 +57331,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75386.031699999992</v>
+        <v>75386.031700000007</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57360,7 +57360,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096234</v>
+        <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57398,7 +57398,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="35">
         <v>7543.9057000000003</v>
@@ -57407,7 +57407,7 @@
       <c r="L1260" s="35"/>
       <c r="M1260" s="35"/>
       <c r="N1260" s="37">
-        <v>70366.67379999999</v>
+        <v>70366.673800000004</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1">
@@ -57424,7 +57424,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5251.2713456055353</v>
+        <v>5251.2713456055344</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57491,16 +57491,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58954.989800000003</v>
+        <v>58958.789799999999</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5219.8072039903755</v>
+        <v>5220.1436516336098</v>
       </c>
       <c r="E1263" s="36">
-        <v>5331.3079547674261</v>
+        <v>5331.400022752422</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57512,7 +57512,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.3913080422872</v>
+        <v>6206.391308042289</v>
       </c>
       <c r="J1263" s="35">
         <v>7830.9169000000002</v>
@@ -57521,7 +57521,7 @@
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69885.229300000006</v>
+        <v>69889.029299999995</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1">
@@ -57529,16 +57529,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41408.165699999998</v>
+        <v>41408.075799999999</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5649.4563088585564</v>
+        <v>5649.4440434970375</v>
       </c>
       <c r="E1264" s="36">
-        <v>5399.95145169845</v>
+        <v>5400.0581610919007</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57559,7 +57559,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49483.5625</v>
+        <v>49483.472600000001</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1">
@@ -57567,16 +57567,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66743.524999999994</v>
+        <v>66766.726699999999</v>
       </c>
       <c r="C1265" s="40">
         <v>12794.5746</v>
       </c>
       <c r="D1265" s="40">
-        <v>5216.5489738126962</v>
+        <v>5218.3623752523981</v>
       </c>
       <c r="E1265" s="41">
-        <v>5316.9781835162548</v>
+        <v>5317.6481410634788</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57597,7 +57597,7 @@
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77848.217399999994</v>
+        <v>77871.419099999999</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57614,7 +57614,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.8018522686316</v>
+        <v>5321.4432313934767</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57652,7 +57652,7 @@
         <v>5709.1813869330381</v>
       </c>
       <c r="E1267" s="41">
-        <v>5386.5268859541893</v>
+        <v>5387.0040045297501</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57690,7 +57690,7 @@
         <v>5129.9365035262454</v>
       </c>
       <c r="E1268" s="41">
-        <v>5330.487536599444</v>
+        <v>5330.9397704201201</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57702,7 +57702,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57711,7 +57711,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81448.45120000001</v>
+        <v>81448.451199999996</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57728,7 +57728,7 @@
         <v>5300.2894234440701</v>
       </c>
       <c r="E1269" s="41">
-        <v>5315.6865570019045</v>
+        <v>5316.1453209084048</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57740,7 +57740,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314459</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57749,7 +57749,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64799.191599999991</v>
+        <v>64799.191599999998</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1">
@@ -57816,7 +57816,7 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="41">
-        <v>7489.2724524389041</v>
+        <v>7489.2724524389059</v>
       </c>
       <c r="J1271" s="40">
         <v>9735.2654000000002</v>
@@ -57863,7 +57863,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>45986.974299999994</v>
+        <v>45986.974300000002</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1">
@@ -57880,7 +57880,7 @@
         <v>5734.4578492489236</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.9646871781533</v>
+        <v>5668.9646871781524</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57939,7 +57939,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61636.791200000007</v>
+        <v>61636.7912</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1">
@@ -57985,16 +57985,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45554.624799999998</v>
+        <v>45554.353900000002</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.8010642670097</v>
+        <v>5803.7665507633819</v>
       </c>
       <c r="E1276" s="41">
-        <v>5700.5904383029092</v>
+        <v>5700.5826316154435</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58015,7 +58015,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52469.760300000002</v>
+        <v>52469.489400000006</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1">
@@ -58032,7 +58032,7 @@
         <v>5849.2860061910824</v>
       </c>
       <c r="E1277" s="41">
-        <v>5648.6045857876179</v>
+        <v>5648.5962175383647</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58070,7 +58070,7 @@
         <v>5127.8091233136347</v>
       </c>
       <c r="E1278" s="41">
-        <v>5539.7385838806958</v>
+        <v>5539.729111539772</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58085,13 +58085,13 @@
         <v>5643.202064907332</v>
       </c>
       <c r="J1278" s="40">
-        <v>12627.7737</v>
+        <v>12650.7237</v>
       </c>
       <c r="K1278" s="40"/>
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42377.902699999999</v>
+        <v>42400.852700000003</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1">
@@ -58099,16 +58099,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>34280.161200000002</v>
+        <v>33888.165699999998</v>
       </c>
       <c r="C1279" s="40">
         <v>5257.8001000000004</v>
       </c>
       <c r="D1279" s="40">
-        <v>6519.8677294711151</v>
+        <v>6445.3126888563129</v>
       </c>
       <c r="E1279" s="41">
-        <v>5763.2405353678496</v>
+        <v>5748.3858869767437</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58123,13 +58123,13 @@
         <v>6125.9423204335426</v>
       </c>
       <c r="J1279" s="40">
-        <v>4317.2205000000004</v>
+        <v>4317.6104999999998</v>
       </c>
       <c r="K1279" s="40"/>
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>39565.797800000008</v>
+        <v>39174.192299999995</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1">
@@ -58137,16 +58137,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61910.565600000002</v>
+        <v>61742.853000000003</v>
       </c>
       <c r="C1280" s="40">
-        <v>9475.2666000000008</v>
+        <v>9434.8724000000002</v>
       </c>
       <c r="D1280" s="40">
-        <v>6533.9127872138179</v>
+        <v>6544.1110788101387</v>
       </c>
       <c r="E1280" s="41">
-        <v>6008.4246709199278</v>
+        <v>5997.2725842604559</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58161,13 +58161,13 @@
         <v>6039.8726482427201</v>
       </c>
       <c r="J1280" s="40">
-        <v>6167.6786000000002</v>
+        <v>6167.7145</v>
       </c>
       <c r="K1280" s="40"/>
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>68184.022100000002</v>
+        <v>68016.345400000006</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1">
@@ -58175,16 +58175,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>57692.023999999998</v>
+        <v>57621.727800000001</v>
       </c>
       <c r="C1281" s="40">
-        <v>8631.2489999999998</v>
+        <v>8634.5971000000009</v>
       </c>
       <c r="D1281" s="40">
-        <v>6684.0875521028302</v>
+        <v>6673.3545448229415</v>
       </c>
       <c r="E1281" s="41">
-        <v>6285.2973397819242</v>
+        <v>6271.9961690505406</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58199,13 +58199,13 @@
         <v>7968.3881375710962</v>
       </c>
       <c r="J1281" s="40">
-        <v>5104.8814000000002</v>
+        <v>5222.5685000000003</v>
       </c>
       <c r="K1281" s="40"/>
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>65425.098099999996</v>
+        <v>65472.489000000001</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1">
@@ -58213,16 +58213,16 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>51580.081100000003</v>
+        <v>59567.664799999999</v>
       </c>
       <c r="C1282" s="40">
-        <v>9002.8482000000004</v>
+        <v>10696.757600000001</v>
       </c>
       <c r="D1282" s="40">
-        <v>5729.3069875375659</v>
+        <v>5568.7589667358634</v>
       </c>
       <c r="E1282" s="41">
-        <v>6354.8186012473689</v>
+        <v>6264.3000387708789</v>
       </c>
       <c r="F1282" s="40">
         <v>2066.8542000000002</v>
@@ -58237,13 +58237,13 @@
         <v>7614.5278909516492</v>
       </c>
       <c r="J1282" s="40">
-        <v>15282.974099999999</v>
+        <v>15038.177299999999</v>
       </c>
       <c r="K1282" s="40"/>
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>68929.909400000004</v>
+        <v>76672.696299999996</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1">
@@ -58251,54 +58251,76 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>37665.340600000003</v>
+        <v>54710.134400000003</v>
       </c>
       <c r="C1283" s="40">
-        <v>6493.8464000000004</v>
+        <v>9832.2266</v>
       </c>
       <c r="D1283" s="40">
-        <v>5800.1588396054458</v>
+        <v>5564.3687463427668</v>
       </c>
       <c r="E1283" s="41">
-        <v>6156.3103501088408</v>
+        <v>5999.5081392186685</v>
       </c>
       <c r="F1283" s="40">
-        <v>1201.9286</v>
+        <v>1648.3975</v>
       </c>
       <c r="G1283" s="40">
-        <v>168.2158</v>
+        <v>251.851</v>
       </c>
       <c r="H1283" s="40">
-        <v>7145.1587781884928</v>
+        <v>6545.1298585274626</v>
       </c>
       <c r="I1283" s="41">
-        <v>7646.8025379423061</v>
+        <v>7431.828400112322</v>
       </c>
       <c r="J1283" s="40">
-        <v>5643.9061000000002</v>
+        <v>7077.3932000000004</v>
       </c>
       <c r="K1283" s="40"/>
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>44511.175300000003</v>
+        <v>63435.925100000008</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1284" s="39"/>
-      <c r="B1284" s="40"/>
-      <c r="C1284" s="40"/>
-      <c r="D1284" s="40"/>
-      <c r="E1284" s="41"/>
-      <c r="F1284" s="40"/>
-      <c r="G1284" s="40"/>
-      <c r="H1284" s="40"/>
-      <c r="I1284" s="41"/>
-      <c r="J1284" s="40"/>
+      <c r="A1284" s="39">
+        <v>46186</v>
+      </c>
+      <c r="B1284" s="40">
+        <v>24101.7084</v>
+      </c>
+      <c r="C1284" s="40">
+        <v>3408.1374999999998</v>
+      </c>
+      <c r="D1284" s="40">
+        <v>7071.812214149224</v>
+      </c>
+      <c r="E1284" s="41">
+        <v>5964.0909533951171</v>
+      </c>
+      <c r="F1284" s="40">
+        <v>591.27030000000002</v>
+      </c>
+      <c r="G1284" s="40">
+        <v>88.416600000000003</v>
+      </c>
+      <c r="H1284" s="40">
+        <v>6687.322290158183</v>
+      </c>
+      <c r="I1284" s="41">
+        <v>7334.9008503305686</v>
+      </c>
+      <c r="J1284" s="40">
+        <v>9730.3516999999993</v>
+      </c>
       <c r="K1284" s="40"/>
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
-      <c r="N1284" s="40"/>
+      <c r="N1284" s="40">
+        <v>34423.330399999999</v>
+      </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1285" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E046B533-FA1F-4014-9AAD-642C0B1777DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C190AC22-59DB-4944-AB83-C78B3CE871E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -56017,7 +56017,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803258</v>
+        <v>4673.0018865803249</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56464,16 +56464,16 @@
         <v>45850</v>
       </c>
       <c r="B1236" s="35">
-        <v>38585.658499999998</v>
+        <v>38581.624600000003</v>
       </c>
       <c r="C1236" s="35">
         <v>8635.1026999999995</v>
       </c>
       <c r="D1236" s="35">
-        <v>4468.4654995475621</v>
+        <v>4467.9983481840936</v>
       </c>
       <c r="E1236" s="36">
-        <v>4832.2703724109051</v>
+        <v>4832.1827724769955</v>
       </c>
       <c r="F1236" s="35">
         <v>509.77510000000001</v>
@@ -56494,7 +56494,7 @@
       <c r="L1236" s="35"/>
       <c r="M1236" s="35"/>
       <c r="N1236" s="37">
-        <v>46129.642399999997</v>
+        <v>46125.608500000002</v>
       </c>
     </row>
     <row r="1237" spans="1:15" ht="15.75" customHeight="1">
@@ -56511,7 +56511,7 @@
         <v>5278.9174410390733</v>
       </c>
       <c r="E1237" s="36">
-        <v>4925.748394190472</v>
+        <v>4925.6527215340466</v>
       </c>
       <c r="F1237" s="35">
         <v>770.73030000000006</v>
@@ -56549,7 +56549,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.3654657565703</v>
+        <v>5020.2761378662899</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56587,7 +56587,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="36">
-        <v>4983.6002426995319</v>
+        <v>4983.5092802101408</v>
       </c>
       <c r="F1239" s="35">
         <v>1951.8497</v>
@@ -56790,7 +56790,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084409</v>
+        <v>6056.50708400844</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56828,7 +56828,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072237</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56904,7 +56904,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5394.2932473875308</v>
+        <v>5394.2932473875317</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -57094,7 +57094,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="36">
-        <v>5768.2127381128485</v>
+        <v>5768.2127381128475</v>
       </c>
       <c r="J1252" s="35">
         <v>10772.394200000001</v>
@@ -57208,7 +57208,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371008</v>
+        <v>5978.5241558371017</v>
       </c>
       <c r="J1255" s="35">
         <v>12541.2435</v>
@@ -57246,16 +57246,16 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244501</v>
+        <v>6258.6852471244511</v>
       </c>
       <c r="J1256" s="35">
-        <v>9248.3009999999995</v>
+        <v>9243.1422999999995</v>
       </c>
       <c r="K1256" s="35"/>
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77386.143499999991</v>
+        <v>77380.984799999991</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1">
@@ -57284,16 +57284,16 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6857.6810418042396</v>
+        <v>6857.6810418042405</v>
       </c>
       <c r="J1257" s="35">
-        <v>6940.3462</v>
+        <v>7037.5686999999998</v>
       </c>
       <c r="K1257" s="35"/>
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78553.431500000006</v>
+        <v>78650.653999999995</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1">
@@ -57301,16 +57301,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="35">
-        <v>60353.478300000002</v>
+        <v>60323.711300000003</v>
       </c>
       <c r="C1258" s="35">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="35">
-        <v>4974.0264714053064</v>
+        <v>4971.5732267847006</v>
       </c>
       <c r="E1258" s="36">
-        <v>5450.8024654324872</v>
+        <v>5450.2447065625283</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57331,7 +57331,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75386.031700000007</v>
+        <v>75356.2647</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1">
@@ -57348,7 +57348,7 @@
         <v>5451.9543190628137</v>
       </c>
       <c r="E1259" s="36">
-        <v>5181.0114263893702</v>
+        <v>5180.4441794289551</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57386,7 +57386,7 @@
         <v>5180.797620340134</v>
       </c>
       <c r="E1260" s="36">
-        <v>5206.7821264556014</v>
+        <v>5206.2021463833635</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57424,7 +57424,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5251.2713456055344</v>
+        <v>5250.6245836389726</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57491,16 +57491,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58958.789799999999</v>
+        <v>58951.246899999998</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5220.1436516336098</v>
+        <v>5219.4758119156731</v>
       </c>
       <c r="E1263" s="36">
-        <v>5331.400022752422</v>
+        <v>5331.2172702250455</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57521,7 +57521,7 @@
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69889.029299999995</v>
+        <v>69881.486399999994</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1">
@@ -57538,7 +57538,7 @@
         <v>5649.4440434970375</v>
       </c>
       <c r="E1264" s="36">
-        <v>5400.0581610919007</v>
+        <v>5399.8412132242247</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57550,7 +57550,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763569</v>
+        <v>6539.4433219763587</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57567,16 +57567,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66766.726699999999</v>
+        <v>66744.3508</v>
       </c>
       <c r="C1265" s="40">
         <v>12794.5746</v>
       </c>
       <c r="D1265" s="40">
-        <v>5218.3623752523981</v>
+        <v>5216.6135167948451</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.6481410634788</v>
+        <v>5316.9033255600962</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57588,7 +57588,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796991011</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57597,7 +57597,7 @@
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77871.419099999999</v>
+        <v>77849.0432</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1">
@@ -57614,7 +57614,7 @@
         <v>5371.4894586361188</v>
       </c>
       <c r="E1266" s="41">
-        <v>5321.4432313934767</v>
+        <v>5320.7301875331477</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57643,16 +57643,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77838.612500000003</v>
+        <v>77826.669200000004</v>
       </c>
       <c r="C1267" s="40">
         <v>13633.935799999999</v>
       </c>
       <c r="D1267" s="40">
-        <v>5709.1813869330381</v>
+        <v>5708.3053889691928</v>
       </c>
       <c r="E1267" s="41">
-        <v>5387.0040045297501</v>
+        <v>5386.2955210789432</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57673,7 +57673,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92913.684900000007</v>
+        <v>92901.741600000008</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1">
@@ -57681,16 +57681,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="40">
-        <v>65282.188399999999</v>
+        <v>65281.560599999997</v>
       </c>
       <c r="C1268" s="40">
         <v>12725.730299999999</v>
       </c>
       <c r="D1268" s="40">
-        <v>5129.9365035262454</v>
+        <v>5129.8871704046724</v>
       </c>
       <c r="E1268" s="41">
-        <v>5330.9397704201201</v>
+        <v>5330.255954562801</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57711,7 +57711,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81448.451199999996</v>
+        <v>81447.823399999994</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1">
@@ -57728,7 +57728,7 @@
         <v>5300.2894234440701</v>
       </c>
       <c r="E1269" s="41">
-        <v>5316.1453209084048</v>
+        <v>5315.4880533314772</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57766,7 +57766,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5429.4744698079076</v>
+        <v>5429.2292392133913</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57804,7 +57804,7 @@
         <v>5455.3153690061854</v>
       </c>
       <c r="E1271" s="41">
-        <v>5409.888535936635</v>
+        <v>5409.8757488922092</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -58108,7 +58108,7 @@
         <v>6445.3126888563129</v>
       </c>
       <c r="E1279" s="41">
-        <v>5748.3858869767437</v>
+        <v>5748.3858869767446</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58146,7 +58146,7 @@
         <v>6544.1110788101387</v>
       </c>
       <c r="E1280" s="41">
-        <v>5997.2725842604559</v>
+        <v>5997.2725842604568</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58175,16 +58175,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>57621.727800000001</v>
+        <v>57622.5838</v>
       </c>
       <c r="C1281" s="40">
         <v>8634.5971000000009</v>
       </c>
       <c r="D1281" s="40">
-        <v>6673.3545448229415</v>
+        <v>6673.4536808903322</v>
       </c>
       <c r="E1281" s="41">
-        <v>6271.9961690505406</v>
+        <v>6272.0248372039869</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58205,7 +58205,7 @@
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>65472.489000000001</v>
+        <v>65473.345000000001</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1">
@@ -58213,37 +58213,37 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>59567.664799999999</v>
+        <v>60577.592100000002</v>
       </c>
       <c r="C1282" s="40">
-        <v>10696.757600000001</v>
+        <v>10848.953100000001</v>
       </c>
       <c r="D1282" s="40">
-        <v>5568.7589667358634</v>
+        <v>5583.7269773062253</v>
       </c>
       <c r="E1282" s="41">
-        <v>6264.3000387708789</v>
+        <v>6265.930802100952</v>
       </c>
       <c r="F1282" s="40">
-        <v>2066.8542000000002</v>
+        <v>1610.2809999999999</v>
       </c>
       <c r="G1282" s="40">
-        <v>307.53489999999999</v>
+        <v>256.69540000000001</v>
       </c>
       <c r="H1282" s="40">
-        <v>6720.7142994177257</v>
+        <v>6273.1198143792217</v>
       </c>
       <c r="I1282" s="41">
-        <v>7614.5278909516492</v>
+        <v>7520.2897060172363</v>
       </c>
       <c r="J1282" s="40">
-        <v>15038.177299999999</v>
+        <v>15077.059499999999</v>
       </c>
       <c r="K1282" s="40"/>
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76672.696299999996</v>
+        <v>77264.9326</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1">
@@ -58251,37 +58251,37 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>54710.134400000003</v>
+        <v>59984.263599999998</v>
       </c>
       <c r="C1283" s="40">
-        <v>9832.2266</v>
+        <v>10810.840099999999</v>
       </c>
       <c r="D1283" s="40">
-        <v>5564.3687463427668</v>
+        <v>5548.529350646857</v>
       </c>
       <c r="E1283" s="41">
-        <v>5999.5081392186685</v>
+        <v>5987.511478150559</v>
       </c>
       <c r="F1283" s="40">
-        <v>1648.3975</v>
+        <v>2104.9731000000002</v>
       </c>
       <c r="G1283" s="40">
-        <v>251.851</v>
+        <v>302.69049999999999</v>
       </c>
       <c r="H1283" s="40">
-        <v>6545.1298585274626</v>
+        <v>6954.2093326351514</v>
       </c>
       <c r="I1283" s="41">
-        <v>7431.828400112322</v>
+        <v>7431.831072355666</v>
       </c>
       <c r="J1283" s="40">
-        <v>7077.3932000000004</v>
+        <v>7452.3090000000002</v>
       </c>
       <c r="K1283" s="40"/>
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>63435.925100000008</v>
+        <v>69541.545700000002</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1">
@@ -58289,16 +58289,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>24101.7084</v>
+        <v>36028.178800000002</v>
       </c>
       <c r="C1284" s="40">
-        <v>3408.1374999999998</v>
+        <v>5629.8756000000003</v>
       </c>
       <c r="D1284" s="40">
-        <v>7071.812214149224</v>
+        <v>6399.4626808450266</v>
       </c>
       <c r="E1284" s="41">
-        <v>5964.0909533951171</v>
+        <v>5920.5168260095916</v>
       </c>
       <c r="F1284" s="40">
         <v>591.27030000000002</v>
@@ -58310,33 +58310,55 @@
         <v>6687.322290158183</v>
       </c>
       <c r="I1284" s="41">
-        <v>7334.9008503305686</v>
+        <v>7334.9033506899959</v>
       </c>
       <c r="J1284" s="40">
-        <v>9730.3516999999993</v>
+        <v>14928.468800000001</v>
       </c>
       <c r="K1284" s="40"/>
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>34423.330399999999</v>
+        <v>51547.9179</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A1285" s="39"/>
-      <c r="B1285" s="40"/>
-      <c r="C1285" s="40"/>
-      <c r="D1285" s="40"/>
-      <c r="E1285" s="41"/>
-      <c r="F1285" s="40"/>
-      <c r="G1285" s="40"/>
-      <c r="H1285" s="40"/>
-      <c r="I1285" s="41"/>
-      <c r="J1285" s="40"/>
+      <c r="A1285" s="39">
+        <v>46193</v>
+      </c>
+      <c r="B1285" s="40">
+        <v>41179.038800000002</v>
+      </c>
+      <c r="C1285" s="40">
+        <v>6639.9225999999999</v>
+      </c>
+      <c r="D1285" s="40">
+        <v>6201.7347611853193</v>
+      </c>
+      <c r="E1285" s="41">
+        <v>5860.7377254267549</v>
+      </c>
+      <c r="F1285" s="40">
+        <v>215.47120000000001</v>
+      </c>
+      <c r="G1285" s="40">
+        <v>34.404699999999998</v>
+      </c>
+      <c r="H1285" s="40">
+        <v>6262.8419954250439</v>
+      </c>
+      <c r="I1285" s="41">
+        <v>7143.2328739461855</v>
+      </c>
+      <c r="J1285" s="40">
+        <v>12138.024299999999</v>
+      </c>
       <c r="K1285" s="40"/>
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
-      <c r="N1285" s="40"/>
+      <c r="N1285" s="40">
+        <v>53532.534299999999</v>
+      </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1286" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D214C2E4-841C-4BF8-952D-56C438FAAE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F1F964-009A-4348-9A95-A686A80CFC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56845,7 +56845,7 @@
         <v>45920</v>
       </c>
       <c r="B1246" s="35">
-        <v>62616</v>
+        <v>62615</v>
       </c>
       <c r="C1246" s="35">
         <v>11947</v>
@@ -56875,7 +56875,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70116</v>
+        <v>70115</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57021,13 +57021,13 @@
         <v>5726</v>
       </c>
       <c r="J1250" s="35">
-        <v>12437</v>
+        <v>12435</v>
       </c>
       <c r="K1250" s="35"/>
       <c r="L1250" s="35"/>
       <c r="M1250" s="35"/>
       <c r="N1250" s="37">
-        <v>61910</v>
+        <v>61908</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57073,7 +57073,7 @@
         <v>45962</v>
       </c>
       <c r="B1252" s="35">
-        <v>49050</v>
+        <v>49049</v>
       </c>
       <c r="C1252" s="35">
         <v>10403</v>
@@ -57103,7 +57103,7 @@
       <c r="L1252" s="35"/>
       <c r="M1252" s="35"/>
       <c r="N1252" s="37">
-        <v>60802</v>
+        <v>60801</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57377,13 +57377,13 @@
         <v>46018</v>
       </c>
       <c r="B1260" s="35">
-        <v>60630</v>
+        <v>60601</v>
       </c>
       <c r="C1260" s="35">
         <v>11703</v>
       </c>
       <c r="D1260" s="35">
-        <v>5181</v>
+        <v>5178</v>
       </c>
       <c r="E1260" s="36">
         <v>5206</v>
@@ -57401,13 +57401,13 @@
         <v>6636</v>
       </c>
       <c r="J1260" s="35">
-        <v>7544</v>
+        <v>7630</v>
       </c>
       <c r="K1260" s="35"/>
       <c r="L1260" s="35"/>
       <c r="M1260" s="35"/>
       <c r="N1260" s="37">
-        <v>70367</v>
+        <v>70423</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57424,7 +57424,7 @@
         <v>5318</v>
       </c>
       <c r="E1261" s="36">
-        <v>5251</v>
+        <v>5250</v>
       </c>
       <c r="F1261" s="35">
         <v>1260</v>
@@ -57453,16 +57453,16 @@
         <v>46032</v>
       </c>
       <c r="B1262" s="35">
-        <v>31628</v>
+        <v>31623</v>
       </c>
       <c r="C1262" s="35">
         <v>5683</v>
       </c>
       <c r="D1262" s="35">
-        <v>5565</v>
+        <v>5564</v>
       </c>
       <c r="E1262" s="36">
-        <v>5251</v>
+        <v>5250</v>
       </c>
       <c r="F1262" s="35">
         <v>1210</v>
@@ -57483,7 +57483,7 @@
       <c r="L1262" s="35"/>
       <c r="M1262" s="35"/>
       <c r="N1262" s="37">
-        <v>40579</v>
+        <v>40574</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57500,7 +57500,7 @@
         <v>5219</v>
       </c>
       <c r="E1263" s="36">
-        <v>5331</v>
+        <v>5330</v>
       </c>
       <c r="F1263" s="35">
         <v>3099</v>
@@ -57529,7 +57529,7 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41408</v>
+        <v>41407</v>
       </c>
       <c r="C1264" s="35">
         <v>7330</v>
@@ -57538,7 +57538,7 @@
         <v>5649</v>
       </c>
       <c r="E1264" s="36">
-        <v>5400</v>
+        <v>5399</v>
       </c>
       <c r="F1264" s="35">
         <v>1803</v>
@@ -57567,13 +57567,13 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66744</v>
+        <v>66740</v>
       </c>
       <c r="C1265" s="40">
         <v>12795</v>
       </c>
       <c r="D1265" s="40">
-        <v>5217</v>
+        <v>5216</v>
       </c>
       <c r="E1265" s="41">
         <v>5317</v>
@@ -57597,7 +57597,7 @@
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77849</v>
+        <v>77845</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57605,7 +57605,7 @@
         <v>46060</v>
       </c>
       <c r="B1266" s="40">
-        <v>45423</v>
+        <v>45422</v>
       </c>
       <c r="C1266" s="40">
         <v>8456</v>
@@ -57614,7 +57614,7 @@
         <v>5371</v>
       </c>
       <c r="E1266" s="41">
-        <v>5321</v>
+        <v>5320</v>
       </c>
       <c r="F1266" s="40">
         <v>1799</v>
@@ -57635,7 +57635,7 @@
       <c r="L1266" s="40"/>
       <c r="M1266" s="40"/>
       <c r="N1266" s="40">
-        <v>57270</v>
+        <v>57269</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -57719,7 +57719,7 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="40">
-        <v>55621</v>
+        <v>55619</v>
       </c>
       <c r="C1269" s="40">
         <v>10494</v>
@@ -57749,7 +57749,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64799</v>
+        <v>64798</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58099,16 +58099,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>33888</v>
+        <v>33572</v>
       </c>
       <c r="C1279" s="40">
-        <v>5258</v>
+        <v>5127</v>
       </c>
       <c r="D1279" s="40">
-        <v>6445</v>
+        <v>6548</v>
       </c>
       <c r="E1279" s="41">
-        <v>5749</v>
+        <v>5766</v>
       </c>
       <c r="F1279" s="40">
         <v>968</v>
@@ -58129,7 +58129,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>39174</v>
+        <v>38858</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58146,7 +58146,7 @@
         <v>6546</v>
       </c>
       <c r="E1280" s="41">
-        <v>5999</v>
+        <v>6015</v>
       </c>
       <c r="F1280" s="40">
         <v>106</v>
@@ -58175,16 +58175,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>57305</v>
+        <v>57174</v>
       </c>
       <c r="C1281" s="40">
-        <v>8504</v>
+        <v>8447</v>
       </c>
       <c r="D1281" s="40">
-        <v>6739</v>
+        <v>6769</v>
       </c>
       <c r="E1281" s="41">
-        <v>6290</v>
+        <v>6315</v>
       </c>
       <c r="F1281" s="40">
         <v>2628</v>
@@ -58205,7 +58205,7 @@
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>65156</v>
+        <v>65025</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58213,16 +58213,16 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>60575</v>
+        <v>60279</v>
       </c>
       <c r="C1282" s="40">
-        <v>10849</v>
+        <v>10727</v>
       </c>
       <c r="D1282" s="40">
-        <v>5583</v>
+        <v>5620</v>
       </c>
       <c r="E1282" s="41">
-        <v>6281</v>
+        <v>6316</v>
       </c>
       <c r="F1282" s="40">
         <v>1610</v>
@@ -58243,7 +58243,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>77262</v>
+        <v>76967</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58251,16 +58251,16 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>61433</v>
+        <v>62411</v>
       </c>
       <c r="C1283" s="40">
-        <v>11090</v>
+        <v>11164</v>
       </c>
       <c r="D1283" s="40">
-        <v>5540</v>
+        <v>5591</v>
       </c>
       <c r="E1283" s="41">
-        <v>5994</v>
+        <v>6033</v>
       </c>
       <c r="F1283" s="40">
         <v>1885</v>
@@ -58275,13 +58275,13 @@
         <v>7405</v>
       </c>
       <c r="J1283" s="40">
-        <v>7449</v>
+        <v>7506</v>
       </c>
       <c r="K1283" s="40"/>
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>70767</v>
+        <v>71802</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58289,16 +58289,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>39409</v>
+        <v>39459</v>
       </c>
       <c r="C1284" s="40">
-        <v>6191</v>
+        <v>6227</v>
       </c>
       <c r="D1284" s="40">
-        <v>6365</v>
+        <v>6337</v>
       </c>
       <c r="E1284" s="41">
-        <v>5928</v>
+        <v>5952</v>
       </c>
       <c r="F1284" s="40">
         <v>1030</v>
@@ -58313,13 +58313,13 @@
         <v>7360</v>
       </c>
       <c r="J1284" s="40">
-        <v>15315</v>
+        <v>15323</v>
       </c>
       <c r="K1284" s="40"/>
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55754</v>
+        <v>55811</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58327,16 +58327,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62616</v>
+        <v>66410</v>
       </c>
       <c r="C1285" s="40">
-        <v>10536</v>
+        <v>11235</v>
       </c>
       <c r="D1285" s="40">
-        <v>5943</v>
+        <v>5911</v>
       </c>
       <c r="E1285" s="41">
-        <v>5824</v>
+        <v>5837</v>
       </c>
       <c r="F1285" s="40">
         <v>601</v>
@@ -58345,19 +58345,19 @@
         <v>86</v>
       </c>
       <c r="H1285" s="40">
-        <v>7004</v>
+        <v>6999</v>
       </c>
       <c r="I1285" s="41">
         <v>7198</v>
       </c>
       <c r="J1285" s="40">
-        <v>16527</v>
+        <v>16651</v>
       </c>
       <c r="K1285" s="40"/>
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>79744</v>
+        <v>83661</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -58365,54 +58365,68 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>35151</v>
+        <v>54798</v>
       </c>
       <c r="C1286" s="40">
-        <v>5283</v>
+        <v>8690</v>
       </c>
       <c r="D1286" s="40">
-        <v>6654</v>
+        <v>6306</v>
       </c>
       <c r="E1286" s="41">
-        <v>5868</v>
+        <v>5872</v>
       </c>
       <c r="F1286" s="40">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G1286" s="40">
         <v>61</v>
       </c>
       <c r="H1286" s="40">
-        <v>7123</v>
+        <v>7114</v>
       </c>
       <c r="I1286" s="41">
-        <v>7019</v>
+        <v>7018</v>
       </c>
       <c r="J1286" s="40">
-        <v>4019</v>
+        <v>6643</v>
       </c>
       <c r="K1286" s="40"/>
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>39605</v>
+        <v>61875</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1287" s="39"/>
-      <c r="B1287" s="40"/>
-      <c r="C1287" s="40"/>
-      <c r="D1287" s="40"/>
-      <c r="E1287" s="41"/>
+      <c r="A1287" s="39">
+        <v>46207</v>
+      </c>
+      <c r="B1287" s="40">
+        <v>32301</v>
+      </c>
+      <c r="C1287" s="40">
+        <v>5021</v>
+      </c>
+      <c r="D1287" s="40">
+        <v>6433</v>
+      </c>
+      <c r="E1287" s="41">
+        <v>6066</v>
+      </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41"/>
-      <c r="J1287" s="40"/>
+      <c r="J1287" s="40">
+        <v>3135</v>
+      </c>
       <c r="K1287" s="40"/>
       <c r="L1287" s="40"/>
       <c r="M1287" s="40"/>
-      <c r="N1287" s="40"/>
+      <c r="N1287" s="40">
+        <v>35436</v>
+      </c>
     </row>
     <row r="1288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1288" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC2D342-A2C6-4107-BD89-DD6E435CAC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0569AD86-6118-4983-8016-2720C0964F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INAC" sheetId="1" r:id="rId1"/>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55486,7 +55486,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55553,16 +55553,16 @@
         <v>45682</v>
       </c>
       <c r="B1212" s="35">
-        <v>38351.395199999999</v>
+        <v>38351.071300000003</v>
       </c>
       <c r="C1212" s="35">
         <v>7934.2707</v>
       </c>
       <c r="D1212" s="35">
-        <v>4833.6383582173466</v>
+        <v>4833.5975353097047</v>
       </c>
       <c r="E1212" s="36">
-        <v>4670.4968488940985</v>
+        <v>4670.4878831151855</v>
       </c>
       <c r="F1212" s="35">
         <v>1637.0943</v>
@@ -55583,7 +55583,7 @@
       <c r="L1212" s="35"/>
       <c r="M1212" s="35"/>
       <c r="N1212" s="37">
-        <v>45765.935099999995</v>
+        <v>45765.611199999999</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55600,7 +55600,7 @@
         <v>4746.7946040659472</v>
       </c>
       <c r="E1213" s="36">
-        <v>4691.4576149978011</v>
+        <v>4691.4493873773254</v>
       </c>
       <c r="F1213" s="35">
         <v>2092.5389</v>
@@ -55629,16 +55629,16 @@
         <v>45696</v>
       </c>
       <c r="B1214" s="35">
-        <v>65724.152499999997</v>
+        <v>65720.755499999999</v>
       </c>
       <c r="C1214" s="35">
         <v>14591.974399999999</v>
       </c>
       <c r="D1214" s="35">
-        <v>4504.1301950200796</v>
+        <v>4503.8973958178003</v>
       </c>
       <c r="E1214" s="36">
-        <v>4602.131659767475</v>
+        <v>4602.0452868263301</v>
       </c>
       <c r="F1214" s="35">
         <v>2171.1239</v>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76702.561400000006</v>
+        <v>76699.164399999994</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.6741633219426</v>
+        <v>4600.5969827764493</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55714,7 +55714,7 @@
         <v>5217.3893298788053</v>
       </c>
       <c r="E1216" s="36">
-        <v>4696.0284167246291</v>
+        <v>4695.9524252670917</v>
       </c>
       <c r="F1216" s="35">
         <v>989.77200000000005</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8736593648064</v>
+        <v>4705.8123550761293</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55781,16 +55781,16 @@
         <v>45724</v>
       </c>
       <c r="B1218" s="35">
-        <v>35974.402399999999</v>
+        <v>35964.451099999998</v>
       </c>
       <c r="C1218" s="35">
         <v>7605.2524000000003</v>
       </c>
       <c r="D1218" s="35">
-        <v>4730.2049304767315</v>
+        <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4736.0595288362119</v>
+        <v>4735.8590672017526</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55811,7 +55811,7 @@
       <c r="L1218" s="35"/>
       <c r="M1218" s="35"/>
       <c r="N1218" s="37">
-        <v>49270.516300000003</v>
+        <v>49260.565000000002</v>
       </c>
     </row>
     <row r="1219" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55828,7 +55828,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4755.0431608158751</v>
+        <v>4754.8215409778977</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.675999999999</v>
+        <v>62640.676000000007</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.4402106695079</v>
+        <v>4662.2080120947376</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -55895,16 +55895,16 @@
         <v>45745</v>
       </c>
       <c r="B1221" s="35">
-        <v>57606.128299999997</v>
+        <v>57605.154399999999</v>
       </c>
       <c r="C1221" s="35">
         <v>12251.911</v>
       </c>
       <c r="D1221" s="35">
-        <v>4701.8076037281035</v>
+        <v>4701.7281140876712</v>
       </c>
       <c r="E1221" s="36">
-        <v>4669.693254518922</v>
+        <v>4669.4458132671598</v>
       </c>
       <c r="F1221" s="35">
         <v>673.16070000000002</v>
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68595.294499999989</v>
+        <v>68594.320600000006</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55942,7 +55942,7 @@
         <v>4849.8060419687263</v>
       </c>
       <c r="E1222" s="36">
-        <v>4694.8372699952697</v>
+        <v>4694.5870651081259</v>
       </c>
       <c r="F1222" s="35">
         <v>1081.6878999999999</v>
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313499999997</v>
+        <v>52967.313500000004</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55980,7 +55980,7 @@
         <v>4613.3343787360272</v>
       </c>
       <c r="E1223" s="36">
-        <v>4695.3520908882838</v>
+        <v>4695.330522427801</v>
       </c>
       <c r="F1223" s="35">
         <v>1661.2738999999999</v>
@@ -56018,7 +56018,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4673.0018865803258</v>
+        <v>4672.9782577126962</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56047,16 +56047,16 @@
         <v>45773</v>
       </c>
       <c r="B1225" s="35">
-        <v>55124.155200000001</v>
+        <v>55115.358999999997</v>
       </c>
       <c r="C1225" s="35">
         <v>10498.2588</v>
       </c>
       <c r="D1225" s="35">
-        <v>5250.790273907136</v>
+        <v>5249.9524016306405</v>
       </c>
       <c r="E1225" s="36">
-        <v>4738.4346146204743</v>
+        <v>4738.2002336751721</v>
       </c>
       <c r="F1225" s="35">
         <v>723.6875</v>
@@ -56077,7 +56077,7 @@
       <c r="L1225" s="35"/>
       <c r="M1225" s="35"/>
       <c r="N1225" s="37">
-        <v>64208.47</v>
+        <v>64199.673799999997</v>
       </c>
     </row>
     <row r="1226" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56094,7 +56094,7 @@
         <v>4811.955965042308</v>
       </c>
       <c r="E1226" s="36">
-        <v>4821.6953261187473</v>
+        <v>4821.4752930804216</v>
       </c>
       <c r="F1226" s="35">
         <v>823.7826</v>
@@ -56132,7 +56132,7 @@
         <v>4954.1257509511597</v>
       </c>
       <c r="E1227" s="36">
-        <v>4890.2983275320939</v>
+        <v>4890.1011625026067</v>
       </c>
       <c r="F1227" s="35">
         <v>699.97680000000003</v>
@@ -56170,7 +56170,7 @@
         <v>5173.8323341700607</v>
       </c>
       <c r="E1228" s="36">
-        <v>5048.0160181896881</v>
+        <v>5047.8451432953889</v>
       </c>
       <c r="F1228" s="35">
         <v>677.62339999999995</v>
@@ -56199,16 +56199,16 @@
         <v>45801</v>
       </c>
       <c r="B1229" s="35">
-        <v>54487.9594</v>
+        <v>54485.823400000001</v>
       </c>
       <c r="C1229" s="35">
         <v>10629.917100000001</v>
       </c>
       <c r="D1229" s="35">
-        <v>5125.9063346787525</v>
+        <v>5125.7053923778949</v>
       </c>
       <c r="E1229" s="36">
-        <v>4983.1533674253005</v>
+        <v>4982.9474278690641</v>
       </c>
       <c r="F1229" s="35">
         <v>465.10070000000002</v>
@@ -56229,7 +56229,7 @@
       <c r="L1229" s="35"/>
       <c r="M1229" s="35"/>
       <c r="N1229" s="37">
-        <v>66442.733099999998</v>
+        <v>66440.597099999999</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56237,16 +56237,16 @@
         <v>45808</v>
       </c>
       <c r="B1230" s="35">
-        <v>47053.949500000002</v>
+        <v>47051.885499999997</v>
       </c>
       <c r="C1230" s="35">
         <v>9007.6190000000006</v>
       </c>
       <c r="D1230" s="35">
-        <v>5223.7943789585233</v>
+        <v>5223.5652396043834</v>
       </c>
       <c r="E1230" s="36">
-        <v>5028.1038873851257</v>
+        <v>5028.0222161538768</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56267,7 +56267,7 @@
       <c r="L1230" s="35"/>
       <c r="M1230" s="35"/>
       <c r="N1230" s="37">
-        <v>52618.0213</v>
+        <v>52615.957299999995</v>
       </c>
     </row>
     <row r="1231" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56275,16 +56275,16 @@
         <v>45815</v>
       </c>
       <c r="B1231" s="35">
-        <v>59291.998699999996</v>
+        <v>59290.369700000003</v>
       </c>
       <c r="C1231" s="35">
         <v>12502.961600000001</v>
       </c>
       <c r="D1231" s="35">
-        <v>4742.2363274314139</v>
+        <v>4742.1060383005579</v>
       </c>
       <c r="E1231" s="36">
-        <v>4961.0532053181669</v>
+        <v>4960.9505974298099</v>
       </c>
       <c r="F1231" s="35">
         <v>1023.9116</v>
@@ -56305,7 +56305,7 @@
       <c r="L1231" s="35"/>
       <c r="M1231" s="35"/>
       <c r="N1231" s="37">
-        <v>75298.126700000008</v>
+        <v>75296.497700000007</v>
       </c>
     </row>
     <row r="1232" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56322,7 +56322,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.4132248546694</v>
+        <v>4909.2993048166982</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56360,7 +56360,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="36">
-        <v>4835.9755920229454</v>
+        <v>4835.8535729451951</v>
       </c>
       <c r="F1233" s="35">
         <v>910.61059999999998</v>
@@ -56398,7 +56398,7 @@
         <v>4897.4427637682502</v>
       </c>
       <c r="E1234" s="36">
-        <v>4765.8101461375481</v>
+        <v>4765.7739607701869</v>
       </c>
       <c r="F1234" s="35">
         <v>556.48080000000004</v>
@@ -56512,7 +56512,7 @@
         <v>5278.9174410390733</v>
       </c>
       <c r="E1237" s="36">
-        <v>4925.6527215340475</v>
+        <v>4925.6527215340466</v>
       </c>
       <c r="F1237" s="35">
         <v>770.73030000000006</v>
@@ -56550,7 +56550,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.2761378662917</v>
+        <v>5020.2761378662899</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56562,7 +56562,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253513</v>
+        <v>5662.7424793253522</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359399999994</v>
+        <v>53725.359400000001</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56600,7 +56600,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316115</v>
+        <v>6067.7529720316097</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56638,7 +56638,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712285</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56676,7 +56676,7 @@
         <v>4084.1946733397849</v>
       </c>
       <c r="I1241" s="36">
-        <v>6187.5045092790242</v>
+        <v>6187.5045092790233</v>
       </c>
       <c r="J1241" s="35">
         <v>12876.365</v>
@@ -56694,16 +56694,16 @@
         <v>45892</v>
       </c>
       <c r="B1242" s="35">
-        <v>84750.342499999999</v>
+        <v>84734.912899999996</v>
       </c>
       <c r="C1242" s="35">
         <v>16082.0092</v>
       </c>
       <c r="D1242" s="35">
-        <v>5269.8852143424965</v>
+        <v>5268.9257819850018</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.5862135207217</v>
+        <v>5374.2340433056661</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56724,7 +56724,7 @@
       <c r="L1242" s="35"/>
       <c r="M1242" s="35"/>
       <c r="N1242" s="37">
-        <v>94230.228499999997</v>
+        <v>94214.798899999994</v>
       </c>
     </row>
     <row r="1243" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56732,16 +56732,16 @@
         <v>45899</v>
       </c>
       <c r="B1243" s="35">
-        <v>73066.317200000005</v>
+        <v>73065.303599999999</v>
       </c>
       <c r="C1243" s="35">
         <v>14216.347299999999</v>
       </c>
       <c r="D1243" s="35">
-        <v>5139.5984958808658</v>
+        <v>5139.52719767897</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.4129440335873</v>
+        <v>5338.0821484626749</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56753,7 +56753,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56762,7 +56762,7 @@
       <c r="L1243" s="35"/>
       <c r="M1243" s="35"/>
       <c r="N1243" s="37">
-        <v>89640.540900000007</v>
+        <v>89639.527300000002</v>
       </c>
     </row>
     <row r="1244" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56770,16 +56770,16 @@
         <v>45906</v>
       </c>
       <c r="B1244" s="35">
-        <v>47987.968800000002</v>
+        <v>47980.181600000004</v>
       </c>
       <c r="C1244" s="35">
         <v>10037.602800000001</v>
       </c>
       <c r="D1244" s="35">
-        <v>4780.81965945096</v>
+        <v>4780.0438566865787</v>
       </c>
       <c r="E1244" s="36">
-        <v>5246.3440285834786</v>
+        <v>5245.8828274293983</v>
       </c>
       <c r="F1244" s="35">
         <v>1388.6704</v>
@@ -56791,7 +56791,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084427</v>
+        <v>6056.50708400844</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57658.490900000004</v>
+        <v>57650.703699999998</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56817,7 +56817,7 @@
         <v>5199.2635555698389</v>
       </c>
       <c r="E1245" s="36">
-        <v>5064.170551694483</v>
+        <v>5063.7055849213466</v>
       </c>
       <c r="F1245" s="35">
         <v>1184.0114000000001</v>
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639500000005</v>
+        <v>48636.639499999997</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56846,16 +56846,16 @@
         <v>45920</v>
       </c>
       <c r="B1246" s="35">
-        <v>62614.916599999997</v>
+        <v>62618.347500000003</v>
       </c>
       <c r="C1246" s="35">
         <v>11947.379300000001</v>
       </c>
       <c r="D1246" s="35">
-        <v>5240.8913308711972</v>
+        <v>5241.1784984511205</v>
       </c>
       <c r="E1246" s="36">
-        <v>5101.0219062871029</v>
+        <v>5100.6651335349852</v>
       </c>
       <c r="F1246" s="35">
         <v>977.74770000000001</v>
@@ -56876,7 +56876,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70114.972000000009</v>
+        <v>70118.402900000001</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56893,7 +56893,7 @@
         <v>5285.8148363219088</v>
       </c>
       <c r="E1247" s="36">
-        <v>5104.0052751575604</v>
+        <v>5103.906901146971</v>
       </c>
       <c r="F1247" s="35">
         <v>1625.8276000000001</v>
@@ -56931,7 +56931,7 @@
         <v>4658.6445909997819</v>
       </c>
       <c r="E1248" s="36">
-        <v>5063.3012256122356</v>
+        <v>5063.3894640616645</v>
       </c>
       <c r="F1248" s="35">
         <v>1018.4743</v>
@@ -56969,7 +56969,7 @@
         <v>4382.8174971698409</v>
       </c>
       <c r="E1249" s="36">
-        <v>4971.0403563576929</v>
+        <v>4971.132415256563</v>
       </c>
       <c r="F1249" s="35">
         <v>1116.6591000000001</v>
@@ -56998,16 +56998,16 @@
         <v>45948</v>
       </c>
       <c r="B1250" s="35">
-        <v>48098.767399999997</v>
+        <v>48095.381600000001</v>
       </c>
       <c r="C1250" s="35">
         <v>9753.8886999999995</v>
       </c>
       <c r="D1250" s="35">
-        <v>4931.2401319486044</v>
+        <v>4930.8930088570733</v>
       </c>
       <c r="E1250" s="36">
-        <v>4939.2631618175101</v>
+        <v>4939.2643909473018</v>
       </c>
       <c r="F1250" s="35">
         <v>1339.0517</v>
@@ -57022,13 +57022,13 @@
         <v>5726.2108069747692</v>
       </c>
       <c r="J1250" s="35">
-        <v>12433.64</v>
+        <v>12434.489799999999</v>
       </c>
       <c r="K1250" s="35"/>
       <c r="L1250" s="35"/>
       <c r="M1250" s="35"/>
       <c r="N1250" s="37">
-        <v>61871.459099999993</v>
+        <v>61868.9231</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57045,7 +57045,7 @@
         <v>5713.2872157805959</v>
       </c>
       <c r="E1251" s="36">
-        <v>5011.0966325321951</v>
+        <v>5011.0026069939822</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57083,7 +57083,7 @@
         <v>4714.8155989034231</v>
       </c>
       <c r="E1252" s="36">
-        <v>4984.1421030730799</v>
+        <v>4984.0493805906481</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57095,7 +57095,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="36">
-        <v>5768.2127381128485</v>
+        <v>5768.2127381128475</v>
       </c>
       <c r="J1252" s="35">
         <v>10772.394200000001</v>
@@ -57121,7 +57121,7 @@
         <v>5680.1652258003896</v>
       </c>
       <c r="E1253" s="36">
-        <v>5197.256388477138</v>
+        <v>5197.188767083524</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57197,7 +57197,7 @@
         <v>6210.2065487022992</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.9414421875572</v>
+        <v>5572.9414421875581</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371008</v>
+        <v>5978.5241558371017</v>
       </c>
       <c r="J1255" s="35">
         <v>12541.2435</v>
@@ -57247,7 +57247,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244511</v>
+        <v>6258.6852471244492</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.1422999999995</v>
@@ -57256,7 +57256,7 @@
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77380.400900000008</v>
+        <v>77380.400899999993</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78650.65400000001</v>
+        <v>78650.653999999995</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57302,16 +57302,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="35">
-        <v>60323.711300000003</v>
+        <v>60220.019399999997</v>
       </c>
       <c r="C1258" s="35">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="35">
-        <v>4971.5732267847006</v>
+        <v>4963.0274681971578</v>
       </c>
       <c r="E1258" s="36">
-        <v>5450.2425985948848</v>
+        <v>5448.299672637685</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57323,16 +57323,16 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="35">
-        <v>10814.7626</v>
+        <v>10810.321599999999</v>
       </c>
       <c r="K1258" s="35"/>
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75499.375700000004</v>
+        <v>75391.242799999993</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57349,7 +57349,7 @@
         <v>5451.9543190628137</v>
       </c>
       <c r="E1259" s="36">
-        <v>5180.4330524930801</v>
+        <v>5178.4570752332056</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57361,7 +57361,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096234</v>
+        <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57387,7 +57387,7 @@
         <v>5176.6167478837451</v>
       </c>
       <c r="E1260" s="36">
-        <v>5205.2488256937922</v>
+        <v>5203.2284932567827</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57399,7 +57399,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="35">
         <v>7674.9405999999999</v>
@@ -57425,7 +57425,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5249.5614926924636</v>
+        <v>5247.308528767293</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57478,13 +57478,13 @@
         <v>6331.7504578958606</v>
       </c>
       <c r="J1262" s="35">
-        <v>7740.6167999999998</v>
+        <v>7789.9580999999998</v>
       </c>
       <c r="K1262" s="35"/>
       <c r="L1262" s="35"/>
       <c r="M1262" s="35"/>
       <c r="N1262" s="37">
-        <v>40574.176099999997</v>
+        <v>40623.517399999997</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57492,16 +57492,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58950.530700000003</v>
+        <v>58950.121700000003</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5219.4124003888091</v>
+        <v>5219.3761879977346</v>
       </c>
       <c r="E1263" s="36">
-        <v>5329.9005768975085</v>
+        <v>5329.8906674749132</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57513,16 +57513,16 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.3913080422872</v>
+        <v>6206.391308042289</v>
       </c>
       <c r="J1263" s="35">
-        <v>7830.9169000000002</v>
+        <v>7879.2038000000002</v>
       </c>
       <c r="K1263" s="35"/>
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69880.770199999999</v>
+        <v>69928.648100000006</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57530,16 +57530,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41405.264199999998</v>
+        <v>41392.236199999999</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5649.0604473852682</v>
+        <v>5647.2829932153591</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.7588668729659</v>
+        <v>5398.3723936997876</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57551,7 +57551,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763569</v>
+        <v>6539.4433219763587</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57560,7 +57560,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49480.661</v>
+        <v>49467.633000000002</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57577,7 +57577,7 @@
         <v>5216.2744355720906</v>
       </c>
       <c r="E1265" s="41">
-        <v>5316.5904855229046</v>
+        <v>5316.2559772565628</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796991011</v>
       </c>
       <c r="J1265" s="40">
         <v>8313.8631000000005</v>
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.4042595574028</v>
+        <v>5320.0840204317956</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57644,16 +57644,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77826.669200000004</v>
+        <v>77826.184899999993</v>
       </c>
       <c r="C1267" s="40">
         <v>13633.935799999999</v>
       </c>
       <c r="D1267" s="40">
-        <v>5708.3053889691928</v>
+        <v>5708.2698673115356</v>
       </c>
       <c r="E1267" s="41">
-        <v>5386.125020727286</v>
+        <v>5385.8460736384168</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92901.741600000008</v>
+        <v>92901.257299999997</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57691,7 +57691,7 @@
         <v>5129.8285725888754</v>
       </c>
       <c r="E1268" s="41">
-        <v>5330.1253159331691</v>
+        <v>5329.8736951000792</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57703,7 +57703,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81447.077700000009</v>
+        <v>81447.077699999994</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57720,16 +57720,16 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="40">
-        <v>55619.460800000001</v>
+        <v>55619.2736</v>
       </c>
       <c r="C1269" s="40">
         <v>10493.8631</v>
       </c>
       <c r="D1269" s="40">
-        <v>5300.1892887281892</v>
+        <v>5300.171449730462</v>
       </c>
       <c r="E1269" s="41">
-        <v>5315.3488623015182</v>
+        <v>5315.3355848277452</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57741,7 +57741,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314459</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57750,7 +57750,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64798.140799999994</v>
+        <v>64797.953600000001</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57767,7 +57767,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5429.1766411708977</v>
+        <v>5429.1635418920587</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57805,7 +57805,7 @@
         <v>5455.2640091469293</v>
       </c>
       <c r="E1271" s="41">
-        <v>5409.8266660319723</v>
+        <v>5409.8129889049706</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -57817,7 +57817,7 @@
         <v>7051.7107967597631</v>
       </c>
       <c r="I1271" s="41">
-        <v>7489.2724524389041</v>
+        <v>7489.2724524389059</v>
       </c>
       <c r="J1271" s="40">
         <v>9735.2654000000002</v>
@@ -57834,16 +57834,16 @@
         <v>46102</v>
       </c>
       <c r="B1272" s="40">
-        <v>37373.6034</v>
+        <v>37373.175799999997</v>
       </c>
       <c r="C1272" s="40">
         <v>6156.4367000000002</v>
       </c>
       <c r="D1272" s="40">
-        <v>6070.6550267949633</v>
+        <v>6070.5855710333217</v>
       </c>
       <c r="E1272" s="41">
-        <v>5601.0796528001683</v>
+        <v>5601.0656177981882</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57864,7 +57864,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>45986.169499999996</v>
+        <v>45985.741899999994</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57872,16 +57872,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="40">
-        <v>62476.6757</v>
+        <v>62465.5893</v>
       </c>
       <c r="C1273" s="40">
         <v>10894.957700000001</v>
       </c>
       <c r="D1273" s="40">
-        <v>5734.4578492489236</v>
+        <v>5733.4402776065845</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.9322598321542</v>
+        <v>5668.6689720091117</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57893,16 +57893,16 @@
         <v>6274.2182633165548</v>
       </c>
       <c r="I1273" s="41">
-        <v>7161.2268208604155</v>
+        <v>7161.2268208604146</v>
       </c>
       <c r="J1273" s="40">
-        <v>11036.475</v>
+        <v>11036.180899999999</v>
       </c>
       <c r="K1273" s="40"/>
       <c r="L1273" s="40"/>
       <c r="M1273" s="40"/>
       <c r="N1273" s="40">
-        <v>74214.141499999998</v>
+        <v>74202.760999999999</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57910,16 +57910,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52077.919300000001</v>
+        <v>52077.833500000001</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5404.5593430574527</v>
+        <v>5404.5504388769887</v>
       </c>
       <c r="E1274" s="41">
-        <v>5580.0455273093694</v>
+        <v>5579.7689625057319</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57931,16 +57931,16 @@
         <v>4533.0580246747986</v>
       </c>
       <c r="I1274" s="41">
-        <v>6471.0708305987373</v>
+        <v>6471.0708305987382</v>
       </c>
       <c r="J1274" s="40">
-        <v>8467.8510000000006</v>
+        <v>8468.0509000000002</v>
       </c>
       <c r="K1274" s="40"/>
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61593.406700000007</v>
+        <v>61593.520799999998</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57957,7 +57957,7 @@
         <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5670.4647523123822</v>
+        <v>5670.1497406014423</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57995,7 +57995,7 @@
         <v>5803.7573777391617</v>
       </c>
       <c r="E1276" s="41">
-        <v>5699.3303196407423</v>
+        <v>5698.9960412601968</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58033,7 +58033,7 @@
         <v>5849.2860061910824</v>
       </c>
       <c r="E1277" s="41">
-        <v>5647.253822471228</v>
+        <v>5646.9087070990963</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58071,7 +58071,7 @@
         <v>5131.8309114425856</v>
       </c>
       <c r="E1278" s="41">
-        <v>5540.4614049643887</v>
+        <v>5540.4614049643897</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42423.862700000005</v>
+        <v>42423.862699999998</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58109,7 +58109,7 @@
         <v>6548.343520002074</v>
       </c>
       <c r="E1279" s="41">
-        <v>5765.8894007253029</v>
+        <v>5765.889400725302</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58130,7 +58130,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>38858.601300000002</v>
+        <v>38858.601299999995</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58147,7 +58147,7 @@
         <v>6545.9925668947044</v>
       </c>
       <c r="E1280" s="41">
-        <v>6015.3090002181143</v>
+        <v>6015.3090002181152</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76965.009600000005</v>
+        <v>76965.00959999999</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58314,13 +58314,13 @@
         <v>7345.0183317717629</v>
       </c>
       <c r="J1284" s="40">
-        <v>15397.2994</v>
+        <v>15396.7754</v>
       </c>
       <c r="K1284" s="40"/>
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55871.347599999994</v>
+        <v>55870.823600000003</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62568.705000000002</v>
+        <v>62564.183400000002</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5908.5800325939017</v>
+        <v>5908.1530422082869</v>
       </c>
       <c r="E1285" s="41">
-        <v>5834.68839219455</v>
+        <v>5834.5761424554439</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58358,7 +58358,7 @@
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80140.625899999999</v>
+        <v>80136.104300000006</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62181.699200000003</v>
+        <v>62180.959900000002</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6204.2034514842608</v>
+        <v>6204.129687536496</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.9900359287585</v>
+        <v>5860.8735172761135</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58390,13 +58390,13 @@
         <v>6928.2649857850765</v>
       </c>
       <c r="J1286" s="40">
-        <v>7536.5888000000004</v>
+        <v>7566.6455999999998</v>
       </c>
       <c r="K1286" s="40"/>
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69918.259600000005</v>
+        <v>69947.577099999995</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58404,29 +58404,29 @@
         <v>46207</v>
       </c>
       <c r="B1287" s="40">
-        <v>39076.9228</v>
+        <v>39076.922899999998</v>
       </c>
       <c r="C1287" s="40">
         <v>6111.1090999999997</v>
       </c>
       <c r="D1287" s="40">
-        <v>6394.4076534323367</v>
+        <v>6394.407669795979</v>
       </c>
       <c r="E1287" s="41">
-        <v>6053.4099125100583</v>
+        <v>6053.2685744542368</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41"/>
       <c r="J1287" s="40">
-        <v>4138.9535999999998</v>
+        <v>4105.1733000000004</v>
       </c>
       <c r="K1287" s="40"/>
       <c r="L1287" s="40"/>
       <c r="M1287" s="40"/>
       <c r="N1287" s="40">
-        <v>43215.876400000001</v>
+        <v>43182.0962</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58434,16 +58434,16 @@
         <v>46214</v>
       </c>
       <c r="B1288" s="40">
-        <v>60125.404300000002</v>
+        <v>65513.3505</v>
       </c>
       <c r="C1288" s="40">
-        <v>10029.9683</v>
+        <v>10867.7673</v>
       </c>
       <c r="D1288" s="40">
-        <v>5994.5757056879238</v>
+        <v>6028.2253651124829</v>
       </c>
       <c r="E1288" s="41">
-        <v>6105.0050067410157</v>
+        <v>6111.7075997284001</v>
       </c>
       <c r="F1288" s="40">
         <v>624.87549999999999</v>
@@ -58455,16 +58455,16 @@
         <v>6414.9733751228068</v>
       </c>
       <c r="I1288" s="41">
-        <v>6733.0825727105384</v>
+        <v>6733.0825727105394</v>
       </c>
       <c r="J1288" s="40">
-        <v>7091.8854000000001</v>
+        <v>7859.0401000000002</v>
       </c>
       <c r="K1288" s="40"/>
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>67842.165200000003</v>
+        <v>73997.266100000008</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58472,16 +58472,16 @@
         <v>46221</v>
       </c>
       <c r="B1289" s="40">
-        <v>31358.2264</v>
+        <v>39701.034599999999</v>
       </c>
       <c r="C1289" s="40">
-        <v>5069.0931</v>
+        <v>6794.2187999999996</v>
       </c>
       <c r="D1289" s="40">
-        <v>6186.1610709024062</v>
+        <v>5843.3553243825472</v>
       </c>
       <c r="E1289" s="41">
-        <v>6144.4071498328285</v>
+        <v>6091.297691139378</v>
       </c>
       <c r="F1289" s="40">
         <v>224.32050000000001</v>
@@ -58493,33 +58493,55 @@
         <v>8978.3506640090291</v>
       </c>
       <c r="I1289" s="41">
-        <v>6696.847239890747</v>
+        <v>6696.8472398907488</v>
       </c>
       <c r="J1289" s="40">
-        <v>16876.227299999999</v>
+        <v>4684.0991999999997</v>
       </c>
       <c r="K1289" s="40"/>
       <c r="L1289" s="40"/>
       <c r="M1289" s="40"/>
       <c r="N1289" s="40">
-        <v>48458.7742</v>
+        <v>44609.454299999998</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1290" s="39"/>
-      <c r="B1290" s="40"/>
-      <c r="C1290" s="40"/>
-      <c r="D1290" s="40"/>
-      <c r="E1290" s="41"/>
-      <c r="F1290" s="40"/>
-      <c r="G1290" s="40"/>
-      <c r="H1290" s="40"/>
-      <c r="I1290" s="41"/>
-      <c r="J1290" s="40"/>
+      <c r="A1290" s="39">
+        <v>46228</v>
+      </c>
+      <c r="B1290" s="40">
+        <v>47863.371500000001</v>
+      </c>
+      <c r="C1290" s="40">
+        <v>7771.6863000000003</v>
+      </c>
+      <c r="D1290" s="40">
+        <v>6158.6854708739338</v>
+      </c>
+      <c r="E1290" s="41">
+        <v>6143.6601315851876</v>
+      </c>
+      <c r="F1290" s="40">
+        <v>3.1762999999999999</v>
+      </c>
+      <c r="G1290" s="40">
+        <v>2.1282000000000001</v>
+      </c>
+      <c r="H1290" s="40">
+        <v>1492.4819095949626</v>
+      </c>
+      <c r="I1290" s="41">
+        <v>6845.1707614014258</v>
+      </c>
+      <c r="J1290" s="40">
+        <v>5634.9993999999997</v>
+      </c>
       <c r="K1290" s="40"/>
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
-      <c r="N1290" s="40"/>
+      <c r="N1290" s="40">
+        <v>53501.547200000001</v>
+      </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1291" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0569AD86-6118-4983-8016-2720C0964F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75279DB1-1F97-401E-9658-BD10FFF45FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55828,7 +55828,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4754.8215409778977</v>
+        <v>4754.8215409778986</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947376</v>
+        <v>4662.2080120947385</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -56123,16 +56123,16 @@
         <v>45787</v>
       </c>
       <c r="B1227" s="35">
-        <v>70759.626999999993</v>
+        <v>70757.422300000006</v>
       </c>
       <c r="C1227" s="35">
         <v>14282.969499999999</v>
       </c>
       <c r="D1227" s="35">
-        <v>4954.1257509511597</v>
+        <v>4953.9713922934598</v>
       </c>
       <c r="E1227" s="36">
-        <v>4890.1011625026067</v>
+        <v>4890.0517446016365</v>
       </c>
       <c r="F1227" s="35">
         <v>699.97680000000003</v>
@@ -56153,7 +56153,7 @@
       <c r="L1227" s="35"/>
       <c r="M1227" s="35"/>
       <c r="N1227" s="37">
-        <v>81062.809599999993</v>
+        <v>81060.604900000006</v>
       </c>
     </row>
     <row r="1228" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56170,7 +56170,7 @@
         <v>5173.8323341700607</v>
       </c>
       <c r="E1228" s="36">
-        <v>5047.8451432953889</v>
+        <v>5047.8023148149696</v>
       </c>
       <c r="F1228" s="35">
         <v>677.62339999999995</v>
@@ -56208,7 +56208,7 @@
         <v>5125.7053923778949</v>
       </c>
       <c r="E1229" s="36">
-        <v>4982.9474278690641</v>
+        <v>4982.9058959779877</v>
       </c>
       <c r="F1229" s="35">
         <v>465.10070000000002</v>
@@ -56246,7 +56246,7 @@
         <v>5223.5652396043834</v>
       </c>
       <c r="E1230" s="36">
-        <v>5028.0222161538768</v>
+        <v>5027.9793445911309</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56512,7 +56512,7 @@
         <v>5278.9174410390733</v>
       </c>
       <c r="E1237" s="36">
-        <v>4925.6527215340466</v>
+        <v>4925.6527215340475</v>
       </c>
       <c r="F1237" s="35">
         <v>770.73030000000006</v>
@@ -56676,7 +56676,7 @@
         <v>4084.1946733397849</v>
       </c>
       <c r="I1241" s="36">
-        <v>6187.5045092790233</v>
+        <v>6187.5045092790242</v>
       </c>
       <c r="J1241" s="35">
         <v>12876.365</v>
@@ -56791,7 +56791,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.50708400844</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -57095,7 +57095,7 @@
         <v>6913.1247380682598</v>
       </c>
       <c r="I1252" s="36">
-        <v>5768.2127381128475</v>
+        <v>5768.2127381128485</v>
       </c>
       <c r="J1252" s="35">
         <v>10772.394200000001</v>
@@ -57247,7 +57247,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244492</v>
+        <v>6258.6852471244511</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.1422999999995</v>
@@ -57264,16 +57264,16 @@
         <v>45997</v>
       </c>
       <c r="B1257" s="35">
-        <v>68664.174299999999</v>
+        <v>68654.878299999997</v>
       </c>
       <c r="C1257" s="35">
         <v>13091.163</v>
       </c>
       <c r="D1257" s="35">
-        <v>5245.0782485864693</v>
+        <v>5244.3681512482881</v>
       </c>
       <c r="E1257" s="36">
-        <v>5419.3248264450785</v>
+        <v>5419.1525845970455</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78650.653999999995</v>
+        <v>78641.357999999993</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57302,16 +57302,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="35">
-        <v>60220.019399999997</v>
+        <v>60220.238700000002</v>
       </c>
       <c r="C1258" s="35">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="35">
-        <v>4963.0274681971578</v>
+        <v>4963.0455417868816</v>
       </c>
       <c r="E1258" s="36">
-        <v>5448.299672637685</v>
+        <v>5448.1295980606383</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75391.242799999993</v>
+        <v>75391.462100000004</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57340,16 +57340,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="35">
-        <v>64199.741600000001</v>
+        <v>64198.712699999996</v>
       </c>
       <c r="C1259" s="35">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="35">
-        <v>5451.9543190628137</v>
+        <v>5451.8669430756354</v>
       </c>
       <c r="E1259" s="36">
-        <v>5178.4570752332056</v>
+        <v>5178.2645005403183</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57370,7 +57370,7 @@
       <c r="L1259" s="35"/>
       <c r="M1259" s="35"/>
       <c r="N1259" s="37">
-        <v>81447.771999999997</v>
+        <v>81446.743099999992</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57387,7 +57387,7 @@
         <v>5176.6167478837451</v>
       </c>
       <c r="E1260" s="36">
-        <v>5203.2284932567827</v>
+        <v>5203.0315957992616</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57425,7 +57425,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5247.308528767293</v>
+        <v>5247.2909381975987</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57463,7 +57463,7 @@
         <v>5564.1977074457418</v>
       </c>
       <c r="E1262" s="36">
-        <v>5249.9817907175802</v>
+        <v>5249.9623796309124</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57492,16 +57492,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58950.121700000003</v>
+        <v>58960.969499999999</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5219.3761879977346</v>
+        <v>5220.3366397725467</v>
       </c>
       <c r="E1263" s="36">
-        <v>5329.8906674749132</v>
+        <v>5330.1285638796189</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57522,7 +57522,7 @@
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69928.648100000006</v>
+        <v>69939.495899999994</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57530,16 +57530,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41392.236199999999</v>
+        <v>41396.216200000003</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5647.2829932153591</v>
+        <v>5647.8259980968633</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.3723936997876</v>
+        <v>5398.7988688741007</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57551,7 +57551,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763587</v>
+        <v>6539.4433219763569</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57560,7 +57560,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49467.633000000002</v>
+        <v>49471.613000000005</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57568,16 +57568,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66740.012400000007</v>
+        <v>66421.520600000003</v>
       </c>
       <c r="C1265" s="40">
-        <v>12794.5746</v>
+        <v>12725.2942</v>
       </c>
       <c r="D1265" s="40">
-        <v>5216.2744355720906</v>
+        <v>5219.6451850991389</v>
       </c>
       <c r="E1265" s="41">
-        <v>5316.2559772565628</v>
+        <v>5317.8681500799594</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,16 +57589,16 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796991011</v>
+        <v>6791.3981796990993</v>
       </c>
       <c r="J1265" s="40">
-        <v>8313.8631000000005</v>
+        <v>8314.8431</v>
       </c>
       <c r="K1265" s="40"/>
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77844.704800000007</v>
+        <v>77527.192999999999</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.0840204317956</v>
+        <v>5321.6336400253795</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57644,16 +57644,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77826.184899999993</v>
+        <v>77390.624400000001</v>
       </c>
       <c r="C1267" s="40">
-        <v>13633.935799999999</v>
+        <v>13530.0152</v>
       </c>
       <c r="D1267" s="40">
-        <v>5708.2698673115356</v>
+        <v>5719.9214676418105</v>
       </c>
       <c r="E1267" s="41">
-        <v>5385.8460736384168</v>
+        <v>5389.6325320580281</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92901.257299999997</v>
+        <v>92465.696800000005</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57682,16 +57682,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="40">
-        <v>65280.814899999998</v>
+        <v>65125.1803</v>
       </c>
       <c r="C1268" s="40">
-        <v>12725.730299999999</v>
+        <v>12691.090099999999</v>
       </c>
       <c r="D1268" s="40">
-        <v>5129.8285725888754</v>
+        <v>5131.5670905212464</v>
       </c>
       <c r="E1268" s="41">
-        <v>5329.8736951000792</v>
+        <v>5333.8436026664886</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81447.077699999994</v>
+        <v>81291.443100000004</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57729,7 +57729,7 @@
         <v>5300.171449730462</v>
       </c>
       <c r="E1269" s="41">
-        <v>5315.3355848277452</v>
+        <v>5319.2153477055026</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57767,7 +57767,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5429.1635418920587</v>
+        <v>5432.3142101446783</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57796,16 +57796,16 @@
         <v>46095</v>
       </c>
       <c r="B1271" s="40">
-        <v>65142.573700000001</v>
+        <v>65104.860200000003</v>
       </c>
       <c r="C1271" s="40">
-        <v>11941.232099999999</v>
+        <v>11933.152700000001</v>
       </c>
       <c r="D1271" s="40">
-        <v>5455.2640091469293</v>
+        <v>5455.7971255995071</v>
       </c>
       <c r="E1271" s="41">
-        <v>5409.8129889049706</v>
+        <v>5412.3026986031427</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -57826,7 +57826,7 @@
       <c r="L1271" s="40"/>
       <c r="M1271" s="40"/>
       <c r="N1271" s="40">
-        <v>76685.904800000004</v>
+        <v>76648.191300000006</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57843,7 +57843,7 @@
         <v>6070.5855710333217</v>
       </c>
       <c r="E1272" s="41">
-        <v>5601.0656177981882</v>
+        <v>5602.1150929682271</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57872,16 +57872,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="40">
-        <v>62465.5893</v>
+        <v>62466.256500000003</v>
       </c>
       <c r="C1273" s="40">
         <v>10894.957700000001</v>
       </c>
       <c r="D1273" s="40">
-        <v>5733.4402776065845</v>
+        <v>5733.5015169448516</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.6689720091117</v>
+        <v>5668.8691650006795</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57893,16 +57893,16 @@
         <v>6274.2182633165548</v>
       </c>
       <c r="I1273" s="41">
-        <v>7161.2268208604146</v>
+        <v>7161.2268208604155</v>
       </c>
       <c r="J1273" s="40">
-        <v>11036.180899999999</v>
+        <v>11036.540800000001</v>
       </c>
       <c r="K1273" s="40"/>
       <c r="L1273" s="40"/>
       <c r="M1273" s="40"/>
       <c r="N1273" s="40">
-        <v>74202.760999999999</v>
+        <v>74203.788100000005</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57910,16 +57910,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52077.833500000001</v>
+        <v>52077.875500000002</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5404.5504388769887</v>
+        <v>5404.5547975667259</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.7689625057319</v>
+        <v>5579.9615703602058</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.6364000000001</v>
@@ -57931,7 +57931,7 @@
         <v>4533.0580246747986</v>
       </c>
       <c r="I1274" s="41">
-        <v>6471.0708305987382</v>
+        <v>6471.0708305987373</v>
       </c>
       <c r="J1274" s="40">
         <v>8468.0509000000002</v>
@@ -57940,7 +57940,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61593.520799999998</v>
+        <v>61593.5628</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57957,7 +57957,7 @@
         <v>6108.0952984412024</v>
       </c>
       <c r="E1275" s="41">
-        <v>5670.1497406014423</v>
+        <v>5670.3889646355983</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57995,7 +57995,7 @@
         <v>5803.7573777391617</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.9960412601968</v>
+        <v>5699.0164787011427</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58033,7 +58033,7 @@
         <v>5849.2860061910824</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.9087070990963</v>
+        <v>5646.8972559732256</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58071,7 +58071,7 @@
         <v>5131.8309114425856</v>
       </c>
       <c r="E1278" s="41">
-        <v>5540.4614049643897</v>
+        <v>5540.4643735939371</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58124,13 +58124,13 @@
         <v>6125.9423204335426</v>
       </c>
       <c r="J1279" s="40">
-        <v>4317.6104999999998</v>
+        <v>4317.6605</v>
       </c>
       <c r="K1279" s="40"/>
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>38858.601299999995</v>
+        <v>38858.651299999998</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58138,16 +58138,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61760.604599999999</v>
+        <v>61763.592600000004</v>
       </c>
       <c r="C1280" s="40">
         <v>9434.8724000000002</v>
       </c>
       <c r="D1280" s="40">
-        <v>6545.9925668947044</v>
+        <v>6546.3092643415084</v>
       </c>
       <c r="E1280" s="41">
-        <v>6015.3090002181152</v>
+        <v>6015.4146038310309</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58168,7 +58168,7 @@
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>68034.096999999994</v>
+        <v>68037.085000000006</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58185,7 +58185,7 @@
         <v>6767.986480232903</v>
       </c>
       <c r="E1281" s="41">
-        <v>6314.9977527088895</v>
+        <v>6315.098902897229</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58223,7 +58223,7 @@
         <v>5619.4321642538889</v>
       </c>
       <c r="E1282" s="41">
-        <v>6315.8549488908811</v>
+        <v>6315.9409392866755</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58252,16 +58252,16 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>62411.133800000003</v>
+        <v>62412.957300000002</v>
       </c>
       <c r="C1283" s="40">
         <v>11163.6018</v>
       </c>
       <c r="D1283" s="40">
-        <v>5590.5911835730294</v>
+        <v>5590.7545269126313</v>
       </c>
       <c r="E1283" s="41">
-        <v>6033.2994873833077</v>
+        <v>6033.4153188591727</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58282,7 +58282,7 @@
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>71801.810299999997</v>
+        <v>71803.633799999996</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58290,16 +58290,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>39458.7673</v>
+        <v>39462.3073</v>
       </c>
       <c r="C1284" s="40">
         <v>6226.7978999999996</v>
       </c>
       <c r="D1284" s="40">
-        <v>6336.9275723562505</v>
+        <v>6337.4960828582534</v>
       </c>
       <c r="E1284" s="41">
-        <v>5952.1792214915067</v>
+        <v>5952.3082443234562</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58320,7 +58320,7 @@
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55870.823600000003</v>
+        <v>55874.363599999997</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62564.183400000002</v>
+        <v>62574.642999999996</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5908.1530422082869</v>
+        <v>5909.1407785488254</v>
       </c>
       <c r="E1285" s="41">
-        <v>5834.5761424554439</v>
+        <v>5834.9689544792518</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58352,13 +58352,13 @@
         <v>7181.0649723522511</v>
       </c>
       <c r="J1285" s="40">
-        <v>16970.973600000001</v>
+        <v>17095.3868</v>
       </c>
       <c r="K1285" s="40"/>
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80136.104300000006</v>
+        <v>80270.977099999989</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62180.959900000002</v>
+        <v>62183.706200000001</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6204.129687536496</v>
+        <v>6204.4037006972494</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.8735172761135</v>
+        <v>5861.2847931924789</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58396,7 +58396,7 @@
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69947.577099999995</v>
+        <v>69950.323399999994</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58413,7 +58413,7 @@
         <v>6394.407669795979</v>
       </c>
       <c r="E1287" s="41">
-        <v>6053.2685744542368</v>
+        <v>6053.7184742696609</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
@@ -58434,37 +58434,37 @@
         <v>46214</v>
       </c>
       <c r="B1288" s="40">
-        <v>65513.3505</v>
+        <v>68442.713399999993</v>
       </c>
       <c r="C1288" s="40">
-        <v>10867.7673</v>
+        <v>11480.580099999999</v>
       </c>
       <c r="D1288" s="40">
-        <v>6028.2253651124829</v>
+        <v>5961.607584620223</v>
       </c>
       <c r="E1288" s="41">
-        <v>6111.7075997284001</v>
+        <v>6091.9278567169531</v>
       </c>
       <c r="F1288" s="40">
-        <v>624.87549999999999</v>
+        <v>420.85899999999998</v>
       </c>
       <c r="G1288" s="40">
-        <v>97.408900000000003</v>
+        <v>74.167199999999994</v>
       </c>
       <c r="H1288" s="40">
-        <v>6414.9733751228068</v>
+        <v>5674.4625656624494</v>
       </c>
       <c r="I1288" s="41">
-        <v>6733.0825727105394</v>
+        <v>6517.7655661061181</v>
       </c>
       <c r="J1288" s="40">
-        <v>7859.0401000000002</v>
+        <v>8176.9858999999997</v>
       </c>
       <c r="K1288" s="40"/>
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>73997.266100000008</v>
+        <v>77040.55829999999</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58472,37 +58472,37 @@
         <v>46221</v>
       </c>
       <c r="B1289" s="40">
-        <v>39701.034599999999</v>
+        <v>44654.748500000002</v>
       </c>
       <c r="C1289" s="40">
-        <v>6794.2187999999996</v>
+        <v>7662.85</v>
       </c>
       <c r="D1289" s="40">
-        <v>5843.3553243825472</v>
+        <v>5827.4334614405861</v>
       </c>
       <c r="E1289" s="41">
-        <v>6091.297691139378</v>
+        <v>6062.4644855589568</v>
       </c>
       <c r="F1289" s="40">
-        <v>224.32050000000001</v>
+        <v>690.25120000000004</v>
       </c>
       <c r="G1289" s="40">
-        <v>24.9846</v>
+        <v>78.057900000000004</v>
       </c>
       <c r="H1289" s="40">
-        <v>8978.3506640090291</v>
+        <v>8842.8102728871781</v>
       </c>
       <c r="I1289" s="41">
-        <v>6696.8472398907488</v>
+        <v>7030.0234587595005</v>
       </c>
       <c r="J1289" s="40">
-        <v>4684.0991999999997</v>
+        <v>5022.7676000000001</v>
       </c>
       <c r="K1289" s="40"/>
       <c r="L1289" s="40"/>
       <c r="M1289" s="40"/>
       <c r="N1289" s="40">
-        <v>44609.454299999998</v>
+        <v>50367.7673</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58510,54 +58510,76 @@
         <v>46228</v>
       </c>
       <c r="B1290" s="40">
-        <v>47863.371500000001</v>
+        <v>69941.0674</v>
       </c>
       <c r="C1290" s="40">
-        <v>7771.6863000000003</v>
+        <v>11786.559300000001</v>
       </c>
       <c r="D1290" s="40">
-        <v>6158.6854708739338</v>
+        <v>5933.9681428489484</v>
       </c>
       <c r="E1290" s="41">
-        <v>6143.6601315851876</v>
+        <v>6052.368252940284</v>
       </c>
       <c r="F1290" s="40">
-        <v>3.1762999999999999</v>
+        <v>89.335999999999999</v>
       </c>
       <c r="G1290" s="40">
-        <v>2.1282000000000001</v>
+        <v>15.245200000000001</v>
       </c>
       <c r="H1290" s="40">
-        <v>1492.4819095949626</v>
+        <v>5859.9428016687216</v>
       </c>
       <c r="I1290" s="41">
-        <v>6845.1707614014258</v>
+        <v>7168.1139879727934</v>
       </c>
       <c r="J1290" s="40">
-        <v>5634.9993999999997</v>
+        <v>6583.1998999999996</v>
       </c>
       <c r="K1290" s="40"/>
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>53501.547200000001</v>
+        <v>76613.603300000002</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1291" s="39"/>
-      <c r="B1291" s="40"/>
-      <c r="C1291" s="40"/>
-      <c r="D1291" s="40"/>
-      <c r="E1291" s="41"/>
-      <c r="F1291" s="40"/>
-      <c r="G1291" s="40"/>
-      <c r="H1291" s="40"/>
-      <c r="I1291" s="41"/>
-      <c r="J1291" s="40"/>
+      <c r="A1291" s="39">
+        <v>46235</v>
+      </c>
+      <c r="B1291" s="40">
+        <v>34781.267599999999</v>
+      </c>
+      <c r="C1291" s="40">
+        <v>5628.7125999999998</v>
+      </c>
+      <c r="D1291" s="40">
+        <v>6179.2580420609866</v>
+      </c>
+      <c r="E1291" s="41">
+        <v>6037.9612282838361</v>
+      </c>
+      <c r="F1291" s="40">
+        <v>653.77359999999999</v>
+      </c>
+      <c r="G1291" s="40">
+        <v>86.800200000000004</v>
+      </c>
+      <c r="H1291" s="40">
+        <v>7531.9365623581507</v>
+      </c>
+      <c r="I1291" s="41">
+        <v>7292.311927651851</v>
+      </c>
+      <c r="J1291" s="40">
+        <v>9229.1733999999997</v>
+      </c>
       <c r="K1291" s="40"/>
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
-      <c r="N1291" s="40"/>
+      <c r="N1291" s="40">
+        <v>44664.214599999999</v>
+      </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1292" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75279DB1-1F97-401E-9658-BD10FFF45FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FDEF3C-0602-4145-9E36-32A7DAA70F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58418,7 +58418,9 @@
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
-      <c r="I1287" s="41"/>
+      <c r="I1287" s="41">
+        <v>6627</v>
+      </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
       </c>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FDEF3C-0602-4145-9E36-32A7DAA70F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0660F924-14F3-4842-903C-A981237703DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INAC" sheetId="1" r:id="rId1"/>
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.5969827764493</v>
+        <v>4600.5969827764502</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8123550761293</v>
+        <v>4705.8123550761275</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55790,7 +55790,7 @@
         <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4735.8590672017526</v>
+        <v>4735.8590672017517</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55828,7 +55828,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4754.8215409778986</v>
+        <v>4754.8215409778977</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947385</v>
+        <v>4662.2080120947376</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -56018,7 +56018,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4672.9782577126962</v>
+        <v>4672.9782577126971</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56123,16 +56123,16 @@
         <v>45787</v>
       </c>
       <c r="B1227" s="35">
-        <v>70757.422300000006</v>
+        <v>70757.422999999995</v>
       </c>
       <c r="C1227" s="35">
         <v>14282.969499999999</v>
       </c>
       <c r="D1227" s="35">
-        <v>4953.9713922934598</v>
+        <v>4953.9714413028751</v>
       </c>
       <c r="E1227" s="36">
-        <v>4890.0517446016365</v>
+        <v>4890.0517602919936</v>
       </c>
       <c r="F1227" s="35">
         <v>699.97680000000003</v>
@@ -56153,7 +56153,7 @@
       <c r="L1227" s="35"/>
       <c r="M1227" s="35"/>
       <c r="N1227" s="37">
-        <v>81060.604900000006</v>
+        <v>81060.605599999995</v>
       </c>
     </row>
     <row r="1228" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56170,7 +56170,7 @@
         <v>5173.8323341700607</v>
       </c>
       <c r="E1228" s="36">
-        <v>5047.8023148149696</v>
+        <v>5047.8023284131623</v>
       </c>
       <c r="F1228" s="35">
         <v>677.62339999999995</v>
@@ -56208,7 +56208,7 @@
         <v>5125.7053923778949</v>
       </c>
       <c r="E1229" s="36">
-        <v>4982.9058959779877</v>
+        <v>4982.9059091645086</v>
       </c>
       <c r="F1229" s="35">
         <v>465.10070000000002</v>
@@ -56246,7 +56246,7 @@
         <v>5223.5652396043834</v>
       </c>
       <c r="E1230" s="36">
-        <v>5027.9793445911309</v>
+        <v>5027.9793582030034</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56550,7 +56550,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.2761378662899</v>
+        <v>5020.2761378662917</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56562,7 +56562,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253522</v>
+        <v>5662.7424793253513</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56600,7 +56600,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316097</v>
+        <v>6067.7529720316115</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56638,7 +56638,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712294</v>
+        <v>6497.7712544712285</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56703,7 +56703,7 @@
         <v>5268.9257819850018</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.2340433056661</v>
+        <v>5374.2340433056652</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56741,7 +56741,7 @@
         <v>5139.52719767897</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.0821484626749</v>
+        <v>5338.082148462674</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56753,7 +56753,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56791,7 +56791,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084409</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56846,16 +56846,16 @@
         <v>45920</v>
       </c>
       <c r="B1246" s="35">
-        <v>62618.347500000003</v>
+        <v>62658.867200000001</v>
       </c>
       <c r="C1246" s="35">
         <v>11947.379300000001</v>
       </c>
       <c r="D1246" s="35">
-        <v>5241.1784984511205</v>
+        <v>5244.5700121029886</v>
       </c>
       <c r="E1246" s="36">
-        <v>5100.6651335349852</v>
+        <v>5101.5184167886719</v>
       </c>
       <c r="F1246" s="35">
         <v>977.74770000000001</v>
@@ -56876,7 +56876,7 @@
       <c r="L1246" s="35"/>
       <c r="M1246" s="35"/>
       <c r="N1246" s="37">
-        <v>70118.402900000001</v>
+        <v>70158.922600000005</v>
       </c>
     </row>
     <row r="1247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56893,7 +56893,7 @@
         <v>5285.8148363219088</v>
       </c>
       <c r="E1247" s="36">
-        <v>5103.906901146971</v>
+        <v>5104.8219174215428</v>
       </c>
       <c r="F1247" s="35">
         <v>1625.8276000000001</v>
@@ -56931,7 +56931,7 @@
         <v>4658.6445909997819</v>
       </c>
       <c r="E1248" s="36">
-        <v>5063.3894640616645</v>
+        <v>5064.4315799785836</v>
       </c>
       <c r="F1248" s="35">
         <v>1018.4743</v>
@@ -56969,7 +56969,7 @@
         <v>4382.8174971698409</v>
       </c>
       <c r="E1249" s="36">
-        <v>4971.132415256563</v>
+        <v>4972.2196515399091</v>
       </c>
       <c r="F1249" s="35">
         <v>1116.6591000000001</v>
@@ -56981,7 +56981,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691884</v>
+        <v>5046.6456948691875</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57007,7 +57007,7 @@
         <v>4930.8930088570733</v>
       </c>
       <c r="E1250" s="36">
-        <v>4939.2643909473018</v>
+        <v>4940.3686918435942</v>
       </c>
       <c r="F1250" s="35">
         <v>1339.0517</v>
@@ -57112,16 +57112,16 @@
         <v>45969</v>
       </c>
       <c r="B1253" s="35">
-        <v>88063.741200000004</v>
+        <v>88054.649099999995</v>
       </c>
       <c r="C1253" s="35">
         <v>15503.728800000001</v>
       </c>
       <c r="D1253" s="35">
-        <v>5680.1652258003896</v>
+        <v>5679.5787797836083</v>
       </c>
       <c r="E1253" s="36">
-        <v>5197.188767083524</v>
+        <v>5197.0071791359587</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57142,7 +57142,7 @@
       <c r="L1253" s="35"/>
       <c r="M1253" s="35"/>
       <c r="N1253" s="37">
-        <v>103444.8993</v>
+        <v>103435.8072</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57159,7 +57159,7 @@
         <v>5045.5549585912104</v>
       </c>
       <c r="E1254" s="36">
-        <v>5301.2769233385989</v>
+        <v>5301.0786076052145</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57197,7 +57197,7 @@
         <v>6210.2065487022992</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.9414421875581</v>
+        <v>5572.7762899099307</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371017</v>
+        <v>5978.5241558371008</v>
       </c>
       <c r="J1255" s="35">
         <v>12541.2435</v>
@@ -57235,7 +57235,7 @@
         <v>5186.7451814499636</v>
       </c>
       <c r="E1256" s="36">
-        <v>5467.716221440277</v>
+        <v>5467.5609879501126</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57302,16 +57302,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="35">
-        <v>60220.238700000002</v>
+        <v>60216.499499999998</v>
       </c>
       <c r="C1258" s="35">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="35">
-        <v>4963.0455417868816</v>
+        <v>4962.7373759560833</v>
       </c>
       <c r="E1258" s="36">
-        <v>5448.1295980606383</v>
+        <v>5448.0595348373854</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57323,7 +57323,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="35">
         <v>10810.321599999999</v>
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75391.462100000004</v>
+        <v>75387.722899999993</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57349,7 +57349,7 @@
         <v>5451.8669430756354</v>
       </c>
       <c r="E1259" s="36">
-        <v>5178.2645005403183</v>
+        <v>5178.1932454647522</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57361,7 +57361,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096225</v>
+        <v>7266.6202217096234</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57387,7 +57387,7 @@
         <v>5176.6167478837451</v>
       </c>
       <c r="E1260" s="36">
-        <v>5203.0315957992616</v>
+        <v>5202.9587412460278</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57399,7 +57399,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="35">
         <v>7674.9405999999999</v>
@@ -57425,7 +57425,7 @@
         <v>5318.4520029168943</v>
       </c>
       <c r="E1261" s="36">
-        <v>5247.2909381975987</v>
+        <v>5247.2096947956634</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57463,7 +57463,7 @@
         <v>5564.1977074457418</v>
       </c>
       <c r="E1262" s="36">
-        <v>5249.9623796309124</v>
+        <v>5249.897708776085</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57492,16 +57492,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58960.969499999999</v>
+        <v>58957.7016</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5220.3366397725467</v>
+        <v>5220.0473036532503</v>
       </c>
       <c r="E1263" s="36">
-        <v>5330.1285638796189</v>
+        <v>5330.0493878353636</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57513,7 +57513,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.391308042289</v>
+        <v>6206.3913080422872</v>
       </c>
       <c r="J1263" s="35">
         <v>7879.2038000000002</v>
@@ -57522,7 +57522,7 @@
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69939.495899999994</v>
+        <v>69936.228000000003</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57530,16 +57530,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41396.216200000003</v>
+        <v>41394.441299999999</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5647.8259980968633</v>
+        <v>5647.5838424777212</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.7988688741007</v>
+        <v>5398.653828543841</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57560,7 +57560,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49471.613000000005</v>
+        <v>49469.838100000001</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57568,16 +57568,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66421.520600000003</v>
+        <v>66539.741299999994</v>
       </c>
       <c r="C1265" s="40">
-        <v>12725.2942</v>
+        <v>12751.894200000001</v>
       </c>
       <c r="D1265" s="40">
-        <v>5219.6451850991389</v>
+        <v>5218.0280244169526</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.8681500799594</v>
+        <v>5317.163447941517</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796990993</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8314.8431</v>
@@ -57598,7 +57598,7 @@
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77527.192999999999</v>
+        <v>77645.41369999999</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5321.6336400253795</v>
+        <v>5320.9566394640242</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57653,7 +57653,7 @@
         <v>5719.9214676418105</v>
       </c>
       <c r="E1267" s="41">
-        <v>5389.6325320580281</v>
+        <v>5389.0411281076204</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57682,16 +57682,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="40">
-        <v>65125.1803</v>
+        <v>65124.980300000003</v>
       </c>
       <c r="C1268" s="40">
         <v>12691.090099999999</v>
       </c>
       <c r="D1268" s="40">
-        <v>5131.5670905212464</v>
+        <v>5131.5513314336968</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.8436026664886</v>
+        <v>5333.3402226005692</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57703,7 +57703,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166811</v>
+        <v>6548.0752800166792</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81291.443100000004</v>
+        <v>81291.243100000007</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57720,16 +57720,16 @@
         <v>46081</v>
       </c>
       <c r="B1269" s="40">
-        <v>55619.2736</v>
+        <v>55618.363499999999</v>
       </c>
       <c r="C1269" s="40">
         <v>10493.8631</v>
       </c>
       <c r="D1269" s="40">
-        <v>5300.171449730462</v>
+        <v>5300.0847228510156</v>
       </c>
       <c r="E1269" s="41">
-        <v>5319.2153477055026</v>
+        <v>5318.7527226548918</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57741,7 +57741,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314478</v>
+        <v>6498.4408173314469</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57750,7 +57750,7 @@
       <c r="L1269" s="40"/>
       <c r="M1269" s="40"/>
       <c r="N1269" s="40">
-        <v>64797.953600000001</v>
+        <v>64797.0435</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57767,7 +57767,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.3142101446783</v>
+        <v>5432.2924961889357</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57805,7 +57805,7 @@
         <v>5455.7971255995071</v>
       </c>
       <c r="E1271" s="41">
-        <v>5412.3026986031427</v>
+        <v>5412.2800363640226</v>
       </c>
       <c r="F1271" s="40">
         <v>1808.0657000000001</v>
@@ -57843,7 +57843,7 @@
         <v>6070.5855710333217</v>
       </c>
       <c r="E1272" s="41">
-        <v>5602.1150929682271</v>
+        <v>5602.0897262395038</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57881,7 +57881,7 @@
         <v>5733.5015169448516</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.8691650006795</v>
+        <v>5668.8483501209412</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57922,16 +57922,16 @@
         <v>5579.9615703602058</v>
       </c>
       <c r="F1274" s="40">
-        <v>1047.6364000000001</v>
+        <v>1047.5085999999999</v>
       </c>
       <c r="G1274" s="40">
         <v>231.1103</v>
       </c>
       <c r="H1274" s="40">
-        <v>4533.0580246747986</v>
+        <v>4532.5050419648105</v>
       </c>
       <c r="I1274" s="41">
-        <v>6471.0708305987373</v>
+        <v>6470.9042455083627</v>
       </c>
       <c r="J1274" s="40">
         <v>8468.0509000000002</v>
@@ -57940,7 +57940,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61593.5628</v>
+        <v>61593.434999999998</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57969,7 +57969,7 @@
         <v>6388.4288957961335</v>
       </c>
       <c r="I1275" s="41">
-        <v>5845.0234884410311</v>
+        <v>5844.8491513754561</v>
       </c>
       <c r="J1275" s="40">
         <v>3741.9837000000002</v>
@@ -58007,7 +58007,7 @@
         <v>4448.9160098100365</v>
       </c>
       <c r="I1276" s="41">
-        <v>5606.9800390513055</v>
+        <v>5606.7869431513891</v>
       </c>
       <c r="J1276" s="40">
         <v>6631.9660000000003</v>
@@ -58024,16 +58024,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32077.017100000001</v>
+        <v>32078.936900000001</v>
       </c>
       <c r="C1277" s="40">
         <v>5483.9201000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>5849.2860061910824</v>
+        <v>5849.6360842310596</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.8972559732256</v>
+        <v>5646.9565596458615</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58045,7 +58045,7 @@
         <v>5233.4920630608849</v>
       </c>
       <c r="I1277" s="41">
-        <v>5450.6954327773046</v>
+        <v>5450.5130737709242</v>
       </c>
       <c r="J1277" s="40">
         <v>5183.0592999999999</v>
@@ -58054,7 +58054,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37838.059600000001</v>
+        <v>37839.979399999997</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58062,16 +58062,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>29360.9274</v>
+        <v>29408.240000000002</v>
       </c>
       <c r="C1278" s="40">
         <v>5721.3356999999996</v>
       </c>
       <c r="D1278" s="40">
-        <v>5131.8309114425856</v>
+        <v>5140.1004139645229</v>
       </c>
       <c r="E1278" s="41">
-        <v>5540.4643735939371</v>
+        <v>5542.1858430560524</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58083,7 +58083,7 @@
         <v>7577.0848344925953</v>
       </c>
       <c r="I1278" s="41">
-        <v>5643.202064907332</v>
+        <v>5643.0070838539059</v>
       </c>
       <c r="J1278" s="40">
         <v>12650.7237</v>
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42423.862699999998</v>
+        <v>42471.175300000003</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58100,16 +58100,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>33572.574699999997</v>
+        <v>33626.934300000001</v>
       </c>
       <c r="C1279" s="40">
         <v>5126.8805000000002</v>
       </c>
       <c r="D1279" s="40">
-        <v>6548.343520002074</v>
+        <v>6558.946380747514</v>
       </c>
       <c r="E1279" s="41">
-        <v>5765.889400725302</v>
+        <v>5769.8318486878788</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58130,7 +58130,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>38858.651299999998</v>
+        <v>38913.010900000001</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58138,16 +58138,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61763.592600000004</v>
+        <v>61462.426899999999</v>
       </c>
       <c r="C1280" s="40">
-        <v>9434.8724000000002</v>
+        <v>9397.5049999999992</v>
       </c>
       <c r="D1280" s="40">
-        <v>6546.3092643415084</v>
+        <v>6540.2920136780986</v>
       </c>
       <c r="E1280" s="41">
-        <v>6015.4146038310309</v>
+        <v>6016.3774303517002</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58168,7 +58168,7 @@
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>68037.085000000006</v>
+        <v>67735.919299999994</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58185,7 +58185,7 @@
         <v>6767.986480232903</v>
       </c>
       <c r="E1281" s="41">
-        <v>6315.098902897229</v>
+        <v>6316.3355735598843</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58214,16 +58214,16 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>60277.669099999999</v>
+        <v>60276.363400000002</v>
       </c>
       <c r="C1282" s="40">
         <v>10726.6477</v>
       </c>
       <c r="D1282" s="40">
-        <v>5619.4321642538889</v>
+        <v>5619.3104393649473</v>
       </c>
       <c r="E1282" s="41">
-        <v>6315.9409392866755</v>
+        <v>6315.5923001401234</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76965.00959999999</v>
+        <v>76963.703899999993</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58261,7 +58261,7 @@
         <v>5590.7545269126313</v>
       </c>
       <c r="E1283" s="41">
-        <v>6033.4153188591727</v>
+        <v>6032.9186044734706</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58299,7 +58299,7 @@
         <v>6337.4960828582534</v>
       </c>
       <c r="E1284" s="41">
-        <v>5952.3082443234562</v>
+        <v>5950.3808729999628</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62574.642999999996</v>
+        <v>62562.398999999998</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5909.1407785488254</v>
+        <v>5907.9845351213953</v>
       </c>
       <c r="E1285" s="41">
-        <v>5834.9689544792518</v>
+        <v>5834.6325801228368</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58352,13 +58352,13 @@
         <v>7181.0649723522511</v>
       </c>
       <c r="J1285" s="40">
-        <v>17095.3868</v>
+        <v>17124.551800000001</v>
       </c>
       <c r="K1285" s="40"/>
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80270.977099999989</v>
+        <v>80287.898099999991</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62183.706200000001</v>
+        <v>62178.606800000001</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6204.4037006972494</v>
+        <v>6203.8949060601217</v>
       </c>
       <c r="E1286" s="41">
-        <v>5861.2847931924789</v>
+        <v>5860.871752076886</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58390,13 +58390,13 @@
         <v>6928.2649857850765</v>
       </c>
       <c r="J1286" s="40">
-        <v>7566.6455999999998</v>
+        <v>7564.5738000000001</v>
       </c>
       <c r="K1286" s="40"/>
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69950.323399999994</v>
+        <v>69943.152199999997</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58404,22 +58404,22 @@
         <v>46207</v>
       </c>
       <c r="B1287" s="40">
-        <v>39076.922899999998</v>
+        <v>39076.130899999996</v>
       </c>
       <c r="C1287" s="40">
         <v>6111.1090999999997</v>
       </c>
       <c r="D1287" s="40">
-        <v>6394.407669795979</v>
+        <v>6394.278069753329</v>
       </c>
       <c r="E1287" s="41">
-        <v>6053.7184742696609</v>
+        <v>6053.2312437766668</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41">
-        <v>6627</v>
+        <v>6419</v>
       </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
@@ -58428,7 +58428,7 @@
       <c r="L1287" s="40"/>
       <c r="M1287" s="40"/>
       <c r="N1287" s="40">
-        <v>43182.0962</v>
+        <v>43181.304199999999</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58445,7 +58445,7 @@
         <v>5961.607584620223</v>
       </c>
       <c r="E1288" s="41">
-        <v>6091.9278567169531</v>
+        <v>6091.4810085526233</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58460,13 +58460,13 @@
         <v>6517.7655661061181</v>
       </c>
       <c r="J1288" s="40">
-        <v>8176.9858999999997</v>
+        <v>8188.4609</v>
       </c>
       <c r="K1288" s="40"/>
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>77040.55829999999</v>
+        <v>77052.033299999996</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58474,37 +58474,37 @@
         <v>46221</v>
       </c>
       <c r="B1289" s="40">
-        <v>44654.748500000002</v>
+        <v>44447.422599999998</v>
       </c>
       <c r="C1289" s="40">
-        <v>7662.85</v>
+        <v>7660.7102999999997</v>
       </c>
       <c r="D1289" s="40">
-        <v>5827.4334614405861</v>
+        <v>5801.9975771698355</v>
       </c>
       <c r="E1289" s="41">
-        <v>6062.4644855589568</v>
+        <v>6057.3458484176554</v>
       </c>
       <c r="F1289" s="40">
-        <v>690.25120000000004</v>
+        <v>506.89749999999998</v>
       </c>
       <c r="G1289" s="40">
-        <v>78.057900000000004</v>
+        <v>57.215899999999998</v>
       </c>
       <c r="H1289" s="40">
-        <v>8842.8102728871781</v>
+        <v>8859.3817452840904</v>
       </c>
       <c r="I1289" s="41">
-        <v>7030.0234587595005</v>
+        <v>6807.6707383696894</v>
       </c>
       <c r="J1289" s="40">
-        <v>5022.7676000000001</v>
+        <v>5421.4993999999997</v>
       </c>
       <c r="K1289" s="40"/>
       <c r="L1289" s="40"/>
       <c r="M1289" s="40"/>
       <c r="N1289" s="40">
-        <v>50367.7673</v>
+        <v>50375.819499999998</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58512,37 +58512,37 @@
         <v>46228</v>
       </c>
       <c r="B1290" s="40">
-        <v>69941.0674</v>
+        <v>79546.274999999994</v>
       </c>
       <c r="C1290" s="40">
-        <v>11786.559300000001</v>
+        <v>13437.256100000001</v>
       </c>
       <c r="D1290" s="40">
-        <v>5933.9681428489484</v>
+        <v>5919.8302397466396</v>
       </c>
       <c r="E1290" s="41">
-        <v>6052.368252940284</v>
+        <v>6038.9200835240836</v>
       </c>
       <c r="F1290" s="40">
-        <v>89.335999999999999</v>
+        <v>272.57619999999997</v>
       </c>
       <c r="G1290" s="40">
-        <v>15.245200000000001</v>
+        <v>36.087200000000003</v>
       </c>
       <c r="H1290" s="40">
-        <v>5859.9428016687216</v>
+        <v>7553.2654237513561</v>
       </c>
       <c r="I1290" s="41">
-        <v>7168.1139879727934</v>
+        <v>7167.4362558614857</v>
       </c>
       <c r="J1290" s="40">
-        <v>6583.1998999999996</v>
+        <v>6993.4607999999998</v>
       </c>
       <c r="K1290" s="40"/>
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>76613.603300000002</v>
+        <v>86812.311999999991</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58550,54 +58550,76 @@
         <v>46235</v>
       </c>
       <c r="B1291" s="40">
-        <v>34781.267599999999</v>
+        <v>55555.541899999997</v>
       </c>
       <c r="C1291" s="40">
-        <v>5628.7125999999998</v>
+        <v>9572.7662999999993</v>
       </c>
       <c r="D1291" s="40">
-        <v>6179.2580420609866</v>
+        <v>5803.4992351166038</v>
       </c>
       <c r="E1291" s="41">
-        <v>6037.9612282838361</v>
+        <v>5956.0062364672203</v>
       </c>
       <c r="F1291" s="40">
-        <v>653.77359999999999</v>
+        <v>1014.8816</v>
       </c>
       <c r="G1291" s="40">
-        <v>86.800200000000004</v>
+        <v>123.6353</v>
       </c>
       <c r="H1291" s="40">
-        <v>7531.9365623581507</v>
+        <v>8208.6717951911796</v>
       </c>
       <c r="I1291" s="41">
-        <v>7292.311927651851</v>
+        <v>7609.658831709181</v>
       </c>
       <c r="J1291" s="40">
-        <v>9229.1733999999997</v>
+        <v>11966.0918</v>
       </c>
       <c r="K1291" s="40"/>
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>44664.214599999999</v>
+        <v>68536.515299999999</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1292" s="39"/>
-      <c r="B1292" s="40"/>
-      <c r="C1292" s="40"/>
-      <c r="D1292" s="40"/>
-      <c r="E1292" s="41"/>
-      <c r="F1292" s="40"/>
-      <c r="G1292" s="40"/>
-      <c r="H1292" s="40"/>
-      <c r="I1292" s="41"/>
-      <c r="J1292" s="40"/>
+      <c r="A1292" s="39">
+        <v>46242</v>
+      </c>
+      <c r="B1292" s="40">
+        <v>38598.6734</v>
+      </c>
+      <c r="C1292" s="40">
+        <v>6027.7784000000001</v>
+      </c>
+      <c r="D1292" s="40">
+        <v>6403.4658938357779</v>
+      </c>
+      <c r="E1292" s="41">
+        <v>5962.5627469983747</v>
+      </c>
+      <c r="F1292" s="40">
+        <v>13.736000000000001</v>
+      </c>
+      <c r="G1292" s="40">
+        <v>2.6227</v>
+      </c>
+      <c r="H1292" s="40">
+        <v>5237.3508216723221</v>
+      </c>
+      <c r="I1292" s="41">
+        <v>7619.3329349505966</v>
+      </c>
+      <c r="J1292" s="40">
+        <v>3673.4850000000001</v>
+      </c>
       <c r="K1292" s="40"/>
       <c r="L1292" s="40"/>
       <c r="M1292" s="40"/>
-      <c r="N1292" s="40"/>
+      <c r="N1292" s="40">
+        <v>42285.894399999997</v>
+      </c>
     </row>
     <row r="1293" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1293" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0660F924-14F3-4842-903C-A981237703DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C25A43-E7A2-4DD0-BFAC-0DAF41E2BB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INAC" sheetId="1" r:id="rId1"/>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.5969827764502</v>
+        <v>4600.5969827764493</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8123550761275</v>
+        <v>4705.8123550761293</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55790,7 +55790,7 @@
         <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4735.8590672017517</v>
+        <v>4735.8590672017526</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55828,7 +55828,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4754.8215409778977</v>
+        <v>4754.8215409778986</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947376</v>
+        <v>4662.2080120947385</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -56018,7 +56018,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4672.9782577126971</v>
+        <v>4672.9782577126962</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56550,7 +56550,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.2761378662917</v>
+        <v>5020.2761378662899</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56562,7 +56562,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253513</v>
+        <v>5662.7424793253522</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56600,7 +56600,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316115</v>
+        <v>6067.7529720316097</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56638,7 +56638,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712285</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56703,7 +56703,7 @@
         <v>5268.9257819850018</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.2340433056652</v>
+        <v>5374.2340433056661</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56741,7 +56741,7 @@
         <v>5139.52719767897</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.082148462674</v>
+        <v>5338.0821484626749</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56753,7 +56753,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56791,7 +56791,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084427</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56981,7 +56981,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691875</v>
+        <v>5046.6456948691884</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57159,7 +57159,7 @@
         <v>5045.5549585912104</v>
       </c>
       <c r="E1254" s="36">
-        <v>5301.0786076052145</v>
+        <v>5301.0786076052154</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57197,7 +57197,7 @@
         <v>6210.2065487022992</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.7762899099307</v>
+        <v>5572.7762899099316</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371008</v>
+        <v>5978.5241558371017</v>
       </c>
       <c r="J1255" s="35">
         <v>12541.2435</v>
@@ -57226,16 +57226,16 @@
         <v>45990</v>
       </c>
       <c r="B1256" s="35">
-        <v>64995.318599999999</v>
+        <v>64982.8246</v>
       </c>
       <c r="C1256" s="35">
         <v>12531.0414</v>
       </c>
       <c r="D1256" s="35">
-        <v>5186.7451814499636</v>
+        <v>5185.7481374213639</v>
       </c>
       <c r="E1256" s="36">
-        <v>5467.5609879501126</v>
+        <v>5467.3476722995892</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57247,7 +57247,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244511</v>
+        <v>6258.6852471244501</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.1422999999995</v>
@@ -57256,7 +57256,7 @@
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77380.400899999993</v>
+        <v>77367.906900000002</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57273,7 +57273,7 @@
         <v>5244.3681512482881</v>
       </c>
       <c r="E1257" s="36">
-        <v>5419.1525845970455</v>
+        <v>5418.9210882922562</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57285,7 +57285,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6857.6810418042405</v>
+        <v>6857.6810418042396</v>
       </c>
       <c r="J1257" s="35">
         <v>7037.5686999999998</v>
@@ -57311,7 +57311,7 @@
         <v>4962.7373759560833</v>
       </c>
       <c r="E1258" s="36">
-        <v>5448.0595348373854</v>
+        <v>5447.8254286351712</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57323,7 +57323,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="35">
         <v>10810.321599999999</v>
@@ -57349,7 +57349,7 @@
         <v>5451.8669430756354</v>
       </c>
       <c r="E1259" s="36">
-        <v>5178.1932454647522</v>
+        <v>5177.9551568591332</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57361,7 +57361,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096234</v>
+        <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57399,7 +57399,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="35">
         <v>7674.9405999999999</v>
@@ -57492,16 +57492,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58957.7016</v>
+        <v>58956.644500000002</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5220.0473036532503</v>
+        <v>5219.953709231233</v>
       </c>
       <c r="E1263" s="36">
-        <v>5330.0493878353636</v>
+        <v>5330.0237759756428</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57513,7 +57513,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.3913080422872</v>
+        <v>6206.391308042289</v>
       </c>
       <c r="J1263" s="35">
         <v>7879.2038000000002</v>
@@ -57522,7 +57522,7 @@
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69936.228000000003</v>
+        <v>69935.170899999997</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57539,7 +57539,7 @@
         <v>5647.5838424777212</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.653828543841</v>
+        <v>5398.6234243768877</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57577,7 +57577,7 @@
         <v>5218.0280244169526</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.163447941517</v>
+        <v>5317.1371039063351</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,16 +57589,16 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796990993</v>
       </c>
       <c r="J1265" s="40">
-        <v>8314.8431</v>
+        <v>8388.1373999999996</v>
       </c>
       <c r="K1265" s="40"/>
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77645.41369999999</v>
+        <v>77718.707999999999</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.9566394640242</v>
+        <v>5320.9314203322911</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57653,7 +57653,7 @@
         <v>5719.9214676418105</v>
       </c>
       <c r="E1267" s="41">
-        <v>5389.0411281076204</v>
+        <v>5389.0192391551263</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57703,7 +57703,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57741,7 +57741,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314469</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57767,7 +57767,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.2924961889357</v>
+        <v>5432.2924961889375</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57808,16 +57808,16 @@
         <v>5412.2800363640226</v>
       </c>
       <c r="F1271" s="40">
-        <v>1808.0657000000001</v>
+        <v>1806.9168</v>
       </c>
       <c r="G1271" s="40">
         <v>256.40100000000001</v>
       </c>
       <c r="H1271" s="40">
-        <v>7051.7107967597631</v>
+        <v>7047.2299250002925</v>
       </c>
       <c r="I1271" s="41">
-        <v>7489.2724524389059</v>
+        <v>7487.938713725157</v>
       </c>
       <c r="J1271" s="40">
         <v>9735.2654000000002</v>
@@ -57826,7 +57826,7 @@
       <c r="L1271" s="40"/>
       <c r="M1271" s="40"/>
       <c r="N1271" s="40">
-        <v>76648.191300000006</v>
+        <v>76647.042400000006</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57855,7 +57855,7 @@
         <v>6795.4583328054659</v>
       </c>
       <c r="I1272" s="41">
-        <v>7304.0585980662427</v>
+        <v>7302.6463313702043</v>
       </c>
       <c r="J1272" s="40">
         <v>7915.2548999999999</v>
@@ -57893,7 +57893,7 @@
         <v>6274.2182633165548</v>
       </c>
       <c r="I1273" s="41">
-        <v>7161.2268208604155</v>
+        <v>7159.6516217257122</v>
       </c>
       <c r="J1273" s="40">
         <v>11036.540800000001</v>
@@ -57931,7 +57931,7 @@
         <v>4532.5050419648105</v>
       </c>
       <c r="I1274" s="41">
-        <v>6470.9042455083627</v>
+        <v>6469.4066742225223</v>
       </c>
       <c r="J1274" s="40">
         <v>8468.0509000000002</v>
@@ -57948,16 +57948,16 @@
         <v>46123</v>
       </c>
       <c r="B1275" s="40">
-        <v>25434.627400000001</v>
+        <v>25430.074199999999</v>
       </c>
       <c r="C1275" s="40">
         <v>4164.0848999999998</v>
       </c>
       <c r="D1275" s="40">
-        <v>6108.0952984412024</v>
+        <v>6107.0018529161116</v>
       </c>
       <c r="E1275" s="41">
-        <v>5670.3889646355983</v>
+        <v>5670.2652878400704</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57969,7 +57969,7 @@
         <v>6388.4288957961335</v>
       </c>
       <c r="I1275" s="41">
-        <v>5844.8491513754561</v>
+        <v>5843.2818911670183</v>
       </c>
       <c r="J1275" s="40">
         <v>3741.9837000000002</v>
@@ -57978,7 +57978,7 @@
       <c r="L1275" s="40"/>
       <c r="M1275" s="40"/>
       <c r="N1275" s="40">
-        <v>30625.602600000002</v>
+        <v>30621.0494</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57986,16 +57986,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45554.281900000002</v>
+        <v>45553.238499999999</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.7573777391617</v>
+        <v>5803.6244453298395</v>
       </c>
       <c r="E1276" s="41">
-        <v>5699.0164787011427</v>
+        <v>5698.855198128671</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58016,7 +58016,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52469.417400000006</v>
+        <v>52468.373999999996</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58033,7 +58033,7 @@
         <v>5849.6360842310596</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.9565596458615</v>
+        <v>5646.7836776090489</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58071,7 +58071,7 @@
         <v>5140.1004139645229</v>
       </c>
       <c r="E1278" s="41">
-        <v>5542.1858430560524</v>
+        <v>5541.9901512760125</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58109,7 +58109,7 @@
         <v>6558.946380747514</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.8318486878788</v>
+        <v>5769.7921395384828</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58138,16 +58138,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61462.426899999999</v>
+        <v>61457.873699999996</v>
       </c>
       <c r="C1280" s="40">
         <v>9397.5049999999992</v>
       </c>
       <c r="D1280" s="40">
-        <v>6540.2920136780986</v>
+        <v>6539.8075020976312</v>
       </c>
       <c r="E1280" s="41">
-        <v>6016.3774303517002</v>
+        <v>6016.2162957369546</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58168,7 +58168,7 @@
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>67735.919299999994</v>
+        <v>67731.366099999999</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58176,16 +58176,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>57168.044099999999</v>
+        <v>57163.490899999997</v>
       </c>
       <c r="C1281" s="40">
         <v>8446.8318999999992</v>
       </c>
       <c r="D1281" s="40">
-        <v>6767.986480232903</v>
+        <v>6767.4474378968052</v>
       </c>
       <c r="E1281" s="41">
-        <v>6316.3355735598843</v>
+        <v>6316.0269120039284</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58206,7 +58206,7 @@
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>65018.802499999998</v>
+        <v>65014.249299999996</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58223,7 +58223,7 @@
         <v>5619.3104393649473</v>
       </c>
       <c r="E1282" s="41">
-        <v>6315.5923001401234</v>
+        <v>6315.329948755395</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58261,7 +58261,7 @@
         <v>5590.7545269126313</v>
       </c>
       <c r="E1283" s="41">
-        <v>6032.9186044734706</v>
+        <v>6032.6991806995202</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58299,7 +58299,7 @@
         <v>6337.4960828582534</v>
       </c>
       <c r="E1284" s="41">
-        <v>5950.3808729999628</v>
+        <v>5950.2712439690786</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62562.398999999998</v>
+        <v>62551.678200000002</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5907.9845351213953</v>
+        <v>5906.9721327580501</v>
       </c>
       <c r="E1285" s="41">
-        <v>5834.6325801228368</v>
+        <v>5834.366433846516</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58358,7 +58358,7 @@
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80287.898099999991</v>
+        <v>80277.17730000001</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58375,7 +58375,7 @@
         <v>6203.8949060601217</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.871752076886</v>
+        <v>5860.634307310539</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58413,7 +58413,7 @@
         <v>6394.278069753329</v>
       </c>
       <c r="E1287" s="41">
-        <v>6053.2312437766668</v>
+        <v>6052.9432159046983</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
@@ -58445,7 +58445,7 @@
         <v>5961.607584620223</v>
       </c>
       <c r="E1288" s="41">
-        <v>6091.4810085526233</v>
+        <v>6091.2168528240391</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58460,13 +58460,13 @@
         <v>6517.7655661061181</v>
       </c>
       <c r="J1288" s="40">
-        <v>8188.4609</v>
+        <v>8205.4748999999993</v>
       </c>
       <c r="K1288" s="40"/>
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>77052.033299999996</v>
+        <v>77069.047299999991</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58483,7 +58483,7 @@
         <v>5801.9975771698355</v>
       </c>
       <c r="E1289" s="41">
-        <v>6057.3458484176554</v>
+        <v>6057.07422588598</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58512,16 +58512,16 @@
         <v>46228</v>
       </c>
       <c r="B1290" s="40">
-        <v>79546.274999999994</v>
+        <v>79763.369600000005</v>
       </c>
       <c r="C1290" s="40">
-        <v>13437.256100000001</v>
+        <v>13474.185299999999</v>
       </c>
       <c r="D1290" s="40">
-        <v>5919.8302397466396</v>
+        <v>5919.7174318212774</v>
       </c>
       <c r="E1290" s="41">
-        <v>6038.9200835240836</v>
+        <v>6038.7836762169109</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58536,13 +58536,13 @@
         <v>7167.4362558614857</v>
       </c>
       <c r="J1290" s="40">
-        <v>6993.4607999999998</v>
+        <v>6905.1966000000002</v>
       </c>
       <c r="K1290" s="40"/>
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86812.311999999991</v>
+        <v>86941.142400000012</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58550,16 +58550,16 @@
         <v>46235</v>
       </c>
       <c r="B1291" s="40">
-        <v>55555.541899999997</v>
+        <v>58008.694799999997</v>
       </c>
       <c r="C1291" s="40">
-        <v>9572.7662999999993</v>
+        <v>10109.5954</v>
       </c>
       <c r="D1291" s="40">
-        <v>5803.4992351166038</v>
+        <v>5737.9838168399892</v>
       </c>
       <c r="E1291" s="41">
-        <v>5956.0062364672203</v>
+        <v>5939.2028252240179</v>
       </c>
       <c r="F1291" s="40">
         <v>1014.8816</v>
@@ -58574,13 +58574,13 @@
         <v>7609.658831709181</v>
       </c>
       <c r="J1291" s="40">
-        <v>11966.0918</v>
+        <v>12253.542799999999</v>
       </c>
       <c r="K1291" s="40"/>
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>68536.515299999999</v>
+        <v>71277.119200000001</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58588,54 +58588,76 @@
         <v>46242</v>
       </c>
       <c r="B1292" s="40">
-        <v>38598.6734</v>
+        <v>50372.4833</v>
       </c>
       <c r="C1292" s="40">
-        <v>6027.7784000000001</v>
+        <v>7858.1157999999996</v>
       </c>
       <c r="D1292" s="40">
-        <v>6403.4658938357779</v>
+        <v>6410.2495537161722</v>
       </c>
       <c r="E1292" s="41">
-        <v>5962.5627469983747</v>
+        <v>5964.8942642006386</v>
       </c>
       <c r="F1292" s="40">
-        <v>13.736000000000001</v>
+        <v>264.58980000000003</v>
       </c>
       <c r="G1292" s="40">
-        <v>2.6227</v>
+        <v>46.1312</v>
       </c>
       <c r="H1292" s="40">
-        <v>5237.3508216723221</v>
+        <v>5735.5932644284139</v>
       </c>
       <c r="I1292" s="41">
-        <v>7619.3329349505966</v>
+        <v>7372.4291167424299</v>
       </c>
       <c r="J1292" s="40">
-        <v>3673.4850000000001</v>
+        <v>4586.1485000000002</v>
       </c>
       <c r="K1292" s="40"/>
       <c r="L1292" s="40"/>
       <c r="M1292" s="40"/>
       <c r="N1292" s="40">
-        <v>42285.894399999997</v>
+        <v>55223.221599999997</v>
       </c>
     </row>
     <row r="1293" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1293" s="39"/>
-      <c r="B1293" s="40"/>
-      <c r="C1293" s="40"/>
-      <c r="D1293" s="40"/>
-      <c r="E1293" s="41"/>
-      <c r="F1293" s="40"/>
-      <c r="G1293" s="40"/>
-      <c r="H1293" s="40"/>
-      <c r="I1293" s="41"/>
-      <c r="J1293" s="40"/>
+      <c r="A1293" s="39">
+        <v>46249</v>
+      </c>
+      <c r="B1293" s="40">
+        <v>48109.909500000002</v>
+      </c>
+      <c r="C1293" s="40">
+        <v>6963.9614000000001</v>
+      </c>
+      <c r="D1293" s="40">
+        <v>6908.4112815444378</v>
+      </c>
+      <c r="E1293" s="41">
+        <v>6167.6295976397805</v>
+      </c>
+      <c r="F1293" s="40">
+        <v>531.94140000000004</v>
+      </c>
+      <c r="G1293" s="40">
+        <v>103.0934</v>
+      </c>
+      <c r="H1293" s="40">
+        <v>5159.8007243916682</v>
+      </c>
+      <c r="I1293" s="41">
+        <v>6797.8959333728999</v>
+      </c>
+      <c r="J1293" s="40">
+        <v>10107.6018</v>
+      </c>
       <c r="K1293" s="40"/>
       <c r="L1293" s="40"/>
       <c r="M1293" s="40"/>
-      <c r="N1293" s="40"/>
+      <c r="N1293" s="40">
+        <v>58749.452700000002</v>
+      </c>
     </row>
     <row r="1294" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1294" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C25A43-E7A2-4DD0-BFAC-0DAF41E2BB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30469D47-7147-4EE7-94FA-F1D83FA80399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164399999994</v>
+        <v>76699.164400000009</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.5969827764493</v>
+        <v>4600.5969827764502</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8123550761293</v>
+        <v>4705.8123550761275</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55790,7 +55790,7 @@
         <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4735.8590672017526</v>
+        <v>4735.8590672017517</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55828,7 +55828,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4754.8215409778986</v>
+        <v>4754.8215409778977</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.676000000007</v>
+        <v>62640.675999999999</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947385</v>
+        <v>4662.2080120947376</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320600000006</v>
+        <v>68594.320599999992</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313500000004</v>
+        <v>52967.313499999997</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56018,7 +56018,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4672.9782577126962</v>
+        <v>4672.9782577126971</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56322,7 +56322,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.2993048166982</v>
+        <v>4909.2993048166973</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56550,7 +56550,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.2761378662899</v>
+        <v>5020.2761378662917</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56562,7 +56562,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253522</v>
+        <v>5662.7424793253513</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359400000001</v>
+        <v>53725.359399999994</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56600,7 +56600,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316097</v>
+        <v>6067.7529720316115</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56638,7 +56638,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712294</v>
+        <v>6497.7712544712285</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56703,7 +56703,7 @@
         <v>5268.9257819850018</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.2340433056661</v>
+        <v>5374.2340433056652</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56741,7 +56741,7 @@
         <v>5139.52719767897</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.0821484626749</v>
+        <v>5338.082148462674</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56753,7 +56753,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571392</v>
+        <v>6430.3532186571383</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56791,7 +56791,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084409</v>
+        <v>6056.5070840084427</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703699999998</v>
+        <v>57650.703700000005</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072227</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639499999997</v>
+        <v>48636.639500000005</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56981,7 +56981,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691884</v>
+        <v>5046.6456948691875</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57159,7 +57159,7 @@
         <v>5045.5549585912104</v>
       </c>
       <c r="E1254" s="36">
-        <v>5301.0786076052154</v>
+        <v>5301.0786076052145</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57197,7 +57197,7 @@
         <v>6210.2065487022992</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.7762899099316</v>
+        <v>5572.7762899099307</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371017</v>
+        <v>5978.5241558371008</v>
       </c>
       <c r="J1255" s="35">
         <v>12541.2435</v>
@@ -57235,7 +57235,7 @@
         <v>5185.7481374213639</v>
       </c>
       <c r="E1256" s="36">
-        <v>5467.3476722995892</v>
+        <v>5467.3476722995883</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57247,7 +57247,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244501</v>
+        <v>6258.6852471244511</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.1422999999995</v>
@@ -57285,7 +57285,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6857.6810418042396</v>
+        <v>6857.6810418042405</v>
       </c>
       <c r="J1257" s="35">
         <v>7037.5686999999998</v>
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.357999999993</v>
+        <v>78641.358000000007</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57311,7 +57311,7 @@
         <v>4962.7373759560833</v>
       </c>
       <c r="E1258" s="36">
-        <v>5447.8254286351712</v>
+        <v>5447.825428635173</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57323,7 +57323,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248455</v>
+        <v>7108.8683732248473</v>
       </c>
       <c r="J1258" s="35">
         <v>10810.321599999999</v>
@@ -57361,7 +57361,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096225</v>
+        <v>7266.6202217096234</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57399,7 +57399,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487983</v>
+        <v>6636.3073234487993</v>
       </c>
       <c r="J1260" s="35">
         <v>7674.9405999999999</v>
@@ -57513,7 +57513,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.391308042289</v>
+        <v>6206.3913080422872</v>
       </c>
       <c r="J1263" s="35">
         <v>7879.2038000000002</v>
@@ -57539,7 +57539,7 @@
         <v>5647.5838424777212</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.6234243768877</v>
+        <v>5398.6234243768859</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796990993</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57644,16 +57644,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77390.624400000001</v>
+        <v>77386.206999999995</v>
       </c>
       <c r="C1267" s="40">
         <v>13530.0152</v>
       </c>
       <c r="D1267" s="40">
-        <v>5719.9214676418105</v>
+        <v>5719.5949787255231</v>
       </c>
       <c r="E1267" s="41">
-        <v>5389.0192391551263</v>
+        <v>5388.92776979675</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92465.696800000005</v>
+        <v>92461.279399999999</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57691,7 +57691,7 @@
         <v>5131.5513314336968</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.3402226005692</v>
+        <v>5333.253478707672</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57703,7 +57703,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166811</v>
+        <v>6548.0752800166792</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57729,7 +57729,7 @@
         <v>5300.0847228510156</v>
       </c>
       <c r="E1269" s="41">
-        <v>5318.7527226548918</v>
+        <v>5318.6650638955552</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57741,7 +57741,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314478</v>
+        <v>6498.4408173314469</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57767,7 +57767,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.2924961889375</v>
+        <v>5432.2060902542544</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57940,7 +57940,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61593.434999999998</v>
+        <v>61593.435000000005</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57957,7 +57957,7 @@
         <v>6107.0018529161116</v>
       </c>
       <c r="E1275" s="41">
-        <v>5670.2652878400704</v>
+        <v>5670.2652878400713</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57986,16 +57986,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45553.238499999999</v>
+        <v>45553.404699999999</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.6244453298395</v>
+        <v>5803.6456197274138</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.855198128671</v>
+        <v>5698.8599876135631</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58016,7 +58016,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52468.373999999996</v>
+        <v>52468.540200000003</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58033,7 +58033,7 @@
         <v>5849.6360842310596</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.7836776090489</v>
+        <v>5646.7888116180038</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58054,7 +58054,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37839.979399999997</v>
+        <v>37839.979400000004</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58071,7 +58071,7 @@
         <v>5140.1004139645229</v>
       </c>
       <c r="E1278" s="41">
-        <v>5541.9901512760125</v>
+        <v>5541.9959626568225</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58109,7 +58109,7 @@
         <v>6558.946380747514</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.7921395384828</v>
+        <v>5769.7984646876403</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76963.703899999993</v>
+        <v>76963.703900000008</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58396,7 +58396,7 @@
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69943.152199999997</v>
+        <v>69943.152200000011</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58413,13 +58413,13 @@
         <v>6394.278069753329</v>
       </c>
       <c r="E1287" s="41">
-        <v>6052.9432159046983</v>
+        <v>6052.9432159046974</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41">
-        <v>6419</v>
+        <v>6419.3350482258738</v>
       </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
@@ -58445,7 +58445,7 @@
         <v>5961.607584620223</v>
       </c>
       <c r="E1288" s="41">
-        <v>6091.2168528240391</v>
+        <v>6091.21685282404</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58542,7 +58542,7 @@
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86941.142400000012</v>
+        <v>86941.142399999997</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58550,37 +58550,37 @@
         <v>46235</v>
       </c>
       <c r="B1291" s="40">
-        <v>58008.694799999997</v>
+        <v>58315.900800000003</v>
       </c>
       <c r="C1291" s="40">
-        <v>10109.5954</v>
+        <v>10142.8843</v>
       </c>
       <c r="D1291" s="40">
-        <v>5737.9838168399892</v>
+        <v>5749.4396145285818</v>
       </c>
       <c r="E1291" s="41">
-        <v>5939.2028252240179</v>
+        <v>5941.6638542603796</v>
       </c>
       <c r="F1291" s="40">
-        <v>1014.8816</v>
+        <v>1001.2517</v>
       </c>
       <c r="G1291" s="40">
-        <v>123.6353</v>
+        <v>121.0335</v>
       </c>
       <c r="H1291" s="40">
-        <v>8208.6717951911796</v>
+        <v>8272.5171130306899</v>
       </c>
       <c r="I1291" s="41">
-        <v>7609.658831709181</v>
+        <v>7631.04125491588</v>
       </c>
       <c r="J1291" s="40">
-        <v>12253.542799999999</v>
+        <v>12283.6664</v>
       </c>
       <c r="K1291" s="40"/>
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>71277.119200000001</v>
+        <v>71600.818899999998</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58588,37 +58588,37 @@
         <v>46242</v>
       </c>
       <c r="B1292" s="40">
-        <v>50372.4833</v>
+        <v>52405.699500000002</v>
       </c>
       <c r="C1292" s="40">
-        <v>7858.1157999999996</v>
+        <v>8214.4930000000004</v>
       </c>
       <c r="D1292" s="40">
-        <v>6410.2495537161722</v>
+        <v>6379.6632975400917</v>
       </c>
       <c r="E1292" s="41">
-        <v>5964.8942642006386</v>
+        <v>5965.2344022446396</v>
       </c>
       <c r="F1292" s="40">
-        <v>264.58980000000003</v>
+        <v>278.08030000000002</v>
       </c>
       <c r="G1292" s="40">
-        <v>46.1312</v>
+        <v>48.732999999999997</v>
       </c>
       <c r="H1292" s="40">
-        <v>5735.5932644284139</v>
+        <v>5706.2011368066824</v>
       </c>
       <c r="I1292" s="41">
-        <v>7372.4291167424299</v>
+        <v>7372.0023645865504</v>
       </c>
       <c r="J1292" s="40">
-        <v>4586.1485000000002</v>
+        <v>4674.5451000000003</v>
       </c>
       <c r="K1292" s="40"/>
       <c r="L1292" s="40"/>
       <c r="M1292" s="40"/>
       <c r="N1292" s="40">
-        <v>55223.221599999997</v>
+        <v>57358.324900000007</v>
       </c>
     </row>
     <row r="1293" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58626,54 +58626,76 @@
         <v>46249</v>
       </c>
       <c r="B1293" s="40">
-        <v>48109.909500000002</v>
+        <v>60561.198499999999</v>
       </c>
       <c r="C1293" s="40">
-        <v>6963.9614000000001</v>
+        <v>9446.9066000000003</v>
       </c>
       <c r="D1293" s="40">
-        <v>6908.4112815444378</v>
+        <v>6410.6909345330032</v>
       </c>
       <c r="E1293" s="41">
-        <v>6167.6295976397805</v>
+        <v>6102.8016249255697</v>
       </c>
       <c r="F1293" s="40">
-        <v>531.94140000000004</v>
+        <v>597.20920000000001</v>
       </c>
       <c r="G1293" s="40">
-        <v>103.0934</v>
+        <v>127.1549</v>
       </c>
       <c r="H1293" s="40">
-        <v>5159.8007243916682</v>
+        <v>4696.7061434518055</v>
       </c>
       <c r="I1293" s="41">
-        <v>6797.8959333728999</v>
+        <v>6510.0605792662072</v>
       </c>
       <c r="J1293" s="40">
-        <v>10107.6018</v>
+        <v>11522.8678</v>
       </c>
       <c r="K1293" s="40"/>
       <c r="L1293" s="40"/>
       <c r="M1293" s="40"/>
       <c r="N1293" s="40">
-        <v>58749.452700000002</v>
+        <v>72681.275500000003</v>
       </c>
     </row>
     <row r="1294" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1294" s="39"/>
-      <c r="B1294" s="40"/>
-      <c r="C1294" s="40"/>
-      <c r="D1294" s="40"/>
-      <c r="E1294" s="41"/>
-      <c r="F1294" s="40"/>
-      <c r="G1294" s="40"/>
-      <c r="H1294" s="40"/>
-      <c r="I1294" s="41"/>
-      <c r="J1294" s="40"/>
+      <c r="A1294" s="39">
+        <v>46256</v>
+      </c>
+      <c r="B1294" s="40">
+        <v>40593.170100000003</v>
+      </c>
+      <c r="C1294" s="40">
+        <v>6210.9745000000003</v>
+      </c>
+      <c r="D1294" s="40">
+        <v>6535.7167542710085</v>
+      </c>
+      <c r="E1294" s="41">
+        <v>6296.3609620343768</v>
+      </c>
+      <c r="F1294" s="40">
+        <v>46.036799999999999</v>
+      </c>
+      <c r="G1294" s="40">
+        <v>6.8227000000000002</v>
+      </c>
+      <c r="H1294" s="40">
+        <v>6747.5925953068436</v>
+      </c>
+      <c r="I1294" s="41">
+        <v>6329.5978423943043</v>
+      </c>
+      <c r="J1294" s="40">
+        <v>6606.9116000000004</v>
+      </c>
       <c r="K1294" s="40"/>
       <c r="L1294" s="40"/>
       <c r="M1294" s="40"/>
-      <c r="N1294" s="40"/>
+      <c r="N1294" s="40">
+        <v>47246.118500000004</v>
+      </c>
     </row>
     <row r="1295" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1295" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30469D47-7147-4EE7-94FA-F1D83FA80399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA0C289-BD28-42E9-AF8F-7C66D61FE84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164400000009</v>
+        <v>76699.164399999994</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.5969827764502</v>
+        <v>4600.5969827764493</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8123550761275</v>
+        <v>4705.8123550761293</v>
       </c>
       <c r="F1217" s="35">
         <v>1668.2316000000001</v>
@@ -55790,7 +55790,7 @@
         <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4735.8590672017517</v>
+        <v>4735.8590672017526</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55828,7 +55828,7 @@
         <v>4756.3024661122618</v>
       </c>
       <c r="E1219" s="36">
-        <v>4754.8215409778977</v>
+        <v>4754.8215409778986</v>
       </c>
       <c r="F1219" s="35">
         <v>1866.9058</v>
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.675999999999</v>
+        <v>62640.676000000007</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947376</v>
+        <v>4662.2080120947385</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320599999992</v>
+        <v>68594.320600000006</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313499999997</v>
+        <v>52967.313500000004</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56018,7 +56018,7 @@
         <v>4504.1722018570981</v>
       </c>
       <c r="E1224" s="36">
-        <v>4672.9782577126971</v>
+        <v>4672.9782577126962</v>
       </c>
       <c r="F1224" s="35">
         <v>678.69989999999996</v>
@@ -56322,7 +56322,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.2993048166973</v>
+        <v>4909.2993048166982</v>
       </c>
       <c r="F1232" s="35">
         <v>1933.1436000000001</v>
@@ -56550,7 +56550,7 @@
         <v>5523.3108409161778</v>
       </c>
       <c r="E1238" s="36">
-        <v>5020.2761378662917</v>
+        <v>5020.2761378662899</v>
       </c>
       <c r="F1238" s="35">
         <v>937.15679999999998</v>
@@ -56562,7 +56562,7 @@
         <v>5904.8972833195967</v>
       </c>
       <c r="I1238" s="36">
-        <v>5662.7424793253513</v>
+        <v>5662.7424793253522</v>
       </c>
       <c r="J1238" s="35">
         <v>5018.8672999999999</v>
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359399999994</v>
+        <v>53725.359400000001</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56600,7 +56600,7 @@
         <v>6823.3180379492396</v>
       </c>
       <c r="I1239" s="36">
-        <v>6067.7529720316115</v>
+        <v>6067.7529720316097</v>
       </c>
       <c r="J1239" s="35">
         <v>8211.3163000000004</v>
@@ -56638,7 +56638,7 @@
         <v>7055.1888353620407</v>
       </c>
       <c r="I1240" s="36">
-        <v>6497.7712544712285</v>
+        <v>6497.7712544712294</v>
       </c>
       <c r="J1240" s="35">
         <v>2117.8483999999999</v>
@@ -56694,16 +56694,16 @@
         <v>45892</v>
       </c>
       <c r="B1242" s="35">
-        <v>84734.912899999996</v>
+        <v>84733.481799999994</v>
       </c>
       <c r="C1242" s="35">
         <v>16082.0092</v>
       </c>
       <c r="D1242" s="35">
-        <v>5268.9257819850018</v>
+        <v>5268.8367943478106</v>
       </c>
       <c r="E1242" s="36">
-        <v>5374.2340433056652</v>
+        <v>5374.2013794132281</v>
       </c>
       <c r="F1242" s="35">
         <v>1157.8651</v>
@@ -56724,7 +56724,7 @@
       <c r="L1242" s="35"/>
       <c r="M1242" s="35"/>
       <c r="N1242" s="37">
-        <v>94214.798899999994</v>
+        <v>94213.367799999993</v>
       </c>
     </row>
     <row r="1243" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56741,7 +56741,7 @@
         <v>5139.52719767897</v>
       </c>
       <c r="E1243" s="36">
-        <v>5338.082148462674</v>
+        <v>5338.0533583523838</v>
       </c>
       <c r="F1243" s="35">
         <v>913.81010000000003</v>
@@ -56753,7 +56753,7 @@
         <v>6152.8741374759629</v>
       </c>
       <c r="I1243" s="36">
-        <v>6430.3532186571383</v>
+        <v>6430.3532186571392</v>
       </c>
       <c r="J1243" s="35">
         <v>15660.4136</v>
@@ -56779,7 +56779,7 @@
         <v>4780.0438566865787</v>
       </c>
       <c r="E1244" s="36">
-        <v>5245.8828274293983</v>
+        <v>5245.8555878885063</v>
       </c>
       <c r="F1244" s="35">
         <v>1388.6704</v>
@@ -56791,7 +56791,7 @@
         <v>6502.2065457971212</v>
       </c>
       <c r="I1244" s="36">
-        <v>6056.5070840084427</v>
+        <v>6056.5070840084409</v>
       </c>
       <c r="J1244" s="35">
         <v>8281.8516999999993</v>
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703700000005</v>
+        <v>57650.703699999998</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56817,7 +56817,7 @@
         <v>5199.2635555698389</v>
       </c>
       <c r="E1245" s="36">
-        <v>5063.7055849213466</v>
+        <v>5063.678122974824</v>
       </c>
       <c r="F1245" s="35">
         <v>1184.0114000000001</v>
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072227</v>
+        <v>6136.9991384072246</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639500000005</v>
+        <v>48636.639499999997</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56981,7 +56981,7 @@
         <v>7293.444020260672</v>
       </c>
       <c r="I1249" s="36">
-        <v>5046.6456948691875</v>
+        <v>5046.6456948691884</v>
       </c>
       <c r="J1249" s="35">
         <v>6200.3991999999998</v>
@@ -57036,16 +57036,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="35">
-        <v>54432.231</v>
+        <v>54246.384400000003</v>
       </c>
       <c r="C1251" s="35">
         <v>9527.3052000000007</v>
       </c>
       <c r="D1251" s="35">
-        <v>5713.2872157805959</v>
+        <v>5693.7804826489655</v>
       </c>
       <c r="E1251" s="36">
-        <v>5011.0026069939822</v>
+        <v>5005.8415441462721</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57066,7 +57066,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>61006.148499999996</v>
+        <v>60820.301900000006</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57083,7 +57083,7 @@
         <v>4714.8155989034231</v>
       </c>
       <c r="E1252" s="36">
-        <v>4984.0493805906481</v>
+        <v>4978.9598424893193</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57121,7 +57121,7 @@
         <v>5679.5787797836083</v>
       </c>
       <c r="E1253" s="36">
-        <v>5197.0071791359587</v>
+        <v>5193.2954400815997</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57159,7 +57159,7 @@
         <v>5045.5549585912104</v>
       </c>
       <c r="E1254" s="36">
-        <v>5301.0786076052145</v>
+        <v>5297.0249451096579</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57188,16 +57188,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="35">
-        <v>84408.196500000005</v>
+        <v>84384.239499999996</v>
       </c>
       <c r="C1255" s="35">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="35">
-        <v>6210.2065487022992</v>
+        <v>6208.4439483334208</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.7762899099307</v>
+        <v>5572.3411260737348</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57218,7 +57218,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99695.302200000006</v>
+        <v>99671.345199999996</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57235,7 +57235,7 @@
         <v>5185.7481374213639</v>
       </c>
       <c r="E1256" s="36">
-        <v>5467.3476722995883</v>
+        <v>5466.938643722704</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57247,7 +57247,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244511</v>
+        <v>6258.6852471244501</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.1422999999995</v>
@@ -57273,7 +57273,7 @@
         <v>5244.3681512482881</v>
       </c>
       <c r="E1257" s="36">
-        <v>5418.9210882922562</v>
+        <v>5418.4771986673286</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57285,7 +57285,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6857.6810418042405</v>
+        <v>6857.6810418042396</v>
       </c>
       <c r="J1257" s="35">
         <v>7037.5686999999998</v>
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.358000000007</v>
+        <v>78641.357999999993</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57311,7 +57311,7 @@
         <v>4962.7373759560833</v>
       </c>
       <c r="E1258" s="36">
-        <v>5447.825428635173</v>
+        <v>5447.3765345831125</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57323,7 +57323,7 @@
         <v>7351.5658294357863</v>
       </c>
       <c r="I1258" s="36">
-        <v>7108.8683732248473</v>
+        <v>7108.8683732248455</v>
       </c>
       <c r="J1258" s="35">
         <v>10810.321599999999</v>
@@ -57340,16 +57340,16 @@
         <v>46011</v>
       </c>
       <c r="B1259" s="35">
-        <v>64198.712699999996</v>
+        <v>64197.623899999999</v>
       </c>
       <c r="C1259" s="35">
         <v>11775.5465</v>
       </c>
       <c r="D1259" s="35">
-        <v>5451.8669430756354</v>
+        <v>5451.7744802757134</v>
       </c>
       <c r="E1259" s="36">
-        <v>5177.9551568591332</v>
+        <v>5177.9344084299837</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57361,7 +57361,7 @@
         <v>7563.7052790897933</v>
       </c>
       <c r="I1259" s="36">
-        <v>7266.6202217096234</v>
+        <v>7266.6202217096225</v>
       </c>
       <c r="J1259" s="35">
         <v>14233.6034</v>
@@ -57370,7 +57370,7 @@
       <c r="L1259" s="35"/>
       <c r="M1259" s="35"/>
       <c r="N1259" s="37">
-        <v>81446.743099999992</v>
+        <v>81445.654299999995</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57387,7 +57387,7 @@
         <v>5176.6167478837451</v>
       </c>
       <c r="E1260" s="36">
-        <v>5202.9587412460278</v>
+        <v>5202.9375270725259</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57399,7 +57399,7 @@
         <v>4885.4697940587566</v>
       </c>
       <c r="I1260" s="36">
-        <v>6636.3073234487993</v>
+        <v>6636.3073234487983</v>
       </c>
       <c r="J1260" s="35">
         <v>7674.9405999999999</v>
@@ -57416,16 +57416,16 @@
         <v>46025</v>
       </c>
       <c r="B1261" s="35">
-        <v>35891.826500000003</v>
+        <v>35886.2716</v>
       </c>
       <c r="C1261" s="35">
         <v>6748.5475999999999</v>
       </c>
       <c r="D1261" s="35">
-        <v>5318.4520029168943</v>
+        <v>5317.6288776565798</v>
       </c>
       <c r="E1261" s="36">
-        <v>5247.2096947956634</v>
+        <v>5247.0653439212983</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57446,7 +57446,7 @@
       <c r="L1261" s="35"/>
       <c r="M1261" s="35"/>
       <c r="N1261" s="37">
-        <v>52564.247600000002</v>
+        <v>52558.6927</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57463,7 +57463,7 @@
         <v>5564.1977074457418</v>
       </c>
       <c r="E1262" s="36">
-        <v>5249.897708776085</v>
+        <v>5249.7384184642106</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57501,7 +57501,7 @@
         <v>5219.953709231233</v>
       </c>
       <c r="E1263" s="36">
-        <v>5330.0237759756428</v>
+        <v>5329.889189541469</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57513,7 +57513,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6206.3913080422872</v>
+        <v>6206.391308042289</v>
       </c>
       <c r="J1263" s="35">
         <v>7879.2038000000002</v>
@@ -57530,16 +57530,16 @@
         <v>46046</v>
       </c>
       <c r="B1264" s="35">
-        <v>41394.441299999999</v>
+        <v>41382.402800000003</v>
       </c>
       <c r="C1264" s="35">
         <v>7329.5842000000002</v>
       </c>
       <c r="D1264" s="35">
-        <v>5647.5838424777212</v>
+        <v>5645.9413891445583</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.6234243768859</v>
+        <v>5398.1174053901341</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57551,7 +57551,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763569</v>
+        <v>6539.4433219763587</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57560,7 +57560,7 @@
       <c r="L1264" s="35"/>
       <c r="M1264" s="35"/>
       <c r="N1264" s="37">
-        <v>49469.838100000001</v>
+        <v>49457.799600000006</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57577,7 +57577,7 @@
         <v>5218.0280244169526</v>
       </c>
       <c r="E1265" s="41">
-        <v>5317.1371039063351</v>
+        <v>5316.6986580180028</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796991011</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.9314203322911</v>
+        <v>5320.6442190103944</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57644,16 +57644,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77386.206999999995</v>
+        <v>77370.473400000003</v>
       </c>
       <c r="C1267" s="40">
         <v>13530.0152</v>
       </c>
       <c r="D1267" s="40">
-        <v>5719.5949787255231</v>
+        <v>5718.4321123305172</v>
       </c>
       <c r="E1267" s="41">
-        <v>5388.92776979675</v>
+        <v>5388.3527038829134</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92461.279399999999</v>
+        <v>92445.545800000007</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57682,16 +57682,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="40">
-        <v>65124.980300000003</v>
+        <v>65031.536500000002</v>
       </c>
       <c r="C1268" s="40">
-        <v>12691.090099999999</v>
+        <v>12665.788</v>
       </c>
       <c r="D1268" s="40">
-        <v>5131.5513314336968</v>
+        <v>5134.4248379966566</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.253478707672</v>
+        <v>5333.6814768159456</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57703,7 +57703,7 @@
         <v>7098.8423726492229</v>
       </c>
       <c r="I1268" s="41">
-        <v>6548.0752800166792</v>
+        <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
         <v>14839.3699</v>
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81291.243100000007</v>
+        <v>81197.799299999999</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57729,7 +57729,7 @@
         <v>5300.0847228510156</v>
       </c>
       <c r="E1269" s="41">
-        <v>5318.6650638955552</v>
+        <v>5319.1692744618276</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57741,7 +57741,7 @@
         <v>7763.917530345162</v>
       </c>
       <c r="I1269" s="41">
-        <v>6498.4408173314469</v>
+        <v>6498.4408173314478</v>
       </c>
       <c r="J1269" s="40">
         <v>8128.2731999999996</v>
@@ -57767,7 +57767,7 @@
         <v>5925.3131200194593</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.2060902542544</v>
+        <v>5432.7593123861698</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57805,7 +57805,7 @@
         <v>5455.7971255995071</v>
       </c>
       <c r="E1271" s="41">
-        <v>5412.2800363640226</v>
+        <v>5413.1684943431601</v>
       </c>
       <c r="F1271" s="40">
         <v>1806.9168</v>
@@ -57872,16 +57872,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="40">
-        <v>62466.256500000003</v>
+        <v>62466.066500000001</v>
       </c>
       <c r="C1273" s="40">
         <v>10894.957700000001</v>
       </c>
       <c r="D1273" s="40">
-        <v>5733.5015169448516</v>
+        <v>5733.4840776848541</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.8483501209412</v>
+        <v>5668.844004634565</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57902,7 +57902,7 @@
       <c r="L1273" s="40"/>
       <c r="M1273" s="40"/>
       <c r="N1273" s="40">
-        <v>74203.788100000005</v>
+        <v>74203.598100000003</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57919,7 +57919,7 @@
         <v>5404.5547975667259</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.9615703602058</v>
+        <v>5579.9570394685643</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.5085999999999</v>
@@ -57940,7 +57940,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61593.435000000005</v>
+        <v>61593.434999999998</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57957,7 +57957,7 @@
         <v>6107.0018529161116</v>
       </c>
       <c r="E1275" s="41">
-        <v>5670.2652878400713</v>
+        <v>5670.2601269441839</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57995,7 +57995,7 @@
         <v>5803.6456197274138</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.8599876135631</v>
+        <v>5698.8545122698242</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58024,16 +58024,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32078.936900000001</v>
+        <v>32078.7127</v>
       </c>
       <c r="C1277" s="40">
         <v>5483.9201000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>5849.6360842310596</v>
+        <v>5849.5952010679366</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.7888116180038</v>
+        <v>5646.7760167533288</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58054,7 +58054,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37839.979400000004</v>
+        <v>37839.7552</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58062,16 +58062,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>29408.240000000002</v>
+        <v>29407.9486</v>
       </c>
       <c r="C1278" s="40">
         <v>5721.3356999999996</v>
       </c>
       <c r="D1278" s="40">
-        <v>5140.1004139645229</v>
+        <v>5140.0494818019515</v>
       </c>
       <c r="E1278" s="41">
-        <v>5541.9959626568225</v>
+        <v>5541.9779340891582</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42471.175300000003</v>
+        <v>42470.883900000001</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58109,7 +58109,7 @@
         <v>6558.946380747514</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.7984646876403</v>
+        <v>5769.778842263423</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58138,16 +58138,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61457.873699999996</v>
+        <v>61457.645499999999</v>
       </c>
       <c r="C1280" s="40">
         <v>9397.5049999999992</v>
       </c>
       <c r="D1280" s="40">
-        <v>6539.8075020976312</v>
+        <v>6539.7832190565478</v>
       </c>
       <c r="E1280" s="41">
-        <v>6016.2162957369546</v>
+        <v>6016.1899731667963</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58168,7 +58168,7 @@
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>67731.366099999999</v>
+        <v>67731.137900000002</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58185,7 +58185,7 @@
         <v>6767.4474378968052</v>
       </c>
       <c r="E1281" s="41">
-        <v>6316.0269120039284</v>
+        <v>6316.0093001546275</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58214,16 +58214,16 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>60276.363400000002</v>
+        <v>60275.661099999998</v>
       </c>
       <c r="C1282" s="40">
         <v>10726.6477</v>
       </c>
       <c r="D1282" s="40">
-        <v>5619.3104393649473</v>
+        <v>5619.2449669061098</v>
       </c>
       <c r="E1282" s="41">
-        <v>6315.329948755395</v>
+        <v>6315.3031414590441</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76963.703900000008</v>
+        <v>76963.001599999989</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58252,16 +58252,16 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>62412.957300000002</v>
+        <v>62409.701300000001</v>
       </c>
       <c r="C1283" s="40">
         <v>11163.6018</v>
       </c>
       <c r="D1283" s="40">
-        <v>5590.7545269126313</v>
+        <v>5590.4628647718337</v>
       </c>
       <c r="E1283" s="41">
-        <v>6032.6991806995202</v>
+        <v>6032.5983046530428</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58276,13 +58276,13 @@
         <v>7404.550893257634</v>
       </c>
       <c r="J1283" s="40">
-        <v>7505.8680999999997</v>
+        <v>7504.5590000000002</v>
       </c>
       <c r="K1283" s="40"/>
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>71803.633799999996</v>
+        <v>71799.068700000003</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58290,16 +58290,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>39462.3073</v>
+        <v>39459.4493</v>
       </c>
       <c r="C1284" s="40">
         <v>6226.7978999999996</v>
       </c>
       <c r="D1284" s="40">
-        <v>6337.4960828582534</v>
+        <v>6337.0370989557887</v>
       </c>
       <c r="E1284" s="41">
-        <v>5950.2712439690786</v>
+        <v>5950.1016310137802</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58320,7 +58320,7 @@
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55874.363599999997</v>
+        <v>55871.505600000004</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62551.678200000002</v>
+        <v>62551.603199999998</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5906.9721327580501</v>
+        <v>5906.9650502476725</v>
       </c>
       <c r="E1285" s="41">
-        <v>5834.366433846516</v>
+        <v>5834.195355770813</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58358,7 +58358,7 @@
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80277.17730000001</v>
+        <v>80277.102299999999</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58375,7 +58375,7 @@
         <v>6203.8949060601217</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.634307310539</v>
+        <v>5860.4816784844888</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58390,13 +58390,13 @@
         <v>6928.2649857850765</v>
       </c>
       <c r="J1286" s="40">
-        <v>7564.5738000000001</v>
+        <v>7563.9697999999999</v>
       </c>
       <c r="K1286" s="40"/>
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69943.152200000011</v>
+        <v>69942.548200000005</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58404,22 +58404,22 @@
         <v>46207</v>
       </c>
       <c r="B1287" s="40">
-        <v>39076.130899999996</v>
+        <v>39049.002899999999</v>
       </c>
       <c r="C1287" s="40">
         <v>6111.1090999999997</v>
       </c>
       <c r="D1287" s="40">
-        <v>6394.278069753329</v>
+        <v>6389.8389410197242</v>
       </c>
       <c r="E1287" s="41">
-        <v>6052.9432159046974</v>
+        <v>6052.1355890616251</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41">
-        <v>6419.3350482258738</v>
+        <v>6419.3350482258757</v>
       </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
@@ -58428,7 +58428,7 @@
       <c r="L1287" s="40"/>
       <c r="M1287" s="40"/>
       <c r="N1287" s="40">
-        <v>43181.304199999999</v>
+        <v>43154.176200000002</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58436,16 +58436,16 @@
         <v>46214</v>
       </c>
       <c r="B1288" s="40">
-        <v>68442.713399999993</v>
+        <v>68436.839699999997</v>
       </c>
       <c r="C1288" s="40">
         <v>11480.580099999999</v>
       </c>
       <c r="D1288" s="40">
-        <v>5961.607584620223</v>
+        <v>5961.0959641316385</v>
       </c>
       <c r="E1288" s="41">
-        <v>6091.21685282404</v>
+        <v>6090.4018576942308</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58466,7 +58466,7 @@
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>77069.047299999991</v>
+        <v>77063.173599999995</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58474,16 +58474,16 @@
         <v>46221</v>
       </c>
       <c r="B1289" s="40">
-        <v>44447.422599999998</v>
+        <v>44441.650600000001</v>
       </c>
       <c r="C1289" s="40">
         <v>7660.7102999999997</v>
       </c>
       <c r="D1289" s="40">
-        <v>5801.9975771698355</v>
+        <v>5801.2441222323732</v>
       </c>
       <c r="E1289" s="41">
-        <v>6057.07422588598</v>
+        <v>6056.0899539803122</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58495,16 +58495,16 @@
         <v>8859.3817452840904</v>
       </c>
       <c r="I1289" s="41">
-        <v>6807.6707383696894</v>
+        <v>6807.6707383696876</v>
       </c>
       <c r="J1289" s="40">
-        <v>5421.4993999999997</v>
+        <v>5420.6954999999998</v>
       </c>
       <c r="K1289" s="40"/>
       <c r="L1289" s="40"/>
       <c r="M1289" s="40"/>
       <c r="N1289" s="40">
-        <v>50375.819499999998</v>
+        <v>50369.243600000002</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58512,16 +58512,16 @@
         <v>46228</v>
       </c>
       <c r="B1290" s="40">
-        <v>79763.369600000005</v>
+        <v>79759.197799999994</v>
       </c>
       <c r="C1290" s="40">
         <v>13474.185299999999</v>
       </c>
       <c r="D1290" s="40">
-        <v>5919.7174318212774</v>
+        <v>5919.4078175546538</v>
       </c>
       <c r="E1290" s="41">
-        <v>6038.7836762169109</v>
+        <v>6037.7937824478595</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58542,7 +58542,7 @@
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86941.142399999997</v>
+        <v>86936.970600000001</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58550,16 +58550,16 @@
         <v>46235</v>
       </c>
       <c r="B1291" s="40">
-        <v>58315.900800000003</v>
+        <v>57770.960500000001</v>
       </c>
       <c r="C1291" s="40">
-        <v>10142.8843</v>
+        <v>10083.671899999999</v>
       </c>
       <c r="D1291" s="40">
-        <v>5749.4396145285818</v>
+        <v>5729.1590873757013</v>
       </c>
       <c r="E1291" s="41">
-        <v>5941.6638542603796</v>
+        <v>5936.9615402059108</v>
       </c>
       <c r="F1291" s="40">
         <v>1001.2517</v>
@@ -58580,7 +58580,7 @@
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>71600.818899999998</v>
+        <v>71055.878599999996</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58588,16 +58588,16 @@
         <v>46242</v>
       </c>
       <c r="B1292" s="40">
-        <v>52405.699500000002</v>
+        <v>55630.779900000001</v>
       </c>
       <c r="C1292" s="40">
-        <v>8214.4930000000004</v>
+        <v>8692.5781000000006</v>
       </c>
       <c r="D1292" s="40">
-        <v>6379.6632975400917</v>
+        <v>6399.802136951751</v>
       </c>
       <c r="E1292" s="41">
-        <v>5965.2344022446396</v>
+        <v>5968.7022055433881</v>
       </c>
       <c r="F1292" s="40">
         <v>278.08030000000002</v>
@@ -58612,13 +58612,13 @@
         <v>7372.0023645865504</v>
       </c>
       <c r="J1292" s="40">
-        <v>4674.5451000000003</v>
+        <v>4736.88</v>
       </c>
       <c r="K1292" s="40"/>
       <c r="L1292" s="40"/>
       <c r="M1292" s="40"/>
       <c r="N1292" s="40">
-        <v>57358.324900000007</v>
+        <v>60645.7402</v>
       </c>
     </row>
     <row r="1293" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58626,37 +58626,37 @@
         <v>46249</v>
       </c>
       <c r="B1293" s="40">
-        <v>60561.198499999999</v>
+        <v>66216.530599999998</v>
       </c>
       <c r="C1293" s="40">
-        <v>9446.9066000000003</v>
+        <v>10551.081200000001</v>
       </c>
       <c r="D1293" s="40">
-        <v>6410.6909345330032</v>
+        <v>6275.8052321690029</v>
       </c>
       <c r="E1293" s="41">
-        <v>6102.8016249255697</v>
+        <v>6082.122986855572</v>
       </c>
       <c r="F1293" s="40">
-        <v>597.20920000000001</v>
+        <v>348.17270000000002</v>
       </c>
       <c r="G1293" s="40">
-        <v>127.1549</v>
+        <v>76.259699999999995</v>
       </c>
       <c r="H1293" s="40">
-        <v>4696.7061434518055</v>
+        <v>4565.6185377073343</v>
       </c>
       <c r="I1293" s="41">
-        <v>6510.0605792662072</v>
+        <v>6792.7589203821335</v>
       </c>
       <c r="J1293" s="40">
-        <v>11522.8678</v>
+        <v>11635.391</v>
       </c>
       <c r="K1293" s="40"/>
       <c r="L1293" s="40"/>
       <c r="M1293" s="40"/>
       <c r="N1293" s="40">
-        <v>72681.275500000003</v>
+        <v>78200.094299999997</v>
       </c>
     </row>
     <row r="1294" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58664,54 +58664,70 @@
         <v>46256</v>
       </c>
       <c r="B1294" s="40">
-        <v>40593.170100000003</v>
+        <v>63116.4162</v>
       </c>
       <c r="C1294" s="40">
-        <v>6210.9745000000003</v>
+        <v>10236.713100000001</v>
       </c>
       <c r="D1294" s="40">
-        <v>6535.7167542710085</v>
+        <v>6165.6916222454256</v>
       </c>
       <c r="E1294" s="41">
-        <v>6296.3609620343768</v>
+        <v>6208.0045569137219</v>
       </c>
       <c r="F1294" s="40">
-        <v>46.036799999999999</v>
+        <v>533.17290000000003</v>
       </c>
       <c r="G1294" s="40">
-        <v>6.8227000000000002</v>
+        <v>84.688199999999995</v>
       </c>
       <c r="H1294" s="40">
-        <v>6747.5925953068436</v>
+        <v>6295.7165224907376</v>
       </c>
       <c r="I1294" s="41">
-        <v>6329.5978423943043</v>
+        <v>6533.3641353385283</v>
       </c>
       <c r="J1294" s="40">
-        <v>6606.9116000000004</v>
+        <v>10216.2161</v>
       </c>
       <c r="K1294" s="40"/>
       <c r="L1294" s="40"/>
       <c r="M1294" s="40"/>
       <c r="N1294" s="40">
-        <v>47246.118500000004</v>
+        <v>73865.805200000003</v>
       </c>
     </row>
     <row r="1295" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1295" s="39"/>
-      <c r="B1295" s="40"/>
-      <c r="C1295" s="40"/>
-      <c r="D1295" s="40"/>
-      <c r="E1295" s="41"/>
+      <c r="A1295" s="39">
+        <v>46263</v>
+      </c>
+      <c r="B1295" s="40">
+        <v>12693.7469</v>
+      </c>
+      <c r="C1295" s="40">
+        <v>1690.7369000000001</v>
+      </c>
+      <c r="D1295" s="40">
+        <v>7507.8191645311581</v>
+      </c>
+      <c r="E1295" s="41">
+        <v>6195.4355067300166</v>
+      </c>
       <c r="F1295" s="40"/>
       <c r="G1295" s="40"/>
       <c r="H1295" s="40"/>
-      <c r="I1295" s="41"/>
-      <c r="J1295" s="40"/>
+      <c r="I1295" s="41">
+        <v>6292.0051946566455</v>
+      </c>
+      <c r="J1295" s="40">
+        <v>2067.6342</v>
+      </c>
       <c r="K1295" s="40"/>
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
-      <c r="N1295" s="40"/>
+      <c r="N1295" s="40">
+        <v>14761.381100000001</v>
+      </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1296" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA0C289-BD28-42E9-AF8F-7C66D61FE84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED110E08-BAAB-4F81-8CAD-250C558B7567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164399999994</v>
+        <v>76699.164400000009</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.676000000007</v>
+        <v>62640.675999999999</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55904,7 +55904,7 @@
         <v>4701.7281140876712</v>
       </c>
       <c r="E1221" s="36">
-        <v>4669.4458132671598</v>
+        <v>4669.4458132671589</v>
       </c>
       <c r="F1221" s="35">
         <v>673.16070000000002</v>
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320600000006</v>
+        <v>68594.320599999992</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313500000004</v>
+        <v>52967.313499999997</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56360,7 +56360,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="36">
-        <v>4835.8535729451951</v>
+        <v>4835.853572945196</v>
       </c>
       <c r="F1233" s="35">
         <v>910.61059999999998</v>
@@ -56389,16 +56389,16 @@
         <v>45836</v>
       </c>
       <c r="B1234" s="35">
-        <v>34669.657500000001</v>
+        <v>34671.1999</v>
       </c>
       <c r="C1234" s="35">
         <v>7079.1347999999998</v>
       </c>
       <c r="D1234" s="35">
-        <v>4897.4427637682502</v>
+        <v>4897.6606435012372</v>
       </c>
       <c r="E1234" s="36">
-        <v>4765.7739607701869</v>
+        <v>4765.808222470997</v>
       </c>
       <c r="F1234" s="35">
         <v>556.48080000000004</v>
@@ -56419,7 +56419,7 @@
       <c r="L1234" s="35"/>
       <c r="M1234" s="35"/>
       <c r="N1234" s="37">
-        <v>43631.230300000003</v>
+        <v>43632.772699999994</v>
       </c>
     </row>
     <row r="1235" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56436,7 +56436,7 @@
         <v>5123.1647487932232</v>
       </c>
       <c r="E1235" s="36">
-        <v>4954.14977322102</v>
+        <v>4954.1827371364488</v>
       </c>
       <c r="F1235" s="35">
         <v>1182.9712999999999</v>
@@ -56474,7 +56474,7 @@
         <v>4467.9983481840936</v>
       </c>
       <c r="E1236" s="36">
-        <v>4832.1827724769955</v>
+        <v>4832.2162671442084</v>
       </c>
       <c r="F1236" s="35">
         <v>509.77510000000001</v>
@@ -56512,7 +56512,7 @@
         <v>5278.9174410390733</v>
       </c>
       <c r="E1237" s="36">
-        <v>4925.6527215340475</v>
+        <v>4925.6893028834274</v>
       </c>
       <c r="F1237" s="35">
         <v>770.73030000000006</v>
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359400000001</v>
+        <v>53725.359399999994</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56588,7 +56588,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="36">
-        <v>4983.5092802101408</v>
+        <v>4983.509280210139</v>
       </c>
       <c r="F1239" s="35">
         <v>1951.8497</v>
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703699999998</v>
+        <v>57650.703700000005</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6136.9991384072246</v>
+        <v>6136.9991384072237</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639499999997</v>
+        <v>48636.639500000005</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56905,7 +56905,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5394.2932473875317</v>
+        <v>5394.2932473875308</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -57066,7 +57066,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>60820.301900000006</v>
+        <v>60820.301899999999</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57212,13 +57212,13 @@
         <v>5978.5241558371008</v>
       </c>
       <c r="J1255" s="35">
-        <v>12541.2435</v>
+        <v>12540.7538</v>
       </c>
       <c r="K1255" s="35"/>
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99671.345199999996</v>
+        <v>99670.855500000005</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.357999999993</v>
+        <v>78641.358000000007</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57302,16 +57302,16 @@
         <v>46004</v>
       </c>
       <c r="B1258" s="35">
-        <v>60216.499499999998</v>
+        <v>60217.353600000002</v>
       </c>
       <c r="C1258" s="35">
         <v>12133.7268</v>
       </c>
       <c r="D1258" s="35">
-        <v>4962.7373759560833</v>
+        <v>4962.80776653056</v>
       </c>
       <c r="E1258" s="36">
-        <v>5447.3765345831125</v>
+        <v>5447.3925382734687</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75387.722899999993</v>
+        <v>75388.57699999999</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57349,7 +57349,7 @@
         <v>5451.7744802757134</v>
       </c>
       <c r="E1259" s="36">
-        <v>5177.9344084299837</v>
+        <v>5177.950684360675</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57387,7 +57387,7 @@
         <v>5176.6167478837451</v>
       </c>
       <c r="E1260" s="36">
-        <v>5202.9375270725259</v>
+        <v>5202.9541683524567</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57425,7 +57425,7 @@
         <v>5317.6288776565798</v>
       </c>
       <c r="E1261" s="36">
-        <v>5247.0653439212983</v>
+        <v>5247.0839013639579</v>
       </c>
       <c r="F1261" s="35">
         <v>1259.8376000000001</v>
@@ -57463,7 +57463,7 @@
         <v>5564.1977074457418</v>
       </c>
       <c r="E1262" s="36">
-        <v>5249.7384184642106</v>
+        <v>5249.7384184642124</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57539,7 +57539,7 @@
         <v>5645.9413891445583</v>
       </c>
       <c r="E1264" s="36">
-        <v>5398.1174053901341</v>
+        <v>5398.1174053901332</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57551,7 +57551,7 @@
         <v>6380.0084555526264</v>
       </c>
       <c r="I1264" s="36">
-        <v>6539.4433219763587</v>
+        <v>6539.4433219763569</v>
       </c>
       <c r="J1264" s="35">
         <v>6272.0586999999996</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796991011</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57653,7 +57653,7 @@
         <v>5718.4321123305172</v>
       </c>
       <c r="E1267" s="41">
-        <v>5388.3527038829134</v>
+        <v>5388.3527038829152</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57691,7 +57691,7 @@
         <v>5134.4248379966566</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.6814768159456</v>
+        <v>5333.6814768159466</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57706,13 +57706,13 @@
         <v>6548.0752800166811</v>
       </c>
       <c r="J1268" s="40">
-        <v>14839.3699</v>
+        <v>14973.267099999999</v>
       </c>
       <c r="K1268" s="40"/>
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81197.799299999999</v>
+        <v>81331.696500000005</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57758,16 +57758,16 @@
         <v>46088</v>
       </c>
       <c r="B1270" s="40">
-        <v>57409.225899999998</v>
+        <v>57405.623699999996</v>
       </c>
       <c r="C1270" s="40">
         <v>9688.8088000000007</v>
       </c>
       <c r="D1270" s="40">
-        <v>5925.3131200194593</v>
+        <v>5924.9413302489766</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.7593123861698</v>
+        <v>5432.6888171676719</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57788,7 +57788,7 @@
       <c r="L1270" s="40"/>
       <c r="M1270" s="40"/>
       <c r="N1270" s="40">
-        <v>64698.907599999999</v>
+        <v>64695.305399999997</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57805,7 +57805,7 @@
         <v>5455.7971255995071</v>
       </c>
       <c r="E1271" s="41">
-        <v>5413.1684943431601</v>
+        <v>5413.0949188940249</v>
       </c>
       <c r="F1271" s="40">
         <v>1806.9168</v>
@@ -57843,7 +57843,7 @@
         <v>6070.5855710333217</v>
       </c>
       <c r="E1272" s="41">
-        <v>5602.0897262395038</v>
+        <v>5602.0074129071836</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57881,7 +57881,7 @@
         <v>5733.4840776848541</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.844004634565</v>
+        <v>5668.7616187870799</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57910,16 +57910,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52077.875500000002</v>
+        <v>52059.355900000002</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5404.5547975667259</v>
+        <v>5402.63286446043</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.9570394685643</v>
+        <v>5579.4295053700225</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.5085999999999</v>
@@ -57940,7 +57940,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61593.434999999998</v>
+        <v>61574.915400000005</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57957,7 +57957,7 @@
         <v>6107.0018529161116</v>
       </c>
       <c r="E1275" s="41">
-        <v>5670.2601269441839</v>
+        <v>5669.7570862733501</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57986,16 +57986,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45553.404699999999</v>
+        <v>45552.934699999998</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.6456197274138</v>
+        <v>5803.5857402637548</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.8545122698242</v>
+        <v>5698.3072775989513</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58016,7 +58016,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52468.540200000003</v>
+        <v>52468.070200000002</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58033,7 +58033,7 @@
         <v>5849.5952010679366</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.7760167533288</v>
+        <v>5646.1894176170217</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58071,7 +58071,7 @@
         <v>5140.0494818019515</v>
       </c>
       <c r="E1278" s="41">
-        <v>5541.9779340891582</v>
+        <v>5541.9614999797677</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58109,7 +58109,7 @@
         <v>6558.946380747514</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.778842263423</v>
+        <v>5769.7609552591903</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58138,16 +58138,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61457.645499999999</v>
+        <v>61456.328300000001</v>
       </c>
       <c r="C1280" s="40">
         <v>9397.5049999999992</v>
       </c>
       <c r="D1280" s="40">
-        <v>6539.7832190565478</v>
+        <v>6539.6430541936406</v>
       </c>
       <c r="E1280" s="41">
-        <v>6016.1899731667963</v>
+        <v>6016.1433583652197</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58168,7 +58168,7 @@
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>67731.137900000002</v>
+        <v>67729.820699999997</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58185,7 +58185,7 @@
         <v>6767.4474378968052</v>
       </c>
       <c r="E1281" s="41">
-        <v>6316.0093001546275</v>
+        <v>6315.9646536421196</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58223,7 +58223,7 @@
         <v>5619.2449669061098</v>
       </c>
       <c r="E1282" s="41">
-        <v>6315.3031414590441</v>
+        <v>6315.2651935055219</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76963.001599999989</v>
+        <v>76963.001600000003</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58261,7 +58261,7 @@
         <v>5590.4628647718337</v>
       </c>
       <c r="E1283" s="41">
-        <v>6032.5983046530428</v>
+        <v>6032.5665659862752</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58282,7 +58282,7 @@
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>71799.068700000003</v>
+        <v>71799.068699999989</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58290,16 +58290,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>39459.4493</v>
+        <v>39451.049299999999</v>
       </c>
       <c r="C1284" s="40">
         <v>6226.7978999999996</v>
       </c>
       <c r="D1284" s="40">
-        <v>6337.0370989557887</v>
+        <v>6335.6880909849342</v>
       </c>
       <c r="E1284" s="41">
-        <v>5950.1016310137802</v>
+        <v>5949.899381198391</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58320,7 +58320,7 @@
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55871.505600000004</v>
+        <v>55863.105599999995</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58337,7 +58337,7 @@
         <v>5906.9650502476725</v>
       </c>
       <c r="E1285" s="41">
-        <v>5834.195355770813</v>
+        <v>5833.9868238775689</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58375,7 +58375,7 @@
         <v>6203.8949060601217</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.4816784844888</v>
+        <v>5860.2956349021733</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58413,13 +58413,13 @@
         <v>6389.8389410197242</v>
       </c>
       <c r="E1287" s="41">
-        <v>6052.1355890616251</v>
+        <v>6051.909912421399</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41">
-        <v>6419.3350482258757</v>
+        <v>6419.3350482258738</v>
       </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
@@ -58445,7 +58445,7 @@
         <v>5961.0959641316385</v>
       </c>
       <c r="E1288" s="41">
-        <v>6090.4018576942308</v>
+        <v>6090.4018576942317</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58474,16 +58474,16 @@
         <v>46221</v>
       </c>
       <c r="B1289" s="40">
-        <v>44441.650600000001</v>
+        <v>43928.746599999999</v>
       </c>
       <c r="C1289" s="40">
-        <v>7660.7102999999997</v>
+        <v>7626.7623999999996</v>
       </c>
       <c r="D1289" s="40">
-        <v>5801.2441222323732</v>
+        <v>5759.8158033610698</v>
       </c>
       <c r="E1289" s="41">
-        <v>6056.0899539803122</v>
+        <v>6048.2971729571036</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58495,7 +58495,7 @@
         <v>8859.3817452840904</v>
       </c>
       <c r="I1289" s="41">
-        <v>6807.6707383696876</v>
+        <v>6807.6707383696894</v>
       </c>
       <c r="J1289" s="40">
         <v>5420.6954999999998</v>
@@ -58504,7 +58504,7 @@
       <c r="L1289" s="40"/>
       <c r="M1289" s="40"/>
       <c r="N1289" s="40">
-        <v>50369.243600000002</v>
+        <v>49856.339599999999</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58521,7 +58521,7 @@
         <v>5919.4078175546538</v>
       </c>
       <c r="E1290" s="41">
-        <v>6037.7937824478595</v>
+        <v>6030.6903550355928</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58542,7 +58542,7 @@
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86936.970600000001</v>
+        <v>86936.970599999986</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58559,19 +58559,19 @@
         <v>5729.1590873757013</v>
       </c>
       <c r="E1291" s="41">
-        <v>5936.9615402059108</v>
+        <v>5929.9488439476581</v>
       </c>
       <c r="F1291" s="40">
         <v>1001.2517</v>
       </c>
       <c r="G1291" s="40">
-        <v>121.0335</v>
+        <v>142.47409999999999</v>
       </c>
       <c r="H1291" s="40">
-        <v>8272.5171130306899</v>
+        <v>7027.6050173329759</v>
       </c>
       <c r="I1291" s="41">
-        <v>7631.04125491588</v>
+        <v>7103.1591472535083</v>
       </c>
       <c r="J1291" s="40">
         <v>12283.6664</v>
@@ -58597,7 +58597,7 @@
         <v>6399.802136951751</v>
       </c>
       <c r="E1292" s="41">
-        <v>5968.7022055433881</v>
+        <v>5962.201993265704</v>
       </c>
       <c r="F1292" s="40">
         <v>278.08030000000002</v>
@@ -58609,7 +58609,7 @@
         <v>5706.2011368066824</v>
       </c>
       <c r="I1292" s="41">
-        <v>7372.0023645865504</v>
+        <v>6917.9290415603364</v>
       </c>
       <c r="J1292" s="40">
         <v>4736.88</v>
@@ -58626,16 +58626,16 @@
         <v>46249</v>
       </c>
       <c r="B1293" s="40">
-        <v>66216.530599999998</v>
+        <v>64769.839800000002</v>
       </c>
       <c r="C1293" s="40">
-        <v>10551.081200000001</v>
+        <v>10228.6834</v>
       </c>
       <c r="D1293" s="40">
-        <v>6275.8052321690029</v>
+        <v>6332.1775899330314</v>
       </c>
       <c r="E1293" s="41">
-        <v>6082.122986855572</v>
+        <v>6093.2215939903417</v>
       </c>
       <c r="F1293" s="40">
         <v>348.17270000000002</v>
@@ -58647,16 +58647,16 @@
         <v>4565.6185377073343</v>
       </c>
       <c r="I1293" s="41">
-        <v>6792.7589203821335</v>
+        <v>6326.7732885907753</v>
       </c>
       <c r="J1293" s="40">
-        <v>11635.391</v>
+        <v>11651.992899999999</v>
       </c>
       <c r="K1293" s="40"/>
       <c r="L1293" s="40"/>
       <c r="M1293" s="40"/>
       <c r="N1293" s="40">
-        <v>78200.094299999997</v>
+        <v>76770.005399999995</v>
       </c>
     </row>
     <row r="1294" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58664,37 +58664,37 @@
         <v>46256</v>
       </c>
       <c r="B1294" s="40">
-        <v>63116.4162</v>
+        <v>65658.519100000005</v>
       </c>
       <c r="C1294" s="40">
-        <v>10236.713100000001</v>
+        <v>11053.063700000001</v>
       </c>
       <c r="D1294" s="40">
-        <v>6165.6916222454256</v>
+        <v>5940.3004345302015</v>
       </c>
       <c r="E1294" s="41">
-        <v>6208.0045569137219</v>
+        <v>6165.7980621688976</v>
       </c>
       <c r="F1294" s="40">
-        <v>533.17290000000003</v>
+        <v>922.0231</v>
       </c>
       <c r="G1294" s="40">
-        <v>84.688199999999995</v>
+        <v>174.06899999999999</v>
       </c>
       <c r="H1294" s="40">
-        <v>6295.7165224907376</v>
+        <v>5296.8828453084698</v>
       </c>
       <c r="I1294" s="41">
-        <v>6533.3641353385283</v>
+        <v>5774.2266878472819</v>
       </c>
       <c r="J1294" s="40">
-        <v>10216.2161</v>
+        <v>11193.4807</v>
       </c>
       <c r="K1294" s="40"/>
       <c r="L1294" s="40"/>
       <c r="M1294" s="40"/>
       <c r="N1294" s="40">
-        <v>73865.805200000003</v>
+        <v>77774.022900000011</v>
       </c>
     </row>
     <row r="1295" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58702,48 +58702,70 @@
         <v>46263</v>
       </c>
       <c r="B1295" s="40">
-        <v>12693.7469</v>
+        <v>26805.156299999999</v>
       </c>
       <c r="C1295" s="40">
-        <v>1690.7369000000001</v>
+        <v>4193.8714</v>
       </c>
       <c r="D1295" s="40">
-        <v>7507.8191645311581</v>
+        <v>6391.5064968372653</v>
       </c>
       <c r="E1295" s="41">
-        <v>6195.4355067300166</v>
-      </c>
-      <c r="F1295" s="40"/>
-      <c r="G1295" s="40"/>
-      <c r="H1295" s="40"/>
+        <v>6113.8699304593802</v>
+      </c>
+      <c r="F1295" s="40">
+        <v>1206.4709</v>
+      </c>
+      <c r="G1295" s="40">
+        <v>137.66929999999999</v>
+      </c>
+      <c r="H1295" s="40">
+        <v>8763.5435060685286</v>
+      </c>
       <c r="I1295" s="41">
-        <v>6292.0051946566455</v>
+        <v>6351.4475282341673</v>
       </c>
       <c r="J1295" s="40">
-        <v>2067.6342</v>
+        <v>3115.2201</v>
       </c>
       <c r="K1295" s="40"/>
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
       <c r="N1295" s="40">
-        <v>14761.381100000001</v>
+        <v>31126.847299999998</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1296" s="39"/>
-      <c r="B1296" s="40"/>
-      <c r="C1296" s="40"/>
-      <c r="D1296" s="40"/>
-      <c r="E1296" s="41"/>
+      <c r="A1296" s="39">
+        <v>46270</v>
+      </c>
+      <c r="B1296" s="40">
+        <v>51450.369899999998</v>
+      </c>
+      <c r="C1296" s="40">
+        <v>9005.3593000000001</v>
+      </c>
+      <c r="D1296" s="40">
+        <v>5713.3056201322252</v>
+      </c>
+      <c r="E1296" s="41">
+        <v>6218.661212658998</v>
+      </c>
       <c r="F1296" s="40"/>
       <c r="G1296" s="40"/>
       <c r="H1296" s="40"/>
-      <c r="I1296" s="41"/>
-      <c r="J1296" s="40"/>
+      <c r="I1296" s="41">
+        <v>6383.1945010025829</v>
+      </c>
+      <c r="J1296" s="40">
+        <v>4599.5405000000001</v>
+      </c>
       <c r="K1296" s="40"/>
       <c r="L1296" s="40"/>
       <c r="M1296" s="40"/>
-      <c r="N1296" s="40"/>
+      <c r="N1296" s="40">
+        <v>56049.910400000001</v>
+      </c>
     </row>
     <row r="1297" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1297" s="39"/>
